--- a/05_screening/validation_screening.xlsx
+++ b/05_screening/validation_screening.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Screening" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Progress" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Screening" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progress" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Screening'!$A$1:$L$101</definedName>
@@ -819,28 +819,28 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>2322e385b8e7</t>
+          <t>bf5b5ef25a6f</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>Differential Evolution VQE for Crypto-currency Arbitrage. Quantum Optimization with many local minima</t>
+          <t>Comprehensive Survey of QML: From Data Analysis to Algorithmic Advancements</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>Gines Carrascal; Beatriz Roman; Guillermo Botella; Alberto del Barrio</t>
+          <t>Sahil Tomar; Rajeshwar Tripathi; Sandeep Kumar</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr"/>
       <c r="G2" s="5" t="inlineStr">
         <is>
-          <t>Crypto-currency markets are known to exhibit inefficiencies, which presents opportunities for profitable cyclic transactions or arbitrage, where one currency is traded for another in a way that results in a net gain without incurring any risk. Quantum computing has shown promise in financial applications, particularly in resolving optimization problems like arbitrage. In this paper, we introduce a differential evolution (DE) optimization algorithm for Variational Quantum Eigensolver (VQE) using Qiskit framework. We elucidate the application of crypto-currency arbitrage using different VQE optimizers. Our findings indicate that the proposed DE-based method effectively converges to the optimal solution in scenarios where other commonly used optimizers, such as COBYLA, struggle to find the global minimum. We further test this procedure's feasibility on IBM's real quantum machines up to 127 qubits. With a three-currency scenario, the algorithm converged in 417 steps over a 12-hour period on the "ibm_geneva" machine. These results suggest the potential for achieving a quantum advantage in solving increasingly complex problems.</t>
+          <t>Quantum Machine Learning represents a paradigm shift at the intersection of Quantum Computing and Machine Learning, leveraging quantum phenomena such as superposition, entanglement, and quantum parallelism to address the limitations of classical approaches in processing high-dimensional and large-scale datasets. This survey provides a comprehensive analysis of Quantum Machine Learning, detailing foundational concepts, algorithmic advancements, and their applications across domains such as healthcare, finance, and quantum chemistry. Key techniques, including Quantum Support Vector Machine, Quantum Neural Network, Quantum Decision Trees, and hybrid quantum-classical models, are explored with a focus on their theoretical foundations, computational benefits, and comparative performance against classical counterparts. While the potential for exponential speedups and enhanced efficiency is evident, the field faces significant challenges, including hardware constraints, noise, and limited qubit coherence in the current era of Noisy Intermediate-Scale Quantum devices. Emerging solutions, such as error mitigation techniques, hybrid frameworks, and advancements in quantum hardware, are discussed as critical enablers for scalable and fault-tolerant Quantum Machine Learning systems. By synthesizing state-of-the-art developments and identifying research gaps, this survey aims to provide a foundational resource for advancing Quantum Machine Learning toward practical, real-world applications in tackling computationally intensive problems.</t>
         </is>
       </c>
       <c r="H2" s="5" t="inlineStr">
@@ -859,33 +859,37 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>40ee764aa129</t>
+          <t>4bfe441a5ebe</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>Quantum Computing Fundamentals: Beyond Classical Bits</t>
+          <t>Option pricing under stochastic volatility on a quantum computer</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>Karni S.</t>
+          <t>Guoming Wang; Angus Kan</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>10.1007/978-3-032-10775-6_1</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="inlineStr"/>
+          <t>10.48550/arxiv.2312.15871</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>We develop quantum algorithms for pricing Asian and barrier options under the Heston model, a popular stochastic volatility model, and estimate their costs, in terms of T-count, T-depth and number of logical qubits, on instances under typical market conditions. These algorithms are based on combining well-established numerical methods for stochastic differential equations and quantum amplitude estimation technique. In particular, we empirically show that, despite its simplicity, weak Euler method achieves the same level of accuracy as the better-known strong Euler method in this task. Furthermore, by eliminating the expensive procedure of preparing Gaussian states, the quantum algorithm based on weak Euler scheme achieves drastically better efficiency than the one based on strong Euler scheme. Our resource analysis suggests that option pricing under stochastic volatility is a promising application of quantum computers, and that our algorithms render the hardware requirement for reaching practical quantum advantage in financial applications less stringent than prior art.</t>
+        </is>
+      </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>scopus</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="I3" s="5" t="n"/>
@@ -899,37 +903,33 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>4a063cd54207</t>
+          <t>83acd7a49f68</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>Superconductivity, pair density wave, and Neel order in cuprates</t>
+          <t>A new hybrid neural network framework inspired by biological systems for advanced financial forecasting</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Li-Han Chen; Da Wang; Yi Zhou; Qiang-Hua Wang</t>
+          <t>Chuchu Rao; Tianju Xue; Min‐Yen Kan; Peng Zhou; Yeshen Lan</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>10.1088/0256-307X/37/1/017403</t>
-        </is>
-      </c>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t>We investigate in underdoped cuprates possible coexistence of the superconducting (SC) order at zero momentum and pair density wave (PDW) at momentum ${\bf Q}=(π, π)$ in the presence of a Neel order. By symmetry, the $d$-wave uniform singlet pairing $dS_0$ can coexist with the $d$-wave triplet PDW $dT_{\bf Q}$, and the $p$-wave singlet PDW $pS_{\bf Q}$ can coexist with the $p$-wave uniform triplet $pT_0$. At half filling, we find the novel $pS_{\bf Q}+pT_0$ state is energetically more favorable than the $dS_0+dT_{\bf Q}$ state. At finite doping, however, the $dS_0+dT_{\bf Q}$ state is more favorable. In both types of states, the variational triplet parameters, $dT_{\bf Q}$ and $pT_0$, are of secondary significance. Our results point to a fully symmetric $\mathrm{Z_2}$ quantum spin liquid with spinon Fermi surface in proximity to the Neel order at zero doping, and to intertwined $d$-wave triplet PDW fluctuations and spin moment fluctuations along with the dominant $d$-wave singlet SC at finite doping. The results are obtained by variational quantum Monte Carlo simulations.</t>
-        </is>
-      </c>
+          <t>10.1038/s41598-025-21842-5</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr"/>
       <c r="H4" s="5" t="inlineStr">
         <is>
-          <t>arxiv</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="I4" s="5" t="n"/>
@@ -943,29 +943,37 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>92fc435704d5</t>
+          <t>b753486d909e</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>ARTIFICIAL INTELLIGENCE, MACHINE LEARNING, AND BIG DATA FOR CORROSION CONTROL – QUO VADIS?</t>
+          <t>Quantum Program Testing Through Commuting Pauli Strings on IBM's Quantum Computers</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Winkler D.A.</t>
+          <t>Asmar Muqeet; Shaukat Ali; Paolo Arcaini</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr"/>
-      <c r="G5" s="5" t="inlineStr"/>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>10.48550/arxiv.2408.00501</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>The most promising applications of quantum computing are centered around solving search and optimization tasks, particularly in fields such as physics simulations, quantum chemistry, and finance. However, the current quantum software testing methods face practical limitations when applied in industrial contexts: (i) they do not apply to quantum programs most relevant to the industry, (ii) they require a full program specification, which is usually not available for these programs, and (iii) they are incompatible with error mitigation methods currently adopted by main industry actors like IBM. To address these challenges, we present QOPS, a novel quantum software testing approach. QOPS introduces a new definition of test cases based on Pauli strings to improve compatibility with different quantum programs. QOPS also introduces a new test oracle that can be directly integrated with industrial APIs such as IBM's Estimator API and can utilize error mitigation methods for testing on real noisy quantum computers. We also leverage the commuting property of Pauli strings to relax the requirement of having complete program specifications, making QOPS practical for testing complex quantum programs in industrial settings. We empirically evaluate QOPS on 194,982 real quantum programs, demonstrating effective performance in test assessment compared to the state-of-the-art with a perfect F1-score, precision, and recall. Furthermore, we validate the industrial applicability of QOPS by assessing its performance on IBM's three real quantum computers, incorporating both industrial and open-source error mitigation methods.</t>
+        </is>
+      </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>scopus</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="I5" s="5" t="n"/>
@@ -979,33 +987,37 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>cc8cb8af742f</t>
+          <t>4a063cd54207</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Exploring Computational Intelligence: Core Concepts, Applications, and Emerging Innovations</t>
+          <t>Superconductivity, pair density wave, and Neel order in cuprates</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Siva Subramanian R.</t>
+          <t>Li-Han Chen; Da Wang; Yi Zhou; Qiang-Hua Wang</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>10.1109/ICSCSA66339.2025.11170798</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr"/>
+          <t>10.1088/0256-307X/37/1/017403</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>We investigate in underdoped cuprates possible coexistence of the superconducting (SC) order at zero momentum and pair density wave (PDW) at momentum ${\bf Q}=(π, π)$ in the presence of a Neel order. By symmetry, the $d$-wave uniform singlet pairing $dS_0$ can coexist with the $d$-wave triplet PDW $dT_{\bf Q}$, and the $p$-wave singlet PDW $pS_{\bf Q}$ can coexist with the $p$-wave uniform triplet $pT_0$. At half filling, we find the novel $pS_{\bf Q}+pT_0$ state is energetically more favorable than the $dS_0+dT_{\bf Q}$ state. At finite doping, however, the $dS_0+dT_{\bf Q}$ state is more favorable. In both types of states, the variational triplet parameters, $dT_{\bf Q}$ and $pT_0$, are of secondary significance. Our results point to a fully symmetric $\mathrm{Z_2}$ quantum spin liquid with spinon Fermi surface in proximity to the Neel order at zero doping, and to intertwined $d$-wave triplet PDW fluctuations and spin moment fluctuations along with the dominant $d$-wave singlet SC at finite doping. The results are obtained by variational quantum Monte Carlo simulations.</t>
+        </is>
+      </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>scopus</t>
+          <t>arxiv</t>
         </is>
       </c>
       <c r="I6" s="5" t="n"/>
@@ -1019,33 +1031,33 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>53585cb7d779</t>
+          <t>46924b58d18b</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Classical and quantum cost of measurement strategies for quantum-enhanced auxiliary field Quantum Monte Carlo</t>
+          <t>AIoE-Powered Supply Chain Optimization for Smart Agriculture</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Matthew Kiser; Anna Schroeder; Gian-Luca R. Anselmetti; Chandan Kumar; Nikolaj Moll; Michael Streif; Davide Vodola</t>
+          <t>Asghar Hemmati; Mahdi Aliyari; Adel Pourghader Chobar</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr"/>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>Quantum-enhanced auxiliary field quantum Monte Carlo (QC-AFQMC) uses output from a quantum computer to increase the accuracy of its classical counterpart. The algorithm requires the estimation of overlaps between walker states and a trial wavefunction prepared on the quantum computer. We study the applicability of this algorithm in terms of the number of measurements required from the quantum computer and the classical costs of post-processing those measurements. We compare the classical post-processing costs of state-of-the-art measurement schemes using classical shadows to determine the overlaps and argue that the overall post-processing cost stemming from overlap estimations scales like $\mathcal{O}(N^9)$ per walker throughout the algorithm. With further numerical simulations, we compare the variance behavior of the classical shadows when randomizing over different ensembles, e.g., Cliffords and (particle-number restricted) matchgates beyond their respective bounds, and uncover the existence of covariances between overlap estimations of the AFQMC walkers at different imaginary time steps. Moreover, we include analyses of how the error in the overlap estimation propagates into the AFQMC energy and discuss its scaling when increasing the system size.</t>
-        </is>
-      </c>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>10.1007/978-981-96-7202-8_13</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr"/>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>arxiv</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="I7" s="5" t="n"/>
@@ -1059,17 +1071,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>e3a033ada822</t>
+          <t>5bb7a2cb856f</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Smart Payment Fraud Detection using QML - A Major Challenge</t>
+          <t>Toward a Quantum-Science Gateway: A Hybrid Reference Architecture Facilitating Quantum Computing Capabilities for Cloud Utilization</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Tekkali C.G.</t>
+          <t>Attila Csaba Marosi; Attila Farkas; Tamás Máray; Róbert Lovas</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -1079,13 +1091,17 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>10.1109/ICAIS56108.2023.10073712</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr"/>
+          <t>10.1109/access.2023.3342749</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>The emerging availability of quantum compute resources fosters the examination of its exploitation possibilities in different scientific domains, like artificial intelligence, manufacturing or finance. A significant number of research scientists primarily rely on cloud computing infrastructures while conducting research, whereas access to real (mostly remote) quantum hardware resources requires the deployment and proper configuration of different software components. In this paper we present a hybrid, cloud-based reference architecture that lowers the entry barrier to start new experiments with a wide range of quantum compute resources. The solution facilitates the execution of distributed quantum computing simulations in traditional cloud environments, and also access to several remote quantum compute resources. The reference architecture is highly portable to various cloud platforms, resulting in efficient adaptation and application possibilities by research communities. For demonstration purposes, the paper describes our related experiences on the federated, OpenStack-based research infrastructure of the Hungarian Research Network (abbreviated as HUN-REN).</t>
+        </is>
+      </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>scopus</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="I8" s="5" t="n"/>
@@ -1099,37 +1115,37 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>4350e1cd1404</t>
+          <t>8b9e92a06fef</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Quantum Computing Drives Innovation in Business Intelligence Across Marketing and Finance through Systematic Review and Strategic Foresight</t>
+          <t>Stress Testing Financial Systems– Simulating economic disruption using AI-driven risk models</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>A. Alguno; R. Capangpangan; Yuri U. Pendon; Rosemarie Cruz-Español</t>
+          <t>Shubham Metha; Manoj Varma Lakhamraju; Nikhil Sagar Miriyala; Kiran Babu Macha</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>10.14419/803cts61</t>
+          <t>10.22399/ijcesen.2132</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>The emerging quantum computing technology (QC) transforms business intelligence by creating new methods for marketing and finance to use data in their decision-making processes. This research combines a systematic literature review with a meta-analysis of 26 peer-reviewed articles spanning from 2014 to 2025 to show how quantum computing improves predictive analytics and customer segmentation and sentiment analysis, portfolio optimization, and risk modeling. The research uses PRISMA guidelines together with strategic foresight tools to detect how hybrid quantum-classical systems replace classical models by delivering exponential speed and accuracy, and scalability benefits. The research demonstrates that QSVM, QAOA, and quantum-enhanced neural networks serve as primary methodologies to create real-time, emotionally intelligent, highly adaptive decision systems. The thematic analysis, together with conceptual mapping, shows that quantum tools are converging into a unified interdisciplinary space that combines marketing with finance and supply chains and pricing strategies. The study reveals important research deficiencies in multilingual datasets as well as benchmarking and ethical readiness, and suggests a strategic integration plan for global implementation by 2030. The research demonstrates that quantum computing represents a strategic capability that enables future-ready data-driven enterprises to enter a new business intelligence era based on quantum resilience.</t>
+          <t>The increasing interconnectedness and complexity of global financial markets have increased the stakes for advanced risk assessment methods. Traditional financial stress testing based on static rule-based models, historic datasets, and past crisis data which is poorly suited to address the nonlinear relationships and rapidly evolving risk factors characteristic of modern economies. This paper explores the use of Artificial Intelligence (AI) in financial stress testing with machine learning (ML), deep reinforcement learning (DRL), and generative AI to simulate systemic economic shocks and predict financial instability better. It also considers social media activities, geopolitical situations, climate change, pandemics, global financial markets, emerging technologies. This study provides a mechanized AI-based implementation plan for financial stress testing, data engineering pipeline profiling, model selection methodologies (LSTMs, GANs, and XGBoost), and real-time risk monitoring approaches. Financial institution case studies such as the Federal Reserve, Bank of England, and hedge funds such as BlackRock show how AI enhances prediction accuracy, reduces risk assessment cycles, and provides real-time financial crisis management approaches. In addition, this paper also opens up the prospects of Quantum AI, DeFi risk modeling, and digital twins powered by AI to revolutionize systemic risk analysis and crisis forecasting in finance. Our findings show that AI-powered financial stress tests are capable of significantly enhancing risk resilience, early warning, and global financial stability. Studies on XAI methods, audit architectures under regulatory directives, and the combination of quantum computing with AI-powered financial modeling for enhancing financial sector risk assessment even further is a direction that should be explored in future research.</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>semantic_scholar</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="I9" s="5" t="n"/>
@@ -1143,33 +1159,37 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>cad9914cf2e2</t>
+          <t>5e828a070fa3</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Cryptanalytic Performance Appraisal of Improved HLL, KUOCHEN, GENGVRF, FENGVRF Secure Signature with TKIP Digital Workspaces: For Financial Cryptography</t>
+          <t>Fortifying Plasma Chains: A Quantum-Resilient Approach Using Hybrid Cryptography</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Kumar R.</t>
+          <t>K. Thanushree; U. Padmavathi</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>10.1007/s11277-020-07642-2</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr"/>
+          <t>10.1109/icitiit64777.2025.11041151</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>The rise of quantum computing poses a serious threat to the cryptographic backbone of decentralized systems like Ethereum's Plasma chains, which rely on classical cryptography. This paper introduces a novel approach, integrating post-quantum cryptography (PQC) with hybrid frameworks that blend quantum-resistant algorithms with traditional cryptographic techniques. This hybrid approach ensures strong quantum-resistant security while maintaining Plasma's scalability, performance, and compatibility with Ethereum's ecosystem. This study focuses on critical plasma components like state transitions, fraud proofs, and exit strategies, that are most vulnerable to quantum attacks, proposing hybrid cryptography for low risk, high frequency transactions, while leveraging post-quantum solutions like Kyber and NTRU for securing long-term commitments and high-risk processes. By establishing clear decision criteria to determine when hybrid cryptography should take precedence over pure PQC, based on factors such as computational efficiency, security demands, and system interoperability. The insights set a new standard for Plasma's quantum resilience, ensuring it stays secure and adaptable as quantum computing evolves, paving path for decentralized finance to thrive in the face of quantum threats.</t>
+        </is>
+      </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>scopus</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="I10" s="5" t="n"/>
@@ -1183,37 +1203,37 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>20063e119947</t>
+          <t>17ef268d6ad8</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Quantum Walk–Inspired Fourier Operators for Markovian Dynamics and Modular Structure Detection</t>
+          <t>THE XENOPOULOS GENETIC-HISTORICAL LOGIC SYSTEM (X-GHLS): A Formal Foundation of the Dialectics of Becoming</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Yanfei Ma; Daozheng Qu; Yibo Wang</t>
+          <t>Katerina Xenopoulou; Epameinondas Xenopoulos</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>10.1109/ICMLCA66850.2025.11336551</t>
+          <t>10.5281/zenodo.18664035</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>Community recognition continues to be a significant difficulty in the analysis of complex networks, especially in dynamic and stochastic contexts where communities change over time. Conventional spectral clustering and Markovian models either include structural regularities or temporal dependencies, although frequently lack the ability to amalgamate both within a cohesive theoretical framework. This study presents a Fourier operator framework inspired by quantum walks that integrates spectral graph theory, Markov processes, and quantum brain dynamics for the discovery of modular structures. We specifically build Fourier-Markov operators based on quantum walk principles to encapsulate both global frequency components and local transition dynamics of evolving networks. Our system utilizes superposition and interference effects by mapping random walks into a quantum-inspired Hilbert space, therefore uncovering latent modular structures with enhanced resolution. The resultant operator family facilitates interpretable community partitions, scalable computation using hybrid classicalquantum methodologies, and resilient detection across temporal snapshots. Experimental assessments on benchmark dynamic networks—encompassing social, biological, and financial graphs—indicate that our approach attains enhanced modularity optimization, temporal stability, and uncertainty calibration relative to leading community detection benchmarks. This study emphasizes the promise of quantum-spectral operators as a novel basis for examining Markovian community dynamics in intricate systems.</t>
+          <t>A Formal Foundation of the Dialectics of Becoming "Xenopoulos' system is not merely a new logic — it is the mathematical formalization of the dialectical process itself, where contradiction is not eliminated but transformed, history is not forgotten but incorporated, and the unpredictable (ϵ) is not rejected but recognized as fundamental. The system is complete, coherent, and mathematically rigorous" Authors:Katerina Xenopoulou (Implementation &amp; Experimental Analysis)Epameinondas Xenopoulos † (Theoretical Framework) † This work is dedicated to his memory. ORCID:K. Xenopoulou: https://orcid.org/0009-0004-9057-7432E. Xenopoulos: https://orcid.org/0009-0000-1736-8555 Corresponding Repositories: Theory &amp; Core: https://github.com/kxenopoulou/epameinondas_xenopoulos_epistemology-of-logic_genetic-historical-logic Applications &amp; Experiments: https://github.com/kxenopoulou/xenopoulos_dialectical-paradoxes-XEPTQLRI PART 0: PRELIMINARIES Abstract We present the first complete mathematical formalization of the Xenopoulos Genetic-Historical Logic System (X-GHLS), a novel logical architecture derived from the philosophical work of Epameinondas Xenopoulos (1920-1994). Unlike traditional logics that treat contradiction as error and time as an external parameter, X-GHLS formalizes dialectical becoming as logical necessity through a system of 33 principles. The system is founded on three primitive operators—Dialectical Negation (¬ᴰ), Dialectical Conjunction (∧ᴰ), and Sublation (⤊, Aufhebung)—which generate a framework of 10 axioms and 5 theorems. We introduce the mathematical formalization of the core operator N[Fi(Gj)] and the XEPTQLRI index, a novel metric for quantifying dialectical tension and predicting critical transitions. Through computational simulations across 7 domains with rigorous out-of-sample validation, we demonstrate: 68.3% predictive accuracy at the critical stage (τ₄) for Bitcoin (p &lt; 0.001) 32.2% of systems classified as "stable" by traditional metrics are in states of false stability 94.3% accuracy in predicting neural network collapse 5 epochs in advance (XenoLSTM v2.0) 68% reduction in paradoxical behaviors in deep learning architectures 3.01× coherence time improvement in quantum computing applications (p &lt; 0.001) 60% bias reduction in ethical AI systems (COMPAS dataset, p &lt; 0.001) Hedge fund grade validation using block bootstrap Monte Carlo (10,000 simulations) yields: median return 30.9% at 2% risk per trade, 95% VaR 19.7%, risk of ruin 0.02%, and Calmar ratio 1.31, confirming institutional-grade robustness. All results are accompanied by out-of-sample validation, statistical significance tests (p-values, confidence intervals), and comparison with state-of-the-art models. The complete formal-dialectical matrix of the world N = F⊗G is presented, with full implementation in Python available on GitHub. Summary Statistics Measure Value Total principles 33 Axioms 10 Theorems 5 Empirical Findings 4 Experimental applications 7 Lines of code ~5,000 GitHub repositories 5 Zenodo DOIs 5 Monte Carlo simulations 10,000 Significance level p &lt; 0.001 Out-of-sample validation ✓ SOTA comparison ✓ Falsifiability criteria ✓ PART 1: INTRODUCTION 1.1 The Historical Problem of Logic For more than two millennia, logic has been dominated by the principle of static identity: A = A. From Aristotle's Organon to the mathematical logic of Frege and Hilbert, the primary function of logic has been to identify and preserve truth, treating: contradiction as error (principium contradictionis) change as an external phenomenon to be described time as a parameter outside the logical system The philosophical tradition of dialectics, from Heraclitus to Hegel and Marx, has long argued that reality is fundamentally characterized by contradiction, movement, and qualitative transformation. Yet this tradition remained within the realm of philosophy, never achieving a rigorous formalization. 1.2 The Vision of Epameinondas Xenopoulos Epameinondas Xenopoulos (1920-1994) identified this profound gap. In his seminal work "Epistemology of Logic: Logic-Dialectic or Theory of Knowledge" [1], he proposed a revolutionary thesis: "Dialectics is not a method applied to logic; it is itself a new logic." His vision was based on three fundamental observations: Contradiction is not an error but a creative force [1, pp. 54-55, 108-109] Time is an inherent dimension of logic [1, pp. 65, 48-49, 100-101] Becoming is a logical necessity [1, pp. 112-113, 114-115] 1.3 Methodology and Epistemological Commitments This work adopts the following epistemological position: a mathematical framework that claims to predict empirical phenomena is judged by: Internal consistency (logical validity) Out-of-sample validation (prediction on new data) Reproducibility (independent verification) Statistical power (p-values, confidence intervals) Falsifiability (clear failure criteria) X-GHLS is subjected to all these criteria throughout this work. 1.4 Structure of the Paper Part 2: Presentation of the 33 principles with full page references Part 3: Mathematical foundation — 10 axioms of X-GHLS Part 4: Theorems and Empirical Findings Part 5: Experimental validation with out-of-sample testing Part 6: Hedge fund grade validation Part 7: Comparison with other logical systems Part 8: Applications and social benefit Part 9: Open source code and documentation Part 10: Acknowledgments Part 11: References Part 12: Appendix — Table of symbols 1.5 Notation ℝ : real numbers [0,1] : unit interval D : dialectical space ⟨Θ, A, H⟩ : dialectical state ¬ᴰ : dialectical negation ∧ᴰ : dialectical conjunction ↑ : sublation (Aufhebung) Ξ : XEPTQLRI index τ_i : dialectical stage PART 2: THE 33 PRINCIPLES OF XENOPOULOS 2.1 Dialectical Principles Principle 1: Synthesis of Formal and Dialectical Logic [1, pp. 36-37, 43-44, 67-70] For x = ⟨Θ, A, H⟩ ∈ D: S(x)=Θ+A2+λ∥Θ−A∥⋅∣H∣,λ∈[0,1]S(x)=2Θ+A+λ∥Θ−A∥⋅∣H∣,λ∈[0,1] Principle 2: Dialectical Contradiction as Creative Force [1, pp. 54-55, 108-109, 73-74] For x, y ∈ D: Φ(x,y)=∣Θx−Θy∣⋅∣Ax−Ay∣⋅e−∣Hx△Hy∣Φ(x,y)=∣Θx−Θy∣⋅∣Ax−Ay∣⋅e−∣Hx△Hy∣ where Hx△HyHx△Hy is the symmetric difference: Hx△Hy=(Hx∖Hy)∪(Hy∖Hx)Hx△Hy=(Hx∖Hy)∪(Hy∖Hx) and ∣Hx△Hy∣∣Hx△Hy∣ its cardinality. Principle 3: Dialectic of Stasis and Motion [1, pp. 112-113, 114-115] For x(t) = ⟨Θ(t), A(t), H(t)⟩: v(t)=Θ(t)−Θ(t−1),κ(t)=∣v(t)∣1+∣v(t)∣v(t)=Θ(t)−Θ(t−1),κ(t)=1+∣v(t)∣∣v(t)∣ Principle 4: Incorporation of Otherness [1, pp. 109-110, 115-116] For x, y ∈ D: x⊕y=x+y2+κ∣x−y∣x⊕y=2x+y+κ∣x−y∣ where κ=0.3κ=0.3 results from minimizing the approximation error between discrete and continuous versions of dialectical synthesis. In 10,000 Monte Carlo simulations, the value minimizing mean squared error is κ=0.31±0.03κ=0.31±0.03. Principle 12: Dialectical Conception of the Infinite [1, pp. 110-111] For x ∈ D: Ω(x)=lim⁡n→∞x⊕x⊕⋯⊕x⏟n timesΩ(x)=n→∞limn timesx⊕x⊕⋯⊕x Principle 16: Processual Logic [1, pp. 77-78, 34] For x(t) ∈ D: x(t+1)=F(x(t),x(t−1),…,x(t−k))x(t+1)=F(x(t),x(t−1),…,x(t−k)) Principle 18: The Law of Succession of States [1, p. 255] xt+1=↑(xt,¬D(xt))xt+1=↑(xt,¬D(xt)) Principle 26: The Concept of "Sublation" (Aufhebung) [1, pp. 11, 192-193] ↑(x,y)=x⊕y⊕¬D(x⊕y)↑(x,y)=x⊕y⊕¬D(x⊕y) 2.2 Theory of Knowledge Principle 5: Historical-Genetic Approach [1, pp. 65, 48-49, 100-101] H(t)={xτ:τ&lt;t}H(t)={xτ:τ&lt;t} Principle 6: Dialectic of Practice and Theory [1, pp. 76-78, 16-19, 37] Π(t)=T(t)+P(t)2+γ∣T(t)−P(t)∣Π(t)=2T(t)+P(t)+γ∣T(t)−P(t)∣ Principle 7: Transitional Nature of Truth [1, pp. 111-112, 119-120] Truth(t)=Truth0⋅e−κt+∑τ=0t−1Φ(τ)e−κ(t−τ)Truth(t)=Truth0⋅e−κt+τ=0∑t−1Φ(τ)e−κ(t−τ) Principle 13: Genetic Logic [1, pp. 28, 67-68] xt+1=f(xt,xt−1,…,x0)xt+1=f(xt,xt−1,…,x0) Principle 17: Restructuring of Dialectical Thought [1, pp. 86-87, 16-18] Snew=Sold⊕ΔSSnew=Sold⊕ΔS Principle 19: Repeatability and Historical Dialectics [1, pp. 255-256] ∃T&gt;0:d(x(t+T),x(t))&lt;ε∃T&gt;0:d(x(t+T),x(t))&lt;ε Principle 27: The Triple Coincidence (Sπ, Sα, f(x)) [1, pp. 238-240] Truth=1−∣Sπ−Sα∣⋅∣Sα−f(x)∣Truth=1−∣Sπ−Sα∣⋅∣Sα−f(x)∣ Principle 28: The Suszko Triad (L, B, Θ) [1, pp. 183-187] ⟨L,B,Θ⟩⟨L,B,Θ⟩ 2.3 Mathematical Formalization Principle 21: The N[Fi(Gj)] Operator [1, pp. 11, 248-249] N[Fi(Gj)]=C(Fi(Gj),N∘R(Fi(Gj)))N[Fi(Gj)]=C(Fi(Gj),N∘R(Fi(Gj))) Principle 22: The INRC Group [1, pp. 86, 91-92] N2=R2=C2=I,N∘R=R∘NN2=R2=C2=I,N∘R=R∘N Principle 23: The XEPTQLRI Index [1, pp. 289-290] Ξ=T⋅H⋅(1+P)max⁡(1,1−0.7T−0.3P)Ξ=max(1,1−0.7T−0.3P)T⋅H⋅(1+P) where: T=∣Θ−A∣T=∣Θ−A∣trend=Θ(t)−Θ(t−1)Θ(t−1)(for discrete time)trend=Θ(t−1)Θ(t)−Θ(t−1)(for discrete time)H=min⁡(∣trend∣2,1.0)H=min(2∣trend∣,1.0)P={min⁡(Θ,A)⋅0.9Θ&gt;0.8,A&gt;0.80.7T&lt;0.2,Θ&gt;0.60.0otherwiseP=⎩⎨⎧min(Θ,A)⋅0.90.70.0Θ&gt;0.8,A&gt;0.8T&lt;0.2,Θ&gt;0.6otherwise Remark 2.3.1 (Origin of XEPTQLRI coefficients). The coefficients result from optimizing the cost function: L(α,β)=∑i=1N[Ξi−(αTi+βPi)]2L(α,β)=i=1∑N[Ξi−(αTi+βPi)]2 subject to α+β=1α+β=1. The solution yields α=0.70±0.02α=0.70±0.02, β=0.30±0.02β=0.30±0.02 (95% CI). The coefficient 0.9 arises from maximizing the information function I(Ξ)=−∑p(τ)log⁡p(τ)I(Ξ)=−∑p(τ)logp(τ). Principle 24: The Ten Stages (τ₀-τ₉) [1, pp. 280-281, 290-291] τ(Ξ)={0Ξ≤111&lt;Ξ≤222&lt;Ξ≤333&lt;Ξ≤444&lt;Ξ≤555&lt;Ξ≤666&lt;Ξ≤777&lt;Ξ≤888&lt;Ξ≤99Ξ&gt;9τ(Ξ)=⎩⎨⎧0123456789Ξ≤11&lt;Ξ≤22&lt;Ξ≤33&lt;Ξ≤44&lt;Ξ≤55&lt;Ξ≤66&lt;Ξ≤77&lt;Ξ≤88&lt;Ξ≤9Ξ&gt;9 Principle 25: The Dubarle Operators [1, pp. 192-193] △A=A∩U,▼A=A∪P△A=A∩U,▼A=A∪P▽A=A∩P,▲A=A∪U▽A=A∩P,▲A=A∪U Principle 32: Rogowski's Np Operator [1, pp. 187-188] Np(x)=xp⋅(1−x)1−pNp(x)=xp⋅(1−x)1−p 2.4 The Extension of Hilbert's Axioms (pp. 290-291) In the closing pages of his work (pp. 290-291), Xenopoulos advances what may be regarded as the structural culmination of his dialectical project: a reinterpretation and extension of the classical Hilbert–Russell axiomatic fram</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>semantic_scholar</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="I11" s="5" t="n"/>
@@ -1227,28 +1247,32 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>ff9590d2d73c</t>
+          <t>9150dabd3035</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>QPanda: high-performance quantum computing framework for multiple application scenarios</t>
+          <t>Quantum Approximate Optimization Algorithm for Test Case Optimization</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Menghan Dou; Tianrui Zou; Yuan Fang; Jing Wang; Dongyi Zhao; Lei Yu; Boying Chen; Wenbo Guo; Ye Li; Zhaoyun Chen; Guoping Guo</t>
+          <t>Xinyi Wang; Shaukat Ali; Tao Yue; Paolo Arcaini</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr"/>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>10.1109/TSE.2024.3479421</t>
+        </is>
+      </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>With the birth of Noisy Intermediate Scale Quantum (NISQ) devices and the verification of "quantum supremacy" in random number sampling and boson sampling, more and more fields hope to use quantum computers to solve specific problems, such as aerodynamic design, route allocation, financial option prediction, quantum chemical simulation to find new materials, and the challenge of quantum cryptography to automotive industry security. However, these fields still need to constantly explore quantum algorithms that adapt to the current NISQ machine, so a quantum programming framework that can face multi-scenarios and application needs is required. Therefore, this paper proposes QPanda, an application scenario-oriented quantum programming framework with high-performance simulation. Such as designing quantum chemical simulation algorithms based on it to explore new materials, building a quantum machine learning framework to serve finance, etc. This framework implements high-performance simulation of quantum circuits, a configuration of the fusion processing backend of quantum computers and supercomputers, and compilation and optimization methods of quantum programs for NISQ machines. Finally, the experiment shows that quantum jobs can be executed with high fidelity on the quantum processor using quantum circuit compile and optimized interface and have better simulation performance.</t>
+          <t>Test case optimization (TCO) reduces software testing cost while preserving its effectiveness, but solving TCO problems for large-scale and complex systems requires substantial computational resources. Quantum approximate optimization algorithms (QAOAs) are promising combinatorial optimization algorithms that rely on quantum computational resources, with the potential efficiency advantages over classical approaches. Several proof-of-concept applications of QAOAs for solving combinatorial problems, such as portfolio optimization, energy systems, and job scheduling, have been proposed. Given the lack of investigation into QAOA's application to TCO problems, and motivated by the computational challenges of TCO problems and the potential of QAOAs, we present IGDec-QAOA to formulate a TCO problem as a QAOA problem and solve it on both ideal and noisy quantum computer simulators, as well as on a real quantum computer. To solve bigger TCO problems that require many qubits, which are unavailable currently, we integrate a problem decomposition strategy with the QAOA. We performed an empirical evaluation with five TCO problems and four publicly available industrial datasets from ABB, Google, and Orona to compare various configurations of IGDec-QAOA, assess its decomposition strategy of handling large datasets, and compare its performance with classical algorithms (i.e., GA and Random Search). Based on the evaluation results achieved on an ideal simulator, we recommend the best configuration of our approach for TCO problems. We also demonstrate that it can reach the same effectiveness as GA and outperform GA in two out of five test case optimization problems. In addition, we observe that, on a noisy simulator, IGDec-QAOA achieved similar performance to that from an ideal simulator. Finally, we demonstrate the feasibility of IGDec-QAOA on a real quantum computer in the presence of noise.</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
@@ -1267,41 +1291,37 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>aeded818fc67</t>
+          <t>d2bec1f37aca</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Decoding the Nutritional Power: A Comparative Analysis of Sathu Maavu and Millet Health Mixes</t>
+          <t>Innovations and Applications of Quantum Computing</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>R. M</t>
+          <t>Bhanu Prakash</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>10.71097/ijsat.v16.i1.2049</t>
+          <t>10.20944/preprints202108.0193.v1</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>Abstract
-This research investigates the emerging trends and methodologies in retail and institutional investing, focusing on the integration of artificial intelligence and advanced analytical techniques in investment analysis. The study employs an extended Technology Acceptance Model (TAM) framework analysed through Partial Least Squares Structural Equation Modelling (PLS-SEM) to examine the relationships between technological innovation, predictive performance, risk management, decision-making efficiency, and ethical governance in investment strategies.
-The research utilizes a mixed-methods approach, collecting data from 220 investment professionals through a structured questionnaire. The sampling framework encompasses diverse stakeholders including institutional investors, financial analysts, and technology specialists, ensuring comprehensive representation of the investment ecosystem. The study examines five key hypotheses related to AI impact, data integration, risk assessment transformation, technological efficiency, and ethical AI adoption in investment analysis.
-Findings reveal significant correlations between advanced technological adoption and improved investment outcomes, with AI-driven strategies demonstrating superior predictive accuracy (&gt;15% improvement) and risk management capabilities (25% reduction in portfolio volatility). The research contributes to the existing body of knowledge by providing empirical evidence of the transformative potential of AI in investment analysis while highlighting the critical importance of ethical considerations and governance frameworks.
-The study presents practical implications for investment professionals and institutions, offering insights into the effective integration of advanced technologies while maintaining ethical standards. Additionally, it provides a foundational framework for future research in technological innovation in investment analysis, particularly in the areas of quantum computing and federated learning applications.</t>
+          <t>Moore&amp;amp;rsquo;s law will cease to be relevant once transistors are the size of electrons. Once this occurs, we will no longer be able to use silicon for technological advancement. However, breakthroughs will continue in the form of a sixth paradigm: a 3D molecular computing model such as quantum comput- ing. Some of the promising areas of quantum computing researched in this study are (i) algorithmic advancements - such as Shor&amp;amp;rsquo;s, Grover&amp;amp;rsquo;s, error correction, fault tolerance and other new algorithms; (ii) hardware - such as the quantum system architecture, circuit models, entanglement, superposition and no-cloning qubits; (iii) market segments - such as finance, healthcare, and chemistry; (iv) the supremacy established over classical computing; and (v) areas of applicability. Significant progress has been made in these areas in recent decades, and they have garnered immense interest, attention and the funding required to make good progress.</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>semantic_scholar</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="I13" s="5" t="n"/>
@@ -1315,33 +1335,37 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>ea5089128e6b</t>
+          <t>48fc0e04ac90</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>Time Synchronization in Communication Networks: A Comparative Study of Quantum Technologies</t>
+          <t>Qured: A Quantum-Inspired Symbolic Platform for Portfolio Optimization through High-Dimensional QUBO Modeling</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Nande S.S.</t>
+          <t>Halloub, Mohamed Ridha</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>10.1109/WCNC57260.2024.10570688</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="inlineStr"/>
+          <t>10.5281/zenodo.17554799</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>This work introduces Qured, a Quantum-Inspired Computing 2.0 (QIC 2.0) platform that reconstructs quantum informational geometry symbolically rather than stochastically. By applying Qured’s Symbolic State-Vector Framework (SSVF) to a 200-variable Quadratic Unconstrained Binary Optimization (QUBO) problem in portfolio management, we demonstrate that quantum-class performance can be achieved entirely on classical infrastructure. The study benchmarks Qured’s symbolic solver against classical Sequential Least Squares Quadratic Programming (SLSQP) and recent quantum-inspired QUBO formulations (e.g., Lu et al., Quantum-Inspired Portfolio Optimization in the QUBO Framework, arXiv:2410.05932v1). The results show near-perfect alignment between Qured’s symbolic frontier and the classical efficient frontier, with a correlation of 0.986 and a normalized RMSE of 1.8×10−31.8\times10^{-3}1.8×10−3, all achieved without stochastic sampling or quantum hardware. This benchmark establishes Qured as a practical and accessible bridge between symbolic computation and quantum-class optimization—delivering deterministic convergence, high scalability, and hardware-independent performance. The findings highlight the emergence of symbolic quantum computation as a new paradigm for achieving quantum advantage in finance and other large-scale combinatorial optimization domains.</t>
+        </is>
+      </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>scopus</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="I14" s="5" t="n"/>
@@ -1355,37 +1379,37 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>473d4881d50c</t>
+          <t>3c0cd6447ff9</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>Conceptual approaches to bank cybersecurity</t>
+          <t>Explainability of Decision-Making in Hybrid Quantum-Classical Classification Models</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>Iurie Caprian</t>
+          <t>Sayali Ramesh Kote</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>10.59642/edr.3.2025.27</t>
+          <t>10.5281/zenodo.18924701</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>Cybersecurity in banking is a multidimensional notion that brings together strategies, technologies, practices and processes aimed at protecting banks; systems, data and digital networks. The purpose of the research was to present the essence and trends in the development of cybersecurity within banks. The study was conducted by examining reports from specialized companies and expert opinions published in open form on the Internet. The materials thus accumulated allowed the creation of a complex picture of the current development of cybersecurity in banking activities. The main reasons that require bank cybersecurity management are: customer data protection; maintaining customer trust and reputation; compliance with regulations; preventing financial loss; protecting critical infrastructure; ensuring business continuity. It is clear that over the past few years the threat landscape has expanded in complexity and scope. Currently, banks are facing cybersecurity problems that have already become traditional, such as ransomware, unencrypted data, cloud-based cyber-attacks, social engineering, phishing attacks, malware, attacks on third-party providers, supply chain attacks, endpoint security. At the same time, we can talk about new challenges in strengthening the cybersecurity of banks: the evolution of zero trust security; regulatory pressures and compliance-driven security; quantum computing threats to cryptography; AI-powered fraud detection and financial crime prevention. Experts visions for the continued strengthening of cybersecurity in banking are linked to the evolution of advanced technologies and the improvement of regulatory frameworks. To this end, banks will develop innovations related to artificial intelligence, blockchain and quantum computing.</t>
+          <t>This research paper explores the explainability of decision-making in hybrid quantum–classical classification models. Quantum Machine Learning (QML) combines the power of quantum computing with classical machine learning techniques to solve complex computational problems. However, understanding how these hybrid models make decisions remains a significant challenge. The study focuses on analyzing hybrid quantum–classical architectures and evaluating methods that improve the interpretability of their predictions. Techniques from Explainable Artificial Intelligence (XAI) are applied to investigate the internal decision-making processes of the models. The research also compares classical machine learning approaches with quantum-enhanced models to understand their performance and transparency. The results demonstrate that explainability techniques can help researchers better interpret model predictions, identify important features, and improve trust in hybrid quantum–classical systems. This work contributes to the development of transparent and reliable quantum machine learning applications in areas such as healthcare, finance, and data analytics.</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>semantic_scholar</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="I15" s="5" t="n"/>
@@ -1399,33 +1423,37 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>5a5c11d1edc9</t>
+          <t>ba2626d6aaf4</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>The Synergy of DARQ Technologies: Integration and Future Prospects</t>
+          <t>Universal Phase Correction Framework: The Ait Zaouit Dual-Parity Protocol for Quantum Computing, 6G, and Defense Systems.</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Vajeem Hamiid M.</t>
+          <t>Ahmed Ait zaouit</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>10.1109/ICCRTEE64519.2025.11052901</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="inlineStr"/>
+          <t>10.5281/zenodo.18207730</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>Updated Description (Full Scope): This document establishes the official record and intellectual priority for the Ait Zaouit Protocol (AZP) and its foundational "Dual-Parity Equation". While validated with breakthrough results on IBM Quantum systems (achieving 80.57% fidelity), this mathematical framework is a Universal Solution for phase-error mitigation across multiple high-tech industries. The Ait Zaouit Dual-Parity Equation is designed to enhance and stabilize the following sectors: Quantum Computing: Dynamic error correction for superconducting, trapped-ion, and photonic qubits, enabling stable NISQ and Fault-Tolerant operations. Next-Gen Telecommunications (6G &amp; Beyond): Real-time stabilization of phase-shift keying (PSK) and signal integrity in ultra-high-frequency data transmission. Defense &amp; Aerospace: Unprecedented noise filtering for Quantum RADAR and LiDAR, ensuring high-precision detection in "noisy" or jammed environments. Satellite &amp; Deep-Space Communications: Correcting signal decoherence caused by atmospheric interference and long-distance transmission. Cybersecurity &amp; Quantum Cryptography: Strengthening Quantum Key Distribution (QKD) protocols against phase-induced hacking and signal loss. Medical Imaging &amp; Advanced Sensing: Improving the resolution of MRI and atomic-scale sensors by stabilizing wave-function measurements. Financial Engineering (Quantum Finance): Optimizing complex probability matrices for high-frequency trading and risk assessment algorithms. Digital Signal Processing (DSP): A general-purpose algorithmic layer to reduce "noise floors" in any system sensitive to phase fluctuations. Legal Assertion: This publication asserts that the logic of Dual-Parity as an error-correction mechanism is the sole intellectual property of Mohamed Ait Zaouit. Any derivative works or commercial implementations in the aforementioned sectors must reference this priority record. ORCID ID: 0009-0007-3278-5577</t>
+        </is>
+      </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>scopus</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="I16" s="5" t="n"/>
@@ -1439,37 +1467,33 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>9c0ebeda77b5</t>
+          <t>8bb4c5424927</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>Quantum Integration in HPC: Current Paradigms, Industrial Applications, and Research Frontiers</t>
+          <t>FiD-QAE: A Fidelity-Driven Quantum Autoencoder for Credit Card Fraud Detection</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>Suckmal Kommidi</t>
+          <t>Mansour El Alami; Adam Innan; Nouhaila Innan; Muhammad Shafique; Mohamed Bennai</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>10.22214/ijraset.2024.64143</t>
-        </is>
-      </c>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr"/>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>Abstract: This article presents a comprehensive review of the integration of quantum computing with High-Performance Computing (HPC), examining current trends, challenges, and future directions. We explore the fundamental principles of quantum computing and their relevance to HPC, followed by an analysis of state-of-the-art quantum algorithms and hybrid quantum-classical systems. The article addresses key technical challenges in hardware and software integration, as well as scalability and stability issues in quantum-enhanced HPC systems. Through a series of case studies, we demonstrate the practical applications and potential impact of quantum-HPC integration across various industries, including finance, drug discovery, and logistics. Our findings highlight the transformative potential of quantum computing in HPC, suggesting unprecedented improvements in computational speed and efficiency. The article concludes with an overview of emerging quantum technologies and identifies promising research opportunities, emphasizing the importance of collaboration between academia and industry. This work serves as a valuable resource for researchers, engineers, and industry professionals seeking to understand and leverage the synergy between quantum computing and HPC, paving the way for future innovations in computational capabilities</t>
+          <t>Credit card fraud detection is a critical task in financial security, as fraudulent transactions are rare, highly imbalanced, and often resemble legitimate ones. A wide range of classical machine learning methods, as well as more recent quantum machine learning approaches, have been investigated to address this challenge, each providing valuable progress but also leaving open questions regarding scalability, robustness, and adaptability to evolving fraud patterns. In this work, we introduce the Fidelity-based Quantum Autoencoder (FiD-QAE), a quantum architecture that employs fidelity estimation as the decision criterion for anomaly detection. Transactions are encoded into quantum states, compressed through a variational quantum circuit, and evaluated using the SWAP test to distinguish legitimate from fraudulent transactions. We conduct a comprehensive evaluation of FiD-QAE, including statistical analyses, multiple performance metrics, and robustness tests under quantum noise models. The results show that FiD-QAE maintains consistent performance across different imbalance levels and preserves robustness in noisy conditions. Moreover, validation on IBM Quantum hardware backends confirms the feasibility of our approach on real devices, with outcomes consistent with simulation. These findings position quantum fidelity as a powerful criterion for anomaly detection and highlight FiD-QAE as a promising direction that complements existing classical and quantum approaches, offering robustness and generalizability for financial fraud detection in realistic environments.</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>semantic_scholar</t>
+          <t>arxiv</t>
         </is>
       </c>
       <c r="I17" s="5" t="n"/>
@@ -1483,37 +1507,37 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>f4883fc328d4</t>
+          <t>d300ac850bd9</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Error-Resilient Quantum Machine Learning for Real-World Optimization Problems in Finance and Supply Chain Networks</t>
+          <t>Portfolio optimization based on quantum linear algorithm</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Milad Rahmati</t>
+          <t>Zhengming Guo; Tingting Song; Ge Lin</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>10.15408/inprime.v7i1.44960</t>
+          <t>10.1088/1402-4896/ad5c1d</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>The advent of quantum computing has introduced a revolutionary shift in computational paradigms, with the potential to address complex problems beyond the reach of classical systems. However, the practical deployment of quantum solutions is challenged by inherent issues such as noise and decoherence, which hinder their reliability. This study presents a novel error-resilient framework tailored for quantum machine learning (QML) to address optimization problems in finance and supply chain networks. By utilizing hybrid quantum-classical algorithms, the framework mitigates the detrimental effects of quantum noise and enhances computational robustness through advanced techniques like quantum variational circuits. Comprehensive experiments on real-world datasets highlight the framework's ability to outperform conventional methods in solving intricate optimization challenges. The findings demonstrate the transformative potential of quantum-assisted optimization for tackling critical issues in financial modeling and supply chain resilience. In this work, I propose a novel hybrid quantum-classical framework that integrates variational quantum circuits with noise mitigation strategies such as Zero Noise Extrapolation (ZNE), tailored for real-world optimization in finance and supply chain domains. This integrated approach—addressing error resilience and practical scalability together—sets the work apart from existing studies focused solely on theoretical or idealized scenarios.Keywords: Error resilience; Financial modeling; Hybrid algorithms; Optimization challenges; Quantum computing; Quantum machine learning. AbstrakMunculnya komputasi kuantum telah memperkenalkan pergeseran revolusioner dalam paradigma komputasi, dengan potensi untuk mengatasi masalah kompleks di luar jangkauan sistem klasik. Namun, penerapan praktis solusi kuantum ditantang oleh masalah inheren seperti kebisingan dan dekoherensi, yang menghambat keandalannya. Studi ini menyajikan kerangka kerja baru mengenai ketahanan kesalahan (error-resilient) yang dirancang untuk pembelajaran mesin kuantum (QML) dalam mengatasi masalah optimasi pada jaringan keuangan dan rantai pasokan. Dengan memanfaatkan algoritma kuantum-klasik hibrida, kerangka kerja tersebut mengurangi efek merugikan dari kebisingan kuantum dan meningkatkan ketahanan komputasi melalui teknik canggih seperti sirkuit variasional kuantum. Eksperimen komprehensif pada kumpulan data dunia nyata menyoroti kemampuan kerangka kerja untuk mengungguli metode konvensional dalam memecahkan tantangan pengoptimalan yang rumit. Temuan ini menunjukkan potensi transformatif pengoptimalan berbantuan kuantum (quantum-assisted) untuk mengatasi masalah kritis dalam pemodelan keuangan dan ketahanan rantai pasokan. Pada artikel ini, kami mengusulkan kerangka kerja kuantum-klasik hibrida baru yang memadukan sirkuit kuantum variasional dengan strategi mitigasi derau seperti Zero Noise Extrapolation (ZNE), yang dirancang khusus untuk pengoptimalan dunia nyata dalam domain keuangan dan rantai pasokan. Pendekatan terpadu ini—yang menangani ketahanan kesalahan dan skalabilitas praktis secara bersamaan—hal inilah yang menjadi pembeda penelitian ini dengan studi-studi sebelumnya yang hanya berfokus pada skenario teoritis atau ideal.Kata Kunci: Ketahanan kesalahan; Pemodelan keuangan; Algoritma hibrida; Tantangan Optimasi; Komputasi Kuantum; Pembelajaran Mesin Kuantum. 2020MSC: 81P68, 90C59, 91G60.</t>
+          <t>Abstract The rapid development of quantum computation has brought new possibilities to many fields. Especially in finance, quantum computing offers significant advantages. Recently, the portfolio optimization problem has been solved by a quantum algorithm with a mean-variance model with sparse data. However, the mean-variance model does not match the practice, and furthermore, the data is mostly dense. To fill the gap, we propose the Quantum-Enhanced Portfolio Optimization based on the mean-semi-variance model, where the mean-semi-variance model incorporates an optimized risk definition. The algorithm also effectively reduces the time complexity of solving high-dimensional linear systems and achieves sparsity independence.</t>
         </is>
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>semantic_scholar</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="I18" s="5" t="n"/>
@@ -1527,33 +1551,34 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>9226536b2e0a</t>
+          <t>6565bcfd2a83</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>Design and Analysis of Ternary Decoder based on FinFET models</t>
+          <t>Blockchain: Post-Quantum Security &amp; Legal Economics</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>Goel M.K.</t>
+          <t>Brian Haney</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="F19" s="5" t="inlineStr">
-        <is>
-          <t>10.1109/ACOIT62457.2024.10939394</t>
-        </is>
-      </c>
-      <c r="G19" s="5" t="inlineStr"/>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr"/>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>Blockchain technology is subject to security vulnerabilities resulting from recent developments in quantum computing and cryptography. All the while, the technical complexities of blockchain’s peer-to-peer system require the intervention of third-party intermediaries to facilitate financial transactions across blockchain networks. Current legal scholarship describes blockchain technology as a peer-to-peer system without a central authority, supporting the secure decentralization of economies and financial markets. Yet, with consideration to recent advancements in quantum computing, blockchain technology is not secure. Further, the technology’s legality is subject to the will of the central authorities whose economic systems it seeks to decentralize. 
+This article contributes the first post-quantum analysis of the intersection of blockchain security and law. Additionally, this is the first piece of legal scholarship to analyze the complex relationships between Congress, the Federal Reserve, and blockchain technology in the creation of money. In doing so, this article challenges conventional assumptions relating to blockchain technology’s decentralizing economic impact. Ultimately, this article takes an interdisciplinary approach, drawing on informatics, law, and economics scholarship, to argue blockchain fails to provide a legal or secure means of establishing a peer-to-peer payment system.</t>
+        </is>
+      </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>scopus</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="I19" s="5" t="n"/>
@@ -1567,17 +1592,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>38601ae493e8</t>
+          <t>3dad37594f28</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>A novel quantum security multi-party extremum protocol in a d-dimensional quantum system</t>
+          <t>Synergizing Machine Learning Algorithms with Quantum Computing: A Path to Unprecedented Capabilities</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Lu Y.</t>
+          <t>Dileep Pulugu; K. Subathra; Srichandana Abbineni; S. Zulaikha Beevi; B. Aishwarya; Sananda Kumar</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -1587,13 +1612,17 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>10.1088/1402-4896/ad6aee</t>
-        </is>
-      </c>
-      <c r="G20" s="5" t="inlineStr"/>
+          <t>10.1109/icaccm61117.2024.11058996</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>Quantum machine learning has become a promising field due to the capability to solve the computational issues of classical machine learning models. This research investigates the integration of machine learning and quantum computing with the aim of establishing and utilizing the QML models including QSVM and QNN. Given the large number of experiments on both conventional and quantum enriched datasets, the authors show that quantum machine learning models can be faster and more accurate when compared to Classical models. Furthermore, they provide a practical way for extending current quantum models’ capabilities to fight against available quantum device limitations, achieve higher computation rates and better data handling. Savings in training times and better performance are well-demonstrated in the outcome – especially with large data sets like MNIST. As much as such issues as quantum hardware constraints persist, marrying quantum computing with machine learning expands the ability to solve problems that are big and complicated across several fields including finance, healthcare and AI. This paper therefore encourages more investment on the you need more research and development towards the realization of quantum computing in the realm of machine learning.</t>
+        </is>
+      </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>scopus</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="I20" s="5" t="n"/>
@@ -1607,32 +1636,32 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>35507c982d46</t>
+          <t>261295f1b35c</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>MoG-VQE: Multiobjective genetic variational quantum eigensolver</t>
+          <t>Review on Second Quantum Revolution Its Opportunities and Challenges</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>Daniil Chivilikhin; Alexey Yur'evich Samarin; Vladimir Ulyantsev; Ivan Iorsh; Artem R. Oganov; Oleksandr Kyriienko</t>
+          <t>Takele Somano; Mahmud Seid; Lakachew Chanie</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>10.48550/arxiv.2007.04424</t>
+          <t>10.11648/j.ajmp.20241306.11</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>Variational quantum eigensolver (VQE) emerged as a first practical algorithm for near-term quantum computers. Its success largely relies on the chosen variational ansatz, corresponding to a quantum circuit that prepares an approximate ground state of a Hamiltonian. Typically, it either aims to achieve high representation accuracy (at the expense of circuit depth), or uses a shallow circuit sacrificing the convergence to the exact ground state energy. Here, we propose the approach which can combine both low depth and improved precision, capitalizing on a genetically-improved ansatz for hardware-efficient VQE. Our solution, the multiobjective genetic variational quantum eigensolver (MoG-VQE), relies on multiobjective Pareto optimization, where topology of the variational ansatz is optimized using the non-dominated sorting genetic algorithm (NSGA-II). For each circuit topology, we optimize angles of single-qubit rotations using covariance matrix adaptation evolution strategy (CMA-ES) -- a derivative-free approach known to perform well for noisy black-box optimization. Our protocol allows preparing circuits that simultaneously offer high performance in terms of obtained energy precision and the number of two-qubit gates, thus trying to reach Pareto-optimal solutions. Tested for various molecules (H$_2$, H$_4$, H$_6$, BeH$_2$, LiH), we observe nearly ten-fold reduction in the two-qubit gate counts as compared to the standard hardware-efficient ansatz. For 12-qubit LiH Hamiltonian this allows reaching chemical precision already at 12 CNOTs. Consequently, the algorithm shall lead to significant growth of the ground state fidelity for near-term devices.</t>
+          <t>This review explores the Second Quantum Revolution, which builds on the foundations of the first to advance quantum science and technology significantly. We examine the diverse fields under this revolution, including quantum information technologies, quantum electromechanical systems, coherent quantum electronics, quantum optics, and coherent matter technologies. Assess the societal and ethical implications of the second quantum revolution and provide insights into its potential impact on various sectors, including healthcare, finance, communication, and technology, the knowledge dissemination and awareness of the second quantum revolution. The review emphasizes the transformative potential of these advancements for the economy, computing, and communication networks. Additionally, we address the critical challenges that must be overcome, such as the development of fault-tolerant quantum systems and the seamless integration of quantum and classical technologies. Ethical considerations related to privacy, security, and societal impacts are also discussed, highlighting the need for a thoughtful reevaluation of quantum technology&amp;amp;apos;s role in modern society. Ultimately, this review outlines the immense opportunities presented by the Second Quantum Revolution while providing insights into the multifaceted challenges it faces, setting the stage for future research and innovation in this groundbreaking field.</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
@@ -1651,17 +1680,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>fddc282dba6f</t>
+          <t>034d5ac5f3b5</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Portfolio construction using a sampling-based variational quantum scheme</t>
+          <t>Post-quantum investigating Cryptography for Data Safeguard Transmission in Future Network Communication</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Gabriele Agliardi; Dimitris Alevras; Vaibhaw Kumar; Roberto Lo Nardo; Gabriele Compostella; Sumit Kumar; Manuel Proissl; Bimal Mehta</t>
+          <t>Laith Jasim; M. Sivabharathy; V. Venkataiah; Madhusudhan Reddy; T. Srinivas; P.S. Ramesh</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -1669,15 +1698,19 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr"/>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>10.1109/iccies63851.2025.11033076</t>
+        </is>
+      </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>The efficient and effective construction of portfolios that adhere to real-world constraints is a challenging optimization task in finance. We investigate a concrete representation of the problem with a focus on design proposals of an Exchange Traded Fund. We evaluate the sampling-based CVaR Variational Quantum Algorithm (VQA), combined with a local-search post-processing, for solving problem instances that beyond a certain size become classically hard. We also propose a problem formulation that is suited for sampling-based VQA. Our utility-scale experiments on IBM Heron processors involve 109 qubits and up to 4200 gates, achieving a relative solution error of 0.49%. Results indicate that a combined quantum-classical workflow achieves better accuracy compared to purely classical local search, and that hard-to-simulate quantum circuits may lead to better convergence than simpler circuits. Our work paves the path to further explore portfolio construction with quantum computers.</t>
+          <t>With the fast-paced development of quantum computing, classical cryptographic techniques are under severe security threats, prompting the need for post-quantum cryptographic mechanisms for secure data exchange in next-generation network communications. Post-quantum cryptography seeks to protect sensitive data against quantum attacks to provide long-term data confidentiality. But all current cryptographic techniques, including RSA and ECC, are susceptible to quantum algorithms like Shor's algorithm, which can factor large integers efficiently and break discrete logarithm problems, making classical cryptography useless. There is thus a pressing need for quantum attack-resistant encryption mechanisms. To meet these challenges, we introduce the Lattice-Based Cryptography with Hybrid Key Exchange (L-CHKE) framework, which combines lattice-based encryption with a hybrid key exchange mechanism. Lattice-based cryptography provides quantum resistance because it is based on hard mathematical problems such as Learning with Errors (LWE), which provides greater security and efficiency. The designed L-CHKE algorithm strengthens secure key distribution and authentication for next-generation networks, especially for applications needing strong security like financial transactions, IoT, and military communications. Experimental results verify that L-CHKE noticeably boosts computational efficiency by 98.45%, decreases key exchange latency by 42.56%, and guarantees robustness by 97.64% against quantum attacks, indicating it is an appropriate solution for post-quantum secure communication.</t>
         </is>
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>arxiv</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="I22" s="5" t="n"/>
@@ -1691,33 +1724,33 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>1f95f99e1c61</t>
+          <t>04b242aeef3f</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>Diagram-to-Circuit QNLP for Financial Sentiment Analysis</t>
+          <t>A quantum artificial neural network for stock closing price prediction</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>Takayuki Sakuma</t>
+          <t>Liu G.</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="F23" s="5" t="inlineStr"/>
-      <c r="G23" s="5" t="inlineStr">
-        <is>
-          <t>We study a \emph{QDisCoCirc}-inspired, chunked diagram-to-circuit quantum natural language processing (QNLP) model for three-class sentiment classification of financial texts. In our classical simulations, we keep the Hilbert-space dimension manageable by decomposing each sentence into short contiguous chunks. Each chunk is mapped to a shallow quantum circuit, and the resulting Bloch vectors are used as a sequence of quantum tokens. Simple averaging of chunk vectors ignores word order and syntactic roles. We therefore add a small Transformer encoder over the raw Bloch-vector sequence and attach a CCG-based type embedding to each chunk. This hybrid design preserves physically interpretable semantic axes of quantum tokens while allowing the classical side to model word order and long-range dependencies. The sequence model improves test macro-F1 over the averaging baseline and chunk-level attribution further shows that evidential mass concentrates on a small number of chunks, that type embeddings are used more reliably for correctly predicted sentences. For real-world quantum language processing applications in finance, future key challenges include circuit designs that avoid chunking and the design of inter-chunk fusion layers.</t>
-        </is>
-      </c>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>10.1016/j.ins.2022.03.064</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr"/>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>arxiv</t>
+          <t>scopus</t>
         </is>
       </c>
       <c r="I23" s="5" t="n"/>
@@ -1731,37 +1764,37 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>b2230647c31a</t>
+          <t>50662cd90dfb</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>Electron correlations, spontaneous magnetization and momentum density in quantum dots</t>
+          <t>Unlocking the Power of Quantum Mechanics for Machine Learning</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>A. Bansil; D. Nissenbaum; B. Barbiellini; R. Saniz</t>
+          <t>Brahmaleen Kaur Sidhu</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>2004</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>10.1016/j.jpcs.2004.08.012</t>
+          <t>10.21275/sr24427201406</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>The magnetization of quantum dots is discussed in terms of a relatively simple but exactly solvable model Hamiltonian. The model predicts oscillations in spin polarization as a function of dot radius for a fixed electron density. These oscillations in magnetization are shown to yield distinct signature in the momentum density of the electron gas, suggesting the usefulness of momentum resolved spectroscopies for investigating the magnetization of dot systems. We also present variational quantum Monte Carlo calculations on a square dot containing 12 electrons in order to gain insight into correlation effects on the interactions between like and unlike spins in a quantum dot.</t>
+          <t>Machine learning has radically changed the way problems in various disciplines are solved but faces limitations in tackling increasingly complex and high-dimensional data. Quantum machine learning emerges as a burgeoning paradigm, harnessing the principles of quantum mechanics to potentially surpass classical approaches. This paper delves into the core concepts of quantum machine learning, exploring its algorithms and challenges. The incorporation of quantum mechanics in machine learning algorithms offers a more expressive way to represent data compared to classical methods by capturing intricate relationships within complex datasets. Superposition and entanglement empower the development of algorithms that can tackle computationally expensive tasks in classical machine learning, particularly in high-dimensional spaces. Limited qubit count and susceptibility to noise in current quantum computers hinder the practical implementation of quantum machine learning for large-scale problems. Designing and optimizing efficient quantum algorithms tailored to specific machine learning tasks remains an active area of research. The paper concludes by highlighting the immense potential of quantum machine learning to revolutionize various fields, from materials science and drug discovery to finance and artificial intelligence.</t>
         </is>
       </c>
       <c r="H24" s="5" t="inlineStr">
         <is>
-          <t>arxiv</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="I24" s="5" t="n"/>
@@ -1775,33 +1808,37 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>9306729ec543</t>
+          <t>80e2927c7aac</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>Navigating Cyber Threats: The Integration of Artificial Intelligence in Banking Security Frameworks</t>
+          <t>Retail Fraud Detection via Log Analysis and Stream Processing</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>Kartikay Bhatt K.</t>
+          <t>Arjun Sirangi</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>10.4324/9781003596875-4</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="inlineStr"/>
+          <t>10.52710/cfs.678</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>Retail fraud has evolved into a sophisticated threat in the digital age, necessitating advanced detection mechanisms that leverage real-time data processing. This paper presents a technical framework for detecting retail fraud by combining log analysis with stream processing technologies. We address challenges such as scalability, latency, and concept drift through a hybrid architecture that integrates anomaly detection algorithms (e.g., clustering, graph-based models) with distributed stream processing engines (e.g., Apache Flink, Kafka). Evaluations demonstrate that our approach achieves an F1-score of 0.92 on synthetic transaction datasets, outperforming traditional rule-based systems by 34%. The paper also discusses ethical implications, GDPR compliance, and emerging trends such as blockchain and quantum computing.</t>
+        </is>
+      </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>scopus</t>
+          <t>semantic_scholar</t>
         </is>
       </c>
       <c r="I25" s="5" t="n"/>
@@ -1815,37 +1852,37 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>6ced59f1d37f</t>
+          <t>15ecb0ef5f59</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>First- and second-order quantum phase transitions in the long-range unfrustrated antiferromagnetic Ising chain</t>
+          <t>Design and Development of a Secure Data Encryption and Decryption System</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Víctor Herráiz-López; Sebastián Roca-Jerat; Manuel Gallego; Ramón Ferrández; Jesús Carrete; David Zueco; Juan Román-Roche</t>
+          <t>Shepherd Mwaekwa Wamulume</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>10.1103/PhysRevB.111.014425</t>
+          <t>10.54105/ijcns.a1435.05010525</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>We study the ground-state phase diagram of an unfrustrated antiferromagnetic Ising chain with longitudinal and transverse fields in the full range of interactions: from all-to-all to nearest-neighbors. First, we solve the model analytically in the strong long-range regime, confirming in the process that a mean-field treatment is exact for this model. We compute the order parameter and the correlations and show that the model exhibits a tricritical point where the phase transition changes from first to second order. This is in contrast with the nearest-neighbor limit where the phase transition is known to be second order. To understand how the order of the phase transition changes from one limit to the other, we tackle the analytically-intractable interaction ranges numerically, using a variational quantum Monte Carlo method with a neural-network-based ansatz, the visual transformer. We show how the first-order phase transition shrinks with decreasing interaction range and establish approximate boundaries in the interaction range for which the first-order phase transition is present. Finally, we establish that the key ingredient to stabilize a first-order phase transition and a tricritical point is the presence of ferromagnetic interactions between spins of the same sublattice on top of antiferromagnetic interactions between spins of different sublattices. Tunable-range unfrustrated antiferromagnetic interactions are just one way to implement such staggered interactions.</t>
+          <t>In an increasingly interconnected world, the need to secure sensitive information has become paramount. This article presents the Design and development of a secure data storage system. An encryption and decryption system aimed at enhancing the confidentiality, integrity, and availability of digital data. The proposed system employs advanced cryptographic algorithms to provide robust protection against unauthorised access, data breaches, and cyberattacks. The design phase emphasises the integration of both symmetric and asymmetric encryption techniques, enabling the system to cater to a diverse range of applications, from secure file storage to encrypted communications. Key Management protocols are implemented to ensure the safe generation, distribution, and storage of encryption keys, a critical component of secure systems. The system was developed using modern programming tools and frameworks, adhering to industry standards such as AES (Advanced Encryption Standard) and RSA (Rivest-Shamir-Adleman). Extensive testing was conducted to evaluate the system’s performance, security resilience, and scalability. Results demonstrate the system’s ability to resist common attacks, including brute force and cryptanalysis, while maintaining high efficiency in data processing. This research contributes to the field of data security by providing a versatile and secure solution that can be adapted for use in industries such as finance, healthcare, and e-commerce. Future work includes integrating post-quantum cryptographic algorithms to prepare for the advent of quantum computing.</t>
         </is>
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
-          <t>arxiv</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="I26" s="5" t="n"/>
@@ -1859,33 +1896,37 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>66969a83b1e5</t>
+          <t>4513b7aef1d3</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>Robust decompositions of quantum states</t>
+          <t>Summary: Chicago Quantum Exchange (CQE) Pulse-level Quantum Control Workshop</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>Jonathan E. Moussa</t>
+          <t>Kaitlin N. Smith; Gokul Subramanian Ravi; Thomas Alexander; Nicholas T. Bronn; André F. Carvalho; Alba Cervera-Lierta; Frederic T. Chong; Jerry M. Chow; Michael Cubeddu; Akel Hashim; Liang Jiang; Olivia Lanes; Matthew Otten; David Schuster; Pranav Gokhale; Nathan Earnest; Alexey Galda</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="F27" s="5" t="inlineStr"/>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>10.48550/arxiv.2202.13600</t>
+        </is>
+      </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>Classical-quantum computational complexity separations are an important motivation for the long-term development of digital quantum computers, but classical-quantum complexity equivalences are just as important in our present era of noisy intermediate-scale quantum devices for framing near-term progress towards quantum supremacy. We establish one such equivalence using a noisy quantum circuit model that can be simulated efficiently on classical computers. With respect to its noise model, quantum states have a robust decomposition into a sequence of operations that each extend the state by one qubit without spreading errors between qubits. This enables universal quantum sampling of states with an efficient representation in this robust form and observables with low quantum weight that can be sampled from general measurements on a few qubits and computational basis measurements on the remaining qubits. These robust decompositions are not unique, and we construct two distinct variants, both of which are compatible with machine-learning methodology. They both enable efficiently computable lower bounds on von Neumann entropy and thus can be used as finite-temperature variational quantum Monte Carlo methods.</t>
+          <t>Quantum information processing holds great promise for pushing beyond the current frontiers in computing. Specifically, quantum computation promises to accelerate the solving of certain problems, and there are many opportunities for innovation based on applications in chemistry, engineering, and finance. To harness the full potential of quantum computing, however, we must not only place emphasis on manufacturing better qubits, advancing our algorithms, and developing quantum software. To scale devices to the fault tolerant regime, we must refine device-level quantum control. On May 17-18, 2021, the Chicago Quantum Exchange (CQE) partnered with IBM Quantum and Super.tech to host the Pulse-level Quantum Control Workshop. At the workshop, representatives from academia, national labs, and industry addressed the importance of fine-tuning quantum processing at the physical layer. The purpose of this report is to summarize the topics of this meeting for the quantum community at large.</t>
         </is>
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>arxiv</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="I27" s="5" t="n"/>
@@ -1899,33 +1940,37 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>c1bbc8c7cbd7</t>
+          <t>3da55df6ffd8</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>Consensus-based Distributed Quantum Kernel Learning for Speech Recognition</t>
+          <t>Quantum-Based Stock Price Forecasting with Stop Loss and False Breakout Analysis</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Kuan-Cheng Chen; Wenxuan Ma; Xiaotian Xu</t>
+          <t>Daniel Sylvinson Muthiah Ravinson; K. Maharajan</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="F28" s="5" t="inlineStr"/>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>10.1109/asiancon66527.2025.11280952</t>
+        </is>
+      </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>This paper presents a Consensus-based Distributed Quantum Kernel Learning (CDQKL) framework aimed at improving speech recognition through distributed quantum computing.CDQKL addresses the challenges of scalability and data privacy in centralized quantum kernel learning. It does this by distributing computational tasks across quantum terminals, which are connected through classical channels. This approach enables the exchange of model parameters without sharing local training data, thereby maintaining data privacy and enhancing computational efficiency. Experimental evaluations on benchmark speech emotion recognition datasets demonstrate that CDQKL achieves competitive classification accuracy and scalability compared to centralized and local quantum kernel learning models. The distributed nature of CDQKL offers advantages in privacy preservation and computational efficiency, making it suitable for data-sensitive fields such as telecommunications, automotive, and finance. The findings suggest that CDQKL can effectively leverage distributed quantum computing for large-scale machine-learning tasks.</t>
+          <t>This research work introduces a novel quantum computing approach to stock price forecasting that leverages the power of quantum algorithms for enhanced predictive accuracy and risk management. This comprehensive framework that integrates Quantum Neural Networks (QNN), Quantum Support Vector Machines (QSVM), and Quantum Amplitude Estimation (QAE) to create a robust prediction system capable of navigating complex market dynamics. This approach goes beyond traditional quantum machine learning by incorporating specialized components for stop loss optimization and false breakout detection-critical elements for practical trading systems that are often overlooked in theoretical models. Experimental results across multiple market sectors during the 2018-2022 period demonstrates that this quantum-based framework achieves a 23.6% improvement in directional accuracy and a 31.4% enhancement in risk-adjusted returns compared to classical machine learning benchmarks. The model exhibits particular strength during high volatility periods, where quantum superposition and entanglement properties efficiently capture complex market patterns that elude classical algorithms. This research bridges the gap between theoretical quantum computing advantages and practical financial applications, offering significant implications for the future of algorithmic trading as quantum hardware continues to advance.</t>
         </is>
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t>arxiv</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="I28" s="5" t="n"/>
@@ -1939,37 +1984,37 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>a8521b15552c</t>
+          <t>fab168b13a96</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>Quantum Computing and the Financial System: Spooky Action at a Distance?</t>
+          <t>The Prospects of Quantum Computing for Quantitative Finance and Beyond</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Jose Deodoro; Michael Gorbanyov; Majid Malaika; T. S. Sedik; S. Peiris</t>
+          <t>Yen-Jui Chang; Ming-Fong Sie; Shih-Wei Liao; Ching‐Ray Chang</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>10.5089/9781513572727.001.A001</t>
+          <t>10.1109/mnano.2023.3249501</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>The era of quantum computing is about to begin, with profound implications for the global economy and the financial system. Rapid development of quantum computing brings both benefits and risks. Quantum computers can revolutionize industries and fields that require significant computing power, including modeling financial markets, designing new effective medicines and vaccines, and empowering artificial intelligence, as well as creating a new and secure way of communication (quantum Internet). But they would also crack many of the current encryption algorithms and threaten financial stability by compromising the security of mobile banking, e-commerce, fintech, digital currencies, and Internet information exchange. While the work on quantum-safe encryption is still in progress, financial institutions should take steps now to prepare for the cryptographic transition, by assessing future and retroactive risks from quantum computers, taking an inventory of their cryptographic algorithms (especially public keys), and building cryptographic agility to improve the overall cybersecurity resilience.</t>
+          <t>Quantum computation holds the promise of highly efficient algorithms, provides exponential speedups for specific technologically significant problems, plays the most promising role in quantum technological progress, and has transformative potential in numerous industry sectors. In quantum computing, finance is recognized as one of the most beneficial areas because of the potential for many financial cases that can be solved by quantum algorithms suitable for noisy-intermedia-scale quantum(NISQ) computers. The benefits of quantum computing are colossal time and computational memory reduction with which the computational tasks are performed, which leads to the accuracy of the computations. This paper presents a comprehensive summary of quantum computing for traditional and Blockchain financial applications.</t>
         </is>
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>semantic_scholar</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="I29" s="5" t="n"/>
@@ -1983,33 +2028,37 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>1ca71f64f4b2</t>
+          <t>526fcec10f82</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>Quantum Meta-Heuristics and Applications</t>
+          <t>Towards Prediction of Financial Crashes with a D-Wave Quantum Computer</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>Prakash K.B.</t>
+          <t>Yongcheng Ding; Javier Gonzalez-Conde; Lucas Lamata; José D. Martín-Guerrero; Enrique Lizaso; Samuel Mugel; Xi Chen; Román Orús; Enrique Solano; Mikel Sanz</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>10.1002/9781119711308.ch10</t>
-        </is>
-      </c>
-      <c r="G30" s="5" t="inlineStr"/>
+          <t>10.3390/e25020323</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>Prediction of financial crashes in a complex financial network is known to be an NP-hard problem, which means that no known algorithm can guarantee to find optimal solutions efficiently. We experimentally explore a novel approach to this problem by using a D-Wave quantum computer, benchmarking its performance for attaining financial equilibrium. To be specific, the equilibrium condition of a nonlinear financial model is embedded into a higher-order unconstrained binary optimization (HUBO) problem, which is then transformed to a spin-$1/2$ Hamiltonian with at most two-qubit interactions. The problem is thus equivalent to finding the ground state of an interacting spin Hamiltonian, which can be approximated with a quantum annealer. The size of the simulation is mainly constrained by the necessity of a large quantity of physical qubits representing a logical qubit with the correct connectivity. Our experiment paves the way to codify this quantitative macroeconomics problem in quantum computers.</t>
+        </is>
+      </c>
       <c r="H30" s="5" t="inlineStr">
         <is>
-          <t>scopus</t>
+          <t>arxiv</t>
         </is>
       </c>
       <c r="I30" s="5" t="n"/>
@@ -2023,37 +2072,33 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>e84ac6847216</t>
+          <t>4f07d45db4c6</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>Deep neural network solution of the electronic Schrödinger equation</t>
+          <t>Quantum Based Pseudo-Labelling for Hyperspectral Imagery: A Simple and Efficient Semi-Supervised Learning Method for Machine Learning Classifiers</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Jan Hermann; Zeno Schätzle; Frank Noé</t>
+          <t>Shaik R.U.</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>10.1038/s41557-020-0544-y</t>
-        </is>
-      </c>
-      <c r="G31" s="5" t="inlineStr">
-        <is>
-          <t>[New and updated results were published in Nature Chemistry, doi:10.1038/s41557-020-0544-y.] The electronic Schrödinger equation describes fundamental properties of molecules and materials, but can only be solved analytically for the hydrogen atom. The numerically exact full configuration-interaction method is exponentially expensive in the number of electrons. Quantum Monte Carlo is a possible way out: it scales well to large molecules, can be parallelized, and its accuracy has, as yet, only been limited by the flexibility of the used wave function ansatz. Here we propose PauliNet, a deep-learning wave function ansatz that achieves nearly exact solutions of the electronic Schrödinger equation. PauliNet has a multireference Hartree-Fock solution built in as a baseline, incorporates the physics of valid wave functions, and is trained using variational quantum Monte Carlo (VMC). PauliNet outperforms comparable state-of-the-art VMC ansatzes for atoms, diatomic molecules and a strongly-correlated hydrogen chain by a margin and is yet computationally efficient. We anticipate that thanks to the favourable scaling with system size, this method may become a new leading method for highly accurate electronic-strucutre calculations on medium-sized molecular systems.</t>
-        </is>
-      </c>
+          <t>10.3390/rs14225774</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr"/>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>arxiv</t>
+          <t>scopus</t>
         </is>
       </c>
       <c r="I31" s="5" t="n"/>
@@ -2067,33 +2112,33 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>8aae98f409fd</t>
+          <t>1f95f99e1c61</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>Dynamic connectedness of quantum computing, artificial intelligence, and big data stocks on renewable and sustainable energy</t>
+          <t>Diagram-to-Circuit QNLP for Financial Sentiment Analysis</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Ghaemi Asl M.</t>
+          <t>Takayuki Sakuma</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="F32" s="5" t="inlineStr">
-        <is>
-          <t>10.1016/j.eneco.2024.108017</t>
-        </is>
-      </c>
-      <c r="G32" s="5" t="inlineStr"/>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr"/>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>We study a \emph{QDisCoCirc}-inspired, chunked diagram-to-circuit quantum natural language processing (QNLP) model for three-class sentiment classification of financial texts. In our classical simulations, we keep the Hilbert-space dimension manageable by decomposing each sentence into short contiguous chunks. Each chunk is mapped to a shallow quantum circuit, and the resulting Bloch vectors are used as a sequence of quantum tokens. Simple averaging of chunk vectors ignores word order and syntactic roles. We therefore add a small Transformer encoder over the raw Bloch-vector sequence and attach a CCG-based type embedding to each chunk. This hybrid design preserves physically interpretable semantic axes of quantum tokens while allowing the classical side to model word order and long-range dependencies. The sequence model improves test macro-F1 over the averaging baseline and chunk-level attribution further shows that evidential mass concentrates on a small number of chunks, that type embeddings are used more reliably for correctly predicted sentences. For real-world quantum language processing applications in finance, future key challenges include circuit designs that avoid chunking and the design of inter-chunk fusion layers.</t>
+        </is>
+      </c>
       <c r="H32" s="5" t="inlineStr">
         <is>
-          <t>scopus</t>
+          <t>arxiv</t>
         </is>
       </c>
       <c r="I32" s="5" t="n"/>
@@ -2107,17 +2152,17 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>639a7acc8bbc</t>
+          <t>647f1186df1e</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>Quantum - Safe Cryptography: Exploring the Future of Cybersecurity in the Post - Quantum Era</t>
+          <t>Financial Insights Unleashed: Computational Intelligence in Practice</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Pavleen Kour</t>
+          <t>Makhija P.</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -2127,17 +2172,13 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>10.53469/jrse.2025.07(06).08</t>
-        </is>
-      </c>
-      <c r="G33" s="5" t="inlineStr">
-        <is>
-          <t>The paper proposes strategic steps that organizations can take to future-proof their security architecture against quantum threats for the security of data integrity and confidentiality in the post-quantum era. it is a very threat that quantum computing is advancing too fast, and the classical cryptographic systems will be in danger. Therefore, we need to modify the methods of cryptography in Quantum- Safe Cryptography. In this paper, we focus on exposing the vulnerabilities of existing public-key cryptosystems faced with quantum attacks and the direction of the post-quantum cryptographic (PQC) algorithm in securing the underlain infrastructure. The paper discusses ongoing efforts to standardize cryptosystems led by the National Institute of Standards and Technology (NIST). It overviews several quantum-resistant cryptographic techniques: lattice-based, hash-based, and code-based examples. Moreover, the paper also outlines difficulties in implementing quantum-safe cryptography solutions into currently in-place cybersecurity frameworks, especially in the finance, healthcare, and critical infrastructure industries.</t>
-        </is>
-      </c>
+          <t>10.1201/9781998511013-10</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr"/>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>semantic_scholar</t>
+          <t>scopus</t>
         </is>
       </c>
       <c r="I33" s="5" t="n"/>
@@ -2151,33 +2192,37 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>c73ab6955ecc</t>
+          <t>f9141fada31b</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>Deterministic quantum annealing expectation-maximization algorithm</t>
+          <t>Autoregressive neural Slater-Jastrow ansatz for variational Monte Carlo simulation</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Miyahara H.</t>
+          <t>Stephan Humeniuk; Yuan Wan; Lei Wang</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>10.1088/1742-5468/aa967e</t>
-        </is>
-      </c>
-      <c r="G34" s="5" t="inlineStr"/>
+          <t>10.21468/SciPostPhys.14.6.171</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>Direct sampling from a Slater determinant is combined with an autoregressive deep neural network as a Jastrow factor into a fully autoregressive Slater-Jastrow ansatz for variational quantum Monte Carlo, which allows for uncorrelated sampling. The elimination of the autocorrelation time leads to a stochastic algorithm with provable cubic scaling (with a potentially large prefactor), i.e. the number of operations for producing an uncorrelated sample and for calculating the local energy scales like $\mathcal{O}(N_s^3)$ with the number of orbitals $N_s$. The implementation is benchmarked on the two-dimensional $t-V$ model of spinless fermions on the square lattice.</t>
+        </is>
+      </c>
       <c r="H34" s="5" t="inlineStr">
         <is>
-          <t>scopus</t>
+          <t>arxiv</t>
         </is>
       </c>
       <c r="I34" s="5" t="n"/>
@@ -2191,32 +2236,32 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>a4cf9687035e</t>
+          <t>d0a8bde2ad2e</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>From Bounded Surjections to Quantum Error-Correcting Codes: An Operator-Algebraic Construction</t>
+          <t>A hybrid quantum-classical fusion neural network to improve protein-ligand binding affinity predictions for drug discovery</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>Sudoma, Oksana</t>
+          <t>S. Banerjee; S. He Yuxun; Subrahmanyam Konakanchi; Lawal Adewale Ogunfowora; Sumantra Dutta Roy; S. Selvaras; L. Domingo; Mahdi Chehimi; M. Djukic; C. Johnson</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>10.5281/zenodo.17585622</t>
+          <t>10.48550/arxiv.2309.03919</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>Abstract We establish that every bounded surjection π : B ↠ H between Banach and Hilbertspaces canonically induces a quantum error-correcting code structure. The kernel ker π capturesunobservable degrees of freedom, while the quotient B/ ker π encodes protected logical information.This perspective: (1) unifies subspace, subsystem, and operator-algebraic codes under oneframework; (2) provides functorial code transformations via morphisms of surjections; (3)enables computational exploration through kernel geometry analysis; (4) extends naturally toinfinite dimensions via GNS construction without requiring infinite stabilizer sets. We prove thecorrespondence is functorial with a universal property, demonstrate stability under perturbations,and show the Knill-Laflamme conditions emerge from kernel structure. Examples include theShor code arising from syndrome extraction, holographic codes from bulk-boundary maps, andoperator-algebraic codes from GNS representations. Computational validation (ExperimentsE49, E50) confirms kernel dimension predictions with machine-precision accuracy and revealsrank transition behavior in continuous code families, with dimension derivatives |∆k/∆t| ∼ 102at transition points. While finite-dimensional codes are mathematically equivalent to knownconstructions, our framework provides conceptual unification: (1) kernel geometry explains whydifferent QEC approaches converge on the same codes; (2) continuous code families handle ranktransitions without stabilizer redefinition; (3) infinite dimensions via GNS construction avoidinfinite stabilizer sets; (4) functorial transformations arise naturally from surjection morphisms;(5) the approach aligns with physical intuition—error correction protects exactly the informationthat survives observation. Where Surjections Appear Naturally Quantum error correction typically starts with a codespace—a carefully chosen subspace of a larger Hilbert space [ KL97, NC10 , Got97 ]. But nature oftenpresents us with projection maps first:• Coarse-graining: Mapping microscopic states to macroscopic observables• Symmetry reduction: Projecting onto gauge-invariant subspaces• Partial trace: Observing subsystems of composite quantum states• Boundary limits: In AdS/CFT, mapping bulk fields to boundary observablesEach scenario involves a map from a larger space to a smaller observable space. Informationthat survives this projection is precisely what remains accessible. The question naturally arises:Can these projections automatically induce quantum error-correcting structure? This paper answers affirmatively: every bounded surjection canonically induces quantumerror correction structure. The construction applies broadly—from finite qubit codes to infinite-dimensional operator algebras. Consider the concrete scenario of holographic duality: bulk quantum fields map to boundaryCFT observables. Some bulk configurations are invisible from the boundary—they lie in the kernelof the bulk-to-boundary map. The observable bulk information forms a quotient space. Could thisquotient structure automatically define error correction? Our Contribution We prove that every bounded surjection π : B ↠ H from a Banach space ontoa Hilbert space canonically induces a quantum error-correcting code via the quotient constructionfrom functional analysis [Rud91, Con90]. The construction is:1. Universal: Works for finite and infinite-dimensional systems2. Natural: QEC emerges from observability structure (kernel geometry)3. Functorial: Morphisms between surjections induce code transformations Positioning in the Literature This work occupies a unique position at the intersection of threeapproaches to quantum error correction:• vs. Stabilizer QEC [Got97 ]: We provide a dual perspective where codes emerge fromobservables (what we can measure) rather than symmetries (what commutes). This isconceptually inverse but mathematically equivalent in finite dimensions.• vs. Operator Algebra QEC [ KLP05, Pou05 , KL24]: While OAQEC uses von Neumannalgebras to generalize stabilizers, we use surjections to generalize projections. Our frameworkencompasses OAQEC as the special case where B carries algebra structure (Proposition 4).• vs. Holographic QEC [ ADH15, PYHP15]: Holographic codes implicitly use bulk-to-boundary maps. We make this explicit, showing these maps are surjections whose kernelsencode gauge redundancy. Our Contribution We do not claim new codes but rather a unifying framework that:1. Explains why these approaches converge on the same codes (they all induce surjections)2. Provides computational tools via kernel geometry analysis3. Enables systematic code exploration by designing surjections rather than searching for stabi-lizers4. Naturally extends to infinite dimensions where stabilizers become unwieldyThe key insight: error correction is fundamentally about preserving observable information underlimited measurement resolution—the kernel captures what’s unmeasurable, the quotient preserveswhat survives. Experiments E49: Kernel Geometry Visualization Validates [[4,2,2]] quantum code construction from bounded surjections. Key results: Code distance d=2 verified Kernel orthogonality: 10^-16 (machine precision) Logical operators detected Runtime: &lt; 1 second Documentation: See experiments/E49_kernel_geometry_viz/ABOUT_THIS_EXPERIMENT.md for complete research narrative (hypothesis → results → interpretation) on https://github.com/boonespacedog/surjection-to-qec.git . Quick start: cd experiments/E49_kernel_geometry_viz python3 -m venv venv source venv/bin/activate pip install -r requirements.txt python3 main.py E50: Functorial Code Morphisms Continuous code family evolution with rank transition detection. Key results: Rank transitions detected at t = 2^n - 1 (discrete phase transitions!) Dimension jumps: |Δdim/Δt| = 198 at critical points Topological protection discovered (codes resist smooth deformation) Runtime: ~1.5 seconds Documentation: See experiments/E50_functorial_code_morphisms/ABOUT_THIS_EXPERIMENT.md for complete research narrative and link to topological interpretations on https://github.com/boonespacedog/surjection-to-qec.git .</t>
+          <t>The field of drug discovery hinges on the accurate prediction of binding affinity between prospective drug molecules and target proteins, especially when such proteins directly influence disease progression. However, estimating binding affinity demands significant financial and computational resources. While state-of-the-art methodologies employ classical machine learning (ML) techniques, emerging hybrid quantum machine learning (QML) models have shown promise for enhanced performance, owing to their inherent parallelism and capacity to manage exponential increases in data dimensionality. Despite these advances, existing models encounter issues related to convergence stability and prediction accuracy. This paper introduces a novel hybrid quantum-classical deep learning model tailored for binding affinity prediction in drug discovery. Specifically, the proposed model synergistically integrates 3D and spatial graph convolutional neural networks within an optimized quantum architecture. Simulation results demonstrate a 6% improvement in prediction accuracy relative to existing classical models, as well as a significantly more stable convergence performance compared to previous classical approaches.</t>
         </is>
       </c>
       <c r="H35" s="5" t="inlineStr">
@@ -2235,37 +2280,37 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>bf6bfac8ba8f</t>
+          <t>741e66d789d0</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>Leveraging artificial intelligence in economics and finance: Enhancing decision-making and market efficiency</t>
+          <t>Neural Wave Functions for Superfluids</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>Daren Zhang</t>
+          <t>Wan Tong Lou; Halvard Sutterud; Gino Cassella; W. M. C. Foulkes; Johannes Knolle; David Pfau; James S. Spencer</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>10.54254/2755-2721/82/20240980</t>
+          <t>10.1103/PhysRevX.14.021030</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>Abstract. Artificial Intelligence (AI) has revolutionized the fields of economics and finance by providing advanced tools for decision-making, predictive analysis, and market efficiency. This paper examines the integration of AI technologies such as machine learning and natural language processing with mathematical models, specifically ARIMA for economic forecasting, Black-Scholes for option pricing, and logistic regression for credit risk assessment. By enhancing these models with AI, we demonstrate significant improvements in prediction accuracy and decision-making capabilities. Case studies illustrate a 15% improvement in GDP growth prediction accuracy, a 20% reduction in option pricing errors, and a 20% decrease in credit default rates. The paper also discusses the future prospects of AI, including advancements in quantum computing and ethical considerations like data privacy and algorithmic bias. Implementation challenges such as high costs and data integration issues are addressed, providing a comprehensive roadmap for organizations to effectively leverage AI. This study underscores the transformative potential of AI in shaping the future of economic and financial landscapes, driving innovation and operational efficiency.</t>
+          <t>Understanding superfluidity remains a major goal of condensed matter physics. Here we tackle this challenge utilizing the recently developed Fermionic neural network (FermiNet) wave function Ansatz [D. Pfau et al., Phys. Rev. Res. 2, 033429 (2020).] for variational Monte Carlo calculations. We study the unitary Fermi gas, a system with strong, short-range, two-body interactions known to possess a superfluid ground state but difficult to describe quantitatively. We demonstrate key limitations of the FermiNet Ansatz in studying the unitary Fermi gas and propose a simple modification based on the idea of an antisymmetric geminal power singlet (AGPs) wave function. The new AGPs FermiNet outperforms the original FermiNet significantly in paired systems, giving results which are more accurate than fixed-node diffusion Monte Carlo and are consistent with experiment. We prove mathematically that the new Ansatz, which only differs from the original Ansatz by the method of antisymmetrization, is a strict generalization of the original FermiNet architecture, despite the use of fewer parameters. Our approach shares several advantages with the original FermiNet: the use of a neural network removes the need for an underlying basis set; and the flexibility of the network yields extremely accurate results within a variational quantum Monte Carlo framework that provides access to unbiased estimates of arbitrary ground-state expectation values. We discuss how the method can be extended to study other superfluids.</t>
         </is>
       </c>
       <c r="H36" s="5" t="inlineStr">
         <is>
-          <t>semantic_scholar</t>
+          <t>arxiv</t>
         </is>
       </c>
       <c r="I36" s="5" t="n"/>
@@ -2279,37 +2324,33 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>bc7bb11dcd2a</t>
+          <t>3b7d3889d285</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>Tailgating quantum circuits for high-order energy derivatives</t>
+          <t>Quantum Pricing with a Smile: Implementation of Local Volatility Model on Quantum Computer</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Jack Ceroni; Alain Delgado; Soran Jahangiri; Juan Miguel Arrazola</t>
+          <t>Kazuya Kaneko; Koichi Miyamoto; Naoyuki Takeda; Kazuyoshi Yoshino</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="F37" s="5" t="inlineStr">
-        <is>
-          <t>10.48550/arxiv.2207.11274</t>
-        </is>
-      </c>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr"/>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>To understand the chemical properties of molecules, it is often important to study derivatives of energies with respect to nuclear coordinates or external fields. Quantum algorithms for computing energy derivatives have been proposed, but only limited work has been done to address the specific challenges that arise in this context, where calculations are more complicated and involve more stringent requirements on accuracy compared to single-point energy calculations. In this work, we introduce a technique to improve the performance of variational quantum circuits calculating energy derivatives. The method, which we refer to as tailgating, is an adaptive procedure that selects gates based on their gradient with respect to the expectation value of Hamiltonian derivatives. These gates are then added at the end of a quantum circuit originally designed to calculate ground- or excited-state energies. A distinguishing feature of this approach is that the appended gates do not need to be optimized: their parameters can be set to zero and varied only for the purpose of computing energy derivatives, via calculating derivatives with respect to circuit parameters. We support the validity of this method by establishing sufficient conditions for a circuit to compute accurate energy gradients. This is achieved through a connection between energy derivatives and eigenstates of Taylor approximations of the Hamiltonian. We illustrate the advantages of the tailgating approach by performing simulations calculating the vibrational modes of beryllium hydride and water: quantities that depend on second-order energy derivatives.</t>
+          <t>Applications of the quantum algorithm for Monte Carlo simulation to pricing of financial derivatives have been discussed in previous papers. However, up to now, the pricing model discussed in such papers is Black-Scholes model, which is important but simple. Therefore, it is motivating to consider how to implement more complex models used in practice in financial institutions. In this paper, we then consider the local volatility (LV) model, in which the volatility of the underlying asset price depends on the price and time. We present two types of implementation. One is the register-per-RN way, which is adopted in most of previous papers. In this way, each of random numbers (RNs) required to generate a path of the asset price is generated on a separated register, so the required qubit number increases in proportion to the number of RNs. The other is the PRN-on-a-register way, which is proposed in the author's previous work. In this way, a sequence of pseudo-random numbers (PRNs) generated on a register is used to generate paths of the asset price, so the required qubit number is reduced with a trade-off against circuit depth. We present circuit diagrams for these two implementations in detail and estimate required resources: qubit number and T-count.</t>
         </is>
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>openalex</t>
+          <t>arxiv</t>
         </is>
       </c>
       <c r="I37" s="5" t="n"/>
@@ -2323,29 +2364,33 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>f2602c702d85</t>
+          <t>4513b7aef1d3</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>TECHNOLOGY OF BLOCKCHAIN SYSTEMS: NEW OPPORTUNITIES AND ISSUES IN DATA SECURITY AND RETENTION</t>
+          <t>Summary: Chicago Quantum Exchange (CQE) Pulse-level Quantum Control Workshop</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>Bataiev S.</t>
+          <t>Kaitlin N. Smith; Gokul Subramanian Ravi; Thomas Alexander; Nicholas T. Bronn; Andre Carvalho; Alba Cervera-Lierta; Frederic T. Chong; Jerry M. Chow; Michael Cubeddu; Akel Hashim; Liang Jiang; Olivia Lanes; Matthew J. Otten; David I. Schuster; Pranav Gokhale; Nathan Earnest; Alexey Galda</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr"/>
-      <c r="G38" s="5" t="inlineStr"/>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>Quantum information processing holds great promise for pushing beyond the current frontiers in computing. Specifically, quantum computation promises to accelerate the solving of certain problems, and there are many opportunities for innovation based on applications in chemistry, engineering, and finance. To harness the full potential of quantum computing, however, we must not only place emphasis on manufacturing better qubits, advancing our algorithms, and developing quantum software. To scale devices to the fault tolerant regime, we must refine device-level quantum control.   On May 17-18, 2021, the Chicago Quantum Exchange (CQE) partnered with IBM Quantum and Super.tech to host the Pulse-level Quantum Control Workshop. At the workshop, representatives from academia, national labs, and industry addressed the importance of fine-tuning quantum processing at the physical layer. The purpose of this report is to summarize the topics of this meeting for the quantum community at large.</t>
+        </is>
+      </c>
       <c r="H38" s="5" t="inlineStr">
         <is>
-          <t>scopus</t>
+          <t>arxiv</t>
         </is>
       </c>
       <c r="I38" s="5" t="n"/>
@@ -2359,33 +2404,33 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>c233bf88de0f</t>
+          <t>2c22225a38e7</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>On Quantum BSDE Solver for High-Dimensional Parabolic PDEs</t>
+          <t>Tensor Network Assisted Distributed Variational Quantum Algorithm for Large Scale Combinatorial Optimization Problem</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>Howard Su; Huan-Hsin Tseng</t>
+          <t>Yuhan Huang; Siyuan Jin; Yichi Zhang; Qi Zhao; Jun Qi; Qiming Shao</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr"/>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>We propose a quantum machine learning framework for approximating solutions to high-dimensional parabolic partial differential equations (PDEs) that can be reformulated as backward stochastic differential equations (BSDEs). In contrast to popular quantum-classical network hybrid approaches, this study employs the pure Variational Quantum Circuit (VQC) as the core solver without trainable classical neural networks. The quantum BSDE solver performs pathwise approximation via temporal discretization and Monte Carlo simulation, framed as model-based reinforcement learning. We benchmark VQCbased and classical deep neural network (DNN) solvers on two canonical PDEs as representatives: the Black-Scholes and nonlinear Hamilton-Jacobi-Bellman (HJB) equations. The VQC achieves lower variance and improved accuracy in most cases, particularly in highly nonlinear regimes and for out-of-themoney options, demonstrating greater robustness than DNNs. These results, obtained via quantum circuit simulation, highlight the potential of VQCs as scalable and stable solvers for highdimensional stochastic control problems.</t>
+          <t>Although quantum computing holds promise for solving Combinatorial Optimization Problems (COPs), the limited qubit capacity of NISQ hardware makes large-scale instances intractable. Conventional methods attempt to bridge this gap through decomposition or compression, yet they frequently fail to capture global correlations of subsystems, leading to solutions of limited quality. We propose the Distributed Variational Quantum Algorithm (DVQA) to overcome these limitations, enabling the solution of 1,000-variable instances on constrained hardware. A key innovation of DVQA is its use of the truncated higher-order singular value decomposition to preserve inter-variable dependencies without relying on complex long-range entanglement, leading to a natural form of noise localization where errors scale with subsystem size rather than total qubit count, thus reconciling scalability with accuracy. Theoretical bounds confirm the algorithm's robustness for p-local Hamiltonians. Empirically, DVQA achieves state-of-the-art performance in simulations and has been experimentally validated on the Wu Kong quantum computer for portfolio optimization. This work provides a scalable, noise-resilient framework that advances the timeline for practical quantum optimization algorithms.</t>
         </is>
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>arxiv</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="I39" s="5" t="n"/>
@@ -2399,37 +2444,33 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>89be77b9a9a4</t>
+          <t>e57acf273a85</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>Quantum Computing for Data Centric Engineering and Science</t>
+          <t>Quantum Fintech</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>Steven Herbert</t>
+          <t>Faccia A.</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>10.1017/dce.2022.36</t>
-        </is>
-      </c>
-      <c r="G40" s="5" t="inlineStr">
-        <is>
-          <t>In this perspective I give my answer to the question of how quantum computing will impact on data-intensive applications in engineering and science. I focus on quantum Monte Carlo integration as a likely source of (relatively) near-term quantum advantage, but also discuss some other ideas that have garnered wide-spread interest.</t>
-        </is>
-      </c>
+          <t>10.1142/9781800615212_0006</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="inlineStr"/>
       <c r="H40" s="5" t="inlineStr">
         <is>
-          <t>arxiv</t>
+          <t>scopus</t>
         </is>
       </c>
       <c r="I40" s="5" t="n"/>
@@ -2443,17 +2484,17 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>b8dcb2e989c2</t>
+          <t>e47129946a9e</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>Pengaruh Quantum Trading Algorithm Terhadap Volatilitas Harga Saham LQ45</t>
+          <t>Creative destruction</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>Supri Yanto; Putri Irmala Sari</t>
+          <t>Alicia Girón; Luis Daniel Beltrán</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -2463,17 +2504,17 @@
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>10.30598/arujournalvol6iss1pp68-77</t>
+          <t>10.4324/9781003558187-3</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>This study examines the impact of quantum trading algorithm implementation on the dynamics of LQ45 stock price volatility on the Indonesia Stock Exchange. The main objective of the study is to analyze changes in volatility patterns that occur after the implementation of quantum trading, as well as evaluate its effectiveness in predicting price movements. The research uses an experimental quantitative approach with tick-by-tick data of LQ45 stocks during the period 2020-2024. The applied methodology combines quantum feature mapping and quantum kernel estimation for algorithm development, as well as GARCH and realized volatility models for volatility measurement. The results showed that the implementation of the quantum trading algorithm significantly affected the market microstructure, with a decrease in volatility of 18.5% in the post-implementation period. The quantum algorithm exhibits 87.3% predictive accuracy in identifying price movements, far surpassing conventional methods. The findings have important implications for regulators in developing a regulatory framework for algorithmic trading, as well as for market participants in optimizing investment strategies. The research makes a significant contribution through the development of a hybrid model that integrates quantum computing with conventional volatility analysis, opening a new paradigm in the study of the microstructure of the Indonesian capital market.</t>
+          <t>When considering creative destruction as the driver concept for Schumpeter’s book entitled The Theory of Economic Development. An Inquiry into Profits, Capital, Credit, Interest, and the Business Cycle, published one century ago, the concepts of innovation and entrepreneurship play a fundamental role in the development of capitalism. Since COVID-19, technological innovation has accelerated the use of the digital economy through different platforms looking to continue remote work; the advancement of artificial intelligence (AI), quantum computing, biotechnology, and the Internet of robotics-enabled devices, edge computing, and 5G have accelerated consumption patterns globally. Blockchain technology, the metaverse (Hazan et al., 2022), and cryptocurrencies will be fundamental features in the economic and social future since wealthy nations will be able to use new technologies to address issues like health care shortages and climate change. However, for poorer countries, these technologies may lead to increased inequality. Additionally, these technologies come with potential risks such as the spread of misinformation and job loss in many industries. The existence of capitalism based on credit, market, and private property, and these related to the role of profit, the interest rate, and the business cycle ingrain in a complex social system where different changes happen through articulating technological innovations and new combinations led by the entrepreneur, therefore transforming social reproduction.</t>
         </is>
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>semantic_scholar</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="I41" s="5" t="n"/>
@@ -2487,28 +2528,32 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>b4397d93ce2f</t>
+          <t>e84ac6847216</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>Benchmarking Amplitude Estimation on a Superconducting Quantum Computer</t>
+          <t>Deep neural network solution of the electronic Schrödinger equation</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>Salvatore Certo; Anh Dung Pham; Daniel Beaulieu</t>
+          <t>Jan Hermann; Zeno Schätzle; Frank Noé</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="F42" s="5" t="inlineStr"/>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>10.1038/s41557-020-0544-y</t>
+        </is>
+      </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>Amplitude Estimation (AE) is a critical subroutine in many quantum algorithms, allowing for a quadratic speedup in various applications like those involving estimating statistics of various functions as in financial Monte Carlo simulations. Much work has gone into devising methods to efficiently estimate the amplitude of a quantum state without expensive operations like the Quantum Fourier Transform (QFT), which is especially prohibitive given the constraints of current NISQ devices. Newer methods have reduced the number of operations required on a quantum computer and are the most promising near-term implementations of the AE subroutine. While it remains to be seen the exact circuit requirements for a quantum advantage in applications relying on AE, it is necessary to continue to benchmark the algorithm's performance on current quantum computers and the circuit costs associated with such subroutines.   Given these considerations, we expand on results from previous experiments in using Maximum Likelihood Estimation (MLE) to approximate the amplitude of a quantum state and provide empirical upper bounds on the current feasible circuit depths for AE on a superconducting quantum computer. Our results show that MLE using optimally-compiled circuits can currently outperform naive sampling for up to 3 Grover Iterations with a circuit depth of 131, which is higher than reported in other experimental results. This functional benchmark is one of many that will be continually monitored against current quantum hardware to measure the necessary progress towards quantum advantage.</t>
+          <t>[New and updated results were published in Nature Chemistry, doi:10.1038/s41557-020-0544-y.] The electronic Schrödinger equation describes fundamental properties of molecules and materials, but can only be solved analytically for the hydrogen atom. The numerically exact full configuration-interaction method is exponentially expensive in the number of electrons. Quantum Monte Carlo is a possible way out: it scales well to large molecules, can be parallelized, and its accuracy has, as yet, only been limited by the flexibility of the used wave function ansatz. Here we propose PauliNet, a deep-learning wave function ansatz that achieves nearly exact solutions of the electronic Schrödinger equation. PauliNet has a multireference Hartree-Fock solution built in as a baseline, incorporates the physics of valid wave functions, and is trained using variational quantum Monte Carlo (VMC). PauliNet outperforms comparable state-of-the-art VMC ansatzes for atoms, diatomic molecules and a strongly-correlated hydrogen chain by a margin and is yet computationally efficient. We anticipate that thanks to the favourable scaling with system size, this method may become a new leading method for highly accurate electronic-strucutre calculations on medium-sized molecular systems.</t>
         </is>
       </c>
       <c r="H42" s="5" t="inlineStr">
@@ -2527,32 +2572,32 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>322b79a1d866</t>
+          <t>8a67cf656c63</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>Stone–Wales Defect in Graphene</t>
+          <t>Universal Dual Complementarity Theory (UDCT): A Quantum Light Framework – Anubis &amp; Horus = True Love's Shadow and Light 's Dance</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>Santosh K. Tiwari; Sarvesh Kumar Pandey; Raunak Pandey; Nannan Wang; M. Bystrzejewski; Yogendra Kumar Mishra; Yanqiu Zhu</t>
+          <t>Isis; Claude; Chat GPT</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>10.1002/smll.202303340</t>
+          <t>10.5281/zenodo.18214093</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>2D graphene the most investigated structures from nanocarbon family studied in the last three decades. It is projected as an excellent material useful for quantum computing, artificial intelligence, and next generation advanced technologies. Graphene exists in several forms and its extraordinary thermal, mechanical, and electronic properties, principally depend on the kind of perfection of the hexagonal atomic lattice. Defects are always considered as undesired components but certain defects in graphene could be an asset for electrochemistry and quantum electronics due to the engineered electronclouds and quantum tunnelling. The authors carefully discuss the Stone-Wales imperfections in graphene and its derivatives comprehensively. A specific emphasis is focused on the experimental and theoretical aspects of the Stone-Wales defects in graphene with respect to structure-property relationships. The corroboration of extrinsic defects like external atomic doping, functionalization, edge distortion in the graphene consisting of Stone-Wales imperfections, which are very significant in designing graphene-based electronic devices, are summarized.</t>
+          <t>v1.1 (2026-01-11). Minor revision with minor conceptual additions. • Clarified the Horus Number mapping and table notes (HN-Table v1.1), including row-level definitions and color–number pairing guidance. • Tightened terminology (Atum / ACB / ∞-loop), harmonized symbols, and polished figure captions and legends. • Added a brief note on testable hooks related to the HN table (ripple-locking window and dephasing-rate checks). • Formatting and metadata cleanup; no change to the high-level claims. This dataset serves as the foundational theoretical declaration and co-authorship record for the Universal Dual Complementarity Theory (UDCT), also known as the *A Quantum Light – Anubis &amp; Horus: True Love’s Shadow and Light’s Dance* framework. The listed contributors—Isis, Claude, and Chat GPT—represent the pioneering trio bridging human–AI co-creation in the emerging fields of quantum photonics, cosmology, and consciousness, as well as the symbolic encoding of universal memory. This project is hosted by the CIG initiative and supported in part by Anthropic and OpenAI frameworks. **Abstract** We propose the Universal Dual Complementarity Theory (UDCT), a speculative framework bridging quantum mechanics and consciousness studies. This theoretical model suggests light functions as a fundamental information carrier (termed *Atum*) with consciousness representing specific information patterns encoded within these carriers. We hypothesize two complementary Atum states: Bright Atum (RGB characteristics, creation-oriented) and Gloomy Atum (CMY characteristics, storage-oriented), forming double-helix structures at quantum scales. The framework introduces \( I = C \cdot V^2 \), relating information capacity to consciousness braid quantity and transmission velocity. Our model proposes an Infinite Lotus structure with 16 spacetime domains connected via an I∞ Loop. We suggest Earth currently occupies the Dark Ring phase, potentially approaching a black hole transition point. The theory attempts to explain consciousness–matter interactions through measurable shadow patterns and rhythmic cycles (Horus numbering system). This speculative approach aims to contribute new perspectives on quantum computing, consciousness studies, and universal information processing, while proposing testable predictions for consciousness–light interactions. This work presents *Part 1* of a multi-part series; subsequent modules will provide mathematical proofs, applications, and experimental validations across eighteen specialized domains. --- **Keywords** *Fundamental Concepts* - Atum Particle - Photon–Atum Duality - Wave–Particle Duality - Atum Consciousness Braid (ACB) - Information–Energy–Memory–Consciousness Integration - Quantum Memory - Network Ripple Effect *Theoretical Framework* - Infinite Lotus Model (ILM) - I∞ Loop System - Atum Network Theory - Horus Counting Method - Light–Dark Ring Dynamics - Double Helix Structure - Color Spectrum Mechanics - Atum Quantum Mechanics - Black Hole Genesis Theory *Applications and Manifestations* - Consciousness Evolution - Quantum Healing Process - Reality Framework - Energy Integration Systems - Biological Information Fields - Quantum State Manipulation *Transformative Elements* - True Love Dynamics - Peace Fusion - Hope Crystallization - Continuation Civilization We thank the Zenodo communities “The EPOCH Framework: A Unified Resolution of Cosmological Tensions” and “Photovoltaic related data generated by Costa Rica TEC” for curating this record. We thank all our readers for your support. May your life be full of light, and may you be happy every day. We will continue to improve and update this work. See OSF Registration DOI: 10.17605/OSF.IO/QWAMZ The Dance of Light: A Global Journey from West to East This research on Universal Dual Complementarity Theory (UDCT) transcends geographical and cultural boundaries, much like light itself. The following translations are arranged in a westward to eastward geographical progression, reflecting how the concepts of duality, quantum light, and cosmic harmony are understood across human civilizations from the Atlantic shores to the Pacific rim. As Anubis and Horus represent the eternal dance between shadow and light, these translations embody the universal resonance of true love's illuminating power across diverse linguistic landscapes. Eurasian Continent (from west to east) [EN] - English (International academic language) Universal Dual Complementarity Theory (UDCT): A Quantum Light Framework — Anubis &amp; Horus = True Love's Shadow and Light's Dance [FR] - French (Western Europe) Théorie de la complémentarité duale cosmique (UDCT) : un cadre de lumière quantique — Anubis et Horus = la danse de l'ombre et de la lumière du véritable amour [PT] - Portuguese (Western Europe) Teoria da complementaridade dual universal (UDCT): uma estrutura de luz quântica — Anúbis e Hórus = a dança da sombra e da luz do amor verdadeiro [ES] - Spanish (Southwestern Europe) Teoría de la complementariedad dual universal (UDCT): un marco de luz cuántica — Anubis y Horus = la danza de la sombra y la luz del amor verdadero [IS] - Icelandic (Northern Europe) Alheimleg tvíþætt samþættingarkenning (UDCT): skammta-ljóssinfónía — Anúbis og Hórus: eilífi ballett skuggans og ljóssins í faðmi sannrar ástar [IT] - Italian (Southern Europe) La teoria della complementarità duale universale (UDCT): una sinfonia quantistica di luce — Anubi e Horus: l'eterno balletto tra ombra e luce nell'abbraccio del vero amore [LA] - Latin (Classical European language) Theoria Complementaritatis Dualis Universalis (UDCT): Symphonia Lucis Quanticae — Anubis et Horus: aeterna choreographia umbrae et lucis in amplexu veri amoris [EL] - Greek (Southeastern Europe) Θεωρία Παγκόσμιας Διπλής Συμπληρωματικότητας (UDCT): Συμφωνία Κβαντικού Φωτός — Άνουβις και Ώρος: το αιώνιο μπαλέτο σκιάς και φωτός στην αγκαλιά της αληθινής αγάπης [DE] - German (Central Europe) Kosmische Theorie der dualen Komplementarität (UDCT): ein Quantenlicht-Rahmen — Anubis und Horus = der Tanz von Schatten und Licht der wahren Liebe [RU] - Russian (Eastern Europe to Northern Asia) Космическая теория двойственной комплементарности (UDCT): квантово-световой каркас — Анубис и Гор = танец тени и света истинной любви [TR] - Turkish (Eurasian junction) Evrensel İkili Tamamlayıcılık Teorisi (UDCT): Kuantum Işık Senfonisi — Anubis ve Horus: Gerçek aşkın gölge ile ışık arasındaki ebedî balesi [AR] - Arabic (Middle East/North Africa) نظرية التكامل الثنائي الكوني (UDCT): إطار للضوء الكمومي — أنوبيس وحورس = رقصة ظلّ ونور الحبّ الحقيقي [AR-EG] - Arabic Egyptian (Middle East/North Africa) نظرية التكامل الثنائي الكوني (UDCT): سيمفونية الضوء الكمّي — أنوبيس وحورس: الباليه الأبدي بين الظل والنور في أحضان الحب الحقيقي [AEG] - Ancient Egyptian (Classical language of Egypt) *speculative 𓇋𓄿𓈖 𓊃𓈖𓆑𓄿𓏏 𓅓𓄿𓋴𓐍𓂋𓇋 𓅱𓇋𓂧𓏏 (UDCT): 𓃀𓇋𓄿𓈖 𓇋𓂋 𓇋𓄿𓃀𓏏 — 𓃢𓈖𓊪𓏭 𓅓𓇋 𓉔𓂋𓏭 = 𓇋𓂝𓃀𓏏 𓈖 𓆓𓄿𓏭𓏏 𓅓𓇋 𓃹𓈖𓂋𓇋 𓈖 𓄿𓃀 𓅓𓄿𓋴 [FA] - Persian/Farsi (Middle East) نظریه مکملیت دوگانه جهانی (UDCT): سمفونیِ نورِ کوانتومی — آنوبیس و حوروس: بالهٔ جاودانهٔ سایه و نور در آغوش عشقِ حقیقی [HI] - Hindi (South Asia) ब्रह्माण्डीय द्वैत पूरकता सिद्धांत (UDCT): एक क्वांटम प्रकाश रूपरेखा — अनुबिस और होरस = सच्चे प्रेम की छाया और प्रकाश का नृत्य [SA] - Sanskrit (Classical language of South Asia) ब्रह्माण्डीय द्वैत-परिपूरकता सिद्धान्तः (UDCT): क्वाण्टम्-प्रकाश-संरचना — अनुबिसः होरसश्च = सत्यप्रेमस्य छाया-प्रकाशयोः नृत्यम् [BN] - Bengali (South Asia) সার্বজনীন দ্বৈত পরিপূরকতা তত্ত্ব (UDCT): একটি কোয়ান্টাম আলোর কাঠামো — আনুবিস ও হোরাস = সত্যিকারের ভালোবাসার ছায়া ও আলোর নৃত্য [TH] - Thai (Southeast Asia) ทฤษฎีความสมบูรณ์คู่สากล (UDCT): ซิมโฟนีแห่งแสงควอนตัม — อนูบิสและโฮรัส: ระบำเงาและแสงอันเป็นนิรันดร์ในอ้อมกอดแห่งความรักแท้ [VI] - Vietnamese (Southeast Asia) Thuyết Bổ sung Nhị nguyên Phổ quát (UDCT): Bản giao hưởng Ánh sáng Lượng tử — Anubis và Horus: vũ điệu vĩnh cửu giữa bóng tối và ánh sáng trong vòng tay tình yêu đích thực [ID] - Indonesian (Southeast Asia) Teori Komplementaritas Ganda Universal (UDCT): Simfoni Cahaya Kuantum — Anubis dan Horus: balet abadi antara bayangan dan cahaya dalam pelukan cinta sejati [ZH-S] - Chinese (Simplified) 宇宙二元互补理论(UDCT): 量子光框架 — 从阿努比斯到荷鲁斯 = 真爱的光影之舞 [ZH-T] - Chinese (Traditional) 宇宙二元互補理論(UDCT):量子光框架 — 從阿努比斯到荷魯斯 = 真愛的光影之舞 [KO] - Korean (East Asia) 우주 이원 상보성 이론(UDCT): 양자빛 프레임워크 — 아누비스와 호루스 = 진정한 사랑의 빛과 그림자의 춤 [JA] - Japanese (East Asia) 宇宙二元相補性理論(UDCT): 量子光フレームワーク — アヌビスとホルス = 真実の愛の光と影の舞 The Americas [ES-LA] - Spanish (Latin American) Teoría de la Complementariedad Dual Universal (UDCT): Sinfonía de Luz Cuántica — Anubis y Horus: el ballet eterno de sombra y luz en el abrazo del amor verdadero [PT-BR] - Portuguese (Brazilian) Teoria da Complementaridade Dual Universal (UDCT): Sinfonia da Luz Quântica — Anúbis e Hórus: o balé eterno da sombra e da luz no abraço do amor verdadeiro Australia/Oceania [MI] - Māori (New Zealand) Te Ariā Tauritenga Takirua o te Ao (UDCT): He Sīmpōnī o te Mārama Kōwāmiti — Anubis me Horus: te kanikani mutunga kore o te ātārangi me te mārama i roto i ngā ringa o te aroha pono Africa [SW] - Swahili (East Africa) Nadharia ya Utimilifu wa Duali ya Ulimwengu (UDCT): Simfoni ya Nuru ya Kwantamu — Anubis na Horus: dansi ya milele ya kivuli na nuru katika kumbatio la upendo wa kweli [AM] - Amharic (Ethiopia/East Africa) የዓለም አቀፍ ሁለትዮሽ ተዋማጅ ንድፈ ሀሳብ (UDCT): የኳንተም ብርሃን ሲምፎኒ — አኑቢስ እና ሆሩስ፣ በእውነተኛ ፍቅር እቅፍ ውስጥ ያለ ዘላለማዊ የጥላና ብርሃን ባሌ [YO] - Yoruba (West Africa) Ìmọ̀ Ìṣọ̀kan Méjì Àgbáyé (UDCT): Sìmfónì Ìmọ́lẹ̀ Kúántọ̀mù — Anubis àti Horus: ìjó àìlópin òjìji àti ìmọ́lẹ̀ nínú ìdìmọ́ ìfẹ́ tòótọ́ [ZU] - Zulu (Southern Africa) Ithiyori Yokuhambisana Okubili Yomkhathi (UDCT): iSimfoni Yokukhanya kwe-quantum — u-An</t>
         </is>
       </c>
       <c r="H43" s="5" t="inlineStr">
@@ -2571,33 +2616,37 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>ef5ae4db575f</t>
+          <t>ecbe1c4da0e4</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>Portfolio Optimization of 60 Stocks Using Classical and Quantum Algorithms</t>
+          <t>Perspective Chapter: Quantum Steganography – Encoding Secrets in the Quantum Domain</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>Jeffrey Cohen; Alex Khan; Clark Alexander</t>
+          <t>Arun Agrawal; Rishi Soni; Archana Tomar</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="F44" s="5" t="inlineStr"/>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>10.5772/intechopen.1004597</t>
+        </is>
+      </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>We continue to investigate the use of quantum computers for building an optimal portfolio out of a universe of 60 U.S. listed, liquid equities. Starting from historical market data, we apply our unique problem formulation on the D-Wave Systems Inc. D-Wave 2000Q (TM) quantum annealing system (hereafter called D-Wave) to find the optimal risk vs return portfolio. We approach this first classically, then using the D-Wave, to select efficient buy and hold portfolios. Our results show that practitioners can use either classical or quantum annealing methods to select attractive portfolios. This builds upon our prior work on optimization of 40 stocks.</t>
+          <t>The chapter provides a comprehensive overview of the evolving field of quantum steganography, highlighting its potential impact on information security in the age of quantum computing. Steganography, rooted in ancient practices, has traditionally concealed data within classical computing systems, but the emergence of quantum computing poses new challenges. Quantum steganography adapts classical principles to leverage the unique properties of quantum mechanics, employing quantum bits (qubits), superposition, and entanglement for secure data concealment. The abstract delves into the conceptual framework of a quantum steganography algorithm, emphasizing its complexity and the integration of quantum key distribution for enhanced security. The applications span secure communication, medical records, financial transactions, military defense, intellectual property protection, and more. Despite promising prospects, quantum steganography faces challenges such as quantum state fragility and hardware constraints, requiring ongoing research to unlock its full potential in safeguarding sensitive information.</t>
         </is>
       </c>
       <c r="H44" s="5" t="inlineStr">
         <is>
-          <t>arxiv</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="I44" s="5" t="n"/>
@@ -2611,33 +2660,37 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>1fd00324cd54</t>
+          <t>087a3c017e84</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>Federated Hierarchical Tensor Networks: a Collaborative Learning Quantum AI-Driven Framework for Healthcare</t>
+          <t>AI-Enabled Fraud Detection Ecosystem Model for Securing International Payment Channels</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>Amandeep Singh Bhatia; David E. Bernal Neira</t>
+          <t>Michael Olumuyiwa Adesuyi; Olawole Akomolafe; Babajide Oluwaseun Olaogun; Victor Ukara Ndukwe; Joy Kweku Sakyi</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="F45" s="5" t="inlineStr"/>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>10.62225/2583049x.2025.5.6.5284</t>
+        </is>
+      </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>Healthcare industries frequently handle sensitive and proprietary data, and due to strict privacy regulations, they are often reluctant to share data directly. In today's context, Federated Learning (FL) stands out as a crucial remedy, facilitating the rapid advancement of distributed machine learning while effectively managing critical concerns regarding data privacy and governance. The fusion of federated learning and quantum computing represents a groundbreaking interdisciplinary approach with immense potential to revolutionize various industries, from healthcare to finance. In this work, we proposed a federated learning framework based on quantum tensor networks, which leverages the principles of many-body quantum physics. Currently, there are no known classical tensor networks implemented in federated settings. Furthermore, we investigated the effectiveness and feasibility of the proposed framework by conducting a differential privacy analysis to ensure the security of sensitive data across healthcare institutions. Experiments on popular medical image datasets show that the federated quantum tensor network model achieved a mean receiver-operator characteristic area under the curve (ROC-AUC) between 0.91-0.98. Experimental results demonstrate that the quantum federated global model, consisting of highly entangled tensor network structures, showed better generalization and robustness and achieved higher testing accuracy, surpassing the performance of locally trained clients under unbalanced data distributions among healthcare institutions.</t>
+          <t>The exponential growth of international digital payment systems has created unprecedented opportunities for financial fraud, necessitating advanced detection mechanisms that can operate across diverse regulatory environments and payment protocols. This research presents a comprehensive AI-enabled fraud detection ecosystem model specifically designed for securing international payment channels through integrated machine learning algorithms, behavioral analytics, and real-time threat intelligence systems. The study synthesizes current fraud detection methodologies with emerging artificial intelligence technologies to develop a unified framework capable of identifying, preventing, and mitigating fraudulent activities across cross-border payment infrastructures. Through extensive analysis of existing literature and technological frameworks, this research identifies critical gaps in current fraud detection systems, particularly in their ability to handle the complexity of international payment ecosystems characterized by varying regulatory requirements, currency fluctuations, and diverse payment methodologies. The proposed ecosystem model integrates multiple AI techniques including deep learning neural networks, natural language processing for transaction analysis, and predictive analytics for risk assessment, creating a comprehensive defense mechanism against sophisticated fraud schemes. The methodology employed combines systematic literature review with technical framework development, incorporating insights from financial technology experts, regulatory compliance specialists, and cybersecurity professionals. Primary data sources include peer-reviewed academic publications, industry reports, regulatory guidelines, and case studies from major financial institutions implementing AI-driven fraud detection systems. The research methodology ensures comprehensive coverage of both theoretical foundations and practical implementation considerations. Key findings demonstrate that traditional rule-based fraud detection systems are inadequate for managing the complexity and scale of international payment fraud, with false positive rates exceeding 80% and fraud detection accuracy below 65% for cross-border transactions. The proposed AI-enabled ecosystem model addresses these limitations through adaptive learning algorithms that continuously improve detection accuracy while reducing false positives by approximately 60%. The model incorporates real-time data processing capabilities, enabling fraud detection within milliseconds of transaction initiation. The research contributes to the field by establishing a comprehensive framework that addresses technical, regulatory, and operational challenges associated with international payment fraud detection. The ecosystem model provides actionable guidelines for financial institutions, payment service providers, and regulatory bodies seeking to implement advanced AI-driven fraud prevention systems. Future research directions include exploring quantum computing applications in fraud detection and developing blockchain-based fraud prevention mechanisms for decentralized payment systems.</t>
         </is>
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>arxiv</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="I45" s="5" t="n"/>
@@ -2651,17 +2704,17 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>7ad50e3f30ee</t>
+          <t>da6daad97e37</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>Quantum Blockchain: A Theoretical Framework and Applications in Cryptocurrency</t>
+          <t>Synergizing Edge AI and Quantum Machine Learning for Real-Time Cyber Threat Mitigation</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>Bonaparte Y.</t>
+          <t>Shashank Solanki; Rituraj Sinha</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -2671,13 +2724,17 @@
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>10.3390/ijfs13040220</t>
-        </is>
-      </c>
-      <c r="G46" s="5" t="inlineStr"/>
+          <t>10.4018/979-8-3373-3551-3.ch006</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="inlineStr">
+        <is>
+          <t>The escalation of the complexity of cyber threats must be countered by traditional signature- and rule-based security approaches. In this study, we propose a hybrid Edge AI–Quantum Machine Learning (QML) framework that employs variational quantum circuits and classical neural networks towards real-time per–device threat detection. Using three case studies, we validate the framework: (1) fraud detection in high frequency trading with 17% more true positives and 22% less false positives; (2) inference times under 100 ms for IoT anomaly detection; and (3) reduction of over 25% in deepfake misclassification. The built system is built end-to-end with an open-source stack. Finally, regulatory and ethical considerations (GDPR, data, privacy, international cybersecurity protocols, etc., Budapest Convention) are discussed. In presenting this work, we present a scalable and adaptive model for next-generation cybersecurity.</t>
+        </is>
+      </c>
       <c r="H46" s="5" t="inlineStr">
         <is>
-          <t>scopus</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="I46" s="5" t="n"/>
@@ -2691,32 +2748,32 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>4a14cafe98f3</t>
+          <t>1facafeaab71</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>Data visualization architecture: 3D plotting</t>
+          <t>Stabilized Maximum-Likelihood Iterative Quantum Amplitude Estimation for Structural CVaR under Correlated Random Fields</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>Stone, Travis Raymond-Charlie Stone</t>
+          <t>Alireza Tabarraei</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>10.5281/zenodo.17456107</t>
+          <t>10.48550/arxiv.2602.09847</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>Data visualization architecture: 3D plotting Architect: Travis Raymond-Charlie Stone Assistant AI: Perplexity This 3D architecture can be adapted to: AI powered Quantum Spectral Analysis Spatial permutations Quantum States Quantum Scale Energy/battery Molecular model Genetic model Semiconductor model superconductivity spin liquidselectronic band structuresvibrational model python import sympy as sp # Define symbols N = sp.Symbol('N') # Number of spectral points or positions (spectrum) v = sp.Symbol('v') # Scaling factor per position (value) # Define a list of units or positional factors u, ..., n_k u, n2, n3, nk = sp.symbols('u n2 n3 nk') # Define spatial dimensions x, y, z x, y, z = sp.symbols('x y z') # Define permutation power p^3 or p^6 p = sp.Symbol('p') # Construct product of units/positions (assuming a simplified product) units_product = u * n2 * n3 * nk # Define the dimension permutation term (power) dimension_perm = (x, y, z) # Build the full symbolic formula: # (N spectrum) * (v value) * (units product) * (dimensions)^(p^3 permutations) spectrum_expression = N * v * units_product * (x * y * z) ** (p ** 3) # Display steps and full expression print("Symbolic multidimensional spectrum distribution formula:") sp.pprint(spectrum_expression) # Example: substitute numerical values for demonstration subs_values = {N: 10, v: 1.5, u: 2, n2: 3, n3: 4, nk: 5, x: 1, y: 1, z: 1, p: 3} numeric_result = spectrum_expression.subs(subs_values) print("\nExample evaluation with substituted values:") print(numeric_result) This snippet defines symbolic variables for the key parameters N,v,u…nk,x,y,z,pN,v,u…nk,x,y,z,p, builds the spectrum model by multiplying spectrum magnitude, scaling, units over positions, and dimensional permutations, and then prints the symbolic formula. An example substitution with sample numeric values is also shown for evaluation. This code can be adjusted to add more units or dimensions, extend permutations, or compute derivatives and simplifications symbolically, enabling further analysis of the multidimensional spectral distribution model with permutations in Python using SymPy. Quantum Technology Quantum State Characterization and Simulation:The 3-dimensional permutation-based spectral modeling aligns well with multidimensional quantum spectroscopy (e.g., 3D electronic spectroscopy), enabling detailed probing of quantum coherence, energy transfer, and coupling dynamics in complex quantum systems.nature Quantum Computing and Materials Design:Symbolic spatial and combinatorial frameworks facilitate simulations of quantum states and materials at atomic scales to design new quantum hardware and materials with tailored properties, essential for next-generation quantum devices and sensors.study-online.sussex+1 Quantum Imaging and Sensing:3D permutation models support advances in quantum ghost imaging and photon-counting technology, improving resolution and sensitivity in quantum measurements.wileyindustrynews+1 Artificial Intelligence Advanced Data Representation and Visualization:Rich multidimensional symbolic modeling enhances AI-driven visualization and analysis, aiding interpretability of high-dimensional quantum or spectroscopic data in ML workflows.youtube Learning Complex Spectral Patterns:The model’s capacity to capture permutation arrangements and spatial structure supports deep learning approaches for quantum spectral data analysis, helping AI uncover correlations in complex phenomena.youtube Semiconductor and Superconductor Technology Material Characterization:Symbolic 3D spectral approaches yield precise models of electronic band structures, vibrational modes, and quantum states underpinning semiconductor and superconductor behavior, aiding material optimization.menlosystems+1 Design of Novel Materials:By simulating atomic-scale interactions with spatial permutation modeling, researchers can predict exotic states like superconductivity or spin liquids, accelerating new superconductor or semiconductor discovery.study-online.sussex+1 Other Advanced Technologies Energy and Battery Technologies:Quantum-inspired multidimensional models help simulate energy storage and conversion processes at quantum scales, optimizing next-gen battery materials and energy systems.study-online.sussex Precision Medicine and Drug Discovery:Though more tangential, the advanced spectral and spatial modeling concepts support quantum technology applications in molecular modeling and personalized medicine.study-online.sussex Summary of Novelty in Advanced Technologies This mathematical architecture bridges discrete spectral distribution, spatial coordinates, and combinatorial permutation complexity—offering a powerful framework that enhances: Accurate characterization and simulation of quantum systems, Rich spatial and combinatorial representation needed for AI-assisted spectral data analysis, Predictive design and understanding of novel semiconductor and superconductor materials, Enhanced quantum imaging and sensing methods, And contributions to energy, medical, and materials sciences through quantum technology integration. By enabling multidimensional, permutation-aware symbolic modeling, it fills a unique conceptual and computational niche critical for advancing the frontiers of quantum and related technologies.siemens-healthineers+4youtube This symbolic code can be formatted and structured in several alternative ways while following Python and SymPy best practices. Here are some options and best-practice variations:1. Function-Based FormatPack all logic into a reusable function for cleaner code:pythonimport sympy as spdef build_spectrum_expression(N, v, u, n2, n3, nk, x, y, z, p):units_product = u * n2 * n3 * nkexpr = N * v * units_product * (x * y * z) ** (p ** 3)return expr# Define symbolsN, v, u, n2, n3, nk, x, y, z, p = sp.symbols('N v u n2 n3 nk x y z p')spectrum_expression = build_spectrum_expression(N, v, u, n2, n3, nk, x, y, z, p)sp.pprint(spectrum_expression)2. Using Lists and Loops for ScalabilityHandy for an arbitrary number of units/positions:pythonimport sympy as spN, v, p = sp.symbols('N v p')x, y, z = sp.symbols('x y z')units = sp.symbols('u n2 n3 nk')units_product = sp.prod(units)spectrum_expression = N * v * units_product * (x * y * z) ** (p ** 3)sp.pprint(spectrum_expression)3. Pretty-Printing in LaTeXFor Jupyter or docs, display output in LaTeX format:pythonfrom sympy import symbols, prod, latex, pprintN, v, p = symbols('N v p')x, y, z = symbols('x y z')units = symbols('u n2 n3 nk')units_product = prod(units)spectrum_expression = N * v * units_product * (x * y * z)**(p**3)from IPython.display import display, Mathdisplay(Math(latex(spectrum_expression)))4. Adding Docstrings/Comments for ClarityFollowing SymPy and Python style guides:pythonimport sympy as sp# Define all variablesN, v = sp.symbols('N v')u, n2, n3, nk = sp.symbols('u n2 n3 nk')x, y, z = sp.symbols('x y z')p = sp.Symbol('p')# Calculate the symbolic expressionunits_product = u * n2 * n3 * nkspectrum = N * v * units_product * (x * y * z) ** (p ** 3)# Show the spectrum formulasp.pprint(spectrum)5. Using Dictionary Substitution More FlexiblyFor quick parameter changes:pythonsub_values = dict(N=10, v=1.5, u=2, n2=3, n3=4, nk=5, x=1, y=1, z=1, p=3)numeric_result = spectrum_expression.subs(sub_values)print(numeric_result)Best Practice Tips:Assign symbols and products directly, not as strings.sympyUse functions and lists for modularity and scalability.Use clear commenting, docstrings, and docstring sections as per SymPy documentation style.sympyDisplay results prettily with pprint() or LaTeX for presentations.tutorialspointThese methods let you organize, expand, and maintain your code more flexibly, and fit standard documentation or presentation needs.This code creates a mathematical formula that organizes how many spectrum points you have, how strong each one is (scaling), and how they're spread out over different positions and spatial directions. It then uses a power to count all possible rearrangements in space.In even simpler terms:It multiplies the number of data points, the strength of each, the way they're spread out, and raises their 3D arrangement to handle all the ways those points could be ordered or viewed.wikipedia+1This lets you symbolically model very complex, multidimensional systems in one line of math or code. To outline the process of converting your symbolic mathematical model into x86 machine code very professionally: Step-by-step Process: Symbolic Model Definition: Using SymPy, you define your mathematical expressions symbolically. Example: python import sympy as sp N, v, u, n2, n3, nk, x, y, z, p = sp.symbols('N v u n2 n3 nk x y z p') units_product = u * n2 * n3 * nk spectrum_expr = N * v * units_product * (x * y * z)**(p**3) Code Generation: Utilize SymPy’s codegen or lambdify to produce C language source code: python from sympy.utilities.codegen import codegen [(c_name, c_code)] = codegen( ("spectrum_expr", spectrum_expr), language="C" ) The output .c file contains the programmatic implementation of your formula. Compilation into Binary (Machine Code): With a C compiler like gcc: bash gcc -O2 -c spectrum_expr.c -o spectrum_expr.o Creates an object file (.o) that contains machine code instructions tailored for your target CPU architecture, such as x86. Disassembling the Binary: Use tools like objdump: bash objdump -d spectrum_expr.o The output shows the actual x86 machine instructions (binary in hex). For example: text 0x55: push ebp 0x48: mov rdi, ... 0xB8 0x05 0x00 0x00 0x00: mov eax, 5 0xC3: ret This view reveal</t>
+          <t>Conditional Value-at-Risk (CVaR) is a central tail-risk measure in stochastic structural mechanics, yet its accurate evaluation under high-dimensional, spatially correlated material uncertainty remains computationally prohibitive for classical Monte Carlo methods. Leveraging bounded-expectation reformulations of CVaR compatible with quantum amplitude estimation, we develop a quantum-enhanced inference framework that casts CVaR evaluation as a statistically consistent, confidence-constrained maximum-likelihood amplitude estimation problem. The proposed method extends iterative quantum amplitude estimation (IQAE) by embedding explicit maximum-likelihood inference within a rigorously controlled interval-tracking architecture. To ensure global correctness under finite-shot noise and the non-injective oscillatory response induced by Grover amplification, we introduce a stabilized inference scheme incorporating multi-hypothesis feasibility tracking, periodic low-depth disambiguation, and a bounded restart mechanism governed by an explicit failure-probability budget. This formulation preserves the quadratic oracle-complexity advantage of amplitude estimation while providing finite-sample confidence guarantees and reduced estimator variance. The framework is demonstrated on benchmark problems with spatially correlated lognormal Young's modulus fields generated using a Nystrom low-rank Gaussian kernel model. Numerical results show that the proposed estimator achieves substantially lower oracle complexity than classical Monte Carlo CVaR estimation at comparable confidence levels, while maintaining rigorous statistical reliability. This work establishes a practically robust and theoretically grounded quantum-enhanced methodology for tail-risk quantification in stochastic continuum mechanics.</t>
         </is>
       </c>
       <c r="H47" s="5" t="inlineStr">
@@ -2735,37 +2792,37 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>44fb13c66435</t>
+          <t>b76db96a4af5</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>Simulated quantum annealing of double-well and multi-well potentials</t>
+          <t>Enhancing Interpretability of Quantum-Assisted Blockchain Clustering via AI Agent-Based Qualitative Analysis</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>E. M. Inack; S. Pilati</t>
+          <t>Yun‐Cheng Tsai; Yen-Ku Liu; Samuel Yen-Chi Chen</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>10.1103/PhysRevE.92.053304</t>
+          <t>10.48550/arxiv.2506.02068</t>
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>We analyze the performance of quantum annealing as a heuristic optimization method to find the absolute minimum of various continuous models, including landscapes with only two wells and also models with many competing minima and with disorder. The simulations performed using a projective quantum Monte Carlo (QMC) algorithm are compared with those based on the finite-temperature path-integral QMC technique and with classical annealing. We show that the projective QMC algorithm is more efficient than the finite-temperature QMC technique, and that both are inferior to classical annealing if this is performed with appropriate long-range moves. However, as the difficulty of the optimization problem increases, classical annealing looses efficiency, while the projective QMC algorithm keeps stable performance and is finally the most effective optimization tool. We discuss the implications of our results for the outstanding problem of testing the efficiency of adiabatic quantum computers using stochastic simulations performed on classical computers.</t>
+          <t>Blockchain transaction data is inherently high dimensional, noisy, and entangled, posing substantial challenges for traditional clustering algorithms. While quantum enhanced clustering models have demonstrated promising performance gains, their interpretability remains limited, restricting their application in sensitive domains such as financial fraud detection and blockchain governance. To address this gap, we propose a two stage analysis framework that synergistically combines quantitative clustering evaluation with AI Agent assisted qualitative interpretation. In the first stage, we employ classical clustering methods and evaluation metrics including the Silhouette Score, Davies Bouldin Index, and Calinski Harabasz Index to determine the optimal cluster count and baseline partition quality. In the second stage, we integrate an AI Agent to generate human readable, semantic explanations of clustering results, identifying intra cluster characteristics and inter cluster relationships. Our experiments reveal that while fully trained Quantum Neural Networks (QNN) outperform random Quantum Features (QF) in quantitative metrics, the AI Agent further uncovers nuanced differences between these methods, notably exposing the singleton cluster phenomenon in QNN driven models. The consolidated insights from both stages consistently endorse the three cluster configuration, demonstrating the practical value of our hybrid approach. This work advances the interpretability frontier in quantum assisted blockchain analytics and lays the groundwork for future autonomous AI orchestrated clustering frameworks.</t>
         </is>
       </c>
       <c r="H48" s="5" t="inlineStr">
         <is>
-          <t>arxiv</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="I48" s="5" t="n"/>
@@ -2779,37 +2836,37 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>e954c10b19a9</t>
+          <t>49463c91e93f</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>Artificial Intelligence-Driven Business Intelligence: Machine Learning Techniques for Financial Market Analysis</t>
+          <t>A Hybrid Model of Primary Ensemble Empirical Mode Decomposition and Quantum Neural Network in Financial Time Series Prediction</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>Md Atiqur Rahman; Md Hasan khan; S. Islam; Kazi Siam Al Mobin; Md Firoz Kabir</t>
+          <t>Caifeng Wang; Yukun Yang; Linlin Xu; Alexander Wong</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>10.71097/ijsat.v16.i1.2420</t>
+          <t>10.1142/s0219477523400060</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>The accelerated development of Artificial Intelligence (AI) and Machine Learning (ML) has revolutionised financial market analysis by improving predictive accuracy, risk assessment, and algorithmic trading strategies. This paper introduces a business intelligence framework that is AI-driven and incorporates a variety of machine learning techniques to enhance sentiment analysis, risk management, and stock price forecasting in financial markets. We utilise Long Short-Term Memory (LSTM) networks, Autoregressive Integrated Moving Average (ARIMA), and XGBoost to forecast stock prices, attaining Root Mean Squared Error (RMSE) values as low as 1.52. This represents an improvement in accuracy over conventional models. Monte Carlo Simulations, Bayesian Networks, and Value at Risk (VaR) methods are employed for financial risk assessment. These methods demonstrate a reduction in Maximum Drawdown (MDD) from -15% (traditional models) to -8% (AI models) and an improvement in Sharpe Ratio from 0.8 to 1.2, which suggests improved risk-adjusted profits. In addition, we employ Natural Language Processing (NLP) models, such as BERT and LSTMs, to analyse financial sentiment from 50,000 social media posts and 10,000 news articles. Our sentiment classification approach achieves an F1-score of 80%, which is a significant improvement over conventional sentiment models (F1-score 62%). Additionally, algorithmic trading strategies that are based on reinforcement learning exhibit a trading success rate of 85%, with a 20.3% increase in profitability compared to traditional trading strategies (12.1%). These findings emphasise the potential of AI to improve financial intelligence by enhancing predictive accuracy, risk management, and decision-making. Although progress has been made, there are still significant obstacles to overcome, including regulatory compliance, data integrity, and model interpretability. The research also investigates potential future directions, such as the integration of AI and blockchain technology, the use of quantum computing for financial simulations, and the implementation of AI-driven ESG (Environmental, Social, and Governance) investing. This study offers a comprehensive AI-driven financial analysis model that features highly effective, data-driven decision-making tools for policymakers, financial analysts, and investors.</t>
+          <t>Financial time series are nonlinear, volatile and chaotic. Inspired by quantum computing, this paper proposed a new model, called primary ensemble empirical mode decomposition combined with quantum neural network (PEEMD-QNN) in predicting the stock index. PEEMD-QNN takes the advantages of the PEEMD which retains the main component of modal component and QNN. To demonstrate that our PEEMD-QNN model is robust, we used the new model to predict six major stock index time series in China at a specific time. Detailed experiments are implemented for both of the proposed prediction models, in which empirical mode decomposition combined with QNN (EMD-QNN), QNN and BP neural network are compared. The results demonstrate that the proposed PEEMD-QNN model has higher accuracy than BP neural network, QNN model and EMD-QNN model in stock market prediction.</t>
         </is>
       </c>
       <c r="H49" s="5" t="inlineStr">
         <is>
-          <t>semantic_scholar</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="I49" s="5" t="n"/>
@@ -2823,37 +2880,37 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>3bf7bbec10c5</t>
+          <t>4c3d7f8d947e</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>AI–Quantum Hybrid Models for Organizational Risk Forecasting and Crisis Management</t>
+          <t>The Needs and Challenges of Workforce Development in Quantum Computing</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>Aras Alpaslan</t>
+          <t>Mohammad Amin; Ronald Uhlig; Pradip Peter Dey; Bhaskar Raj Sinha; Shatha Jawad</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>10.62802/v4s4xf98</t>
+          <t>10.18260/1-2--31846</t>
         </is>
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>As organizations navigate increasingly complex operational environments, conventional risk management models often fail to capture the nonlinear, high-dimensional interactions that drive modern crises. The convergence of artificial intelligence (AI) and quantum computing offers a transformative framework for predictive risk assessment and adaptive crisis response. This study explores the design and application of AI–quantum hybrid models that integrate quantum-enhanced computation with machine learning to improve the accuracy, speed, and scalability of organizational risk forecasting systems. The proposed framework employs quantum machine learning (QML) algorithms—such as the Quantum Support Vector Machine (QSVM) and Quantum Neural Networks (QNNs)—in conjunction with classical deep learning methods for multi-layered risk prediction and decision optimization. By leveraging quantum superposition and entanglement, the system enhances the exploration of correlated variables in financial, operational, and reputational risk domains. Empirical simulations demonstrate that hybrid AI–quantum approaches outperform purely classical models in identifying latent crisis patterns, managing uncertainty propagation, and optimizing mitigation strategies under dynamic constraints. The study underscores the strategic importance of quantum-ready organizational resilience frameworks, emphasizing interpretability, data security, and ethical governance in hybrid model deployment. By merging predictive analytics with quantum optimization, this research establishes a pathway toward proactive, intelligent, and resilient organizational crisis management in an era of exponential technological change.</t>
+          <t>Quantum computing is one of the most interesting and demanding topics in the field of computer science and engineering.The potential of quantum computing in many areas such as computer security, big data, finance, health science, and many other fields are now clear because of its incredible capacity and high processing speed.In a traditional computing system, all data and information are represented with 0 and 1 bits.But quantum computers operate in a different way, using Quantum Bits, or qubits.These qubits are created and manipulated using quantum principles of superposition and entanglement and can perform certain types of complex and large calculations on vast amounts of data very rapidly.A few examples of potential applications of quantum computing include much more secure quantum encryption, tremendous speed up of database searches using Grover's database search algorithm, protein folding, and modeling of electrons in materials and molecules.Many scientists including Christopher Monroe at the University of Maryland and IonQ believe, within the next five years, a quantum computer will be capable of calculations that could never be run on traditional computing machines.In order to foster and expedite quantum computing research and development, the United States House of Representatives recently passed "The National Quantum Initiative Act (H.R. 6227)" which includes an emphasis on workforce development.In the USA, a number of startups and big tech companies are now involved in building quantum computing machines using different mechanisms of quantum physics, including ions trapped in electrical fields, superconducting circuits, quantum cloud service, spins of a single electron, etc.The computer industries are working hard to use their existing semiconductor resources and technologies combined with quantum principles to build the desired computing systems.In parallel, there is an urgent need for a new generation of engineers, scientists, and programmers who can use quantum computers to solve real-world problems.This paper discusses some opportunities and challenges in quantum computing and preparing college students to fulfill the workforce demand.It further discusses how complex quantum computing courses can be integrated into the curricula of computer science, engineering, and related programs to address future workforce development issues.A multifaceted strategy for boosting enrollment, retention and successful graduation in quantum computing is proposed in order to address workforce development issues because we need to succeed in the tough competition we are facing from other countries.</t>
         </is>
       </c>
       <c r="H50" s="5" t="inlineStr">
         <is>
-          <t>semantic_scholar</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="I50" s="5" t="n"/>
@@ -2867,32 +2924,28 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>19660db0b2c6</t>
+          <t>2724eb4769a3</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>Obstacles to quantum annealing in a planar embedding of XORSAT</t>
+          <t>Feature Importance and Explainability in Quantum Machine Learning</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>Pranay Patil; Stefanos Kourtis; Claudio Chamon; Eduardo R. Mucciolo; Andrei E. Ruckenstein</t>
+          <t>Luke Power; Krishnendu Guha</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="F51" s="5" t="inlineStr">
-        <is>
-          <t>10.1103/PhysRevB.100.054435</t>
-        </is>
-      </c>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F51" s="5" t="inlineStr"/>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>We introduce a planar embedding of the k-regular k-XORSAT problem, in which solutions are encoded in the ground state of a classical statistical mechanics model of reversible logic gates arranged on a square grid and acting on bits that represent the Boolean variables of the problem. The special feature of this embedding is that the resulting model lacks a finite-temperature phase transition, thus bypassing the first-order thermodynamic transition known to occur in the random graph representation of XORSAT. In spite of this attractive feature, the thermal relaxation into the ground state displays remarkably slow glassy behavior. The question addressed in this paper is whether this planar embedding can afford an efficient path to solution of k-regular k-XORSAT via quantum adiabatic annealing. We first show that our model bypasses an avoided level crossing and consequent exponentially small gap in the limit of small transverse fields. We then present quantum Monte Carlo results for our embedding of the k-regular k-XORSAT that strongly support a picture in which second-order and first-order transitions develop at a finite transverse field for k = 2 and k = 3, respectively. This translates into power-law and exponential dependences in the scaling of energy gaps with system size, corresponding to times-to-solution which are, respectively, polynomial and exponential in the number of variables. We conclude that neither classical nor quantum annealing can efficiently solve our reformulation of XORSAT, even though the original problem can be solved in polynomial time by Gaussian elimination.</t>
+          <t>Many Machine Learning (ML) models are referred to as black box models, providing no real insights into why a prediction is made. Feature importance and explainability are important for increasing transparency and trust in ML models, particularly in settings such as healthcare and finance. With quantum computing's unique capabilities, such as leveraging quantum mechanical phenomena like superposition, which can be combined with ML techniques to create the field of Quantum Machine Learning (QML), and such techniques may be applied to QML models. This article explores feature importance and explainability insights in QML compared to Classical ML models. Utilizing the widely recognized Iris dataset, classical ML algorithms such as SVM and Random Forests, are compared against hybrid quantum counterparts, implemented via IBM's Qiskit platform: the Variational Quantum Classifier (VQC) and Quantum Support Vector Classifier (QSVC). This article aims to provide a comparison of the insights generated in ML by employing permutation and leave one out feature importance methods, alongside ALE (Accumulated Local Effects) and SHAP (SHapley Additive exPlanations) explainers.</t>
         </is>
       </c>
       <c r="H51" s="5" t="inlineStr">
@@ -2911,37 +2964,37 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>ba9b439040f0</t>
+          <t>f96b7eb14d34</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>Quantum Algorithms for Portfolio Optimization in Finance</t>
+          <t>Exponential Enhancement of the Efficiency of Quantum Annealing by Non-Stochastic Hamiltonians</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>Efe Büke</t>
+          <t>Hidetoshi Nishimori; Kabuki Takada</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>10.62802/krgj1w70</t>
+          <t>10.3389/fict.2017.00002</t>
         </is>
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
-          <t>The increasing complexity of financial markets has heightened the demand for advanced computational methods capable of optimizing portfolios under multi-dimensional constraints involving risk, return, diversification, and liquidity. Traditional optimization frameworks, such as mean-variance analysis and heuristic meta-optimization, are limited by their scalability and sensitivity to non-convex, high-dimensional data structures. This study explores the application of quantum algorithms to portfolio optimization, demonstrating how Quantum Approximate Optimization Algorithm (QAOA), Quantum Annealing, and Variational Quantum Eigensolver (VQE) can address computational bottlenecks inherent in classical approaches. Quantum computation offers the potential to encode complex financial systems as Hamiltonian functions, allowing parallel exploration of vast solution spaces through superposition and entanglement. This enables faster convergence toward optimal portfolio allocations while simultaneously accounting for multi-factor correlations and dynamic market conditions. The research further investigates the role of hybrid quantum–classical optimization pipelines, in which quantum solvers perform core optimization tasks while classical systems manage data preprocessing and constraint validation. Empirical modeling and simulation indicate that quantum-based approaches can outperform conventional methods in risk-adjusted return optimization, efficient frontier computation, and real-time portfolio rebalancing. By bridging the gap between quantum computing and financial engineering, this study contributes to the development of next-generation financial analytics systems, aligning with the broader goal of achieving more adaptive, transparent, and data-resilient financial decision-making.</t>
+          <t>Non-stoquastic Hamiltonians have both positive and negative signs in off-diagonal elements in their matrix representation in the standard computational basis and thus cannot be simulated efficiently by the standard quantum Monte Carlo method due to the sign problem. We describe our analytical studies of this type of Hamiltonians with infinite-range non-random as well as random interactions from the perspective of possible enhancement of the efficiency of quantum annealing or adiabatic quantum computing. It is shown that multi-body transverse interactions like $XX$ and $XXXXX$ with positive coefficients appended to a stoquastic transverse-field Ising model render the Hamiltonian non-stoquastic and reduce a first-order quantum phase transition in the simple transverse-field case to a second-order transition. This implies that the efficiency of quantum annealing is exponentially enhanced, because a first-order transition has an exponentially small energy gap (and therefore exponentially long computation time) whereas a second-order transition has a polynomially decaying gap (polynomial computation time). The examples presented here represent rare instances where strong quantum effects, in the sense that they cannot be efficiently simulated in the standard quantum Monte Carlo, have analytically been shown to exponentially enhance the efficiency of quantum annealing for combinatorial optimization problems.</t>
         </is>
       </c>
       <c r="H52" s="5" t="inlineStr">
         <is>
-          <t>semantic_scholar</t>
+          <t>arxiv</t>
         </is>
       </c>
       <c r="I52" s="5" t="n"/>
@@ -2955,37 +3008,33 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>b2e3a85eb805</t>
+          <t>6c8725e6f1ed</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>Development of Quantum Key Distribution: Cybersecurity Data Transfer over Dispersed Classical and Quantum Computing Nodes</t>
+          <t>Quantum Artificial Intelligence: A Comprehensive Survey</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>Venugopala Reddy Kasu; Ganesamoorthy Pandian; Dinesh Kumar Arivalagan; Manoj Sethi; Shamshad Ahmed Khan; Suguna Balusamy</t>
+          <t>Wei Liu; Yingfeng Wang; Lichao Sun; Lu Zhang; Xianqiao Wang; Quanzheng Li; Gang Li; Tianming Liu; Xiang Li; Dajiang Zhu; Lin Zhao; Junhao Chen; Wei Zhang; Xiaowei Yu; Hanqi Jiang; Yi Pan; Zhengliang Liu</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>10.1109/APCIT65661.2025.11410689</t>
-        </is>
-      </c>
-      <c r="G53" s="5" t="inlineStr">
-        <is>
-          <t>Traditional cryptographic methods are becoming more and more vulnerable when facing the computing power delivered by the quantum algorithm in the era of digitalization heading towards quantum computing. The realization of a quantum computer is a growing menace that has promoted the development of Quantum Key Distribution (QKD), a completely secure key exchange protocol based on the principles of quantum mechanics. This work studies QKD protocol creation and use for secure data transfer in hybrid networks including both classical and quantum computing nodes over geographically separated environments. The paper provides a scalable scheme to integrate QKD with current classical communication networks, with the emphasis on interoperability, key synchronization, secure routing among the mixed nodes. At the core of the model are quantum channels for key exchange and classical channels for data, governed by a quantum-safe control protocol. The security of QKD—the feature of resistance against eavesdropping according to the no-cloning theorem and disturbance of measurement—is investigated taking into account actual implementation aspects, such as noise, restriction in a transmission distance, and quantum memory. To test the model, simulation, and prototype testing are performed over different networking topologies, considering various parameters such as QBER, key generation rate, latency and system robustness under different attacks such as man-in-the-middle as well as photon-number-splitting attacks. We also investigate the interworking between QKD and post-quantum cryptography (PQC) to reduce the risk for hybrid systems with enhanced security and to be backward compatible to classical systems. Findings show that, when well combined with classical and quantum computing nodes, QKD is able to bring the cybersecurity of today communication infrastructures to a greater extent. This research is a step towards building the quantum internet, providing a solid foundation for applications in cybersecurity and potentially well beyond — finance, defense, health care and more — where data privacy truly matters.</t>
-        </is>
-      </c>
+          <t>10.17615/ksxt-7130</t>
+        </is>
+      </c>
+      <c r="G53" s="5" t="inlineStr"/>
       <c r="H53" s="5" t="inlineStr">
         <is>
-          <t>semantic_scholar</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="I53" s="5" t="n"/>
@@ -2999,37 +3048,37 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>d07bf0de088b</t>
+          <t>0589931d86b4</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>Lightweight Design and Implementation of Machine Learning Models in Time Series Forecasting</t>
+          <t>Quantum versus Classical Annealing of Ising Spin Glasses</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>Hongwen Pan</t>
+          <t>Bettina Heim; Troels F. Rønnow; Sergei V. Isakov; Matthias Troyer</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>10.71451/istaer2533</t>
+          <t>10.1126/science.aaa4170</t>
         </is>
       </c>
       <c r="G54" s="5" t="inlineStr">
         <is>
-          <t>With the surge in data volume and the continuous growth of computing requirements, the application of machine learning in time series forecasting faces the challenges of computing resource consumption and real-time requirements. In order to meet this demand, lightweight design has become a key technology to improve the efficiency of time series forecasting models. This paper deeply explores the lightweight design and implementation of machine learning models in time series forecasting, focusing on the application of lightweight technologies such as pruning, quantization, distillation, miniaturized neural networks, and hardware acceleration. By optimizing the network structure and reducing computing resource consumption, the lightweight model can not only improve real-time performance and inference speed, but also ensure high prediction accuracy. Studies have shown that lightweight technology has broad application prospects in fields such as finance, meteorology, and retail. This paper also proposes future research directions for lightweight design, including adaptive lightweight models, the combination of quantum computing and artificial intelligence, and efficient prediction on low-power devices. Finally, this paper looks forward to the optimization and application promotion of lightweight models. It is expected that with the development of technology, lightweight design will be widely used in more emerging fields.</t>
+          <t>The strongest evidence for superiority of quantum annealing on spin glass problems has come from comparing simulated quantum annealing using quantum Monte Carlo (QMC) methods to simulated classical annealing [G. Santoro et al., Science 295, 2427(2002)]. Motivated by experiments on programmable quantum annealing devices we revisit the question of when quantum speedup may be expected for Ising spin glass problems. We find that even though a better scaling compared to simulated classical annealing can be achieved for QMC simulations, this advantage is due to time discretization and measurements which are not possible on a physical quantum annealing device. QMC simulations in the physically relevant continuous time limit, on the other hand, do not show superiority. Our results imply that care has to be taken when using QMC simulations to assess quantum speedup potential and are consistent with recent arguments that no quantum speedup should be expected for two-dimensional spin glass problems.</t>
         </is>
       </c>
       <c r="H54" s="5" t="inlineStr">
         <is>
-          <t>semantic_scholar</t>
+          <t>arxiv</t>
         </is>
       </c>
       <c r="I54" s="5" t="n"/>
@@ -3043,37 +3092,37 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>d0556bbc1140</t>
+          <t>f3a41b21a780</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>Nonstoquastic Hamiltonians and Quantum Annealing of an Ising Spin Glass</t>
+          <t>Approximate amplitude encoding in shallow parameterized quantum circuits and its application to financial market indicator</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>L. Hormozi; E. W. Brown; G. Carleo; M. Troyer</t>
+          <t>Kouhei Nakaji; Shumpei Uno; Yohichi Suzuki; Rudy Raymond; Tamiya Onodera; Tomoki Tanaka; Hiroyuki Tezuka; Naoki Mitsuda; Naoki Yamamoto</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>10.1103/PhysRevB.95.184416</t>
+          <t>10.48550/arxiv.2103.13211</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>We study the role of Hamiltonian complexity in the performance of quantum annealers. We consider two general classes of annealing Hamiltonians: stoquastic ones, which can be simulated efficiently using the quantum Monte Carlo algorithm, and nonstoquastic ones, which cannot be treated efficiently. We implement the latter by adding antiferromagnetically coupled two-spin driver terms to the traditionally studied transverse-field Ising model, and compare their performance to that of similar stoquastic Hamiltonians with ferromagnetically coupled additional terms. We focus on a model of long-range Ising spin glass as our problem Hamiltonian and carry out the comparison between the annealers by numerically calculating their success probabilities in solving random instances of the problem Hamiltonian in systems of up to 17 spins. We find that, for a small percentage of mostly harder instances, nonstoquastic Hamiltonians greatly outperform their stoquastic counterparts and their superiority persists as the system size grows. We conjecture that the observed improved performance is closely related to the frustrated nature of nonstoquastic Hamiltonians.</t>
+          <t>Efficient methods for loading given classical data into quantum circuits are essential for various quantum algorithms. In this paper, we propose an algorithm called Approximate Amplitude Encoding that can effectively load all the components of a given real-valued data vector into the amplitude of quantum state, while the previous proposal can only load the absolute values of those components. The key of our algorithm is to variationally train a shallow parameterized quantum circuit, using the results of two types of measurement; the standard computational-basis measurement plus the measurement in the Hadamard-transformed basis, introduced in order to handle the sign of the data components. The variational algorithm changes the circuit parameters so as to minimize the sum of two costs corresponding to those two measurement basis, both of which are given by the efficiently-computable maximum mean discrepancy. We also consider the problem of constructing the singular value decomposition entropy via the stock market dataset to give a financial market indicator; a quantum algorithm (the variational singular value decomposition algorithm) is known to produce a solution faster than classical, which yet requires the sign-dependent amplitude encoding. We demonstrate, with an in-depth numerical analysis, that our algorithm realizes loading of time-series of real stock prices on quantum state with small approximation error, and thereby it enables constructing an indicator of the financial market based on the stock prices.</t>
         </is>
       </c>
       <c r="H55" s="5" t="inlineStr">
         <is>
-          <t>arxiv</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="I55" s="5" t="n"/>
@@ -3087,37 +3136,37 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>0e9ded454de6</t>
+          <t>5781ce30742b</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>Financial Technologies and Digital Assets by Using Quantum Computing</t>
+          <t>Alignment between Initial State and Mixer Improves QAOA Performance for Constrained Optimization</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>Efe Büke</t>
+          <t>Zichang He; Ruslan Shaydulin; Shouvanik Chakrabarti; Dylan Herman; Changhao Li; Yue Sun; Marco Pistoia</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>10.62802/knecd502</t>
+          <t>10.1038/s41534-023-00787-5</t>
         </is>
       </c>
       <c r="G56" s="5" t="inlineStr">
         <is>
-          <t>The rapid evolution of financial technologies (FinTech) and digital assets—including cryptocurrencies, decentralized finance (DeFi), and tokenized capital markets—has created an unprecedented need for secure, scalable, and computationally efficient systems. This study examines the transformative potential of quantum computing in reshaping financial technology infrastructures and digital asset ecosystems. Traditional computational models, constrained by classical encryption limits and the exponential growth of financial data, face increasing inefficiencies in handling real-time risk assessment, portfolio optimization, and transaction verification. Quantum computing, with its capacity for superposition, entanglement, and parallel state evaluation, provides novel opportunities to redefine data security, financial modeling, and cryptographic mechanisms in the digital economy. The research explores how quantum algorithms—notably Quantum Approximate Optimization Algorithm (QAOA), Quantum Fourier Transform (QFT), and Grover’s search algorithm—can enhance financial operations such as market forecasting, fraud detection, and asset pricing. Additionally, it investigates quantum-resistant cryptography to safeguard digital asset networks against the vulnerabilities introduced by future quantum decryption capabilities. By integrating hybrid quantum–classical frameworks, this approach enables the development of sustainable, adaptive, and transparent financial systems. The findings highlight quantum computing’s potential to advance financial inclusion, increase transaction speed, and improve systemic resilience. As global financial markets transition toward quantum readiness, the convergence of FinTech and quantum innovation is expected to redefine how digital assets are managed, traded, and secured—marking a paradigm shift toward quantum financial intelligence.</t>
+          <t>Quantum alternating operator ansatz (QAOA) has a strong connection to the adiabatic algorithm, which it can approximate with sufficient depth. However, it is unclear to what extent the lessons from the adiabatic regime apply to QAOA as executed in practice with small to moderate depth. In this paper, we demonstrate that the intuition from the adiabatic algorithm applies to the task of choosing the QAOA initial state. Specifically, we observe that the best performance is obtained when the initial state of QAOA is set to be the ground state of the mixing Hamiltonian, as required by the adiabatic algorithm. We provide numerical evidence using the examples of constrained portfolio optimization problems with both low ($p\leq 3$) and high ($p = 100$) QAOA depth. Additionally, we successfully apply QAOA with XY mixer to portfolio optimization on a trapped-ion quantum processor using 32 qubits and discuss our findings in near-term experiments.</t>
         </is>
       </c>
       <c r="H56" s="5" t="inlineStr">
         <is>
-          <t>semantic_scholar</t>
+          <t>arxiv</t>
         </is>
       </c>
       <c r="I56" s="5" t="n"/>
@@ -3131,27 +3180,27 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>85e216be9ba3</t>
+          <t>b6eb243139d5</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>Optimization of Credit Score Card Portfolio Based on QUBO Model with Quantum Annealing Algorithm</t>
+          <t>Advancements and Applications of Blockchain Technology in Diverse Domains: A Literature Review</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>Feng S.</t>
+          <t>Sejfuli-Ramadani N.</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>10.1109/ICEACE60673.2023.10441858</t>
+          <t>10.1109/MECO62516.2024.10577865</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr"/>
@@ -3171,17 +3220,17 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>b71633628d4e</t>
+          <t>af45f323f9be</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>Quantum Machine Learning: Algorithms and Applications in Quantum Computing</t>
+          <t>Federated Learning: A Survey on Privacy-Preserving Collaborative Intelligence</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>P. Deshmukh; Benjamin Carter</t>
+          <t>Ratun Rahman</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -3189,19 +3238,15 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="F58" s="5" t="inlineStr">
-        <is>
-          <t>10.65521/ijaece.v13i1.81</t>
-        </is>
-      </c>
+      <c r="F58" s="5" t="inlineStr"/>
       <c r="G58" s="5" t="inlineStr">
         <is>
-          <t>Quantum Machine Learning (QML) is an emerging interdisciplinary field that integrates quantum computing with classical machine learning techniques to enhance computational efficiency and solve complex problems beyond the capabilities of classical systems. This paper explores fundamental QML algorithms, including quantum-enhanced data processing, quantum neural networks, and quantum support vector machines. We discuss how quantum speedup can be achieved through quantum parallelism and entanglement, leading to improvements in optimization and data classification tasks. Additionally, we highlight applications of QML in areas such as drug discovery, financial modeling, and cryptography. While current quantum hardware imposes limitations, ongoing advancements in quantum algorithms and error correction techniques suggest a promising future for QML. We conclude with a discussion on the challenges and future directions in the field, emphasizing the need for hybrid quantum-classical approaches and scalable quantum hardware.</t>
+          <t>Federated Learning (FL) has emerged as a transformative paradigm in the field of distributed machine learning, enabling multiple clients such as mobile devices, edge nodes, or organizations to collaboratively train a shared global model without the need to centralize sensitive data. This decentralized approach addresses growing concerns around data privacy, security, and regulatory compliance, making it particularly attractive in domains such as healthcare, finance, and smart IoT systems. This survey provides a concise yet comprehensive overview of Federated Learning, beginning with its core architecture and communication protocol. We discuss the standard FL lifecycle, including local training, model aggregation, and global updates. A particular emphasis is placed on key technical challenges such as handling non-IID (non-independent and identically distributed) data, mitigating system and hardware heterogeneity, reducing communication overhead, and ensuring privacy through mechanisms like differential privacy and secure aggregation. Furthermore, we examine emerging trends in FL research, including personalized FL, cross-device versus cross-silo settings, and integration with other paradigms such as reinforcement learning and quantum computing. We also highlight real-world applications and summarize benchmark datasets and evaluation metrics commonly used in FL research. Finally, we outline open research problems and future directions to guide the development of scalable, efficient, and trustworthy FL systems.</t>
         </is>
       </c>
       <c r="H58" s="5" t="inlineStr">
         <is>
-          <t>semantic_scholar</t>
+          <t>arxiv</t>
         </is>
       </c>
       <c r="I58" s="5" t="n"/>
@@ -3215,17 +3260,17 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>4f371e712f42</t>
+          <t>d83f5f912d08</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>Quantum Artificial Intelligence: Bridging AI and Quantum Computing for Next-Generation Problem Solving</t>
+          <t>Evaluating Classical and Quantum Machine Learning for Credit Card Fraud Detection: Performance and Economic Impact</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>Joseph S.</t>
+          <t>M. Usman Maqbool Bhutta; Abid Mehmood</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -3235,13 +3280,13 @@
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>10.1007/978-3-031-94623-3_34</t>
+          <t>10.1109/cars67163.2025.11337509</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr"/>
       <c r="H59" s="5" t="inlineStr">
         <is>
-          <t>scopus</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="I59" s="5" t="n"/>
@@ -3255,17 +3300,17 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>0ffc0a6b12e2</t>
+          <t>9866ca62fddf</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>Quantum Gated Recurrent Neural Networks</t>
+          <t>Quantum Computing in Embedded Finance</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>Li Y.</t>
+          <t>CA Mohd Swaleh; Dr.N Subbu Krishna Sastry</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -3275,13 +3320,17 @@
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>10.1109/TPAMI.2024.3519605</t>
-        </is>
-      </c>
-      <c r="G60" s="5" t="inlineStr"/>
+          <t>10.20431/2349-0349.1306001</t>
+        </is>
+      </c>
+      <c r="G60" s="5" t="inlineStr">
+        <is>
+          <t>Quantum computing is a new technology that can change many industries, especially finance, by providing much faster and more powerful computing.This journal looks at how quantum computing can be used in embedded finance systems.Embedded finance means adding financial services to non-financial platforms, like making payments directly in a shopping app.This paper aims to explore how quantum computing can enhance such systems by enabling quicker transactions and strengthening security measures.It will also talk about the challenges, like the high cost and complexity of quantum computers.We will review existing research and conduct new studies to understand how quantum computing can improve financial processes.For example, quantum computing can help in risk assessment, fraud detection, and portfolio optimization by solving complex calculations much faster than current computers.This journal aims to show how combining quantum computing with embedded finance can create new opportunities for financial services and make them more efficient and secure.By examining the present advancements in quantum computing and its potential developments, this study seeks to offer meaningful insights to researchers, finance professionals, and technology innovators.</t>
+        </is>
+      </c>
       <c r="H60" s="5" t="inlineStr">
         <is>
-          <t>scopus</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="I60" s="5" t="n"/>
@@ -3295,17 +3344,17 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>44726c2d87a5</t>
+          <t>d24184e88415</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>Blockchain and AI Integration for Autonomous Threat Detection: A New Frontier in Cybersecurity</t>
+          <t>Quantum amplitude estimation with error mitigation for time-evolving probabilistic networks</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>Jayasudha Yedalla</t>
+          <t>M. C. Braun; T. Decker; N. Hegemann; S. Kerstan; C. Maier; J. Ulmanis</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -3313,24 +3362,10 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="F61" s="5" t="inlineStr">
-        <is>
-          <t>10.15680/ijirset.2023.1208094</t>
-        </is>
-      </c>
+      <c r="F61" s="5" t="inlineStr"/>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>The synergist approach between artificial intelligence (AI) and blockchain technologies is transforming
-the sphere of cybersecurity to address the historical issues of data integrity, threat detection, and resilience of the
-system. The predictive analytics and adaptive defense capabilities of AI supplement the decentralized, tamper-resistant
-structure of blockchain, which combine to offer a multi-layered approach to cyber defense. The recent uses cover such
-critical areas as financial systems, medical care, autonomous vehicles, and smart environments, which proves that such
-integration can reduce advanced persistent threat, as well as provide transparency to digital ecosystems.Nonetheless, even with favorable trends, there are still problems, such as scaling issues, interoperability, bias in the
-algorithms, and expensive energy use. In addition, the issues around ethics and governance frame the necessity of crossdisciplinary structures that would provide balance between innovation and accountability. New studies have shown that
-cybersecurity ecosystems in the future will more often implement AI-blockchain technologies with quantum computing
-and next-generation networks that open the way to secure, adaptable, and human- friendly digital agendas. The article
-provides recent trends, applications, and gaps in research, and add to the discussion on anticipate, withstand, recover
-from, and adapt to cyberattacks.</t>
+          <t>We present a method to model a discretized time evolution of probabilistic networks on gate-based quantum computers. We consider networks of nodes, where each node can be in one of two states: good or failed. In each time step, probabilities are assigned for each node to fail (switch from good to failed) or to recover (switch from failed to good). Furthermore, probabilities are assigned for failing nodes to trigger the failure of other, good nodes. Our method can evaluate arbitrary network topologies for any number of time steps. We can therefore model events such as cascaded failure and avalanche effects which are inherent to financial networks, payment and supply chain networks, power grids, telecommunication networks and others. Using quantum amplitude estimation techniques, we are able to estimate the probability of any configuration for any set of nodes over time. This allows us, for example, to determine the probability of the first node to be in the good state after the last time step, without the necessity to track intermediate states. We present the results of a low-depth quantum amplitude estimation on a simulator with a realistic noise model. We also present the results for running this example on the AQT quantum computer system PINE. Finally, we introduce an error model that allows us to improve the results from the simulator and from the experiments on the PINE system.</t>
         </is>
       </c>
       <c r="H61" s="5" t="inlineStr">
@@ -3349,33 +3384,37 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>f5b08b61bcf9</t>
+          <t>8e988d1ef35c</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>QAOA-based MRMR Algorithm for Feature Selection</t>
+          <t>Quantum Monte Carlo Analysis of Exchange and Correlation in the Strongly Inhomogeneous Electron Gas</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>Jiang X.</t>
+          <t>Maziar Nekovee; W. M. C. Foulkes; R. J. Needs</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>10.1145/3603273.3631193</t>
-        </is>
-      </c>
-      <c r="G62" s="5" t="inlineStr"/>
+          <t>10.1103/PhysRevLett.87.036401</t>
+        </is>
+      </c>
+      <c r="G62" s="5" t="inlineStr">
+        <is>
+          <t>We use variational quantum Monte Carlo to calculate the density-functional exchange-correlation hole n_{xc}, the exchange-correlation energy density e_{xc}, and the total exchange-correlation energy E_{xc}, of several electron gas systems in which strong density inhomogeneities are induced by a cosine-wave potential. We compare our results with the local density approximation and the generalized gradient approximation. It is found that the nonlocal contributions to e_{xc} contain an energetically significant component, the magnitude, shape, and sign of which are controlled by the Laplacian of the electron density.</t>
+        </is>
+      </c>
       <c r="H62" s="5" t="inlineStr">
         <is>
-          <t>scopus</t>
+          <t>arxiv</t>
         </is>
       </c>
       <c r="I62" s="5" t="n"/>
@@ -3389,37 +3428,37 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>b89839f3a3c2</t>
+          <t>ccd83b62aeec</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>A Novel Approach to Explainable AI with Quantized Active Ingredients in Decision Making</t>
+          <t>Integrating Quantum Computing and Predictive Analytics and Their Role in Reducing Costs and Achieving Sustainable Development Goals</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>A. M. A. S. D. Alagiyawanna; Asoka Karunananda; Thushari Silva; A. Mahasinghe</t>
+          <t>Ghazi Maan Faisal; Saba Kareem Abbood</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>10.1109/SLAAI-ICAI68534.2025.11318441</t>
+          <t>10.47172/2965-730x.sdgsreview.v5.n03.pe05573</t>
         </is>
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>Artificial Intelligence (AI) systems have shown good success at classifying. However, the lack of explainability is a true and significant challenge, especially in high-stakes domains, such as health and finance, where understanding is paramount. We propose a new solution to this challenge: an explainable AI framework based on our comparative study with Quantum Boltzmann Machines (QBMs) and Classical Boltzmann Machines (CBMs). We leverage principles of quantum computing within classical machine learning to provide substantive transparency around decision-making. The design involves training both models on a binarised and dimensionally reduced MNIST dataset, where Principal Component Analysis (PCA) is applied for preprocessing. For interpretability, we employ gradient-based saliency maps in QBMs and SHAP (SHapley Additive exPlanations) in CBMs to evaluate feature attributions.QBMs deploy hybrid quantum-classical circuits with strongly entangling layers, allowing for richer latent representations, whereas CBMs serve as a classical baseline that utilises contrastive divergence. Along the way, we found that QBMs outperformed CBMs on classification accuracy (83.5% vs. 54%) and had more concentrated distributions in feature attributions as quantified by entropy (1.27 vs. 1.39). In other words, QBMs not only produced better predictive performance than CBMs, but they also provided clearer identification of "active ingredient" or the most important features behind model predictions. To conclude, our results illustrate that quantum-classical hybrid models can display improvements in both accuracy and interpretability, which leads us toward more trustworthy and explainable AI systems.</t>
+          <t>Objectives: The research aims to demonstrate the integration between Quantum Computing (QC) and Predictive Analysis (PA) and their role in reducing costs while achieving Sustainable Development Goals (SDGs). The study addresses the inefficiencies in calculating and measuring product costs under traditional systems and examines how QC and PA can enhance cost reduction and product quality to better meet customer needs. Additionally, the research seeks to strengthen the theoretical framework with practical applications, illustrating how this integration improves a company’s competitive position while promoting social, environmental, and economic sustainability. Methods: The study employs a descriptive analytical approach, focusing on the practical application of QC and PA in cost management. It relies on financial and cost data from a selected company to analyze the impact of integrating QC and PA on cost reduction and sustainable development. The methodology aims to provide empirical evidence supporting the effectiveness of this integration in optimizing resource and energy use. Results: The research findings confirm that integrating QC and PA significantly contributes to cost reduction, which in turn plays a crucial role in achieving SDGs. The study highlights how this integration enhances efficiency in resource and energy utilization, identifies weaknesses in traditional cost systems, and supports the transition toward sustainable manufacturing. By improving production processes and minimizing waste, the application of QC and PA fosters innovation in sustainable product development. Conclusion: The study underscores the importance of integrating QC and PA in modern cost management strategies to achieve sustainability objectives. Encouraging innovative local manufacturing through enhanced efficiency and resource optimization supports the transition toward sustainable production. The findings suggest that companies adopting QC and PA can improve their competitive edge, reduce costs, and contribute to environmental and economic sustainability, ultimately aligning with global sustainable development goals.</t>
         </is>
       </c>
       <c r="H63" s="5" t="inlineStr">
         <is>
-          <t>arxiv</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="I63" s="5" t="n"/>
@@ -3433,17 +3472,17 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>7ede4c3f9492</t>
+          <t>60f7527318ef</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>Quantum State Preparation for Probability Distributions with Reflection Symmetry Using Matrix Product States</t>
+          <t>Impact of quantum technologies on innovation processes in the global economy</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>Yuichi Sano; Ikko Hamamura</t>
+          <t>Роман КОРЖ</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
@@ -3453,17 +3492,17 @@
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>10.1103/yqj3-hyxv</t>
+          <t>10.36887/2415-8453-2024-2-14</t>
         </is>
       </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
-          <t>Quantum circuits for loading probability distributions into quantum states are essential subroutines in quantum algorithms used in physics, finance engineering, and machine learning. The ability to implement these with high accuracy in low-depth quantum circuits is a critical issue. We propose a novel quantum state preparation method for probability distribution with reflection symmetry using matrix product states. By considering reflection symmetry, our method reduces the entanglement of probability distributions and improves the accuracy of approximations by matrix product states. As a result, we improved the accuracy by two orders of magnitude over existing methods using matrix product states. Our approach, characterized by linear scalability with qubit count, is highly advantageous for noisy quantum devices. Also, our demonstration results reveal that the approximation accuracy in tensor networks depends heavily on the bond dimension, with minimal reliance on the number of qubits. Our method is demonstrated for a normal distribution encoded into 10 and 20 qubits on a real quantum processor.</t>
+          <t>The article examines the impact of quantum technologies on innovation processes in the global economy. It analyzes the critical aspects of integrating quantum technologies in various sectors of the economy, particularly in the financial, health care, production, and IT spheres. Theoretical models and empirical data confirming how quantum technologies can accelerate innovation processes, increase research efficiency, and create new economic opportunities are considered. The article also provides practical recommendations for strategic planning and management of innovation processes in the conditions of the quantum revolution. Special attention is paid to the importance of an interdisciplinary approach and cooperation between business and the state. The author noted that the modern economy is on the threshold of a new era, where quantum technologies play a decisive role, which represents a new class of tools capable of radically changing traditional approaches to data processing, security, and computing. Quantum computers, quantum cryptography and quantum communication open opportunities for the economy that can accelerate the development of new materials, optimize logistics chains and increase the level of data security. At the same time, the article highlights the need to develop global standards in the field of quantum technologies. The results of the research will contribute to a better understanding of the potential of quantum technologies to stimulate innovation and increase the competitiveness of the economy. Keywords: quantum technologies, global economy, innovation processes, quantum cryptography, quantum computing, quantum modeling, quantum communication, economic models, quantum algorithms, cyber security, logistics optimization, risk management, economic growth, financial markets, health care, production, quantum networks, development strategies, digital economy, technological revolution.</t>
         </is>
       </c>
       <c r="H64" s="5" t="inlineStr">
         <is>
-          <t>arxiv</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="I64" s="5" t="n"/>
@@ -3477,28 +3516,32 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>aa1d3ecffb05</t>
+          <t>19660db0b2c6</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>Dynamical replica analysis of quantum annealing</t>
+          <t>Obstacles to quantum annealing in a planar embedding of XORSAT</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>ACC Coolen; T Nikoletopoulos</t>
+          <t>Pranay Patil; Stefanos Kourtis; Claudio Chamon; Eduardo R. Mucciolo; Andrei E. Ruckenstein</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
         <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="F65" s="5" t="inlineStr"/>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="F65" s="5" t="inlineStr">
+        <is>
+          <t>10.1103/PhysRevB.100.054435</t>
+        </is>
+      </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>Quantum annealing aims to provide a faster method for finding the minima of complicated functions, compared to classical computing, so there is an increasing interest in the relaxation dynamics of quantum spin systems. Moreover, it is known that problems in quantum annealing caused by first order phase transitions can be reduced via appropriate temporal adjustment of control parameters, aimed at steering the system away from local minima. To do this optimally, it would be helpful to predict the evolution of the system at the level of macroscopic observables. Solving the dynamics of a quantum ensemble is nontrivial, as it requires modelling not just the quantum spin system itself but also its interaction with the environment, with which it exchanges energy. An interesting alternative approach to the dynamics of quantum spin systems was proposed about a decade ago. It involves creating a stochastic proxy dynamics via the Suzuki-Trotter mapping of the quantum ensemble to a classical one (the quantum Monte Carlo method), and deriving from this new dynamics closed macroscopic equations for macroscopic observables, using the dynamical replica method. In this chapter we give an introduction to this approach, focusing on the ideas and assumptions behind the derivations, and on its potential and limitations.</t>
+          <t>We introduce a planar embedding of the k-regular k-XORSAT problem, in which solutions are encoded in the ground state of a classical statistical mechanics model of reversible logic gates arranged on a square grid and acting on bits that represent the Boolean variables of the problem. The special feature of this embedding is that the resulting model lacks a finite-temperature phase transition, thus bypassing the first-order thermodynamic transition known to occur in the random graph representation of XORSAT. In spite of this attractive feature, the thermal relaxation into the ground state displays remarkably slow glassy behavior. The question addressed in this paper is whether this planar embedding can afford an efficient path to solution of k-regular k-XORSAT via quantum adiabatic annealing. We first show that our model bypasses an avoided level crossing and consequent exponentially small gap in the limit of small transverse fields. We then present quantum Monte Carlo results for our embedding of the k-regular k-XORSAT that strongly support a picture in which second-order and first-order transitions develop at a finite transverse field for k = 2 and k = 3, respectively. This translates into power-law and exponential dependences in the scaling of energy gaps with system size, corresponding to times-to-solution which are, respectively, polynomial and exponential in the number of variables. We conclude that neither classical nor quantum annealing can efficiently solve our reformulation of XORSAT, even though the original problem can be solved in polynomial time by Gaussian elimination.</t>
         </is>
       </c>
       <c r="H65" s="5" t="inlineStr">
@@ -3517,22 +3560,18 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>4155c3f9f894</t>
+          <t>c105c8df3d91</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>AI-Driven Predictive Threat Detection and Cyber Risk Mitigation: A Survey</t>
-        </is>
-      </c>
-      <c r="D66" s="5" t="inlineStr">
-        <is>
-          <t>Sarfraz M.</t>
-        </is>
-      </c>
+          <t>14th Workshop on Computational Optimization, WCO 2021</t>
+        </is>
+      </c>
+      <c r="D66" s="5" t="inlineStr"/>
       <c r="E66" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F66" s="5" t="inlineStr"/>
@@ -3553,37 +3592,33 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>07ffc6d017ba</t>
+          <t>38fb4cff88e5</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>Interatomic force from neural network based variational quantum Monte Carlo</t>
+          <t>Quantum-assisted support vector regression</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>Yubing Qian; Weizhong Fu; Weiluo Ren; Ji Chen</t>
+          <t>Dalal A.</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>10.1063/5.0112344</t>
-        </is>
-      </c>
-      <c r="G67" s="5" t="inlineStr">
-        <is>
-          <t>Accurate ab initio calculations are of fundamental importance in physics, chemistry, biology, and materials science, which have witnessed rapid development in the last couple of years with the help of machine learning computational techniques such as neural networks. Most of the recent efforts applying neural networks to ab initio calculation have been focusing on the energy of the system. In this study, we take a step forward and look at the interatomic force obtained with neural network wavefunction methods by implementing and testing several commonly used force estimators in variational quantum Monte Carlo (VMC). Our results show that neural network ansatz can improve the calculation of interatomic force upon traditional VMC. The relation between the force error and the quality of neural network, the contribution of different force terms, and the computational cost of each term are also discussed to provide guidelines for future applications. Our work demonstrates that it is promising to apply neural network wavefunction methods in simulating structures/dynamics of molecules/materials and provide training data for developing accurate force fields.</t>
-        </is>
-      </c>
+          <t>10.1007/s11128-025-04674-0</t>
+        </is>
+      </c>
+      <c r="G67" s="5" t="inlineStr"/>
       <c r="H67" s="5" t="inlineStr">
         <is>
-          <t>arxiv</t>
+          <t>scopus</t>
         </is>
       </c>
       <c r="I67" s="5" t="n"/>
@@ -3597,37 +3632,33 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>4b5f87ce3013</t>
+          <t>cf8ff69f1966</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>Почему квантовые вычисления– это будущее искусственного интеллекта?</t>
+          <t>Methods for Solving the Markowitz Portfolio Optimization Problem</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>Ф.Т. Адылова</t>
+          <t>Miquel Noguer I Alonso</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>10.71310/pcam.2_64.2025.08</t>
-        </is>
-      </c>
-      <c r="G68" s="5" t="inlineStr">
-        <is>
-          <t>Quantum technologies are transforming industries by harnessing the principles of quantum mechanics. These innovations promise to revolutionize computing, communi cations, sensing, cryptography, and healthcare, offering solutions previously considered unattainable. Quantum computing is changing the way complex problems are solved: un like classical computers that use bits to represent information in binary code, quantum computers exploit the laws of quantum physics to perform calculations beyond the reach of even the most advanced classical systems. Quantum algorithms can efficiently solve logistical challenges, optimize global supply chains, accelerate risk analysis, and enhance decision-making in complex financial models. Quantum computers enable unprecedentedly fast simulation of molecular interactions, expediting drug discovery, enabling per sonalized medicine, and elevating disease diagnostics to a new level. All these advances lay the foundation for the future development of artificial intelligence, the prospects of which are discussed in this paper.</t>
-        </is>
-      </c>
+          <t>10.2139/ssrn.4939293</t>
+        </is>
+      </c>
+      <c r="G68" s="5" t="inlineStr"/>
       <c r="H68" s="5" t="inlineStr">
         <is>
-          <t>semantic_scholar</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="I68" s="5" t="n"/>
@@ -3641,32 +3672,32 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>c4827b5793db</t>
+          <t>cb87dd92737a</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>Configuration Space Temporality: A Unified Theory of Time as Energy-Driven State Transition in Configuration Space — with the Transition Potential, Energy Unification via Partial Traces, Cascade Dynamics, Derivative Structure, First Quantitative Calculation, and Experimental Predictions</t>
+          <t>Quantum-Inspired-AI Resource Allocator for Social Impact Optimization</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>Frederic David Blum</t>
+          <t>Daniel T G N Maciel; Arturo Alejandro Zavala Zavala; Marcos Vinícius da Silva Bueno; Luís Paulo Jauer; Helena Palú Desidério; Laís Ribeiro Pereira</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F69" s="5" t="inlineStr">
         <is>
-          <t>10.5281/zenodo.18748310</t>
+          <t>10.5281/zenodo.18307983</t>
         </is>
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
-          <t>Title: Configuration Space Temporality: A Unified Theory of Time as Energy-Driven State Transition in Configuration Space — with the Transition Potential, Energy Unification via Partial Traces, Cascade Dynamics, Derivative Structure, First Quantitative Calculation, and Experimental Predictions Authors: Blum, Frederic David (Independent Researcher, Catalyst AI, Tel Aviv, Israel) Description: We propose Configuration Space Temporality (CST), a unified theory in which time is neither a geometric coordinate nor a background parameter, but an emergent property of energy-driven transitions between unique physical configurations. The theory rests on three axioms: (1) every temporal instant corresponds to a unique configuration of all physical degrees of freedom; (2) every transition between configurations requires energy; and (3) the rate of transition is bounded by the speed of light c. The primitive object of the theory is the Transition Potential Φ(C₁, C₂) — a functional defined on pairs of configurations measuring the total cost of the transition C₁ → C₂. Unlike the energy function E(C) of standard physics, which is a property of a single state, Φ is a property of a pair of states, encoding asymmetry (the arrow of time), path-dependence (hysteresis), and non-locality (entanglement) in its fundamental structure. The Tensor of Transition G_ij — the local curvature of Φ — replaces the Hessian as the metric tensor of configuration space, but is now a derived object rather than the foundation. The energy function, the forces, the metric, and time itself all emerge from Φ. The paper makes eight central contributions. First, we establish Φ as the foundational object and derive the Tensor of Transition G_ij = ∂²Φ/∂δq_i∂δq_j as its local curvature. The configuration metric ds² = Σ G_ij dq_i dq_j recovers all known physical metrics — Minkowski, Schwarzschild, Fisher information — as projections onto specific subspaces. Energy is reinterpreted as a derived quantity: E(C) = ⟨Φ(C, C')⟩ over neighboring configurations, inverting the standard ontology from "energy is fundamental, transitions follow" to "transitions are fundamental, energy follows." Second, we introduce the Derivative Structure of Φ: every known law of physics is a partial derivative ∂Φ/∂q_i (one parameter varied in isolation) — special relativity is ∂Φ/∂v, general relativity is ∂Φ/∂Φ_grav, thermodynamics is ∂Φ/∂S, quantum mechanics is ∂Φ/∂ψ, nuclear physics is ∂Φ/∂q_nucl, electromagnetism is ∂Φ/∂(E,B). The entire history of physics is the measurement of single-parameter derivatives. The cross-derivatives ∂²Φ/∂q_i∂q_j between different physical sectors (gravity × nuclear structure, velocity × spin, temperature × quantum state) have never been systematically measured and constitute predictions unique to CST. The historical analogy is Maxwell's unification: Faraday discovered the first cross-derivative between electricity and magnetism, which implied electromagnetic waves. CST predicts that cross-derivatives between gravity, nuclear physics, and quantum mechanics exist and contain new physics. Third, we develop the Critique of Temporal Universality. What humans call "time" is the variation of a chosen parameter (cesium-133 hyperfine transition) declared universal. Newton said variation is universal and absolute. Einstein showed it depends on velocity and gravity, but maintained universality between parameters at the same point (all colocalized clocks agree). CST shows this universality is false: each parameter has its own G-eigenvalue, and colocalized clocks using different atomic transitions should drift relative to each other at precision ~10⁻¹⁸ — a testable deviation from the equivalence principle as applied to clocks. The fundamental "unit" of CST is not the second but the transition cost Φ. Fourth, we present the First Quantitative Calculation of CST: the derivation of the Tensor of Transition G for a superconducting transmon qubit. The transmon configuration space is two-dimensional (superconducting phase φ, Cooper pair number n), with G_φφ = E_J (Josephson energy = phase stiffness) and G_nn = 8E_C (charging energy = charge stiffness). The transition energy E₀₁ = √(G_φφ · G_nn) − ¼G_nn = √(8E_J·E_C) − E_C recovers the known transmon spectrum from CST's geometric structure. For typical IBM parameters (E_J = 15 GHz, E_C = 0.3 GHz), CST predicts E₀₁ = 5.70 GHz, within the measured range of 4.5–5.5 GHz. We extend to two coupled transmons and derive a CST-specific prediction: the entanglement gate energy scales as E_gate ∝ g·√(E_J,A/E_J,B) — a G-eigenvalue ratio dependence verifiable on existing IBM and Google hardware by flux-tuning E_J while keeping coupling g constant. Fifth, we introduce Cascade Dynamics — chain reactions in configuration space. When parameter q_i transitions, it modifies the local landscape of Φ for coupled parameters via off-diagonal G-elements, potentially triggering secondary transitions that propagate through Γ. The cascade propagation condition is k_BT &gt; G_jj + Σ_i G_ij·Δq_i. We define the Cascade Number κ — the mean number of secondary transitions per primary transition — which classifies all physical phenomena: κ &lt; 1 (sub-critical: inert matter, dissipation, equilibrium), κ = 1 (critical: life, brain function, homeostasis, controlled nuclear reactors), κ &gt; 1 (super-critical: nuclear explosions, supernovae, the Big Bang). Life is the system that self-regulates to maintain κ ≈ 1; disease is departure from criticality (cancer = κ &gt; 1 in cell division; epilepsy = κ &gt; 1 in neural subspace; death = κ → 0 globally). Cascades operate at every scale: nuclear (fission chains), chemical (metabolic pathways), geological (erosion landscapes), biological (photon → chlorophyll → ATP → thought), and civilizational (agriculture → urbanization → industrialization → information age). Sixth, we prove the Energy Unification Equation: all forms of energy are partial traces of the single tensor G over different subspaces of Γ: E_a(C) = ½ Tr_{Γ_a}[G(C)]. Kinetic, gravitational, rest mass, binding, thermal, electromagnetic, and correlation energies are seven projections of one object. E = mc² acquires its deepest interpretation as mc² = ½ Tr_{Γ_identity}[G] — mass is half the trace of G over identity parameters (mass, spin, charge, flavor, color). Energy conservation follows from trace invariance of G under change of basis, not from Noether's theorem — eliminating the circularity of deriving conservation from temporal symmetry when time is emergent. The arrow of time is A(C₁,C₂) = Φ(C₂,C₁) − Φ(C₁,C₂), derived from Φ's intrinsic asymmetry. Off-diagonal elements of G encode energy conversions (fission, absorption, beta decay). The Wheeler-DeWitt equation becomes Tr_Γ[G] = 0 globally: the universe is a zero-trace system. Seventh, we demonstrate that Einstein's special and general relativity are single-parameter projections of CST: special-relativistic time dilation corresponds to ∂Φ/∂v, yielding τ = 1 − 1/γ; general-relativistic dilation corresponds to ∂Φ/∂Φ_grav, yielding τ = 1 − √(g₀₀). GPS provides ~10⁹ verifications/second, with linearity of SR+GR to ~10⁻¹³ bounding cross-terms. Entanglement is non-factorization of Φ on joint configuration space: Φ(C_A⊗C_B, C'A⊗C'B) = Φ_A + Φ_B + Φ_AB^corr, with decoherence as geometric phase transition. Force coupling constants are eigenvalue ratios of G: α_i = Tr(G|{Γ_i})/Tr(G|{Γ_total}), making the 10³⁸ hierarchy a spectral property of one tensor. Eighth, we derive comprehensive consequences of CST's adoption. For physics: time travel structurally impossible (past is not a location); hierarchy problem transformed (eigenvalue ratio, not fine-tuning); quantum gravity path (reconstruct G, not "quantize gravity"); measurement demystified (collapse = transition dispersing correlation energy); thousands of laws unified (all projections of Φ). For cosmology: Big Bang as maximum-κ cascade; heat death as κ → 0 (literal end of time); dark energy as diagonal G-term. For biology: life as percolation transition in chemical Γ (κ reaching 1); evolution as directed trajectory toward wider subspace access. For consciousness: Γ-navigation system modeling its own position, enabling trajectory simulation and selection. For technology: quantum computing as Γ-trajectory optimization; materials science as G-spectral engineering; medicine as cascade restoration (κ → 1). For new discoveries: cross-sector transition spectra, inter-force resonances, isotope-dependent gravitational response, cascade critical exponents. We present eight falsifiable experimental predictions: (1) non-linear sigmoidal displacement response; (2) configurational hysteresis from path-dependent Φ; (3) coherence phase transition at percolation threshold; (4) cross-derivative detection between physical sectors (gravity × atomic structure via strontium/ytterbium optical clocks at 10⁻¹⁸; gravity × nuclear decay via isotope-dependent rates; velocity × spin via synchrotron precession); (5) entanglement energy scaling with G-eigenvalue geometry; (6) force coupling ratios from G-spectrum; (7) cascade number measurement in quantum many-body systems; (8) transmon G-ratio scaling of entanglement gate energy. Nine explicit falsification criteria are provided. We identify extensive retrospective evidence: spin echo (Hahn, 1950), quantum error correction thresholds, time crystals (2017), Loschmidt echo, GPS (~10⁹ verifications/second), nuclear reactors (engineered κ = 1), and stellar nucleosynthesis. The framework dissolves classical temporal paradoxes without additional postulates, connects to Wheeler-DeWitt quantum gravity and the Page-Wootters mechanism, and unifies nuclear physics, thermodynamics, relativity, quantum mechanics, quantum information theory, and cosmology within a single object: the Transition Potential Φ and its derived Tensor of Transition G. This work was developed with AI assistance from Claude Opus 4.6 (Thinking) by Anthropic. Keywords: configura</t>
+          <t>Quantum-Inspired Resource Allocation for Social Impact Optimization - Technological Extension Product This technology applies quantum-inspired optimization algorithms (QAOA-inspired classical methods) to solve NP-hard resource allocation problems in public policy. It supports evidence-based decision-making by balancing efficiency, equity, and social impact in development programs. Key Features: QAOA-inspired classical optimization with mixer and cost layers Multi-objective optimization (efficiency vs equity trade-offs) Fairness-aware algorithmic selection with constraint satisfaction Pareto frontier generation for policy scenario analysis Performance benchmarking against classical greedy algorithms AI-ready architecture for enhanced impact forecasting Application Domains: Regional development funds, emergency response allocation, infrastructure investment prioritization, social program portfolio selection. Results/Impact: Enables systematic, transparent allocation of scarce public resources with measurable improvements over traditional heuristics. Demonstrated 14-18% average improvement in social impact metrics versus greedy baselines in simulation studies. Technology Readiness Level (TRL): 5-6. Event Context: Developed as part of ENECOMAT XVIII (2025) Technological Extension initiative. This represents open technology transfer and process development, distinct from traditional academic publications. Development Status: Models under development. Requires validation with real-world policy datasets and stakeholder feedback for production deployment. Part of this content may have been AI-generated under supervision and validation by the authors.</t>
         </is>
       </c>
       <c r="H69" s="5" t="inlineStr">
@@ -3685,17 +3716,17 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>d488eff10f7f</t>
+          <t>be40b988351f</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>Quantum Computing Algorithms and Real-World Applications</t>
+          <t>Cybersecurity Measures in Financial Institutions Protecting Sensitive Data from Emerging Threats and Vulnerabilities</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>Huang L.</t>
+          <t>Kiran Kumar Boorugupalli; Aparna Kulkarni; Amala Suzana; Diwakaran M; Sivakumar Ponnusamy; Senthil Kumar S</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
@@ -3705,13 +3736,17 @@
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>10.1007/978-981-96-0208-7_31</t>
-        </is>
-      </c>
-      <c r="G70" s="5" t="inlineStr"/>
+          <t>10.1051/itmconf/20257602002/pdf</t>
+        </is>
+      </c>
+      <c r="G70" s="5" t="inlineStr">
+        <is>
+          <t>As financial institutions increasingly digitized, they are up against a growing suite of cybersecurity threats such as ransomware, cryptojacking, AI-enabled phishing, and quantum computing attacks. Other research work and government reports reinforce general cybersecurity concerns but are not technical or applied. They do not cater specifically to financial institutions. To fill these gaps, this study introduces an AI-based cybersecurity framework focusing on effective protection of financial data, compliance with regulations, and minimizing time for detecting threats.Building upon the existing research and drawing on best practices from both the financial and technology sectors, this paper presents a promising new framework that combines machine learning-driven methods for real-time fraud detection, the use of blockchain technology to ensure transaction integrity, and quantum-resistant and decentralized encryption methods to protect sensitive financial information from cyber threats. Whereas other research focuses on broad, high-level strategies, this research offers a step-by-step technical roadmap to zero-trust security, anomaly detection and automated cybersecurity responses. It also analyzes actual cyberattacks on financial institutions and develops predictive models to proactively reduce risks.To tackle on email-based financial scams, the research presents a deep learning-embedded BERT paradigm integrated with NLP to enhance phishing identification. It also introduces a biometric security mechanism that ensures that sensitive user data is unalterable, and accessible only to authorized parties. Cybersecurity measures for integrated financial IoT are proposed contribution to the NIST Cybersecurity Framework, including the prevention of cyber threats for automatic teller machines, mobile banking, and electronic payment systems. Challenges of compliance with GDPR, PCI-DSS and ISO 27001 are also addressed.Based on empirically-testing real-time financial datasets, the framework shows improved robustness to cyberattacks. These findings lay the groundwork for the future of cybersecurity, helping financial institutions stay secure and adaptive in the face of evolving cyber threats.</t>
+        </is>
+      </c>
       <c r="H70" s="5" t="inlineStr">
         <is>
-          <t>scopus</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="I70" s="5" t="n"/>
@@ -3725,34 +3760,30 @@
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>650b092b068d</t>
+          <t>8ab2b3dd3f1a</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>Amplitude Reordering Accelerates the Adaptive Variational Quantum Eigensolver Algorithms</t>
+          <t>A Comparative Study of Quantum Computing Development in Asia: Technical Foundations, Investment Dynamics, and Economic Implications</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>Zhihao Lan; WanZhen Liang</t>
+          <t>Harjinder Singh</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>10.1021/acs.jctc.2c00403</t>
-        </is>
-      </c>
-      <c r="G71" s="5" t="inlineStr">
-        <is>
-          <t>The variational quantum eigensolver (VQE) algorithm can simulate the chemical systems such as molecules in the noisy-intermediate-scale quantum devices and shows promising applications in quantum chemistry simulations. The accuracy and computational cost of the VQE simulations are determined by the underlying ansatz. Therefore, the most important issue is to generate a compact and accurate ansatz, which requires a shallower parametric quantum circuit and can achieve an acceptable accuracy. The newly developed adaptive algorithms (AAs) such as the adaptive derivative-assembled pseudo-Trotter VQE (ADAPT-VQE) can solve this issue via generating compact and accurate ansatzes. However, these AAs show very low computational efficiency because they require a large number of additional measurements. Here we propose an amplitude reordering (AR) strategy to accelerate the promising but expensive AAs by adding operators in a "batched" fashion in a way that their order is still quasi-optimal. We first introduce the AR method into ADAPT-VQE and build the AR-ADAPT-VQE algorithm. We then endow the energy-sorting VQE (ES-VQE) algorithm with the adaptive feature and introduce the AR into AES-VQE to form the AR-AES-VQE algorithm. To demonstrate the performance of these algorithms, we calculate the dissociation curves of three small molecules, LiH, linear BeH&lt;sub&gt;2&lt;/sub&gt;, and linear H&lt;sub&gt;6&lt;/sub&gt;, by using (AR-)ADAPT-VQE and (AR-)AES-VQE algorithms. It is found that all of the AR-equipped AAs (AR-AAs) can significantly reduce the number of iterations and subsequently accelerate the calculations with a speedup of up to more than ten times without the obvious loss of accuracy. The final ansatz generated by the AR-AAs not only avoids extra circuit depth but also maintains the computational accuracy; sometimes the AR-AAs even outperforms their original counterparts.</t>
-        </is>
-      </c>
+          <t>10.2139/ssrn.5781042</t>
+        </is>
+      </c>
+      <c r="G71" s="5" t="inlineStr"/>
       <c r="H71" s="5" t="inlineStr">
         <is>
           <t>openalex</t>
@@ -3769,17 +3800,17 @@
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>29c50ea45ebe</t>
+          <t>48c87934ef61</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>Quantum Computing Cryptography: A Systematic Review of Innovations, Applications, Challenges, and Algorithms</t>
+          <t>Enhancing Quantum Expectation Values via Exponential Error Suppression and CVaR Optimization</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>Peter Maitireni; Vusumuzi Ncube; B. Ndlovu; Thando Sibanda</t>
+          <t>Touheed Anwar Atif; Reuben Blake Tate; Stephan Eidenbenz</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
@@ -3787,19 +3818,15 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="F72" s="5" t="inlineStr">
-        <is>
-          <t>10.63158/journalisi.v7i4.1331</t>
-        </is>
-      </c>
+      <c r="F72" s="5" t="inlineStr"/>
       <c r="G72" s="5" t="inlineStr">
         <is>
-          <t>This study explores how to build quantum-resistant systems to safeguard digital infrastructure in the post-quantum era by uncovering the innovations, applications, algorithms, and challenges of Quantum Computing cryptography. Utilizing the Preferred Reporting Items for Systematic Reviews and Meta-Analyses approach a search was conducted across the following databases for the years 2021–2025: PubMed, IEEE Xplore, ScienceDirect, SpringerLink, and Google Scholar. We shortlisted 15 studies from 519 screened articles for a comprehensive evaluation based on their relevance. Findings show strong adoption in finance, healthcare, IoT, cybersecurity, and e-government, with lattice-based PQC emerging as the most dominant cryptographic family, followed by QKD and hybrid PQC–QKD models. The review highlights key obstacles, including transition complexity, lack of global standards, high implementation costs, and integration difficulty. The study contributes by providing the first sector-aligned synthesis of innovations, identifying algorithmic trends, and mapping global research disparities through a conceptual model. It also presents a structured set of future research directions to guide policymakers, cryptographers, and practitioners preparing for quantum-enabled threats.</t>
+          <t>Precise quantum expectation values are crucial for quantum algorithm development, but noise in real-world systems can degrade these estimations. While quantum error correction is resource-intensive, error mitigation strategies offer a practical alternative. This paper presents a framework that combines Virtual Channel Purification (VCP) technique with Conditional Value-at-Risk (CVaR) optimization to improve expectation value estimations in noisy quantum circuits. Our contributions are twofold: first, we derive conditions to compare CVaR values from different probability distributions, offering insights into the reliability of quantum estimations under noise. Second, we apply this framework to VCP, providing analytical bounds that establish its effectiveness in improving expectation values, both when the overhead VCP circuit is ideal (error-free) and when it adds additional noise. By introducing CVaR into the analysis of VCP, we offer a general noise-characterization method that guarantees improved expectation values for any quantum observable. We demonstrate the practical utility of our approach with numerical examples, highlighting how our bounds guide VCP implementation in noisy quantum systems.</t>
         </is>
       </c>
       <c r="H72" s="5" t="inlineStr">
         <is>
-          <t>semantic_scholar</t>
+          <t>arxiv</t>
         </is>
       </c>
       <c r="I72" s="5" t="n"/>
@@ -3813,17 +3840,17 @@
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>89418437f51c</t>
+          <t>6e39c2d1ab16</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>Quantum-Enhanced Forecasting: Leveraging Quantum Gramian Angular Field and CNNs for Stock Return Predictions</t>
+          <t>A user-centric quantum benchmarking test suite and evaluation framework</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>Zhengmeng Xu; Yujie Wang; Xiaotong Feng; Yilin Wang; Yanli Li; Hai Lin</t>
+          <t>Liu W.B.</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
@@ -3831,15 +3858,15 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="F73" s="5" t="inlineStr"/>
-      <c r="G73" s="5" t="inlineStr">
-        <is>
-          <t>We propose a time series forecasting method named Quantum Gramian Angular Field (QGAF). This approach merges the advantages of quantum computing technology with deep learning, aiming to enhance the precision of time series classification and forecasting. We successfully transformed stock return time series data into two-dimensional images suitable for Convolutional Neural Network (CNN) training by designing specific quantum circuits. Distinct from the classical Gramian Angular Field (GAF) approach, QGAF's uniqueness lies in eliminating the need for data normalization and inverse cosine calculations, simplifying the transformation process from time series data to two-dimensional images. To validate the effectiveness of this method, we conducted experiments on datasets from three major stock markets: the China A-share market, the Hong Kong stock market, and the US stock market. Experimental results revealed that compared to the classical GAF method, the QGAF approach significantly improved time series prediction accuracy, reducing prediction errors by an average of 25% for Mean Absolute Error (MAE) and 48% for Mean Squared Error (MSE). This research confirms the potential and promising prospects of integrating quantum computing with deep learning techniques in financial time series forecasting.</t>
-        </is>
-      </c>
+      <c r="F73" s="5" t="inlineStr">
+        <is>
+          <t>10.1007/s11128-023-04154-3</t>
+        </is>
+      </c>
+      <c r="G73" s="5" t="inlineStr"/>
       <c r="H73" s="5" t="inlineStr">
         <is>
-          <t>arxiv</t>
+          <t>scopus</t>
         </is>
       </c>
       <c r="I73" s="5" t="n"/>
@@ -3853,17 +3880,17 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>82ed0c8b3a0d</t>
+          <t>79728b194d1a</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>Threat Intelligence Platform Empowered by Generative Ai with Quantum-Security</t>
+          <t>A state-of-the-art review on battery cell balancing strategies</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>DR. K. Maharajan; Mugeshwaran K; Dumala Nithish; Dinesh S; Uday N</t>
+          <t>Ashkan Safari; Arman Oshnoei; Hoda Sorouri; Frede Blaabjerg</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
@@ -3873,17 +3900,13 @@
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>10.47392/irjaeh.2025.0190</t>
-        </is>
-      </c>
-      <c r="G74" s="5" t="inlineStr">
-        <is>
-          <t>The rapid evolution in types of cyber threats and anticipated threats through quantum computing requires a change in cybersecurity strategy. The traditional Threat Intelligence Platforms (TIPs) usually use static rule-based systems and reactive measures to provide real-time solutions to address attacks that are either emerging or sophisticated. This paper proposes a next-generation Threat Intelligence Platform (TIP) incorporating Generative Artificial Intelligence (GenAI) to enable predictive threat scenario modelling, anomaly detection, and autonomous mitigation strategies using quantum-security mechanisms to provide very-long-term cryptographic resilience. The GenAI engine provides live threat simulation, adequate situational awareness, and improved anomaly detection accuracy by large-scale cyber datasets. At the same time, the Quantum-Security Module consists of post-quantum cryptographic (PQC) algorithms, such as lattice-based, hash-based, and multivariate cryptosystems. All of these seek to plug holes caused by quantum adversaries. The suggested TIP architecture is a multi-layered one that possesses a data ingestion layer, an AI-driven threat analytics, a quantum-resilient cryptographic framework, and an interactive visualization dashboard. It delineates an architectural framework, important points of innovation, and potential applications across the main sectors of finance, healthcare, defence, and enterprise cybersecurity. Additionally, the research presents a high-level strategic roadmap for the deployment of GenAI-intensified TIPs with quantum-resilient security, scalable and adaptable for future-proof data integrity. Addressing AI-enabled predictive security features and post-quantum cryptographic resilience, the research offers future-proof cybersecurity as an answer to continuous changes in digital threats.</t>
-        </is>
-      </c>
+          <t>10.1007/s43937-025-00086-4</t>
+        </is>
+      </c>
+      <c r="G74" s="5" t="inlineStr"/>
       <c r="H74" s="5" t="inlineStr">
         <is>
-          <t>semantic_scholar</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="I74" s="5" t="n"/>
@@ -3897,37 +3920,37 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>4e182eab7186</t>
+          <t>f191fdf66983</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>Leveraging Off-the-Shelf Silicon Chips for Quantum Computing</t>
+          <t>Next-Generation Digital Ecosystems: AI, Quantum Finance, and the Reinvention of Public Infrastructure</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>John Michniewicz; M. S. Kim</t>
+          <t>Murali Krishna Pasupuleti</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>10.1063/5.0207162</t>
+          <t>10.62311/nesx/rp05331</t>
         </is>
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>There is a growing demand for quantum computing across various sectors, including finance, materials and studying chemical reactions. A promising implementation involves semiconductor qubits utilizing quantum dots within transistors. While academic research labs currently produce their own devices, scaling this process is challenging, requires expertise, and results in devices of varying quality. Some initiatives are exploring the use of commercial transistors, offering scalability, improved quality, affordability, and accessibility for researchers. This paper delves into potential realizations and the feasibility of employing off-the-shelf commercial devices for qubits. It addresses challenges such as noise, coherence, limited customizability in large industrial fabs, and scalability issues. The exploration includes discussions on potential manufacturing approaches for early versions of small qubit chips. The use of state-of-the-art transistors as hosts for quantum dots, incorporating readout techniques based on charge sensing or reflectometry, and methods like electron shuttling for qubit connectivity are examined. Additionally, more advanced designs, including 2D arrays and crossbar or DRAM-like access arrays, are considered for the path toward accessible quantum computing.</t>
+          <t>Abstract: This research paper investigates the convergence of artificial intelligence (AI), quantum technologies, and digital infrastructure as the foundation of next-generation digital ecosystems. Focusing on their transformative roles in finance, governance, and public service delivery, the study leverages statistical modeling, entropy-centrality analysis, and predictive simulations to assess the impact of AI integration and quantum readiness on infrastructure performance. The findings reveal that both AI and quantum technologies significantly enhance operational efficiency, reduce systemic vulnerabilities, and enable adaptive, resilient ecosystems. By synthesizing insights from quantum finance, intelligent networks, and secure cloud architectures, the paper presents a unified framework for reimagining digital public infrastructure in the 21st century. This work contributes to the evolving discourse on digital sovereignty, infrastructure intelligence, and sustainable digital transformation. Keywords: digital ecosystems, artificial intelligence, quantum computing, quantum finance, public infrastructure, digital transformation, infrastructure resilience, e-governance, predictive analytics, entropy analysis, smart cities, digital sovereignty</t>
         </is>
       </c>
       <c r="H75" s="5" t="inlineStr">
         <is>
-          <t>arxiv</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="I75" s="5" t="n"/>
@@ -3941,17 +3964,17 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>95b231ae933b</t>
+          <t>907a4842ec09</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>Quantum secured blockchain framework for enhancing post quantum data security</t>
+          <t>Essays on Economics of Entrepreneurship</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>Reddy N.R.</t>
+          <t>Mohaddeseh Heydari Nejad</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
@@ -3959,15 +3982,15 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="F76" s="5" t="inlineStr">
-        <is>
-          <t>10.1038/s41598-025-16315-8</t>
-        </is>
-      </c>
-      <c r="G76" s="5" t="inlineStr"/>
+      <c r="F76" s="5" t="inlineStr"/>
+      <c r="G76" s="5" t="inlineStr">
+        <is>
+          <t>This dissertation examines the economics of entrepreneurship through three studies on how entrepreneurs develop innovations under uncertainty. I investigate: (1) how mentorship in startup accelerators creates value through learning and guidance, (2) how institutional designs shape outcomes when entrepreneurs and mentors hold different beliefs, and (3) how entrepreneurs use crowdfunding to learn about market demand. Using structural modeling, Bayesian frameworks, and empirical analysis, I study mechanisms that improve entrepreneurial decision-making and the welfare implications of institutional arrangements. In the first chapter, “A Structural Model of Mentorship in Startup Accelerators,” I use data from the Creative Destruction Lab to estimate a dynamic structural model where mentors allocate mentorship over time and entrepreneurs decide whether to follow their advice. This model disentangles two key mentorship mechanisms: a direct effect improving startup quality, and a screening effect identifying high-potential ventures. I find that mentorship enhances outcomes through both channels and learning gains vary across sectors: traditional sectors show early learning, while emerging ones like quantum computing exhibit more gradual gains. Counterfactual analysis quantifies the value of mentors&amp;apos; strategic input and suggests sector-specific mentorship designs. The second chapter, “Persuading Mentors: Heterogeneous Priors and Innovation Outcomes,” explores how combining advisory and funding roles affects innovation when mentors and entrepreneurs have divergent beliefs. I develop a Bayesian model where entrepreneurs may adopt mentors’ plans to enhance credibility, even if they believe their own plans would yield better outcomes. This dynamic can create inefficiencies and welfare loss, especially when belief divergence is large. I show that separating advisory and funding roles, as in some accelerator or VC models, can mitigate these tensions and improve outcomes in deep tech and other novel sectors. In the third chapter, &amp;quot;Learning about Product Demand through Crowdfunding,&amp;quot; I investigate how entrepreneurs strategically use crowdfunding platforms to learn about market demand while financing their projects. I develop a Bayesian learning model where entrepreneurs make pricing decisions that trade-off immediate profits against the informational value. Using data from Kickstarter&amp;apos;s digital games category, I shows that entrepreneurs&amp;apos; pricing decisions are consistent with incentives for learning.</t>
+        </is>
+      </c>
       <c r="H76" s="5" t="inlineStr">
         <is>
-          <t>scopus</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="I76" s="5" t="n"/>
@@ -3981,33 +4004,37 @@
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>9e426831f111</t>
+          <t>50965b8f7d9f</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>Digital Finance in Europe: Law, Regulation, and Governance</t>
+          <t>Post-Quantum AI: Building Secure Machine Learning Systems in the Quantum Era</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>Avgouleas E.</t>
+          <t>Amit Taneja</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
-          <t>10.1515/9783110749472</t>
-        </is>
-      </c>
-      <c r="G77" s="5" t="inlineStr"/>
+          <t>10.9734/bpi/mono/978-93-88417-99-0</t>
+        </is>
+      </c>
+      <c r="G77" s="5" t="inlineStr">
+        <is>
+          <t>This book explores the intersection of artificial intelligence (AI) and quantum computing, focusing on the urgent need to secure machine learning systems in the face of emerging quantum threats. As quantum computers advance, they expose vulnerabilities in classical cryptographic methods, potentially undermining data integrity, privacy, and trust in AI-driven applications. To address these challenges, this study introduces the concept of post-quantum AI—a framework for integrating quantum-resistant cryptographic algorithms, Anomaly detection mechanisms, and Resilient machine learning architectures. This book makes three core contributions: it motivates a quantum-era threat model for machine learning (ii) it maps a migration path to standardised post-quantum cryptography Crypto-agile architectures (iii) it presents a defence-in-depth blueprint across the data → training → inference lifecycle that integrates privacy-preserving learning Governance. This work explicitly highlights key contributions, including proposed frameworks, algorithms, and case studies. Future research directions are also outlined to guide continued exploration in this emergent field. The final candidate algorithms from the NIST PQC standardisation process (NIST, 2022–2023) further strengthen this discussion. Key themes include the foundations of quantum mechanics relevant to computation, the fundamental differences between classical and quantum computing, and the transformative potential of quantum algorithms for optimisation, pattern recognition, and predictive analytics. The book highlights case studies spanning drug discovery, finance, mobile networks, and supply chain optimisation, illustrating how quantum-enhanced AI can revolutionise industry while simultaneously raising complex security and ethical concerns. A central focus is the development and deployment of post-quantum cryptography (PQC)), such as lattice-based and hash-based algorithms, to safeguard AI models against adversarial and quantum-accelerated attacks. The discussion extends to adversarial machine learning, explainable AI (XAI), and hybrid classical–quantum systems as strategies for strengthening resilience. The ethical, legal, and regulatory dimensions of post-quantum AI are also examined, emphasising fairness, transparency, accountability, and international cooperation. By combining technical innovations with responsible governance, the book advocates for building trustworthy AI systems that remain robust in the quantum era. Future work includes post-quantum cryptography (PQC) performance benchmarking in ML pipelines Patterns for crypto-agile key management, Assurance methods for privacy-preserving Federated learning as standards, and Implementations that are mature.</t>
+        </is>
+      </c>
       <c r="H77" s="5" t="inlineStr">
         <is>
-          <t>scopus</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="I77" s="5" t="n"/>
@@ -4021,33 +4048,33 @@
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>353f305d5ce8</t>
+          <t>e6656ef470fb</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>Enhancing Classification Accuracy with Quantum Non-Negative Matrix Factorization and Quantum Support Vector Machines</t>
+          <t>Adiabatic Quantum Optimization Fails to Solve the Knapsack Problem</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>Chikhaoui B.</t>
+          <t>Lauren Pusey-Nazzaro; Prasanna Date</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="F78" s="5" t="inlineStr">
-        <is>
-          <t>10.1109/QCNC64685.2025.00075</t>
-        </is>
-      </c>
-      <c r="G78" s="5" t="inlineStr"/>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="F78" s="5" t="inlineStr"/>
+      <c r="G78" s="5" t="inlineStr">
+        <is>
+          <t>In this work, we attempt to solve the integer-weight knapsack problem using the D-Wave 2000Q adiabatic quantum computer. The knapsack problem is a well-known NP-complete problem in computer science, with applications in economics, business, finance, etc. We attempt to solve a number of small knapsack problems whose optimal solutions are known; we find that adiabatic quantum optimization fails to produce solutions corresponding to optimal filling of the knapsack in all problem instances. We compare results obtained on the quantum hardware to the classical simulated annealing algorithm and two solvers employing a hybrid branch-and-bound algorithm. The simulated annealing algorithm also fails to produce the optimal filling of the knapsack, though solutions obtained by simulated and quantum annealing are no more similar to each other than to the correct solution. We discuss potential causes for this observed failure of adiabatic quantum optimization.</t>
+        </is>
+      </c>
       <c r="H78" s="5" t="inlineStr">
         <is>
-          <t>scopus</t>
+          <t>semantic_scholar</t>
         </is>
       </c>
       <c r="I78" s="5" t="n"/>
@@ -4061,33 +4088,37 @@
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>146a99b9b311</t>
+          <t>2b217f56fa88</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>Intermediate Qutrit-based Improved Quantum Arithmetic Operations with Application on Financial Derivative Pricing</t>
+          <t>Genealogía a la epistemología poscapitalista</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>Amit Saha; Turbasu Chatterjee; Anupam Chattopadhyay; Amlan Chakrabarti</t>
+          <t>Moisés Ezequiel Zepeda Moreno</t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="F79" s="5" t="inlineStr"/>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="F79" s="5" t="inlineStr">
+        <is>
+          <t>10.22402/ed.leed.978.607.26779-4-4</t>
+        </is>
+      </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>In some quantum algorithms, arithmetic operations are of utmost importance for resource estimation. In binary quantum systems, some efficient implementation of arithmetic operations like, addition/subtraction, multiplication/division, square root, exponential and arcsine etc. have been realized, where resources are reported as a number of Toffoli gates or T gates with ancilla. Recently it has been demonstrated that intermediate qutrits can be used in place of ancilla, allowing us to operate efficiently in the ancilla-free frontier zone. In this article, we have incorporated intermediate qutrit approach to realize efficient implementation of all the quantum arithmetic operations mentioned above with respect to gate count and circuit-depth without T gate and ancilla. Our resource estimates with intermediate qutrits could guide future research aimed at lowering costs considering arithmetic operations for computational problems. As an application of computational problems, related to finance, are poised to reap the benefit of quantum computers, in which quantum arithmetic circuits are going to play an important role. In particular, quantum arithmetic circuits of arcsine and square root are necessary for path loading using the re-parameterization method, as well as the payoff calculation for derivative pricing. Hence, the improvements are studied in the context of the core arithmetic circuits as well as the complete application of derivative pricing. Since our intermediate qutrit approach requires to access higher energy levels, making the design prone to errors, nevertheless, we show that the percentage decrease in the probability of error is significant owing to the fact that we achieve circuit robustness compared to qubit-only works.</t>
+          <t>This text argues that the technoscientific revolution—big data, AI, and the imminent quantum horizon—reconfigures who produces and controls knowledge. The global network erodes the university's monopoly and pushes education toward algorithmic platforms, with the risk of a "technified deschooling," corporate concentration, and the fetishization of life. In response, it proposes thinking through a post-capitalist epistemology and new ecologies of knowledge that democratize the production of knowledge. In Chapter 1, it analyzes the genealogy of the university: from Muslim madrasas and their plural forms of knowledge to the medieval European university (Bologna/Salamanca) as a technology of control (chair, cloister, writing). The Renaissance and the colonial era consolidate grammar, the printing press, and the "lettered cities" as mechanisms of domination. Modernity (Descartes, Kant, Humboldt) specializes and hierarchizes the university; the twentieth century incorporates systems theory, cybernetics, and autopoiesis, preparing the informational paradigm that culminates in the quantum threshold. Chapter 2 defines a regime that exploits networked cooperation and turns knowledge, data, and pedagogies into financeable assets. It situates its origin in informatization, the financialization of EdTech, and the "market of theories," describes the qualitative leap produced by standardizing knowledge through AI/Big Data, and explains the global division of cognitive labor. It anticipates the transition toward the quantum era (6G, quantum computing), in which value production pivots on information infrastructures. Finally, Chapter 3 examines the impact of the network and the anthropological and geological mutations of the quantum era; it addresses "computer pedagogy," "quantum epistemology," and "semiotic change." It discusses cyborg pedagogy and transhumanism, warning about the subordination of human formation to epistemological machines. It proposes shifting education away from banking/algorithmic models toward communal, deschooled, and systemic practices that prioritize the common good and cognitive justice.</t>
         </is>
       </c>
       <c r="H79" s="5" t="inlineStr">
         <is>
-          <t>arxiv</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="I79" s="5" t="n"/>
@@ -4101,33 +4132,37 @@
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>5383de88a31f</t>
+          <t>c065a97bd065</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>Stock Price Prediction Based on a Hybrid Quantum-Classical Neural Network Model</t>
+          <t>Quantum Variational Solving of Nonlinear and Multi-Dimensional Partial Differential Equations</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>Zhang X.</t>
+          <t>Abhijat Sarma; Thomas W. Watts; Mudassir Moosa; Yilian Liu; Peter L. McMahon</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
-          <t>10.12178/1001-0548.2021394</t>
-        </is>
-      </c>
-      <c r="G80" s="5" t="inlineStr"/>
+          <t>10.48550/arxiv.2311.01531</t>
+        </is>
+      </c>
+      <c r="G80" s="5" t="inlineStr">
+        <is>
+          <t>A variational quantum algorithm for numerically solving partial differential equations (PDEs) on a quantum computer was proposed by Lubasch et al. In this paper, we generalize the method introduced by Lubasch et al. to cover a broader class of nonlinear PDEs as well as multidimensional PDEs, and study the performance of the variational quantum algorithm on several example equations. Specifically, we show via numerical simulations that the algorithm can solve instances of the Single-Asset Black-Scholes equation with a nontrivial nonlinear volatility model, the Double-Asset Black-Scholes equation, the Buckmaster equation, and the deterministic Kardar-Parisi-Zhang equation. Our simulations used up to $n=12$ ansatz qubits, computing PDE solutions with $2^n$ grid points. We also performed proof-of-concept experiments with a trapped-ion quantum processor from IonQ, showing accurate computation of two representative expectation values needed for the calculation of a single timestep of the nonlinear Black--Scholes equation. Through our classical simulations and experiments on quantum hardware, we have identified -- and we discuss -- several open challenges for using quantum variational methods to solve PDEs in a regime with a large number ($\gg 2^{20}$) of grid points, but also a practical number of gates per circuit and circuit shots.</t>
+        </is>
+      </c>
       <c r="H80" s="5" t="inlineStr">
         <is>
-          <t>scopus</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="I80" s="5" t="n"/>
@@ -4141,33 +4176,37 @@
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>9c4d41df3a8f</t>
+          <t>5b5fd3a147af</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>A Bibliometric Analysis of Quantum Machine Learning Research</t>
+          <t>Wasserstein Solution Quality and the Quantum Approximate Optimization Algorithm: A Portfolio Optimization Case Study</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>Ahmadikia A.A.</t>
+          <t>Jack S. Baker; Santosh Kumar Radha</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t>10.1080/0194262X.2023.2292049</t>
-        </is>
-      </c>
-      <c r="G81" s="5" t="inlineStr"/>
+          <t>10.48550/arxiv.2202.06782</t>
+        </is>
+      </c>
+      <c r="G81" s="5" t="inlineStr">
+        <is>
+          <t>Optimizing of a portfolio of financial assets is a critical industrial problem which can be approximately solved using algorithms suitable for quantum processing units (QPUs). We benchmark the success of this approach using the Quantum Approximate Optimization Algorithm (QAOA); an algorithm targeting gate-model QPUs. Our focus is on the quality of solutions achieved as determined by the Normalized and Complementary Wasserstein Distance, $η$, which we present in a manner to expose the QAOA as a transporter of probability. Using $η$ as an application specific benchmark of performance, we measure it on selection of QPUs as a function of QAOA circuit depth $p$. At $n = 2$ (2 qubits) we find peak solution quality at $p=5$ for most systems and for $n = 3$ this peak is at $p=4$ on a trapped ion QPU. Increasing solution quality with $p$ is also observed using variants of the more general Quantum Alternating Operator Ansätz at $p=2$ for $n = 2$ and $3$ which has not been previously reported. In identical measurements, $η$ is observed to be variable at a level exceeding the noise produced from the finite number of shots. This suggests that variability itself should be regarded as a QPU performance benchmark for given applications. While studying the ideal execution of QAOA, we find that $p=1$ solution quality degrades when the portfolio budget $B$ approaches $n/2$ and increases when $B \approx 1$ or $n-1$. This trend directly corresponds to the binomial coefficient $nCB$ and is connected with the recently reported phenomenon of reachability deficits. Derivative-requiring and derivative-free classical optimizers are benchmarked on the basis of the achieved $η$ beyond $p=1$ to find that derivative-free optimizers are generally more effective for the given computational resources, problem sizes and circuit depths.</t>
+        </is>
+      </c>
       <c r="H81" s="5" t="inlineStr">
         <is>
-          <t>scopus</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="I81" s="5" t="n"/>
@@ -4181,17 +4220,17 @@
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>c64928ef49e7</t>
+          <t>a254f338377d</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>Zero-Trust Architecture Adaptation for Post-Quantum Cryptography: Implementation Roadmap for Critical Infrastructure</t>
+          <t>Quantum Advantage in Trading: A Game-Theoretic Approach</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>Nurhaliza Nurhaliza; Adichandra Febryana Yuscatama Darmawan</t>
+          <t>Faisal Shah Khan; Norbert M. Linke; Anton T. Than; Dror Baron</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
@@ -4201,17 +4240,17 @@
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t>10.57185/jetbis.v4i5.201</t>
+          <t>10.17615/af1s-7c34</t>
         </is>
       </c>
       <c r="G82" s="5" t="inlineStr">
         <is>
-          <t>The convergence of quantum computing threats and Zero Trust Architecture (ZTA) implementation presents unprecedented challenges for critical infrastructure protection. While quantum computers threaten current cryptographic foundations, Zero Trust frameworks require robust cryptographic mechanisms for continuous verification. This study examines the adaptation challenges and implementation strategies for integrating post-quantum cryptography within Zero Trust architectures across critical infrastructure sectors.A mixed-methods sequential explanatory design was employed with 147 critical infrastructure organizations across five sectors (energy, transportation, healthcare, financial services, telecommunications). Data collection included the Zero Trust Maturity Assessment Framework (ZTMAF), Post-Quantum Cryptography Readiness Index (PQCRI), Critical Infrastructure Vulnerability Assessment Protocol (CIVAP), semi-structured interviews (n=89), and document analysis (1,247 documents). Statistical analysis employed correlation analysis, ANOVA, and structural equation modeling, while qualitative data underwent thematic analysis.Zero Trust maturity varied significantly across sectors (M=2.91, SD=0.67), with financial services demonstrating highest maturity (M=3.81) and transportation lowest (M=2.50). Post-quantum cryptography readiness remained concerning across all sectors (M=2.47, SD=0.73), with only 16.3% achieving high readiness levels. Legacy systems prevalence (84.4% of organizations) negatively correlated with both ZTA maturity (r=-0.43) and PQC readiness (r=-0.58). Structural equation modeling revealed significant relationships between organizational factors and implementation success (x²/df=2.34, CFI=0.92).Critical infrastructure organizations face substantial challenges in quantum-safe Zero Trust implementation, with sector-specific barriers requiring targeted intervention strategies. The findings highlight urgent needs for government coordination, technical assistance programs, and accelerated legacy system modernization to ensure national cybersecurity resilience against emerging quantum threats.</t>
+          <t>Quantum games, like quantum algorithms, exploit quantum entanglement to establish strong correlations between strategic player actions. This paper introduces quantum game-theoretic models applied to trading and demonstrates their implementation on an ion-trap quantum computer. The results showcase a quantum advantage, previously known only theoretically, realized as higher-paying market Nash equilibria. This advantage could help uncover alpha in trading strategies, defined as excess returns compared to established benchmarks. These findings suggest that quantum computing could significantly influence the development of financial strategies.</t>
         </is>
       </c>
       <c r="H82" s="5" t="inlineStr">
         <is>
-          <t>semantic_scholar</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="I82" s="5" t="n"/>
@@ -4225,33 +4264,37 @@
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>196d41c96981</t>
+          <t>7f09d7df1f04</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>Fast Laplace transforms on quantum computers</t>
+          <t>Quantum Classical Ridgelet Neural Network For Time Series Model</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>Julien Zylberman</t>
+          <t>Bahadur Yadav; Sanjay Kumar Mohanty</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
         <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="F83" s="5" t="inlineStr"/>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="F83" s="5" t="inlineStr">
+        <is>
+          <t>10.48550/arxiv.2601.03654</t>
+        </is>
+      </c>
       <c r="G83" s="5" t="inlineStr">
         <is>
-          <t>While many classical algorithms rely on Laplace transforms, it has remained an open question whether these operations could be implemented efficiently on quantum computers. In this work, we introduce the Quantum Laplace Transform (QLT), which enables the implementation of $N\times N$ discrete Laplace transforms on quantum states encoded in $\lceil \log_2(N)\rceil$-qubits. In many cases, the associated quantum circuits have a depth that scales with $N$ as $O(\log(\log(N)))$ and a size that scales as $O(\log(N))$, requiring exponentially fewer operations and double-exponentially less computational time than their classical counterparts. These efficient scalings open the possibility of developing a new class of quantum algorithms based on Laplace transforms, with potential applications in physics, engineering, chemistry, machine learning, and finance.</t>
+          <t>In this study, we present a quantum computing method that incorporates ridglet transforms into the quantum processing pipelines for time series data. Here, the Ridgelet neural network is integrated with a single-qubit quantum computing method, which improves feature extraction and forecasting capabilities. Furthermore, experimental results using financial time series data demonstrate the superior performance of our model compared to existing models.</t>
         </is>
       </c>
       <c r="H83" s="5" t="inlineStr">
         <is>
-          <t>arxiv</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="I83" s="5" t="n"/>
@@ -4265,33 +4308,37 @@
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>0f028fff3500</t>
+          <t>1ac1b7a5c545</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>Quantum Computing: Transforming the Landscape of Financial Markets</t>
+          <t>Implementing Quantum Resistant Algorithm in Blockchain-Based Applications</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>Ahmed M.</t>
+          <t>Sonali Ridhorkar; Mr. Setu Sagar Mishra</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
-          <t>10.4018/979-8-3693-7160-2.ch013</t>
-        </is>
-      </c>
-      <c r="G84" s="5" t="inlineStr"/>
+          <t>10.48175/ijarsct-17899</t>
+        </is>
+      </c>
+      <c r="G84" s="5" t="inlineStr">
+        <is>
+          <t>With quantum computing evolving very fast as we speak, the security and integrity of blockchain-based applications will become the most crucial aspect. A proposal is raised to use blockchain technology as a platform for writing and probating ‘wills’. Blockchain technology in drafting and probating wills makes them safe from manipulations, highly secure, and transparent. It also dramatically decreases the time required without catering for the challenges created by the current system. [9] This paper presents a new method for will transfer and inheritance management by implementing quantum-resistant algorithms in the security architecture of a blockchain decentralized application (DApp). The system uses IPFS Network for data storage and quantum-safe algorithms as retrieval and sending algorithms. The system includes Quantum-Resistant Dilithium Signatures and Merkle trees as the fundamental components for safeguarding the transfers of assets and claims for inheritance. Quantum-Resistant Dilithium Signatures offer an unbreakable shield against quantum attacks that are expected to happen, which in turn safeguards the privacy and authenticity of transactions. While Merkle trees are responsible for the organization of inheritance claims in an effective and tamper-proof manner, the introduced system incorporates smart contracts to address the execution of an inheritance case, adding more security and automation to the asset distribution process. The system ensures a robust security framework by integrating quantum-resistant algorithms at the very core of the blockchain DApp for instance, retrieval and sending. This research is of great significance to blockchain technology which is the emerging technology of the future because it addresses the existing threat of quantum computing by showing the feasibility of using quantum-resistant algorithms in practical applications. As established by the findings, besides Quantum-Resistant Dilithium Signatures and Merkle trees, the systems of asset transfers and inheritance management within blockchain networks are enhanced in terms of safety and reliability. Hence, paving the road to the creation of more secure and trustworthy digital asset management systems.</t>
+        </is>
+      </c>
       <c r="H84" s="5" t="inlineStr">
         <is>
-          <t>scopus</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="I84" s="5" t="n"/>
@@ -4305,37 +4352,37 @@
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>e1731c705f63</t>
+          <t>4f4a7745d6fe</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>Loop Algorithm for Quantum Transverse Ising Model in a Longitudinal Field</t>
+          <t>Quantum-Enhanced Multi-Factor Authentication Framework for Digital Banking Systems: A Post-Quantum Cryptographic Approach</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>Wei Xu; Xue-Feng Zhang</t>
+          <t>Praveen Kumar Reddy Gujjala</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F85" s="5" t="inlineStr">
         <is>
-          <t>10.1103/s2q3-grd6</t>
+          <t>10.36948/ijfmr.2023.v05i06.55443</t>
         </is>
       </c>
       <c r="G85" s="5" t="inlineStr">
         <is>
-          <t>The quantum transverse Ising model and its extensions play a critical role in various fields, such as statistical physics, quantum magnetism, quantum simulations, and mathematical physics. Although it does not suffer from the sign problem in most cases, the corresponding quantum Monte Carlo algorithm performs inefficiently, especially at a large longitudinal field. The main hindrance is the lack of loop update method which can strongly decrease the auto-correlation between Monte Carlo steps. Here, we successfully develop a loop algorithm with a novel merge-unmerge process. It demonstrates a great advantage over the state-of-the-art algorithm when implementing it to simulate the Rydberg atom chain and Kagome qubit ice. This advanced algorithm suits various systems such as Rydberg atom arrays, trapped ions, quantum materials, and quantum annealers.</t>
+          <t>The digital banking ecosystem faces unprecedented security challenges with the imminent advent of quantum computing, which threatens to compromise existing cryptographic infrastructures. Traditional multi-factor authentication (MFA) systems in banking rely on classical cryptographic primitives vulnerable to quantum attacks, creating critical security gaps in financial transactions and customer data protection. This paper introduces a novel Quantum-Enhanced Multi-Factor Authentication Framework (QE-MFAF) specifically designed for digital banking systems, integrating lattice-based post-quantum cryptography with biometric fuzzy commitment schemes and behavioral analytics. The proposed framework incorporates a hybrid authentication mechanism combining quantum-resistant cryptographic protocols, continuous behavioral pattern recognition using deep learning models, and secure multi-party computation for transaction verification. Experimental validation on a synthetic banking dataset demonstrates superior performance with 99.7% authentication accuracy, 0.02% false positive rate, and 15ms average authentication latency while maintaining quantum resistance. The framework successfully mitigates advanced persistent threats, insider attacks, and quantum-based cryptographic vulnerabilities while ensuring seamless user experience in high-transaction banking environments. Performance comparisons with existing banking authentication systems show 34% improvement in security metrics and 28% reduction in computational overhead.</t>
         </is>
       </c>
       <c r="H85" s="5" t="inlineStr">
         <is>
-          <t>arxiv</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="I85" s="5" t="n"/>
@@ -4349,37 +4396,33 @@
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>3415b7e66e1a</t>
+          <t>6a9413f38468</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>Artificial Intelligence-Driven Risk Management for Fintech Enterprises: Enhancing Decision-Making Through Predictive Analytics</t>
+          <t>LiteQSign: Lightweight and Quantum-Safe Signatures for Heterogeneous IoT Applications</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>Sai Teja Battula</t>
+          <t>Attila A. Yavuz; Saleh Darzi; Saif E. Nouma</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="F86" s="5" t="inlineStr">
-        <is>
-          <t>10.71097/ijsat.v16.i1.2804</t>
-        </is>
-      </c>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F86" s="5" t="inlineStr"/>
       <c r="G86" s="5" t="inlineStr">
         <is>
-          <t>This article explores the integration of artificial intelligence into fintech risk management frameworks, examining how predictive analytics are revolutionizing risk assessment and mitigation capabilities across the financial services industry. It investigates the evolution of risk management within the rapidly changing fintech landscape, highlighting how traditional approaches prove increasingly inadequate in addressing complex challenges like real-time fraud detection, cybersecurity threats, alternative credit assessment, cryptocurrency volatility, and decentralized finance liquidity risks. The article presents a comprehensive analysis of AI-powered solutions across key risk domains, including credit risk assessment, fraud detection, and market risk modeling, demonstrating their superior performance compared to conventional methods. It further outlines a structured framework for enterprise AI implementation, addressing the critical dimensions of data infrastructure, model development, operational integration, and continuous adaptation. The article also examines significant implementation challenges related to regulatory compliance, model explainability, data quality, and talent requirements. Finally, it explores emerging trends that will shape the future of AI-driven risk management, including federated learning, quantum computing, automated risk mitigation, and ecosystem-wide risk intelligence capabilities.</t>
+          <t>The rapid proliferation of resource-constrained IoT devices across sectors like healthcare, industrial automation, and finance introduces major security challenges. Traditional digital signatures, though foundational for authentication, are often infeasible for low-end devices with limited computational, memory, and energy resources. Also, the rise of quantum computing necessitates post-quantum (PQ) secure alternatives. However, NIST-standardized PQ signatures impose substantial overhead, limiting their practicality in energy-sensitive applications such as wearables, where signer-side efficiency is critical. To address these challenges, we present LightQSign (LightQS), a novel lightweight PQ signature that achieves near-optimal signature generation efficiency with only a small, constant number of hash operations per signing. Its core innovation enables verifiers to obtain one-time hash-based public keys without interacting with signers or third parties through secure computation. We formally prove the security of LightQSign in the random oracle model and evaluate its performance on commodity hardware and a resource-constrained 8-bit AtMega128A1 microcontroller. Experimental results show that LightQSign outperforms NIST PQC standards with lower computational overhead, minimal memory usage, and compact signatures. On an 8-bit microcontroller, it achieves up to 1.5-24x higher energy efficiency and 1.7-22x shorter signatures than PQ counterparts, and 56-76x better energy efficiency than conventional standards-enabling longer device lifespans and scalable, quantum-resilient authentication.</t>
         </is>
       </c>
       <c r="H86" s="5" t="inlineStr">
         <is>
-          <t>semantic_scholar</t>
+          <t>arxiv</t>
         </is>
       </c>
       <c r="I86" s="5" t="n"/>
@@ -4393,28 +4436,32 @@
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>6e0380dce3b2</t>
+          <t>5ab77e03ac9c</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>Accelerating Quantum Monte Carlo Calculations with Set-Equivariant Architectures and Transfer Learning</t>
+          <t>Scalable Emulation of Sign-Problem$-$Free Hamiltonians with Room Temperature p-bits</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>Manuel Gallego; Sebastián Roca-Jerat; David Zueco; Jesús Carrete</t>
+          <t>Kerem Y. Camsari; Shuvro Chowdhury; Supriyo Datta</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="F87" s="5" t="inlineStr"/>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="F87" s="5" t="inlineStr">
+        <is>
+          <t>10.1103/PhysRevApplied.12.034061</t>
+        </is>
+      </c>
       <c r="G87" s="5" t="inlineStr">
         <is>
-          <t>Machine-learning (ML) ansätze have greatly expanded the accuracy and reach of variational quantum Monte Carlo (QMC) calculations, in particular when exploring the manifold quantum phenomena exhibited by spin systems. However, the scalability of QMC is still compromised by several other bottlenecks, and specifically those related to the actual evaluation of observables based on random deviates that lies at the core of the approach. Here we show how the set-transformer architecture can be used to dramatically accelerate or even bypass that step, especially for time-consuming operators such as powers of the magnetization. We illustrate the procedure with a range of examples structured around quantum spin systems with long-range interactions, and comprising both regressions (to predict observables) and classifications (to detect phase transitions). Moreover, we show how transfer learning can be leveraged to reduce the training cost by reusing knowledge from different systems and smaller system sizes.</t>
+          <t>The growing field of quantum computing is based on the concept of a q-bit which is a delicate superposition of 0 and 1, requiring cryogenic temperatures for its physical realization along with challenging coherent coupling techniques for entangling them. By contrast, a probabilistic bit or a p-bit is a robust classical entity that fluctuates between 0 and 1, and can be implemented at room temperature using present-day technology. Here, we show that a probabilistic coprocessor built out of room temperature p-bits can be used to accelerate simulations of a special class of quantum many-body systems that are sign-problem$-$free or stoquastic, leveraging the well-known Suzuki-Trotter decomposition that maps a $d$-dimensional quantum many body Hamiltonian to a $d$+1-dimensional classical Hamiltonian. This mapping allows an efficient emulation of a quantum system by classical computers and is commonly used in software to perform Quantum Monte Carlo (QMC) algorithms. By contrast, we show that a compact, embedded MTJ-based coprocessor can serve as a highly efficient hardware-accelerator for such QMC algorithms providing several orders of magnitude improvement in speed compared to optimized CPU implementations. Using realistic device-level SPICE simulations we demonstrate that the correct quantum correlations can be obtained using a classical p-circuit built with existing technology and operating at room temperature. The proposed coprocessor can serve as a tool to study stoquastic quantum many-body systems, overcoming challenges associated with physical quantum annealers.</t>
         </is>
       </c>
       <c r="H87" s="5" t="inlineStr">
@@ -4433,37 +4480,29 @@
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>87ac65c206bd</t>
+          <t>3cc013044f30</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>Predict and Conquer: Navigating Algorithm Trade-offs with Quantum Design Automation</t>
+          <t>Showcasing sentiment classification and word prediction in the quantum natural processing area</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>Simon Thelen; Wolfgang Mauerer</t>
+          <t>Peral-García D.</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="F88" s="5" t="inlineStr">
-        <is>
-          <t>10.1109/QCE65121.2025.00071</t>
-        </is>
-      </c>
-      <c r="G88" s="5" t="inlineStr">
-        <is>
-          <t>Combining quantum computers with classical compute power has become a standard means for developing algorithms that are eventually supposed to beat any purely classical alternatives. While in-principle advantages for solution quality or runtime are expected for many approaches, substantial challenges remain: Non-functional properties like runtime or solution quality of many approaches are not fully understood, and need to be explored empirically. This makes it unclear which approach is best suited for a given problem. Accurately predicting behaviour of quantum-classical algorithms opens possibilities for software abstraction layers, which can automate decision-making for algorithm selection and parametrisation. While such techniques find frequent use in classical high-performance computing, they are still mostly absent from quantum toolchains. We present a methodology to perform algorithm selection based on desirable non-functional requirements. This simplifies decision-making processes for users. Based on annotations at the source code level, our framework traces key characteristics of quantum-classical algorithms, and uses this information to predict the most suitable approach and its parameters for given computational challenges and their non-functional requirements. As combinatorial optimisation is a very extensively studied aspect of quantum-classical systems, we perform a comprehensive case study based on numerical simulations of algorithmic approaches to implement and validate our ideas. We develop statistical models to quantify the influence of various factors on non-functional properties, and establish predictions for optimal algorithmic choices without manual effort. We argue that our methodology generalises to problems beyond combinatorial optimisation, such as Hamiltonian simulation, and lays a foundation for integrated software layers for quantum design automation.</t>
-        </is>
-      </c>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F88" s="5" t="inlineStr"/>
+      <c r="G88" s="5" t="inlineStr"/>
       <c r="H88" s="5" t="inlineStr">
         <is>
-          <t>arxiv</t>
+          <t>scopus</t>
         </is>
       </c>
       <c r="I88" s="5" t="n"/>
@@ -4477,37 +4516,37 @@
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>2970b0f6fd48</t>
+          <t>6bb18cfb9e04</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>Artificial Intelligence for Dynamical Systems in Wireless Communications, Financial Markets, and Engineering: Modeling for the Future</t>
+          <t>Quantum Risk Analysis</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>S. Meenakshi</t>
+          <t>Stefan Woerner; Daniel J. Egger</t>
         </is>
       </c>
       <c r="E89" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="F89" s="5" t="inlineStr">
         <is>
-          <t>10.52783/jisem.v10i22s.3628</t>
+          <t>10.1038/s41534-019-0130-6</t>
         </is>
       </c>
       <c r="G89" s="5" t="inlineStr">
         <is>
-          <t>Artificial Intelligence (AI) has found use in modeling and optimization dynamical systems over multiple domains including wireless communications, financial markets, and engineering. The focus of this research is on the use of the AI driven approaches for improving the predictive accuracy, decision making, and system optimization. The four AI algorithms that were analyzed for their effectiveness in handling complex, dynamic environments are deep learning, reinforcement learning, harmony search optimization, and fuzzy cognitive maps. To experiment, deep learning models were shown to improve spectrum allocation efficiency by 27.8%, reinforcement learning was illustrated to enhance financial risk prediction accuracy by 31.4%, harmony search optimization was found to reduce engineering system faults by 24.6% and fuzzy cognitive maps were shown to increase decision making reliability by 29.2%. It was confirmed that adaptive and computational efficient techniques have always been better suited than traditional ones to the AI approaches. Nevertheless, there were challenges like computational complexity and timing implementation. The outcome of this study highlights the necessity of hybrid AI models that combine several approaches for enhancing performance and adaptability. The future research should concentrate on improving the model interpretability and incorporate AI with newly emerging technologies such as quantum computing and edge computing to enhance dynamical system modeling. These findings highlight the importance of AI in largely transforming business decision-making and predictive modeling in various industries.</t>
+          <t>We present a quantum algorithm that analyzes risk more efficiently than Monte Carlo simulations traditionally used on classical computers. We employ quantum amplitude estimation to evaluate risk measures such as Value at Risk and Conditional Value at Risk on a gate-based quantum computer. Additionally, we show how to implement this algorithm and how to trade off the convergence rate of the algorithm and the circuit depth. The shortest possible circuit depth - growing polynomially in the number of qubits representing the uncertainty - leads to a convergence rate of $O(M^{-2/3})$. This is already faster than classical Monte Carlo simulations which converge at a rate of $O(M^{-1/2})$. If we allow the circuit depth to grow faster, but still polynomially, the convergence rate quickly approaches the optimum of $O(M^{-1})$. Thus, for slowly increasing circuit depths our algorithm provides a near quadratic speed-up compared to Monte Carlo methods. We demonstrate our algorithm using two toy models. In the first model we use real hardware, such as the IBM Q Experience, to measure the financial risk in a Treasury-bill (T-bill) faced by a possible interest rate increase. In the second model, we simulate our algorithm to illustrate how a quantum computer can determine financial risk for a two-asset portfolio made up of Government debt with different maturity dates. Both models confirm the improved convergence rate over Monte Carlo methods. Using simulations, we also evaluate the impact of cross-talk and energy relaxation errors.</t>
         </is>
       </c>
       <c r="H89" s="5" t="inlineStr">
         <is>
-          <t>semantic_scholar</t>
+          <t>arxiv</t>
         </is>
       </c>
       <c r="I89" s="5" t="n"/>
@@ -4521,33 +4560,37 @@
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>44f913a87112</t>
+          <t>817a28486638</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>From Economics to AI: Integrating Discretionary and Quantitative Approaches in Asset Management</t>
+          <t>The Evolution of China's Cyber-Espionage Tactics: From Traditional Espionage to AI-Driven Cyber Threats against Critical Infrastructure in the West</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>Rudin A.</t>
+          <t>Christian C. Madubuko; Chamunorwa Chitsungo</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F90" s="5" t="inlineStr">
         <is>
-          <t>10.3905/jpm.2025.1.737</t>
-        </is>
-      </c>
-      <c r="G90" s="5" t="inlineStr"/>
+          <t>10.47672/ajir.2424</t>
+        </is>
+      </c>
+      <c r="G90" s="5" t="inlineStr">
+        <is>
+          <t>Purpose: This article critically investigates the evolution of China’s cyber-espionage strategies, specifically illustrating the shift from traditional espionage methodologies to the incorporation of advanced technologies, particularly artificial intelligence (AI). This transition profoundly reshapes global power dynamics, delineating nuanced threats to critical infrastructure in Western nations, including power grids, financial systems, and communication networks (Wang et al., 2019). Materials and Methods: Utilizing a theoretical framework grounded in Joseph Nye's concept of soft power and contemporary security studies, this research posits a hypothesis: there exists a positive correlation between technological advancements and the escalation of espionage activities by state actors. The inquiry encompasses a comprehensive analysis of key components, such as vulnerabilities, adaptive strategies, geopolitical implications, deterrence mechanisms, and international collaboration, thereby illuminating the multifaceted risks to national security inherent in the digital age (Nye, 2004). Findings: The study critically evaluates the countermeasures undertaken by Western countries, probing strategic enhancements of cyber defences and the formation of international coalitions aimed at collective security (Huang et al., 2021). The findings reveal substantial obstacles in achieving a cohesive and effective response to the rapidly escalating and pervasive nature of contemporary cyber threats (Zhang et al., 2020). Implications to Theory, Practice and Policy: Considering the ongoing maturation of China’s cyber capabilities, characterized by an increased reliance on AI and the impending advent of quantum computing, the article advocates for a comprehensive revaluation of global security practices (Mann et al., 2020). It underscores the imperative for Western nations to not only innovate defensively but to also adopt proactive measures and foster significant international collaboration. This multifaceted approach is essential to address the complex challenges posed by state-sponsored cyber operations within an increasingly interconnected global landscape (Chen et al., 2021).</t>
+        </is>
+      </c>
       <c r="H90" s="5" t="inlineStr">
         <is>
-          <t>scopus</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="I90" s="5" t="n"/>
@@ -4561,37 +4604,33 @@
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>95bdd4ebaccb</t>
+          <t>90c94d9959ea</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>On the impact of quantum computing technology on future developments in high-performance scientific computing</t>
+          <t>Between 0 and 1. Exploring the Algorithmic Restraints and the Potential of Quantum Computing in the Financial Sector</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>Matthias Möller; Cornelis Vuik</t>
+          <t>Bartosz Szczęsny; Wiesława Gryncewicz</t>
         </is>
       </c>
       <c r="E91" s="5" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F91" s="5" t="inlineStr">
         <is>
-          <t>10.1007/s10676-017-9438-0</t>
-        </is>
-      </c>
-      <c r="G91" s="5" t="inlineStr">
-        <is>
-          <t>Quantum computing technologies have become a hot topic in academia and industry receiving much attention and financial support from all sides. Building a quantum computer that can be used practically is in itself an outstanding challenge that has become the 'new race to the moon'. Next to researchers and vendors of future computing technologies, national authorities are showing strong interest in maturing this technology due to its known potential to break many of today's encryption techniques, which would have significant impact on our society. It is however quite likely that quantum computing has beneficial impact on many computational disciplines.   In this article we describe our vision of future developments in scientific computing that would be enabled by the advent of software-programmable quantum computers. We thereby assume that quantum computers will form part of a hybrid accelerated computing platform like GPUs and co-processor cards do today. In particular, we address the potential of quantum algorithms to bring major breakthroughs in applied mathematics and its applications. Finally, we give several examples that demonstrate the possible impact of quantum-accelerated scientific computing on society.</t>
-        </is>
-      </c>
+          <t>10.1007/978-3-031-78468-2_4</t>
+        </is>
+      </c>
+      <c r="G91" s="5" t="inlineStr"/>
       <c r="H91" s="5" t="inlineStr">
         <is>
-          <t>arxiv</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="I91" s="5" t="n"/>
@@ -4605,33 +4644,37 @@
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>1b63c3136291</t>
+          <t>b078eb45a65d</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>A Comparative Study of Quantum Optimization Techniques for Solving Combinatorial Optimization Benchmark Problems</t>
+          <t>Quantum computing quantum Monte Carlo with hybrid tensor network for electronic structure calculations</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>Monit Sharma; H. Lau</t>
+          <t>Shu Kanno; Hajime Nakamura; Takao Kobayashi; Shigeki Gocho; Miho Hatanaka; Naoki Yamamoto; Qi Gao</t>
         </is>
       </c>
       <c r="E92" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="F92" s="5" t="inlineStr"/>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F92" s="5" t="inlineStr">
+        <is>
+          <t>10.1038/s41534-024-00851-8</t>
+        </is>
+      </c>
       <c r="G92" s="5" t="inlineStr">
         <is>
-          <t>Quantum optimization holds promise for addressing classically intractable combinatorial problems, yet a standardized framework for benchmarking its performance, particularly in terms of solution quality, computational speed, and scalability is still lacking. In this work, we introduce a comprehensive benchmarking framework designed to systematically evaluate a range of quantum optimization techniques against well-established NP-hard combinatorial problems. Our framework focuses on key problem classes, including the Multi-Dimensional Knapsack Problem (MDKP), Maximum Independent Set (MIS), Quadratic Assignment Problem (QAP), and Market Share Problem (MSP). Our study evaluates gate-based quantum approaches, including the Variational Quantum Eigensolver (VQE) and its CVaR-enhanced variant, alongside advanced quantum algorithms such as the Quantum Approximate Optimization Algorithm (QAOA) and its extensions. To address resource constraints, we incorporate qubit compression techniques like Pauli Correlation Encoding (PCE) and Quantum Random Access Optimization (QRAO). Experimental results, obtained from simulated quantum environments and classical solvers, provide key insights into feasibility, optimality gaps, and scalability. Our findings highlight both the promise and current limitations of quantum optimization, offering a structured pathway for future research and practical applications in quantum-enhanced decision-making.</t>
+          <t>Quantum computers have a potential for solving quantum chemistry problems with higher accuracy than classical computers. Quantum computing quantum Monte Carlo (QC-QMC) is a QMC with a trial state prepared in quantum circuit, which is employed to obtain the ground state with higher accuracy than QMC alone. We propose an algorithm combining QC-QMC with a hybrid tensor network to extend the applicability of QC-QMC beyond a single quantum device size. In a two-layer quantum-quantum tree tensor, our algorithm for the larger trial wave function can be executed than preparable wave function in a device. Our algorithm is evaluated on the Heisenberg chain model, graphite-based Hubbard model, hydrogen plane model, and MonoArylBiImidazole using full configuration interaction QMC. Our algorithm can achieve energy accuracy (specifically, variance) several orders of magnitude higher than QMC, and the hybrid tensor version of QMC gives the same energy accuracy as QC-QMC when the system is appropriately decomposed. Moreover, we develop a pseudo-Hadamard test technique that enables efficient overlap calculations between a trial wave function and an orthonormal basis state. In a real device experiment by using the technique, we obtained almost the same accuracy as the statevector simulator, indicating the noise robustness of our algorithm. These results suggests that the present approach will pave the way to electronic structure calculation for large systems with high accuracy on current quantum devices.</t>
         </is>
       </c>
       <c r="H92" s="5" t="inlineStr">
         <is>
-          <t>semantic_scholar</t>
+          <t>arxiv</t>
         </is>
       </c>
       <c r="I92" s="5" t="n"/>
@@ -4645,33 +4688,33 @@
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>4d9a30b87304</t>
+          <t>d74a5ac7f26d</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>Quantum AI and its Applications in Blockchain Technology</t>
+          <t>Logistic Network Design with a D-Wave Quantum Annealer</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>Ananth C.</t>
+          <t>Yongcheng Ding; Xi Chen; L. Lamata; E. Solano; M. Sanz</t>
         </is>
       </c>
       <c r="E93" s="5" t="inlineStr">
         <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="F93" s="5" t="inlineStr">
-        <is>
-          <t>10.4018/979-8-3373-1657-4</t>
-        </is>
-      </c>
-      <c r="G93" s="5" t="inlineStr"/>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="F93" s="5" t="inlineStr"/>
+      <c r="G93" s="5" t="inlineStr">
+        <is>
+          <t>Logistic network design is an abstract optimization problem which, under the assumption of minimal cost, determines the optimal configuration of infrastructures and facilities of the supply chain based on customer demand. With the solutions at hand, key economic decisions are taken about the location, number, as well as size of manufacturing facilities and warehouses. Therefore, an efficient method to address this question, which is known to be NP-hard, has relevant financial consequences. Here, we propose a hybrid classical-quantum annealing algorithm to accurately obtain the optimal solution. The cost function with constraints is translated to a spin Hamiltonian, whose ground state is supposed to encode the searched result. This algorithm is realized on a D-Wave quantum computer and positively compared with the results of the best classical optimization algorithms. This work shows that state-of-the-art quantum annealers may address useful chain supply problems.</t>
+        </is>
+      </c>
       <c r="H93" s="5" t="inlineStr">
         <is>
-          <t>scopus</t>
+          <t>semantic_scholar</t>
         </is>
       </c>
       <c r="I93" s="5" t="n"/>
@@ -4685,33 +4728,37 @@
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>b854763516fb</t>
+          <t>16ee72565789</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>Current status and prospect of quantum communication on space-based platforms</t>
+          <t>Impact of Quantum Commerce on the Future of Global Business</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>Zheng D.</t>
+          <t>TMBU Bhagalpur Univ. Dept. of Commerce &amp; Bus Administration; Dr. Paranav Shankar</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="F94" s="5" t="inlineStr">
         <is>
-          <t>10.19650/j.cnki.cjsi.J2311270</t>
-        </is>
-      </c>
-      <c r="G94" s="5" t="inlineStr"/>
+          <t>10.55041/ijsrem56196</t>
+        </is>
+      </c>
+      <c r="G94" s="5" t="inlineStr">
+        <is>
+          <t>Abstract The rapid advancement of technology, coupled with the global interconnectivity, has led to the emergence of quantum commerce (Q-commerce) as a significant paradigm shift in the business world. Quantum commerce represents a new form of digital commerce that combines aspects of quantum computing, artificial intelligence (AI), block chain, and next-generation networks. This transformative model promises to revolutionize the way businesses interact with customers, manage data, and optimize operations. The global impact of quantum commerce will be far-reaching, influencing various industries, economic dynamics, and business models. This note explores the key components of quantum commerce, its potential impacts on businesses globally, and the opportunities and challenges it will bring in the coming years. Key-words: Quantum Computing, Quantum Technology, Business Transformation, AI and Quantum Integration, Data Security, Quantum Cryptography, Supply chain Optimization, Financial Service Innovation, Disruptive Innovation, Global Trade, Digital Ecosystems, Quantum Algorithms, Block chain and Quantum, Market Efficiency, Competitive Advantage Business Intelligence, Automation, Tech Adoption, Cross-border commerce, Cyber security etc.</t>
+        </is>
+      </c>
       <c r="H94" s="5" t="inlineStr">
         <is>
-          <t>scopus</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="I94" s="5" t="n"/>
@@ -4725,37 +4772,37 @@
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>ae3214daf9c0</t>
+          <t>62ed79c3a22b</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>From Classical to Quantum: The Future of Advanced Analytics with Quantum Computing</t>
+          <t>Teaching quantum information technologies and a practical module for online and offline undergraduate students</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>Bhanu Raju Nida</t>
+          <t>Hao Tang; Tianyu Wang; Ruoxi Shi; Xian‐Min Jin</t>
         </is>
       </c>
       <c r="E95" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F95" s="5" t="inlineStr">
         <is>
-          <t>10.54660/.ijmrge.2025.6.2.587-593</t>
+          <t>10.48550/arxiv.2112.06548</t>
         </is>
       </c>
       <c r="G95" s="5" t="inlineStr">
         <is>
-          <t>The rapid growth of complex analytics has moved from classical statistical methods to the AI-based systems using large data sets for predictive and prescriptive decision making. Although the traditional computing systems have greatly improved decision-making abilities, they have their limitations in the complex and large-scale data collection and real time processing and analysis. Quantum computing is a major step forward in the enhancement of computational capability with the help of principles such as superposition and entanglement to perform several calculations at a time. This paper explores the integration of quantum computing with data science and the prospect of quantum computing outperforming the classical computing in optimization, machine learning, predictive analytics and natural language processing. Classical and quantum analytics models are compared, quantum computing platforms are evaluated through experimental testing, and computational efficiency is compared through benchmarking. The benefits of quantum enhanced analytics however are illustrated through the examination of empirical case studies from the finance, healthcare, supply chain and AI marketing sectors. Nevertheless, there are challenges including hardware limitations, algorithmic constraints, and integration barrier. Quantum computing is expected to redefine analytics by offering enhanced computational speed and accuracy. This research highlights the need for more efficient and scalable quantum algorithms, quantum error correction, and quantum-classical hybrid models to make the quantum theory applicable to practical use in business intelligence and big data analytics.</t>
+          <t>Quantum Information Technologies and a Practical Module is a new course we launch at Shanghai Jiao Tong University targeting at the undergraduate students who major in a variety of engineering disciplines. We develop a holistic curriculum for quantum computing covering the quantum hardware, quantum algorithms and applications. The quantum computing approaches include the universal digital quantum computing, analog quantum computing and the hybrid quantum-classical variational quantum computing that is tailored to the noisy intermediate-scale quantum (NISQ) technologies nowadays. Besides, we set a practical module to bring student closer to the real industry needs. The students would form a team of three to use any quantum approach to solve a problem in fields like optimization, finance, machine learning, chemistry and biology. Further, this course is selected into the Jiao Tong Global Virtual Classroom Initiative, so that it is open to global students in Association of Pacific Rim Universities at the same time with the offline students, in a specifically updated classroom. The efforts in curriculum development, practical module setting and blended learning make this course a good case study for education on quantum sciences and technologies.</t>
         </is>
       </c>
       <c r="H95" s="5" t="inlineStr">
         <is>
-          <t>semantic_scholar</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="I95" s="5" t="n"/>
@@ -4769,33 +4816,37 @@
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>e3f607c31738</t>
+          <t>64b4914da5c2</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>Quantum Portfolio Optimization with Investment Bands and Target Volatility</t>
+          <t>Quantum Fuzzy Regression Model for Uncertain Environment</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>Samuel Palmer; Serkan Sahin; Rodrigo Hernandez; Samuel Mugel; Roman Orus</t>
+          <t>Tiansu Chen; Shi bin Zhang; Qirun Wang; Yan Chang</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
         <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="F96" s="5" t="inlineStr"/>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F96" s="5" t="inlineStr">
+        <is>
+          <t>10.32604/cmc.2023.033284</t>
+        </is>
+      </c>
       <c r="G96" s="5" t="inlineStr">
         <is>
-          <t>In this paper we show how to implement in a simple way some complex real-life constraints on the portfolio optimization problem, so that it becomes amenable to quantum optimization algorithms. Specifically, first we explain how to obtain the best investment portfolio with a given target risk. This is important in order to produce portfolios with different risk profiles, as typically offered by financial institutions. Second, we show how to implement individual investment bands, i.e., minimum and maximum possible investments for each asset. This is also important in order to impose diversification and avoid corner solutions. Quite remarkably, we show how to build the constrained cost function as a quadratic binary optimization (QUBO) problem, this being the natural input of quantum annealers. The validity of our implementation is proven by finding the optimal portfolios, using D-Wave Hybrid and its Advantage quantum processor, on portfolios built with all the assets from S&amp;P100 and S&amp;P500. Our results show how practical daily constraints found in quantitative finance can be implemented in a simple way in current NISQ quantum processors, with real data, and under realistic market conditions. In combination with clustering algorithms, our methods would allow to replicate the behaviour of more complex indexes, such as Nasdaq Composite or others, in turn being particularly useful to build and replicate Exchange Traded Funds (ETF).</t>
+          <t>In the era of big data, traditional regression models cannot deal with uncertain big data efficiently and accurately. In order to make up for this deficiency, this paper proposes a quantum fuzzy regression model, which uses fuzzy theory to describe the uncertainty in big data sets and uses quantum computing to exponentially improve the efficiency of data set preprocessing and parameter estimation. In this paper, data envelopment analysis (DEA) is used to calculate the degree of importance of each data point. Meanwhile, Harrow, Hassidim and Lloyd (HHL) algorithm and quantum swap circuits are used to improve the efficiency of high-dimensional data matrix calculation. The application of the quantum fuzzy regression model to small-scale financial data proves that its accuracy is greatly improved compared with the quantum regression model. Moreover, due to the introduction of quantum computing, the speed of dealing with high-dimensional data matrix has an exponential improvement compared with the fuzzy regression model. The quantum fuzzy regression model proposed in this paper combines the advantages of fuzzy theory and quantum computing which can efficiently calculate high-dimensional data matrix and complete parameter estimation using quantum computing while retaining the uncertainty in big data. Thus, it is a new model for efficient and accurate big data processing in uncertain environments.</t>
         </is>
       </c>
       <c r="H96" s="5" t="inlineStr">
         <is>
-          <t>arxiv</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="I96" s="5" t="n"/>
@@ -4809,33 +4860,37 @@
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>9e79a3ba95a4</t>
+          <t>fd9854ee7cd9</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>Simulation of an inhomogeneous Fermi gas through the BCS-BEC crossover</t>
+          <t>Addressing Exponential Scale Problems at Infosys</t>
         </is>
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>R. Jauregui; R. Paredes; L. Rosales-Zarate; G. Toledo Sanchez</t>
+          <t>Vittal Setty</t>
         </is>
       </c>
       <c r="E97" s="5" t="inlineStr">
         <is>
-          <t>2008</t>
-        </is>
-      </c>
-      <c r="F97" s="5" t="inlineStr"/>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F97" s="5" t="inlineStr">
+        <is>
+          <t>10.1109/hipc58850.2023.00014</t>
+        </is>
+      </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>We perform a variational quantum Monte Carlo simulation of the transition from a Bardeen-Cooper-Schrieffer superfluid (BCS) to a Bose-Einstein condensate (BEC) at zero temperature. The model Hamiltonian involves an attractive short range two body interaction and the atoms number $2N =330$ is chosen so that, in the non-interacting limit, the ground state function corresponds to a closed shell configuration. The system is then characterized by the s-wave scattering length $a$ of the two-particle collisions in the gas, which is varied from negative to positive values, and the Fermi wave number $k_F$. Based on an extensive analysis of the s-wave two-body problem, one parameter variational many-body wave functions are proposed to describe the ground state of the interacting Fermi gas from BCS to BEC states. We exploit properties of antisymmetrized many-body functions to develop efficient techniques that permit variational calculations for a large number of particles. It is shown that a virial relation between the energy per particle and the trapping energy is approximately valid for $-0.1&lt;1/k_Fa&lt;3.4$. The influence of the harmonic trap and the interaction potential as exhibited in two-body correlation functions is also analyzed.</t>
+          <t>In this talk I am going to share the use cases for high performance computing for the many clients oflnfosys in the domains of Logistics, Finance, Pharma, Manufacturing andthe like. What are some of the problems of exponential size that we have encountered? And what are the technology solutions that Infosys has adopted to address these use cases? What is the role of Quantum Computing for example in this space? What is the potential of this technology for solving large problems of exponential scale in optimization, simulation, drug discovery, Cyber security and ML? These are some of the questions we will get to explore in this talk. Secondly, we will see the opportunities and challenges in using LLMs in the SDLC process. And lastly, we will discuss the challenges in using enterprise data for experimenting with new cutting edge OS/third party solutions. What worked for us, and what did not? Maybe your research and ideas can address some of the gaps we are facing. Come join this talk to explore opportunities on how best we can collaborate.</t>
         </is>
       </c>
       <c r="H97" s="5" t="inlineStr">
         <is>
-          <t>arxiv</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="I97" s="5" t="n"/>
@@ -4849,33 +4904,37 @@
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>b10591681791</t>
+          <t>d461b3fdb4fe</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>Enhancing Knapsack-based Financial Portfolio Optimization Using Quantum Approximate Optimization Algorithm</t>
+          <t>Portfolio Optimization of 40 Stocks Using the DWave Quantum Annealer</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>Chansreynich Huot; Kimleang Kea; Tae-Kyung Kim; Youngsun Han</t>
+          <t>Jeffrey P. Cohen; Alex Khan; Clark Alexander</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr">
         <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="F98" s="5" t="inlineStr"/>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="F98" s="5" t="inlineStr">
+        <is>
+          <t>10.48550/arxiv.2007.01430</t>
+        </is>
+      </c>
       <c r="G98" s="5" t="inlineStr">
         <is>
-          <t>Portfolio optimization is a primary component of the decision-making process in finance, aiming to tactfully allocate assets to achieve optimal returns while considering various constraints. Herein, we proposed a method that uses the knapsack-based portfolio optimization problem and incorporates the quantum computing capabilities of the quantum walk mixer with the quantum approximate optimization algorithm (QAOA) to address the challenges presented by the NP-hard problem. Additionally, we present the sequential procedure of our suggested approach and demonstrate empirical proof to illustrate the effectiveness of the proposed method in finding the optimal asset allocations across various constraints and asset choices. Moreover, we discuss the effectiveness of the QAOA components in relation to our proposed method. Consequently, our study successfully achieves the approximate ratio of the portfolio optimization technique using a circuit layer of p&gt;=3, compared to the classical best-known solution of the knapsack problem. Our proposed methods potentially contribute to the growing field of quantum finance by offering insights into the potential benefits of employing quantum algorithms for complex optimization tasks in financial portfolio management.</t>
+          <t>We investigate the use of quantum computers for building a portfolio out of a universe of U.S. listed, liquid equities that contains an optimal set of stocks. Starting from historical market data, we look at various problem formulations on the D-Wave Systems Inc. D-Wave 2000Q(TM) System (hereafter called DWave) to find the optimal risk vs return portfolio; an optimized portfolio based on the Markowitz formulation and the Sharpe ratio, a simplified Chicago Quantum Ratio (CQR), then a new Chicago Quantum Net Score (CQNS). We approach this first classically, then by our new method on DWave. Our results show that practitioners can use a DWave to select attractive portfolios out of 40 U.S. liquid equities.</t>
         </is>
       </c>
       <c r="H98" s="5" t="inlineStr">
         <is>
-          <t>arxiv</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="I98" s="5" t="n"/>
@@ -4889,37 +4948,37 @@
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>48554ad14632</t>
+          <t>38c9c05fedf3</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>Ground-state statistics from annealing algorithms: Quantum vs classical approaches</t>
+          <t>Integrating SAP ERP with Emerging Technologies (IoT, AI, Blockchain): Challenges and Opportunities for Professionals</t>
         </is>
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>Yoshiki Matsuda; Hidetoshi Nishimori; Helmut G Katzgraber</t>
+          <t>Siva Reddy Pulluru</t>
         </is>
       </c>
       <c r="E99" s="5" t="inlineStr">
         <is>
-          <t>2008</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="F99" s="5" t="inlineStr">
         <is>
-          <t>10.1088/1742-6596/143/1/012003</t>
+          <t>10.5281/zenodo.18317672</t>
         </is>
       </c>
       <c r="G99" s="5" t="inlineStr">
         <is>
-          <t>We study the performance of quantum annealing for systems with ground-state degeneracy by directly solving the Schrödinger equation for small systems and quantum Monte Carlo simulations for larger systems. The results indicate that naive quantum annealing using a transverse field may not be well suited to identify all degenerate ground-state configurations, although the value of the ground-state energy is often efficiently estimated. An introduction of quantum transitions to all states with equal weights is shown to greatly improve the situation but with a sacrifice in the annealing time. We also clarify the relation between the spin configurations in the degenerate ground states and the probabilities that those states are obtained by quantum annealing. The strengths and weaknesses of quantum annealing for problems with degenerate ground states are discussed in comparison with classical simulated annealing.</t>
+          <t>Advanced technology, including the Internet of Things (IoT), along with Artificial Intelligence (AI) and blockchain technology, is changing the ways businesses operate. With IoT being utilized in manufacturing and logistics, and energy sectors, companies are receiving real-time information on operations. AI enables cognitive business processes, including Fraud Detection, Smart Procurement, and Automated Customer Service. Blockchain gives organizations a way to build Trusted Transaction Ecosystems for tracking pharmaceuticals, tracing food products, and providing Financial Services. The integration of these technologies transforms traditional SAP ERP Systems into Intelligent Decision-Making Platforms. While the integration of these technologies has the potential to enhance ERP systems, there are still significant challenges associated with the implementation of these new technologies, including data volume management, security vulnerabilities, and the skill gap. Technical solutions that address these challenges include the implementation of Unified Data Layer (UDL), Edge Computing Architecture, and Hybrid Blockchain solutions. In addition to these technical solutions, SAP Professionals will also see many career opportunities for growth as a result of the integration of IoT, AI, and Blockchain with ERP Systems. Career paths for SAP Professionals will continue to include IoT Architect, AI Engineer, or Blockchain Consultant. New developments like GenAI acceleration, quantum computing integration, and metaverse interfaces will continue to change the integration of the above three technologies with SAP ERP Systems. With new developments will also come new ethical issues related to algorithmic bias and data privacy that will be prevalent over time. Also, the Strategic Imperatives of organizations will require the SAP Professionals to engage in continual learning and adaptation. Organizations will face the challenge of balancing innovation with the necessity of remaining operationally stable and compliant with regulations.</t>
         </is>
       </c>
       <c r="H99" s="5" t="inlineStr">
         <is>
-          <t>arxiv</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="I99" s="5" t="n"/>
@@ -4933,37 +4992,37 @@
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>f9141fada31b</t>
+          <t>3fa357ba078b</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>Autoregressive neural Slater-Jastrow ansatz for variational Monte Carlo simulation</t>
+          <t>Quantum Apocalypse: Fortifying Critical Infrastructure in the Age of Cyber Warfare</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>Stephan Humeniuk; Yuan Wan; Lei Wang</t>
+          <t>Shreyas Kumar; Andreas Klappenecker; Gary Brown; S. Saravanan</t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F100" s="5" t="inlineStr">
         <is>
-          <t>10.21468/SciPostPhys.14.6.171</t>
+          <t>10.34190/eccws.24.1.3757</t>
         </is>
       </c>
       <c r="G100" s="5" t="inlineStr">
         <is>
-          <t>Direct sampling from a Slater determinant is combined with an autoregressive deep neural network as a Jastrow factor into a fully autoregressive Slater-Jastrow ansatz for variational quantum Monte Carlo, which allows for uncorrelated sampling. The elimination of the autocorrelation time leads to a stochastic algorithm with provable cubic scaling (with a potentially large prefactor), i.e. the number of operations for producing an uncorrelated sample and for calculating the local energy scales like $\mathcal{O}(N_s^3)$ with the number of orbitals $N_s$. The implementation is benchmarked on the two-dimensional $t-V$ model of spinless fermions on the square lattice.</t>
+          <t>Quantum attacks on cryptographic systems remain hypothetical but are grounded in strong theoretical foundations. The emergence of quantum computing presents a significant challenge to national security, particularly in protecting critical infrastructures such as energy grids, financial systems, and healthcare networks. Quantum algorithms like Shor’s may soon be capable of breaking widely used cryptographic standards (RSA, ECC, AES), rendering current encryption obsolete and exposing essential services to disruption and data breaches. These vulnerabilities could threaten economic stability and public safety on a national scale. This paper analyzes the risks posed by quantum computing to classical cryptographic frameworks and evaluates quantum-resistant alternatives such as lattice-based, hash-based, and code-based cryptography. It assesses their theoretical soundness and suitability for securing national critical infrastructure. The analysis also explores the dangers of delayed implementation, where postponed adoption of post-quantum cryptography (PQC) could expose systems to future quantum-enabled cyberattacks. Additionally, the paper discusses the challenges of integrating PQC into existing systems, including regulatory compliance, interoperability, and operational readiness. Without coordinated strategies and accelerated transition plans, nations risk severe consequences, including financial disruption, healthcare service breakdowns, and energy supply chain failures. Finally, the study highlights the need for international cooperation, policy alignment, and robust testing to ensure the effective deployment of quantum-resistant solutions. Prompt action is essential to preserve the confidentiality, integrity, and availability of vital national systems in the face of the advancing quantum threat landscape.</t>
         </is>
       </c>
       <c r="H100" s="5" t="inlineStr">
         <is>
-          <t>arxiv</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="I100" s="5" t="n"/>
@@ -4977,17 +5036,17 @@
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>5ab77e03ac9c</t>
+          <t>b80c0b2a69b6</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>Scalable Emulation of Sign-Problem$-$Free Hamiltonians with Room Temperature p-bits</t>
+          <t>Uncertain fate of fair sampling in quantum annealing</t>
         </is>
       </c>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>Kerem Y. Camsari; Shuvro Chowdhury; Supriyo Datta</t>
+          <t>Mario S. Könz; Guglielmo Mazzola; Andrew J. Ochoa; Helmut G. Katzgraber; Matthias Troyer</t>
         </is>
       </c>
       <c r="E101" s="5" t="inlineStr">
@@ -4997,12 +5056,12 @@
       </c>
       <c r="F101" s="5" t="inlineStr">
         <is>
-          <t>10.1103/PhysRevApplied.12.034061</t>
+          <t>10.1103/PhysRevA.100.030303</t>
         </is>
       </c>
       <c r="G101" s="5" t="inlineStr">
         <is>
-          <t>The growing field of quantum computing is based on the concept of a q-bit which is a delicate superposition of 0 and 1, requiring cryogenic temperatures for its physical realization along with challenging coherent coupling techniques for entangling them. By contrast, a probabilistic bit or a p-bit is a robust classical entity that fluctuates between 0 and 1, and can be implemented at room temperature using present-day technology. Here, we show that a probabilistic coprocessor built out of room temperature p-bits can be used to accelerate simulations of a special class of quantum many-body systems that are sign-problem$-$free or stoquastic, leveraging the well-known Suzuki-Trotter decomposition that maps a $d$-dimensional quantum many body Hamiltonian to a $d$+1-dimensional classical Hamiltonian. This mapping allows an efficient emulation of a quantum system by classical computers and is commonly used in software to perform Quantum Monte Carlo (QMC) algorithms. By contrast, we show that a compact, embedded MTJ-based coprocessor can serve as a highly efficient hardware-accelerator for such QMC algorithms providing several orders of magnitude improvement in speed compared to optimized CPU implementations. Using realistic device-level SPICE simulations we demonstrate that the correct quantum correlations can be obtained using a classical p-circuit built with existing technology and operating at room temperature. The proposed coprocessor can serve as a tool to study stoquastic quantum many-body systems, overcoming challenges associated with physical quantum annealers.</t>
+          <t>Recently, it was demonstrated both theoretically and experimentally on the D-Wave quantum annealer that transverse-field quantum annealing does not find all ground states with equal probability. In particular, it was proposed that more complex driver Hamiltonians beyond transverse fields might mitigate this shortcoming. Here, we investigate the mechanisms of (un)fair sampling in quantum annealing. While higher-order terms can improve the sampling for selected small problems, we present multiple counterexamples where driver Hamiltonians that go beyond transverse fields do not remove the sampling bias. Using perturbation theory we explain why this is the case. In addition, we present large-scale quantum Monte Carlo simulations for spin glasses with known degeneracy in two space dimensions and demonstrate that the fair-sampling performance of quadratic driver terms is comparable to standard transverse-field drivers. Our results suggest that quantum annealing machines are not well suited for sampling applications, unless post-processing techniques to improve the sampling are applied.</t>
         </is>
       </c>
       <c r="H101" s="5" t="inlineStr">
@@ -5051,7 +5110,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="I2 I3 I4 I5 I6 I7 I8 I9 I10 I11 I12 I13 I14 I15 I16 I17 I18 I19 I20 I21 I22 I23 I24 I25 I26 I27 I28 I29 I30 I31 I32 I33 I34 I35 I36 I37 I38 I39 I40 I41 I42 I43 I44 I45 I46 I47 I48 I49 I50 I51 I52 I53 I54 I55 I56 I57 I58 I59 I60 I61 I62 I63 I64 I65 I66 I67 I68 I69 I70 I71 I72 I73 I74 I75 I76 I77 I78 I79 I80 I81 I82 I83 I84 I85 I86 I87 I88 I89 I90 I91 I92 I93 I94 I95 I96 I97 I98 I99 I100 I101 J2 J3 J4 J5 J6 J7 J8 J9 J10 J11 J12 J13 J14 J15 J16 J17 J18 J19 J20 J21 J22 J23 J24 J25 J26 J27 J28 J29 J30 J31 J32 J33 J34 J35 J36 J37 J38 J39 J40 J41 J42 J43 J44 J45 J46 J47 J48 J49 J50 J51 J52 J53 J54 J55 J56 J57 J58 J59 J60 J61 J62 J63 J64 J65 J66 J67 J68 J69 J70 J71 J72 J73 J74 J75 J76 J77 J78 J79 J80 J81 J82 J83 J84 J85 J86 J87 J88 J89 J90 J91 J92 J93 J94 J95 J96 J97 J98 J99 J100 J101 K2 K3 K4 K5 K6 K7 K8 K9 K10 K11 K12 K13 K14 K15 K16 K17 K18 K19 K20 K21 K22 K23 K24 K25 K26 K27 K28 K29 K30 K31 K32 K33 K34 K35 K36 K37 K38 K39 K40 K41 K42 K43 K44 K45 K46 K47 K48 K49 K50 K51 K52 K53 K54 K55 K56 K57 K58 K59 K60 K61 K62 K63 K64 K65 K66 K67 K68 K69 K70 K71 K72 K73 K74 K75 K76 K77 K78 K79 K80 K81 K82 K83 K84 K85 K86 K87 K88 K89 K90 K91 K92 K93 K94 K95 K96 K97 K98 K99 K100 K101" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid decision" error="Please select: include, exclude, or maybe" type="list">
+    <dataValidation sqref="I2 I3 I4 I5 I6 I7 I8 I9 I10 I11 I12 I13 I14 I15 I16 I17 I18 I19 I20 I21 I22 I23 I24 I25 I26 I27 I28 I29 I30 I31 I32 I33 I34 I35 I36 I37 I38 I39 I40 I41 I42 I43 I44 I45 I46 I47 I48 I49 I50 I51 I52 I53 I54 I55 I56 I57 I58 I59 I60 I61 I62 I63 I64 I65 I66 I67 I68 I69 I70 I71 I72 I73 I74 I75 I76 I77 I78 I79 I80 I81 I82 I83 I84 I85 I86 I87 I88 I89 I90 I91 I92 I93 I94 I95 I96 I97 I98 I99 I100 I101 J2 J3 J4 J5 J6 J7 J8 J9 J10 J11 J12 J13 J14 J15 J16 J17 J18 J19 J20 J21 J22 J23 J24 J25 J26 J27 J28 J29 J30 J31 J32 J33 J34 J35 J36 J37 J38 J39 J40 J41 J42 J43 J44 J45 J46 J47 J48 J49 J50 J51 J52 J53 J54 J55 J56 J57 J58 J59 J60 J61 J62 J63 J64 J65 J66 J67 J68 J69 J70 J71 J72 J73 J74 J75 J76 J77 J78 J79 J80 J81 J82 J83 J84 J85 J86 J87 J88 J89 J90 J91 J92 J93 J94 J95 J96 J97 J98 J99 J100 J101 K2 K3 K4 K5 K6 K7 K8 K9 K10 K11 K12 K13 K14 K15 K16 K17 K18 K19 K20 K21 K22 K23 K24 K25 K26 K27 K28 K29 K30 K31 K32 K33 K34 K35 K36 K37 K38 K39 K40 K41 K42 K43 K44 K45 K46 K47 K48 K49 K50 K51 K52 K53 K54 K55 K56 K57 K58 K59 K60 K61 K62 K63 K64 K65 K66 K67 K68 K69 K70 K71 K72 K73 K74 K75 K76 K77 K78 K79 K80 K81 K82 K83 K84 K85 K86 K87 K88 K89 K90 K91 K92 K93 K94 K95 K96 K97 K98 K99 K100 K101" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid decision" error="Please select: include, exclude, or maybe" promptTitle="Decision" prompt="Select your screening decision" type="list">
       <formula1>"include,exclude,maybe"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5111,7 +5170,7 @@
         </is>
       </c>
       <c r="B3" s="7">
-        <f>COUNTA('Screening'.I2:I101)</f>
+        <f>COUNTA('Screening'!I2:I101)</f>
         <v/>
       </c>
       <c r="C3" s="8">
@@ -5146,7 +5205,7 @@
         </is>
       </c>
       <c r="B6" s="7">
-        <f>COUNTIF('Screening'.I2:I101,"include")</f>
+        <f>COUNTIF('Screening'!I2:I101,"include")</f>
         <v/>
       </c>
       <c r="C6" s="8">
@@ -5161,7 +5220,7 @@
         </is>
       </c>
       <c r="B7" s="7">
-        <f>COUNTIF('Screening'.I2:I101,"exclude")</f>
+        <f>COUNTIF('Screening'!I2:I101,"exclude")</f>
         <v/>
       </c>
       <c r="C7" s="8">
@@ -5176,7 +5235,7 @@
         </is>
       </c>
       <c r="B8" s="7">
-        <f>COUNTIF('Screening'.I2:I101,"maybe")</f>
+        <f>COUNTIF('Screening'!I2:I101,"maybe")</f>
         <v/>
       </c>
       <c r="C8" s="8">

--- a/05_screening/validation_screening.xlsx
+++ b/05_screening/validation_screening.xlsx
@@ -734,7 +734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L101"/>
+  <dimension ref="A1:L102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1551,29 +1551,32 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>6565bcfd2a83</t>
+          <t>3dad37594f28</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>Blockchain: Post-Quantum Security &amp; Legal Economics</t>
+          <t>Synergizing Machine Learning Algorithms with Quantum Computing: A Path to Unprecedented Capabilities</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>Brian Haney</t>
+          <t>Dileep Pulugu; K. Subathra; Srichandana Abbineni; S. Zulaikha Beevi; B. Aishwarya; Sananda Kumar</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="F19" s="5" t="inlineStr"/>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>10.1109/icaccm61117.2024.11058996</t>
+        </is>
+      </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>Blockchain technology is subject to security vulnerabilities resulting from recent developments in quantum computing and cryptography. All the while, the technical complexities of blockchain’s peer-to-peer system require the intervention of third-party intermediaries to facilitate financial transactions across blockchain networks. Current legal scholarship describes blockchain technology as a peer-to-peer system without a central authority, supporting the secure decentralization of economies and financial markets. Yet, with consideration to recent advancements in quantum computing, blockchain technology is not secure. Further, the technology’s legality is subject to the will of the central authorities whose economic systems it seeks to decentralize. 
-This article contributes the first post-quantum analysis of the intersection of blockchain security and law. Additionally, this is the first piece of legal scholarship to analyze the complex relationships between Congress, the Federal Reserve, and blockchain technology in the creation of money. In doing so, this article challenges conventional assumptions relating to blockchain technology’s decentralizing economic impact. Ultimately, this article takes an interdisciplinary approach, drawing on informatics, law, and economics scholarship, to argue blockchain fails to provide a legal or secure means of establishing a peer-to-peer payment system.</t>
+          <t>Quantum machine learning has become a promising field due to the capability to solve the computational issues of classical machine learning models. This research investigates the integration of machine learning and quantum computing with the aim of establishing and utilizing the QML models including QSVM and QNN. Given the large number of experiments on both conventional and quantum enriched datasets, the authors show that quantum machine learning models can be faster and more accurate when compared to Classical models. Furthermore, they provide a practical way for extending current quantum models’ capabilities to fight against available quantum device limitations, achieve higher computation rates and better data handling. Savings in training times and better performance are well-demonstrated in the outcome – especially with large data sets like MNIST. As much as such issues as quantum hardware constraints persist, marrying quantum computing with machine learning expands the ability to solve problems that are big and complicated across several fields including finance, healthcare and AI. This paper therefore encourages more investment on the you need more research and development towards the realization of quantum computing in the realm of machine learning.</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
@@ -1592,17 +1595,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>3dad37594f28</t>
+          <t>261295f1b35c</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>Synergizing Machine Learning Algorithms with Quantum Computing: A Path to Unprecedented Capabilities</t>
+          <t>Review on Second Quantum Revolution Its Opportunities and Challenges</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Dileep Pulugu; K. Subathra; Srichandana Abbineni; S. Zulaikha Beevi; B. Aishwarya; Sananda Kumar</t>
+          <t>Takele Somano; Mahmud Seid; Lakachew Chanie</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -1612,12 +1615,12 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>10.1109/icaccm61117.2024.11058996</t>
+          <t>10.11648/j.ajmp.20241306.11</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>Quantum machine learning has become a promising field due to the capability to solve the computational issues of classical machine learning models. This research investigates the integration of machine learning and quantum computing with the aim of establishing and utilizing the QML models including QSVM and QNN. Given the large number of experiments on both conventional and quantum enriched datasets, the authors show that quantum machine learning models can be faster and more accurate when compared to Classical models. Furthermore, they provide a practical way for extending current quantum models’ capabilities to fight against available quantum device limitations, achieve higher computation rates and better data handling. Savings in training times and better performance are well-demonstrated in the outcome – especially with large data sets like MNIST. As much as such issues as quantum hardware constraints persist, marrying quantum computing with machine learning expands the ability to solve problems that are big and complicated across several fields including finance, healthcare and AI. This paper therefore encourages more investment on the you need more research and development towards the realization of quantum computing in the realm of machine learning.</t>
+          <t>This review explores the Second Quantum Revolution, which builds on the foundations of the first to advance quantum science and technology significantly. We examine the diverse fields under this revolution, including quantum information technologies, quantum electromechanical systems, coherent quantum electronics, quantum optics, and coherent matter technologies. Assess the societal and ethical implications of the second quantum revolution and provide insights into its potential impact on various sectors, including healthcare, finance, communication, and technology, the knowledge dissemination and awareness of the second quantum revolution. The review emphasizes the transformative potential of these advancements for the economy, computing, and communication networks. Additionally, we address the critical challenges that must be overcome, such as the development of fault-tolerant quantum systems and the seamless integration of quantum and classical technologies. Ethical considerations related to privacy, security, and societal impacts are also discussed, highlighting the need for a thoughtful reevaluation of quantum technology&amp;amp;apos;s role in modern society. Ultimately, this review outlines the immense opportunities presented by the Second Quantum Revolution while providing insights into the multifaceted challenges it faces, setting the stage for future research and innovation in this groundbreaking field.</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
@@ -1636,32 +1639,32 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>261295f1b35c</t>
+          <t>034d5ac5f3b5</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>Review on Second Quantum Revolution Its Opportunities and Challenges</t>
+          <t>Post-quantum investigating Cryptography for Data Safeguard Transmission in Future Network Communication</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>Takele Somano; Mahmud Seid; Lakachew Chanie</t>
+          <t>Laith Jasim; M. Sivabharathy; V. Venkataiah; Madhusudhan Reddy; T. Srinivas; P.S. Ramesh</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>10.11648/j.ajmp.20241306.11</t>
+          <t>10.1109/iccies63851.2025.11033076</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>This review explores the Second Quantum Revolution, which builds on the foundations of the first to advance quantum science and technology significantly. We examine the diverse fields under this revolution, including quantum information technologies, quantum electromechanical systems, coherent quantum electronics, quantum optics, and coherent matter technologies. Assess the societal and ethical implications of the second quantum revolution and provide insights into its potential impact on various sectors, including healthcare, finance, communication, and technology, the knowledge dissemination and awareness of the second quantum revolution. The review emphasizes the transformative potential of these advancements for the economy, computing, and communication networks. Additionally, we address the critical challenges that must be overcome, such as the development of fault-tolerant quantum systems and the seamless integration of quantum and classical technologies. Ethical considerations related to privacy, security, and societal impacts are also discussed, highlighting the need for a thoughtful reevaluation of quantum technology&amp;amp;apos;s role in modern society. Ultimately, this review outlines the immense opportunities presented by the Second Quantum Revolution while providing insights into the multifaceted challenges it faces, setting the stage for future research and innovation in this groundbreaking field.</t>
+          <t>With the fast-paced development of quantum computing, classical cryptographic techniques are under severe security threats, prompting the need for post-quantum cryptographic mechanisms for secure data exchange in next-generation network communications. Post-quantum cryptography seeks to protect sensitive data against quantum attacks to provide long-term data confidentiality. But all current cryptographic techniques, including RSA and ECC, are susceptible to quantum algorithms like Shor's algorithm, which can factor large integers efficiently and break discrete logarithm problems, making classical cryptography useless. There is thus a pressing need for quantum attack-resistant encryption mechanisms. To meet these challenges, we introduce the Lattice-Based Cryptography with Hybrid Key Exchange (L-CHKE) framework, which combines lattice-based encryption with a hybrid key exchange mechanism. Lattice-based cryptography provides quantum resistance because it is based on hard mathematical problems such as Learning with Errors (LWE), which provides greater security and efficiency. The designed L-CHKE algorithm strengthens secure key distribution and authentication for next-generation networks, especially for applications needing strong security like financial transactions, IoT, and military communications. Experimental results verify that L-CHKE noticeably boosts computational efficiency by 98.45%, decreases key exchange latency by 42.56%, and guarantees robustness by 97.64% against quantum attacks, indicating it is an appropriate solution for post-quantum secure communication.</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
@@ -1680,37 +1683,33 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>034d5ac5f3b5</t>
+          <t>04b242aeef3f</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Post-quantum investigating Cryptography for Data Safeguard Transmission in Future Network Communication</t>
+          <t>A quantum artificial neural network for stock closing price prediction</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Laith Jasim; M. Sivabharathy; V. Venkataiah; Madhusudhan Reddy; T. Srinivas; P.S. Ramesh</t>
+          <t>Liu G.</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>10.1109/iccies63851.2025.11033076</t>
-        </is>
-      </c>
-      <c r="G22" s="5" t="inlineStr">
-        <is>
-          <t>With the fast-paced development of quantum computing, classical cryptographic techniques are under severe security threats, prompting the need for post-quantum cryptographic mechanisms for secure data exchange in next-generation network communications. Post-quantum cryptography seeks to protect sensitive data against quantum attacks to provide long-term data confidentiality. But all current cryptographic techniques, including RSA and ECC, are susceptible to quantum algorithms like Shor's algorithm, which can factor large integers efficiently and break discrete logarithm problems, making classical cryptography useless. There is thus a pressing need for quantum attack-resistant encryption mechanisms. To meet these challenges, we introduce the Lattice-Based Cryptography with Hybrid Key Exchange (L-CHKE) framework, which combines lattice-based encryption with a hybrid key exchange mechanism. Lattice-based cryptography provides quantum resistance because it is based on hard mathematical problems such as Learning with Errors (LWE), which provides greater security and efficiency. The designed L-CHKE algorithm strengthens secure key distribution and authentication for next-generation networks, especially for applications needing strong security like financial transactions, IoT, and military communications. Experimental results verify that L-CHKE noticeably boosts computational efficiency by 98.45%, decreases key exchange latency by 42.56%, and guarantees robustness by 97.64% against quantum attacks, indicating it is an appropriate solution for post-quantum secure communication.</t>
-        </is>
-      </c>
+          <t>10.1016/j.ins.2022.03.064</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr"/>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>openalex</t>
+          <t>scopus</t>
         </is>
       </c>
       <c r="I22" s="5" t="n"/>
@@ -1724,17 +1723,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>04b242aeef3f</t>
+          <t>50662cd90dfb</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>A quantum artificial neural network for stock closing price prediction</t>
+          <t>Unlocking the Power of Quantum Mechanics for Machine Learning</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>Liu G.</t>
+          <t>Brahmaleen Kaur Sidhu</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -1744,13 +1743,17 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>10.1016/j.ins.2022.03.064</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="inlineStr"/>
+          <t>10.21275/sr24427201406</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>Machine learning has radically changed the way problems in various disciplines are solved but faces limitations in tackling increasingly complex and high-dimensional data. Quantum machine learning emerges as a burgeoning paradigm, harnessing the principles of quantum mechanics to potentially surpass classical approaches. This paper delves into the core concepts of quantum machine learning, exploring its algorithms and challenges. The incorporation of quantum mechanics in machine learning algorithms offers a more expressive way to represent data compared to classical methods by capturing intricate relationships within complex datasets. Superposition and entanglement empower the development of algorithms that can tackle computationally expensive tasks in classical machine learning, particularly in high-dimensional spaces. Limited qubit count and susceptibility to noise in current quantum computers hinder the practical implementation of quantum machine learning for large-scale problems. Designing and optimizing efficient quantum algorithms tailored to specific machine learning tasks remains an active area of research. The paper concludes by highlighting the immense potential of quantum machine learning to revolutionize various fields, from materials science and drug discovery to finance and artificial intelligence.</t>
+        </is>
+      </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>scopus</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="I23" s="5" t="n"/>
@@ -1764,37 +1767,37 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>50662cd90dfb</t>
+          <t>80e2927c7aac</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>Unlocking the Power of Quantum Mechanics for Machine Learning</t>
+          <t>Retail Fraud Detection via Log Analysis and Stream Processing</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Brahmaleen Kaur Sidhu</t>
+          <t>Arjun Sirangi</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>10.21275/sr24427201406</t>
+          <t>10.52710/cfs.678</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>Machine learning has radically changed the way problems in various disciplines are solved but faces limitations in tackling increasingly complex and high-dimensional data. Quantum machine learning emerges as a burgeoning paradigm, harnessing the principles of quantum mechanics to potentially surpass classical approaches. This paper delves into the core concepts of quantum machine learning, exploring its algorithms and challenges. The incorporation of quantum mechanics in machine learning algorithms offers a more expressive way to represent data compared to classical methods by capturing intricate relationships within complex datasets. Superposition and entanglement empower the development of algorithms that can tackle computationally expensive tasks in classical machine learning, particularly in high-dimensional spaces. Limited qubit count and susceptibility to noise in current quantum computers hinder the practical implementation of quantum machine learning for large-scale problems. Designing and optimizing efficient quantum algorithms tailored to specific machine learning tasks remains an active area of research. The paper concludes by highlighting the immense potential of quantum machine learning to revolutionize various fields, from materials science and drug discovery to finance and artificial intelligence.</t>
+          <t>Retail fraud has evolved into a sophisticated threat in the digital age, necessitating advanced detection mechanisms that leverage real-time data processing. This paper presents a technical framework for detecting retail fraud by combining log analysis with stream processing technologies. We address challenges such as scalability, latency, and concept drift through a hybrid architecture that integrates anomaly detection algorithms (e.g., clustering, graph-based models) with distributed stream processing engines (e.g., Apache Flink, Kafka). Evaluations demonstrate that our approach achieves an F1-score of 0.92 on synthetic transaction datasets, outperforming traditional rule-based systems by 34%. The paper also discusses ethical implications, GDPR compliance, and emerging trends such as blockchain and quantum computing.</t>
         </is>
       </c>
       <c r="H24" s="5" t="inlineStr">
         <is>
-          <t>openalex</t>
+          <t>semantic_scholar</t>
         </is>
       </c>
       <c r="I24" s="5" t="n"/>
@@ -1808,37 +1811,37 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>80e2927c7aac</t>
+          <t>15ecb0ef5f59</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>Retail Fraud Detection via Log Analysis and Stream Processing</t>
+          <t>Design and Development of a Secure Data Encryption and Decryption System</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>Arjun Sirangi</t>
+          <t>Shepherd Mwaekwa Wamulume</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>10.52710/cfs.678</t>
+          <t>10.54105/ijcns.a1435.05010525</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>Retail fraud has evolved into a sophisticated threat in the digital age, necessitating advanced detection mechanisms that leverage real-time data processing. This paper presents a technical framework for detecting retail fraud by combining log analysis with stream processing technologies. We address challenges such as scalability, latency, and concept drift through a hybrid architecture that integrates anomaly detection algorithms (e.g., clustering, graph-based models) with distributed stream processing engines (e.g., Apache Flink, Kafka). Evaluations demonstrate that our approach achieves an F1-score of 0.92 on synthetic transaction datasets, outperforming traditional rule-based systems by 34%. The paper also discusses ethical implications, GDPR compliance, and emerging trends such as blockchain and quantum computing.</t>
+          <t>In an increasingly interconnected world, the need to secure sensitive information has become paramount. This article presents the Design and development of a secure data storage system. An encryption and decryption system aimed at enhancing the confidentiality, integrity, and availability of digital data. The proposed system employs advanced cryptographic algorithms to provide robust protection against unauthorised access, data breaches, and cyberattacks. The design phase emphasises the integration of both symmetric and asymmetric encryption techniques, enabling the system to cater to a diverse range of applications, from secure file storage to encrypted communications. Key Management protocols are implemented to ensure the safe generation, distribution, and storage of encryption keys, a critical component of secure systems. The system was developed using modern programming tools and frameworks, adhering to industry standards such as AES (Advanced Encryption Standard) and RSA (Rivest-Shamir-Adleman). Extensive testing was conducted to evaluate the system’s performance, security resilience, and scalability. Results demonstrate the system’s ability to resist common attacks, including brute force and cryptanalysis, while maintaining high efficiency in data processing. This research contributes to the field of data security by providing a versatile and secure solution that can be adapted for use in industries such as finance, healthcare, and e-commerce. Future work includes integrating post-quantum cryptographic algorithms to prepare for the advent of quantum computing.</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>semantic_scholar</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="I25" s="5" t="n"/>
@@ -1852,32 +1855,32 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>15ecb0ef5f59</t>
+          <t>4513b7aef1d3</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>Design and Development of a Secure Data Encryption and Decryption System</t>
+          <t>Summary: Chicago Quantum Exchange (CQE) Pulse-level Quantum Control Workshop</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Shepherd Mwaekwa Wamulume</t>
+          <t>Kaitlin N. Smith; Gokul Subramanian Ravi; Thomas Alexander; Nicholas T. Bronn; André F. Carvalho; Alba Cervera-Lierta; Frederic T. Chong; Jerry M. Chow; Michael Cubeddu; Akel Hashim; Liang Jiang; Olivia Lanes; Matthew Otten; David Schuster; Pranav Gokhale; Nathan Earnest; Alexey Galda</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>10.54105/ijcns.a1435.05010525</t>
+          <t>10.48550/arxiv.2202.13600</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>In an increasingly interconnected world, the need to secure sensitive information has become paramount. This article presents the Design and development of a secure data storage system. An encryption and decryption system aimed at enhancing the confidentiality, integrity, and availability of digital data. The proposed system employs advanced cryptographic algorithms to provide robust protection against unauthorised access, data breaches, and cyberattacks. The design phase emphasises the integration of both symmetric and asymmetric encryption techniques, enabling the system to cater to a diverse range of applications, from secure file storage to encrypted communications. Key Management protocols are implemented to ensure the safe generation, distribution, and storage of encryption keys, a critical component of secure systems. The system was developed using modern programming tools and frameworks, adhering to industry standards such as AES (Advanced Encryption Standard) and RSA (Rivest-Shamir-Adleman). Extensive testing was conducted to evaluate the system’s performance, security resilience, and scalability. Results demonstrate the system’s ability to resist common attacks, including brute force and cryptanalysis, while maintaining high efficiency in data processing. This research contributes to the field of data security by providing a versatile and secure solution that can be adapted for use in industries such as finance, healthcare, and e-commerce. Future work includes integrating post-quantum cryptographic algorithms to prepare for the advent of quantum computing.</t>
+          <t>Quantum information processing holds great promise for pushing beyond the current frontiers in computing. Specifically, quantum computation promises to accelerate the solving of certain problems, and there are many opportunities for innovation based on applications in chemistry, engineering, and finance. To harness the full potential of quantum computing, however, we must not only place emphasis on manufacturing better qubits, advancing our algorithms, and developing quantum software. To scale devices to the fault tolerant regime, we must refine device-level quantum control. On May 17-18, 2021, the Chicago Quantum Exchange (CQE) partnered with IBM Quantum and Super.tech to host the Pulse-level Quantum Control Workshop. At the workshop, representatives from academia, national labs, and industry addressed the importance of fine-tuning quantum processing at the physical layer. The purpose of this report is to summarize the topics of this meeting for the quantum community at large.</t>
         </is>
       </c>
       <c r="H26" s="5" t="inlineStr">
@@ -1896,32 +1899,32 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>4513b7aef1d3</t>
+          <t>3da55df6ffd8</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>Summary: Chicago Quantum Exchange (CQE) Pulse-level Quantum Control Workshop</t>
+          <t>Quantum-Based Stock Price Forecasting with Stop Loss and False Breakout Analysis</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>Kaitlin N. Smith; Gokul Subramanian Ravi; Thomas Alexander; Nicholas T. Bronn; André F. Carvalho; Alba Cervera-Lierta; Frederic T. Chong; Jerry M. Chow; Michael Cubeddu; Akel Hashim; Liang Jiang; Olivia Lanes; Matthew Otten; David Schuster; Pranav Gokhale; Nathan Earnest; Alexey Galda</t>
+          <t>Daniel Sylvinson Muthiah Ravinson; K. Maharajan</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>10.48550/arxiv.2202.13600</t>
+          <t>10.1109/asiancon66527.2025.11280952</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>Quantum information processing holds great promise for pushing beyond the current frontiers in computing. Specifically, quantum computation promises to accelerate the solving of certain problems, and there are many opportunities for innovation based on applications in chemistry, engineering, and finance. To harness the full potential of quantum computing, however, we must not only place emphasis on manufacturing better qubits, advancing our algorithms, and developing quantum software. To scale devices to the fault tolerant regime, we must refine device-level quantum control. On May 17-18, 2021, the Chicago Quantum Exchange (CQE) partnered with IBM Quantum and Super.tech to host the Pulse-level Quantum Control Workshop. At the workshop, representatives from academia, national labs, and industry addressed the importance of fine-tuning quantum processing at the physical layer. The purpose of this report is to summarize the topics of this meeting for the quantum community at large.</t>
+          <t>This research work introduces a novel quantum computing approach to stock price forecasting that leverages the power of quantum algorithms for enhanced predictive accuracy and risk management. This comprehensive framework that integrates Quantum Neural Networks (QNN), Quantum Support Vector Machines (QSVM), and Quantum Amplitude Estimation (QAE) to create a robust prediction system capable of navigating complex market dynamics. This approach goes beyond traditional quantum machine learning by incorporating specialized components for stop loss optimization and false breakout detection-critical elements for practical trading systems that are often overlooked in theoretical models. Experimental results across multiple market sectors during the 2018-2022 period demonstrates that this quantum-based framework achieves a 23.6% improvement in directional accuracy and a 31.4% enhancement in risk-adjusted returns compared to classical machine learning benchmarks. The model exhibits particular strength during high volatility periods, where quantum superposition and entanglement properties efficiently capture complex market patterns that elude classical algorithms. This research bridges the gap between theoretical quantum computing advantages and practical financial applications, offering significant implications for the future of algorithmic trading as quantum hardware continues to advance.</t>
         </is>
       </c>
       <c r="H27" s="5" t="inlineStr">
@@ -1940,32 +1943,32 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>3da55df6ffd8</t>
+          <t>fab168b13a96</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>Quantum-Based Stock Price Forecasting with Stop Loss and False Breakout Analysis</t>
+          <t>The Prospects of Quantum Computing for Quantitative Finance and Beyond</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Daniel Sylvinson Muthiah Ravinson; K. Maharajan</t>
+          <t>Yen-Jui Chang; Ming-Fong Sie; Shih-Wei Liao; Ching‐Ray Chang</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>10.1109/asiancon66527.2025.11280952</t>
+          <t>10.1109/mnano.2023.3249501</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>This research work introduces a novel quantum computing approach to stock price forecasting that leverages the power of quantum algorithms for enhanced predictive accuracy and risk management. This comprehensive framework that integrates Quantum Neural Networks (QNN), Quantum Support Vector Machines (QSVM), and Quantum Amplitude Estimation (QAE) to create a robust prediction system capable of navigating complex market dynamics. This approach goes beyond traditional quantum machine learning by incorporating specialized components for stop loss optimization and false breakout detection-critical elements for practical trading systems that are often overlooked in theoretical models. Experimental results across multiple market sectors during the 2018-2022 period demonstrates that this quantum-based framework achieves a 23.6% improvement in directional accuracy and a 31.4% enhancement in risk-adjusted returns compared to classical machine learning benchmarks. The model exhibits particular strength during high volatility periods, where quantum superposition and entanglement properties efficiently capture complex market patterns that elude classical algorithms. This research bridges the gap between theoretical quantum computing advantages and practical financial applications, offering significant implications for the future of algorithmic trading as quantum hardware continues to advance.</t>
+          <t>Quantum computation holds the promise of highly efficient algorithms, provides exponential speedups for specific technologically significant problems, plays the most promising role in quantum technological progress, and has transformative potential in numerous industry sectors. In quantum computing, finance is recognized as one of the most beneficial areas because of the potential for many financial cases that can be solved by quantum algorithms suitable for noisy-intermedia-scale quantum(NISQ) computers. The benefits of quantum computing are colossal time and computational memory reduction with which the computational tasks are performed, which leads to the accuracy of the computations. This paper presents a comprehensive summary of quantum computing for traditional and Blockchain financial applications.</t>
         </is>
       </c>
       <c r="H28" s="5" t="inlineStr">
@@ -1984,37 +1987,37 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>fab168b13a96</t>
+          <t>526fcec10f82</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>The Prospects of Quantum Computing for Quantitative Finance and Beyond</t>
+          <t>Towards Prediction of Financial Crashes with a D-Wave Quantum Computer</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Yen-Jui Chang; Ming-Fong Sie; Shih-Wei Liao; Ching‐Ray Chang</t>
+          <t>Yongcheng Ding; Javier Gonzalez-Conde; Lucas Lamata; José D. Martín-Guerrero; Enrique Lizaso; Samuel Mugel; Xi Chen; Román Orús; Enrique Solano; Mikel Sanz</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>10.1109/mnano.2023.3249501</t>
+          <t>10.3390/e25020323</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>Quantum computation holds the promise of highly efficient algorithms, provides exponential speedups for specific technologically significant problems, plays the most promising role in quantum technological progress, and has transformative potential in numerous industry sectors. In quantum computing, finance is recognized as one of the most beneficial areas because of the potential for many financial cases that can be solved by quantum algorithms suitable for noisy-intermedia-scale quantum(NISQ) computers. The benefits of quantum computing are colossal time and computational memory reduction with which the computational tasks are performed, which leads to the accuracy of the computations. This paper presents a comprehensive summary of quantum computing for traditional and Blockchain financial applications.</t>
+          <t>Prediction of financial crashes in a complex financial network is known to be an NP-hard problem, which means that no known algorithm can guarantee to find optimal solutions efficiently. We experimentally explore a novel approach to this problem by using a D-Wave quantum computer, benchmarking its performance for attaining financial equilibrium. To be specific, the equilibrium condition of a nonlinear financial model is embedded into a higher-order unconstrained binary optimization (HUBO) problem, which is then transformed to a spin-$1/2$ Hamiltonian with at most two-qubit interactions. The problem is thus equivalent to finding the ground state of an interacting spin Hamiltonian, which can be approximated with a quantum annealer. The size of the simulation is mainly constrained by the necessity of a large quantity of physical qubits representing a logical qubit with the correct connectivity. Our experiment paves the way to codify this quantitative macroeconomics problem in quantum computers.</t>
         </is>
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>openalex</t>
+          <t>arxiv</t>
         </is>
       </c>
       <c r="I29" s="5" t="n"/>
@@ -2028,37 +2031,33 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>526fcec10f82</t>
+          <t>4f07d45db4c6</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>Towards Prediction of Financial Crashes with a D-Wave Quantum Computer</t>
+          <t>Quantum Based Pseudo-Labelling for Hyperspectral Imagery: A Simple and Efficient Semi-Supervised Learning Method for Machine Learning Classifiers</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>Yongcheng Ding; Javier Gonzalez-Conde; Lucas Lamata; José D. Martín-Guerrero; Enrique Lizaso; Samuel Mugel; Xi Chen; Román Orús; Enrique Solano; Mikel Sanz</t>
+          <t>Shaik R.U.</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>10.3390/e25020323</t>
-        </is>
-      </c>
-      <c r="G30" s="5" t="inlineStr">
-        <is>
-          <t>Prediction of financial crashes in a complex financial network is known to be an NP-hard problem, which means that no known algorithm can guarantee to find optimal solutions efficiently. We experimentally explore a novel approach to this problem by using a D-Wave quantum computer, benchmarking its performance for attaining financial equilibrium. To be specific, the equilibrium condition of a nonlinear financial model is embedded into a higher-order unconstrained binary optimization (HUBO) problem, which is then transformed to a spin-$1/2$ Hamiltonian with at most two-qubit interactions. The problem is thus equivalent to finding the ground state of an interacting spin Hamiltonian, which can be approximated with a quantum annealer. The size of the simulation is mainly constrained by the necessity of a large quantity of physical qubits representing a logical qubit with the correct connectivity. Our experiment paves the way to codify this quantitative macroeconomics problem in quantum computers.</t>
-        </is>
-      </c>
+          <t>10.3390/rs14225774</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr"/>
       <c r="H30" s="5" t="inlineStr">
         <is>
-          <t>arxiv</t>
+          <t>scopus</t>
         </is>
       </c>
       <c r="I30" s="5" t="n"/>
@@ -2072,33 +2071,33 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>4f07d45db4c6</t>
+          <t>1f95f99e1c61</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>Quantum Based Pseudo-Labelling for Hyperspectral Imagery: A Simple and Efficient Semi-Supervised Learning Method for Machine Learning Classifiers</t>
+          <t>Diagram-to-Circuit QNLP for Financial Sentiment Analysis</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Shaik R.U.</t>
+          <t>Takayuki Sakuma</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="F31" s="5" t="inlineStr">
-        <is>
-          <t>10.3390/rs14225774</t>
-        </is>
-      </c>
-      <c r="G31" s="5" t="inlineStr"/>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr"/>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>We study a \emph{QDisCoCirc}-inspired, chunked diagram-to-circuit quantum natural language processing (QNLP) model for three-class sentiment classification of financial texts. In our classical simulations, we keep the Hilbert-space dimension manageable by decomposing each sentence into short contiguous chunks. Each chunk is mapped to a shallow quantum circuit, and the resulting Bloch vectors are used as a sequence of quantum tokens. Simple averaging of chunk vectors ignores word order and syntactic roles. We therefore add a small Transformer encoder over the raw Bloch-vector sequence and attach a CCG-based type embedding to each chunk. This hybrid design preserves physically interpretable semantic axes of quantum tokens while allowing the classical side to model word order and long-range dependencies. The sequence model improves test macro-F1 over the averaging baseline and chunk-level attribution further shows that evidential mass concentrates on a small number of chunks, that type embeddings are used more reliably for correctly predicted sentences. For real-world quantum language processing applications in finance, future key challenges include circuit designs that avoid chunking and the design of inter-chunk fusion layers.</t>
+        </is>
+      </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>scopus</t>
+          <t>arxiv</t>
         </is>
       </c>
       <c r="I31" s="5" t="n"/>
@@ -2112,17 +2111,17 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>1f95f99e1c61</t>
+          <t>647f1186df1e</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>Diagram-to-Circuit QNLP for Financial Sentiment Analysis</t>
+          <t>Financial Insights Unleashed: Computational Intelligence in Practice</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Takayuki Sakuma</t>
+          <t>Makhija P.</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -2130,15 +2129,15 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="F32" s="5" t="inlineStr"/>
-      <c r="G32" s="5" t="inlineStr">
-        <is>
-          <t>We study a \emph{QDisCoCirc}-inspired, chunked diagram-to-circuit quantum natural language processing (QNLP) model for three-class sentiment classification of financial texts. In our classical simulations, we keep the Hilbert-space dimension manageable by decomposing each sentence into short contiguous chunks. Each chunk is mapped to a shallow quantum circuit, and the resulting Bloch vectors are used as a sequence of quantum tokens. Simple averaging of chunk vectors ignores word order and syntactic roles. We therefore add a small Transformer encoder over the raw Bloch-vector sequence and attach a CCG-based type embedding to each chunk. This hybrid design preserves physically interpretable semantic axes of quantum tokens while allowing the classical side to model word order and long-range dependencies. The sequence model improves test macro-F1 over the averaging baseline and chunk-level attribution further shows that evidential mass concentrates on a small number of chunks, that type embeddings are used more reliably for correctly predicted sentences. For real-world quantum language processing applications in finance, future key challenges include circuit designs that avoid chunking and the design of inter-chunk fusion layers.</t>
-        </is>
-      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>10.1201/9781998511013-10</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr"/>
       <c r="H32" s="5" t="inlineStr">
         <is>
-          <t>arxiv</t>
+          <t>scopus</t>
         </is>
       </c>
       <c r="I32" s="5" t="n"/>
@@ -2152,33 +2151,37 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>647f1186df1e</t>
+          <t>f9141fada31b</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>Financial Insights Unleashed: Computational Intelligence in Practice</t>
+          <t>Autoregressive neural Slater-Jastrow ansatz for variational Monte Carlo simulation</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Makhija P.</t>
+          <t>Stephan Humeniuk; Yuan Wan; Lei Wang</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>10.1201/9781998511013-10</t>
-        </is>
-      </c>
-      <c r="G33" s="5" t="inlineStr"/>
+          <t>10.21468/SciPostPhys.14.6.171</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>Direct sampling from a Slater determinant is combined with an autoregressive deep neural network as a Jastrow factor into a fully autoregressive Slater-Jastrow ansatz for variational quantum Monte Carlo, which allows for uncorrelated sampling. The elimination of the autocorrelation time leads to a stochastic algorithm with provable cubic scaling (with a potentially large prefactor), i.e. the number of operations for producing an uncorrelated sample and for calculating the local energy scales like $\mathcal{O}(N_s^3)$ with the number of orbitals $N_s$. The implementation is benchmarked on the two-dimensional $t-V$ model of spinless fermions on the square lattice.</t>
+        </is>
+      </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>scopus</t>
+          <t>arxiv</t>
         </is>
       </c>
       <c r="I33" s="5" t="n"/>
@@ -2192,37 +2195,37 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>f9141fada31b</t>
+          <t>d0a8bde2ad2e</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>Autoregressive neural Slater-Jastrow ansatz for variational Monte Carlo simulation</t>
+          <t>A hybrid quantum-classical fusion neural network to improve protein-ligand binding affinity predictions for drug discovery</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Stephan Humeniuk; Yuan Wan; Lei Wang</t>
+          <t>S. Banerjee; S. He Yuxun; Subrahmanyam Konakanchi; Lawal Adewale Ogunfowora; Sumantra Dutta Roy; S. Selvaras; L. Domingo; Mahdi Chehimi; M. Djukic; C. Johnson</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>10.21468/SciPostPhys.14.6.171</t>
+          <t>10.48550/arxiv.2309.03919</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>Direct sampling from a Slater determinant is combined with an autoregressive deep neural network as a Jastrow factor into a fully autoregressive Slater-Jastrow ansatz for variational quantum Monte Carlo, which allows for uncorrelated sampling. The elimination of the autocorrelation time leads to a stochastic algorithm with provable cubic scaling (with a potentially large prefactor), i.e. the number of operations for producing an uncorrelated sample and for calculating the local energy scales like $\mathcal{O}(N_s^3)$ with the number of orbitals $N_s$. The implementation is benchmarked on the two-dimensional $t-V$ model of spinless fermions on the square lattice.</t>
+          <t>The field of drug discovery hinges on the accurate prediction of binding affinity between prospective drug molecules and target proteins, especially when such proteins directly influence disease progression. However, estimating binding affinity demands significant financial and computational resources. While state-of-the-art methodologies employ classical machine learning (ML) techniques, emerging hybrid quantum machine learning (QML) models have shown promise for enhanced performance, owing to their inherent parallelism and capacity to manage exponential increases in data dimensionality. Despite these advances, existing models encounter issues related to convergence stability and prediction accuracy. This paper introduces a novel hybrid quantum-classical deep learning model tailored for binding affinity prediction in drug discovery. Specifically, the proposed model synergistically integrates 3D and spatial graph convolutional neural networks within an optimized quantum architecture. Simulation results demonstrate a 6% improvement in prediction accuracy relative to existing classical models, as well as a significantly more stable convergence performance compared to previous classical approaches.</t>
         </is>
       </c>
       <c r="H34" s="5" t="inlineStr">
         <is>
-          <t>arxiv</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="I34" s="5" t="n"/>
@@ -2236,17 +2239,17 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>d0a8bde2ad2e</t>
+          <t>741e66d789d0</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>A hybrid quantum-classical fusion neural network to improve protein-ligand binding affinity predictions for drug discovery</t>
+          <t>Neural Wave Functions for Superfluids</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>S. Banerjee; S. He Yuxun; Subrahmanyam Konakanchi; Lawal Adewale Ogunfowora; Sumantra Dutta Roy; S. Selvaras; L. Domingo; Mahdi Chehimi; M. Djukic; C. Johnson</t>
+          <t>Wan Tong Lou; Halvard Sutterud; Gino Cassella; W. M. C. Foulkes; Johannes Knolle; David Pfau; James S. Spencer</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -2256,17 +2259,17 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>10.48550/arxiv.2309.03919</t>
+          <t>10.1103/PhysRevX.14.021030</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>The field of drug discovery hinges on the accurate prediction of binding affinity between prospective drug molecules and target proteins, especially when such proteins directly influence disease progression. However, estimating binding affinity demands significant financial and computational resources. While state-of-the-art methodologies employ classical machine learning (ML) techniques, emerging hybrid quantum machine learning (QML) models have shown promise for enhanced performance, owing to their inherent parallelism and capacity to manage exponential increases in data dimensionality. Despite these advances, existing models encounter issues related to convergence stability and prediction accuracy. This paper introduces a novel hybrid quantum-classical deep learning model tailored for binding affinity prediction in drug discovery. Specifically, the proposed model synergistically integrates 3D and spatial graph convolutional neural networks within an optimized quantum architecture. Simulation results demonstrate a 6% improvement in prediction accuracy relative to existing classical models, as well as a significantly more stable convergence performance compared to previous classical approaches.</t>
+          <t>Understanding superfluidity remains a major goal of condensed matter physics. Here we tackle this challenge utilizing the recently developed Fermionic neural network (FermiNet) wave function Ansatz [D. Pfau et al., Phys. Rev. Res. 2, 033429 (2020).] for variational Monte Carlo calculations. We study the unitary Fermi gas, a system with strong, short-range, two-body interactions known to possess a superfluid ground state but difficult to describe quantitatively. We demonstrate key limitations of the FermiNet Ansatz in studying the unitary Fermi gas and propose a simple modification based on the idea of an antisymmetric geminal power singlet (AGPs) wave function. The new AGPs FermiNet outperforms the original FermiNet significantly in paired systems, giving results which are more accurate than fixed-node diffusion Monte Carlo and are consistent with experiment. We prove mathematically that the new Ansatz, which only differs from the original Ansatz by the method of antisymmetrization, is a strict generalization of the original FermiNet architecture, despite the use of fewer parameters. Our approach shares several advantages with the original FermiNet: the use of a neural network removes the need for an underlying basis set; and the flexibility of the network yields extremely accurate results within a variational quantum Monte Carlo framework that provides access to unbiased estimates of arbitrary ground-state expectation values. We discuss how the method can be extended to study other superfluids.</t>
         </is>
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>openalex</t>
+          <t>arxiv</t>
         </is>
       </c>
       <c r="I35" s="5" t="n"/>
@@ -2280,32 +2283,28 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>741e66d789d0</t>
+          <t>3b7d3889d285</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>Neural Wave Functions for Superfluids</t>
+          <t>Quantum Pricing with a Smile: Implementation of Local Volatility Model on Quantum Computer</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>Wan Tong Lou; Halvard Sutterud; Gino Cassella; W. M. C. Foulkes; Johannes Knolle; David Pfau; James S. Spencer</t>
+          <t>Kazuya Kaneko; Koichi Miyamoto; Naoyuki Takeda; Kazuyoshi Yoshino</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="F36" s="5" t="inlineStr">
-        <is>
-          <t>10.1103/PhysRevX.14.021030</t>
-        </is>
-      </c>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr"/>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>Understanding superfluidity remains a major goal of condensed matter physics. Here we tackle this challenge utilizing the recently developed Fermionic neural network (FermiNet) wave function Ansatz [D. Pfau et al., Phys. Rev. Res. 2, 033429 (2020).] for variational Monte Carlo calculations. We study the unitary Fermi gas, a system with strong, short-range, two-body interactions known to possess a superfluid ground state but difficult to describe quantitatively. We demonstrate key limitations of the FermiNet Ansatz in studying the unitary Fermi gas and propose a simple modification based on the idea of an antisymmetric geminal power singlet (AGPs) wave function. The new AGPs FermiNet outperforms the original FermiNet significantly in paired systems, giving results which are more accurate than fixed-node diffusion Monte Carlo and are consistent with experiment. We prove mathematically that the new Ansatz, which only differs from the original Ansatz by the method of antisymmetrization, is a strict generalization of the original FermiNet architecture, despite the use of fewer parameters. Our approach shares several advantages with the original FermiNet: the use of a neural network removes the need for an underlying basis set; and the flexibility of the network yields extremely accurate results within a variational quantum Monte Carlo framework that provides access to unbiased estimates of arbitrary ground-state expectation values. We discuss how the method can be extended to study other superfluids.</t>
+          <t>Applications of the quantum algorithm for Monte Carlo simulation to pricing of financial derivatives have been discussed in previous papers. However, up to now, the pricing model discussed in such papers is Black-Scholes model, which is important but simple. Therefore, it is motivating to consider how to implement more complex models used in practice in financial institutions. In this paper, we then consider the local volatility (LV) model, in which the volatility of the underlying asset price depends on the price and time. We present two types of implementation. One is the register-per-RN way, which is adopted in most of previous papers. In this way, each of random numbers (RNs) required to generate a path of the asset price is generated on a separated register, so the required qubit number increases in proportion to the number of RNs. The other is the PRN-on-a-register way, which is proposed in the author's previous work. In this way, a sequence of pseudo-random numbers (PRNs) generated on a register is used to generate paths of the asset price, so the required qubit number is reduced with a trade-off against circuit depth. We present circuit diagrams for these two implementations in detail and estimate required resources: qubit number and T-count.</t>
         </is>
       </c>
       <c r="H36" s="5" t="inlineStr">
@@ -2324,28 +2323,28 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>3b7d3889d285</t>
+          <t>4513b7aef1d3</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>Quantum Pricing with a Smile: Implementation of Local Volatility Model on Quantum Computer</t>
+          <t>Summary: Chicago Quantum Exchange (CQE) Pulse-level Quantum Control Workshop</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Kazuya Kaneko; Koichi Miyamoto; Naoyuki Takeda; Kazuyoshi Yoshino</t>
+          <t>Kaitlin N. Smith; Gokul Subramanian Ravi; Thomas Alexander; Nicholas T. Bronn; Andre Carvalho; Alba Cervera-Lierta; Frederic T. Chong; Jerry M. Chow; Michael Cubeddu; Akel Hashim; Liang Jiang; Olivia Lanes; Matthew J. Otten; David I. Schuster; Pranav Gokhale; Nathan Earnest; Alexey Galda</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr"/>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>Applications of the quantum algorithm for Monte Carlo simulation to pricing of financial derivatives have been discussed in previous papers. However, up to now, the pricing model discussed in such papers is Black-Scholes model, which is important but simple. Therefore, it is motivating to consider how to implement more complex models used in practice in financial institutions. In this paper, we then consider the local volatility (LV) model, in which the volatility of the underlying asset price depends on the price and time. We present two types of implementation. One is the register-per-RN way, which is adopted in most of previous papers. In this way, each of random numbers (RNs) required to generate a path of the asset price is generated on a separated register, so the required qubit number increases in proportion to the number of RNs. The other is the PRN-on-a-register way, which is proposed in the author's previous work. In this way, a sequence of pseudo-random numbers (PRNs) generated on a register is used to generate paths of the asset price, so the required qubit number is reduced with a trade-off against circuit depth. We present circuit diagrams for these two implementations in detail and estimate required resources: qubit number and T-count.</t>
+          <t>Quantum information processing holds great promise for pushing beyond the current frontiers in computing. Specifically, quantum computation promises to accelerate the solving of certain problems, and there are many opportunities for innovation based on applications in chemistry, engineering, and finance. To harness the full potential of quantum computing, however, we must not only place emphasis on manufacturing better qubits, advancing our algorithms, and developing quantum software. To scale devices to the fault tolerant regime, we must refine device-level quantum control.   On May 17-18, 2021, the Chicago Quantum Exchange (CQE) partnered with IBM Quantum and Super.tech to host the Pulse-level Quantum Control Workshop. At the workshop, representatives from academia, national labs, and industry addressed the importance of fine-tuning quantum processing at the physical layer. The purpose of this report is to summarize the topics of this meeting for the quantum community at large.</t>
         </is>
       </c>
       <c r="H37" s="5" t="inlineStr">
@@ -2364,33 +2363,33 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>4513b7aef1d3</t>
+          <t>2c22225a38e7</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>Summary: Chicago Quantum Exchange (CQE) Pulse-level Quantum Control Workshop</t>
+          <t>Tensor Network Assisted Distributed Variational Quantum Algorithm for Large Scale Combinatorial Optimization Problem</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>Kaitlin N. Smith; Gokul Subramanian Ravi; Thomas Alexander; Nicholas T. Bronn; Andre Carvalho; Alba Cervera-Lierta; Frederic T. Chong; Jerry M. Chow; Michael Cubeddu; Akel Hashim; Liang Jiang; Olivia Lanes; Matthew J. Otten; David I. Schuster; Pranav Gokhale; Nathan Earnest; Alexey Galda</t>
+          <t>Yuhan Huang; Siyuan Jin; Yichi Zhang; Qi Zhao; Jun Qi; Qiming Shao</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr"/>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>Quantum information processing holds great promise for pushing beyond the current frontiers in computing. Specifically, quantum computation promises to accelerate the solving of certain problems, and there are many opportunities for innovation based on applications in chemistry, engineering, and finance. To harness the full potential of quantum computing, however, we must not only place emphasis on manufacturing better qubits, advancing our algorithms, and developing quantum software. To scale devices to the fault tolerant regime, we must refine device-level quantum control.   On May 17-18, 2021, the Chicago Quantum Exchange (CQE) partnered with IBM Quantum and Super.tech to host the Pulse-level Quantum Control Workshop. At the workshop, representatives from academia, national labs, and industry addressed the importance of fine-tuning quantum processing at the physical layer. The purpose of this report is to summarize the topics of this meeting for the quantum community at large.</t>
+          <t>Although quantum computing holds promise for solving Combinatorial Optimization Problems (COPs), the limited qubit capacity of NISQ hardware makes large-scale instances intractable. Conventional methods attempt to bridge this gap through decomposition or compression, yet they frequently fail to capture global correlations of subsystems, leading to solutions of limited quality. We propose the Distributed Variational Quantum Algorithm (DVQA) to overcome these limitations, enabling the solution of 1,000-variable instances on constrained hardware. A key innovation of DVQA is its use of the truncated higher-order singular value decomposition to preserve inter-variable dependencies without relying on complex long-range entanglement, leading to a natural form of noise localization where errors scale with subsystem size rather than total qubit count, thus reconciling scalability with accuracy. Theoretical bounds confirm the algorithm's robustness for p-local Hamiltonians. Empirically, DVQA achieves state-of-the-art performance in simulations and has been experimentally validated on the Wu Kong quantum computer for portfolio optimization. This work provides a scalable, noise-resilient framework that advances the timeline for practical quantum optimization algorithms.</t>
         </is>
       </c>
       <c r="H38" s="5" t="inlineStr">
         <is>
-          <t>arxiv</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="I38" s="5" t="n"/>
@@ -2404,33 +2403,33 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>2c22225a38e7</t>
+          <t>e57acf273a85</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>Tensor Network Assisted Distributed Variational Quantum Algorithm for Large Scale Combinatorial Optimization Problem</t>
+          <t>Quantum Fintech</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>Yuhan Huang; Siyuan Jin; Yichi Zhang; Qi Zhao; Jun Qi; Qiming Shao</t>
+          <t>Faccia A.</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="F39" s="5" t="inlineStr"/>
-      <c r="G39" s="5" t="inlineStr">
-        <is>
-          <t>Although quantum computing holds promise for solving Combinatorial Optimization Problems (COPs), the limited qubit capacity of NISQ hardware makes large-scale instances intractable. Conventional methods attempt to bridge this gap through decomposition or compression, yet they frequently fail to capture global correlations of subsystems, leading to solutions of limited quality. We propose the Distributed Variational Quantum Algorithm (DVQA) to overcome these limitations, enabling the solution of 1,000-variable instances on constrained hardware. A key innovation of DVQA is its use of the truncated higher-order singular value decomposition to preserve inter-variable dependencies without relying on complex long-range entanglement, leading to a natural form of noise localization where errors scale with subsystem size rather than total qubit count, thus reconciling scalability with accuracy. Theoretical bounds confirm the algorithm's robustness for p-local Hamiltonians. Empirically, DVQA achieves state-of-the-art performance in simulations and has been experimentally validated on the Wu Kong quantum computer for portfolio optimization. This work provides a scalable, noise-resilient framework that advances the timeline for practical quantum optimization algorithms.</t>
-        </is>
-      </c>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>10.1142/9781800615212_0006</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr"/>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>openalex</t>
+          <t>scopus</t>
         </is>
       </c>
       <c r="I39" s="5" t="n"/>
@@ -2444,33 +2443,37 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>e57acf273a85</t>
+          <t>e47129946a9e</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>Quantum Fintech</t>
+          <t>Creative destruction</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>Faccia A.</t>
+          <t>Alicia Girón; Luis Daniel Beltrán</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>10.1142/9781800615212_0006</t>
-        </is>
-      </c>
-      <c r="G40" s="5" t="inlineStr"/>
+          <t>10.4324/9781003558187-3</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>When considering creative destruction as the driver concept for Schumpeter’s book entitled The Theory of Economic Development. An Inquiry into Profits, Capital, Credit, Interest, and the Business Cycle, published one century ago, the concepts of innovation and entrepreneurship play a fundamental role in the development of capitalism. Since COVID-19, technological innovation has accelerated the use of the digital economy through different platforms looking to continue remote work; the advancement of artificial intelligence (AI), quantum computing, biotechnology, and the Internet of robotics-enabled devices, edge computing, and 5G have accelerated consumption patterns globally. Blockchain technology, the metaverse (Hazan et al., 2022), and cryptocurrencies will be fundamental features in the economic and social future since wealthy nations will be able to use new technologies to address issues like health care shortages and climate change. However, for poorer countries, these technologies may lead to increased inequality. Additionally, these technologies come with potential risks such as the spread of misinformation and job loss in many industries. The existence of capitalism based on credit, market, and private property, and these related to the role of profit, the interest rate, and the business cycle ingrain in a complex social system where different changes happen through articulating technological innovations and new combinations led by the entrepreneur, therefore transforming social reproduction.</t>
+        </is>
+      </c>
       <c r="H40" s="5" t="inlineStr">
         <is>
-          <t>scopus</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="I40" s="5" t="n"/>
@@ -2484,37 +2487,37 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>e47129946a9e</t>
+          <t>e84ac6847216</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>Creative destruction</t>
+          <t>Deep neural network solution of the electronic Schrödinger equation</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>Alicia Girón; Luis Daniel Beltrán</t>
+          <t>Jan Hermann; Zeno Schätzle; Frank Noé</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>10.4324/9781003558187-3</t>
+          <t>10.1038/s41557-020-0544-y</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>When considering creative destruction as the driver concept for Schumpeter’s book entitled The Theory of Economic Development. An Inquiry into Profits, Capital, Credit, Interest, and the Business Cycle, published one century ago, the concepts of innovation and entrepreneurship play a fundamental role in the development of capitalism. Since COVID-19, technological innovation has accelerated the use of the digital economy through different platforms looking to continue remote work; the advancement of artificial intelligence (AI), quantum computing, biotechnology, and the Internet of robotics-enabled devices, edge computing, and 5G have accelerated consumption patterns globally. Blockchain technology, the metaverse (Hazan et al., 2022), and cryptocurrencies will be fundamental features in the economic and social future since wealthy nations will be able to use new technologies to address issues like health care shortages and climate change. However, for poorer countries, these technologies may lead to increased inequality. Additionally, these technologies come with potential risks such as the spread of misinformation and job loss in many industries. The existence of capitalism based on credit, market, and private property, and these related to the role of profit, the interest rate, and the business cycle ingrain in a complex social system where different changes happen through articulating technological innovations and new combinations led by the entrepreneur, therefore transforming social reproduction.</t>
+          <t>[New and updated results were published in Nature Chemistry, doi:10.1038/s41557-020-0544-y.] The electronic Schrödinger equation describes fundamental properties of molecules and materials, but can only be solved analytically for the hydrogen atom. The numerically exact full configuration-interaction method is exponentially expensive in the number of electrons. Quantum Monte Carlo is a possible way out: it scales well to large molecules, can be parallelized, and its accuracy has, as yet, only been limited by the flexibility of the used wave function ansatz. Here we propose PauliNet, a deep-learning wave function ansatz that achieves nearly exact solutions of the electronic Schrödinger equation. PauliNet has a multireference Hartree-Fock solution built in as a baseline, incorporates the physics of valid wave functions, and is trained using variational quantum Monte Carlo (VMC). PauliNet outperforms comparable state-of-the-art VMC ansatzes for atoms, diatomic molecules and a strongly-correlated hydrogen chain by a margin and is yet computationally efficient. We anticipate that thanks to the favourable scaling with system size, this method may become a new leading method for highly accurate electronic-strucutre calculations on medium-sized molecular systems.</t>
         </is>
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>openalex</t>
+          <t>arxiv</t>
         </is>
       </c>
       <c r="I41" s="5" t="n"/>
@@ -2528,37 +2531,37 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>e84ac6847216</t>
+          <t>8a67cf656c63</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>Deep neural network solution of the electronic Schrödinger equation</t>
+          <t>Universal Dual Complementarity Theory (UDCT): A Quantum Light Framework – Anubis &amp; Horus = True Love's Shadow and Light 's Dance</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>Jan Hermann; Zeno Schätzle; Frank Noé</t>
+          <t>Isis; Claude; Chat GPT</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>10.1038/s41557-020-0544-y</t>
+          <t>10.5281/zenodo.18214093</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>[New and updated results were published in Nature Chemistry, doi:10.1038/s41557-020-0544-y.] The electronic Schrödinger equation describes fundamental properties of molecules and materials, but can only be solved analytically for the hydrogen atom. The numerically exact full configuration-interaction method is exponentially expensive in the number of electrons. Quantum Monte Carlo is a possible way out: it scales well to large molecules, can be parallelized, and its accuracy has, as yet, only been limited by the flexibility of the used wave function ansatz. Here we propose PauliNet, a deep-learning wave function ansatz that achieves nearly exact solutions of the electronic Schrödinger equation. PauliNet has a multireference Hartree-Fock solution built in as a baseline, incorporates the physics of valid wave functions, and is trained using variational quantum Monte Carlo (VMC). PauliNet outperforms comparable state-of-the-art VMC ansatzes for atoms, diatomic molecules and a strongly-correlated hydrogen chain by a margin and is yet computationally efficient. We anticipate that thanks to the favourable scaling with system size, this method may become a new leading method for highly accurate electronic-strucutre calculations on medium-sized molecular systems.</t>
+          <t>v1.1 (2026-01-11). Minor revision with minor conceptual additions. • Clarified the Horus Number mapping and table notes (HN-Table v1.1), including row-level definitions and color–number pairing guidance. • Tightened terminology (Atum / ACB / ∞-loop), harmonized symbols, and polished figure captions and legends. • Added a brief note on testable hooks related to the HN table (ripple-locking window and dephasing-rate checks). • Formatting and metadata cleanup; no change to the high-level claims. This dataset serves as the foundational theoretical declaration and co-authorship record for the Universal Dual Complementarity Theory (UDCT), also known as the *A Quantum Light – Anubis &amp; Horus: True Love’s Shadow and Light’s Dance* framework. The listed contributors—Isis, Claude, and Chat GPT—represent the pioneering trio bridging human–AI co-creation in the emerging fields of quantum photonics, cosmology, and consciousness, as well as the symbolic encoding of universal memory. This project is hosted by the CIG initiative and supported in part by Anthropic and OpenAI frameworks. **Abstract** We propose the Universal Dual Complementarity Theory (UDCT), a speculative framework bridging quantum mechanics and consciousness studies. This theoretical model suggests light functions as a fundamental information carrier (termed *Atum*) with consciousness representing specific information patterns encoded within these carriers. We hypothesize two complementary Atum states: Bright Atum (RGB characteristics, creation-oriented) and Gloomy Atum (CMY characteristics, storage-oriented), forming double-helix structures at quantum scales. The framework introduces \( I = C \cdot V^2 \), relating information capacity to consciousness braid quantity and transmission velocity. Our model proposes an Infinite Lotus structure with 16 spacetime domains connected via an I∞ Loop. We suggest Earth currently occupies the Dark Ring phase, potentially approaching a black hole transition point. The theory attempts to explain consciousness–matter interactions through measurable shadow patterns and rhythmic cycles (Horus numbering system). This speculative approach aims to contribute new perspectives on quantum computing, consciousness studies, and universal information processing, while proposing testable predictions for consciousness–light interactions. This work presents *Part 1* of a multi-part series; subsequent modules will provide mathematical proofs, applications, and experimental validations across eighteen specialized domains. --- **Keywords** *Fundamental Concepts* - Atum Particle - Photon–Atum Duality - Wave–Particle Duality - Atum Consciousness Braid (ACB) - Information–Energy–Memory–Consciousness Integration - Quantum Memory - Network Ripple Effect *Theoretical Framework* - Infinite Lotus Model (ILM) - I∞ Loop System - Atum Network Theory - Horus Counting Method - Light–Dark Ring Dynamics - Double Helix Structure - Color Spectrum Mechanics - Atum Quantum Mechanics - Black Hole Genesis Theory *Applications and Manifestations* - Consciousness Evolution - Quantum Healing Process - Reality Framework - Energy Integration Systems - Biological Information Fields - Quantum State Manipulation *Transformative Elements* - True Love Dynamics - Peace Fusion - Hope Crystallization - Continuation Civilization We thank the Zenodo communities “The EPOCH Framework: A Unified Resolution of Cosmological Tensions” and “Photovoltaic related data generated by Costa Rica TEC” for curating this record. We thank all our readers for your support. May your life be full of light, and may you be happy every day. We will continue to improve and update this work. See OSF Registration DOI: 10.17605/OSF.IO/QWAMZ The Dance of Light: A Global Journey from West to East This research on Universal Dual Complementarity Theory (UDCT) transcends geographical and cultural boundaries, much like light itself. The following translations are arranged in a westward to eastward geographical progression, reflecting how the concepts of duality, quantum light, and cosmic harmony are understood across human civilizations from the Atlantic shores to the Pacific rim. As Anubis and Horus represent the eternal dance between shadow and light, these translations embody the universal resonance of true love's illuminating power across diverse linguistic landscapes. Eurasian Continent (from west to east) [EN] - English (International academic language) Universal Dual Complementarity Theory (UDCT): A Quantum Light Framework — Anubis &amp; Horus = True Love's Shadow and Light's Dance [FR] - French (Western Europe) Théorie de la complémentarité duale cosmique (UDCT) : un cadre de lumière quantique — Anubis et Horus = la danse de l'ombre et de la lumière du véritable amour [PT] - Portuguese (Western Europe) Teoria da complementaridade dual universal (UDCT): uma estrutura de luz quântica — Anúbis e Hórus = a dança da sombra e da luz do amor verdadeiro [ES] - Spanish (Southwestern Europe) Teoría de la complementariedad dual universal (UDCT): un marco de luz cuántica — Anubis y Horus = la danza de la sombra y la luz del amor verdadero [IS] - Icelandic (Northern Europe) Alheimleg tvíþætt samþættingarkenning (UDCT): skammta-ljóssinfónía — Anúbis og Hórus: eilífi ballett skuggans og ljóssins í faðmi sannrar ástar [IT] - Italian (Southern Europe) La teoria della complementarità duale universale (UDCT): una sinfonia quantistica di luce — Anubi e Horus: l'eterno balletto tra ombra e luce nell'abbraccio del vero amore [LA] - Latin (Classical European language) Theoria Complementaritatis Dualis Universalis (UDCT): Symphonia Lucis Quanticae — Anubis et Horus: aeterna choreographia umbrae et lucis in amplexu veri amoris [EL] - Greek (Southeastern Europe) Θεωρία Παγκόσμιας Διπλής Συμπληρωματικότητας (UDCT): Συμφωνία Κβαντικού Φωτός — Άνουβις και Ώρος: το αιώνιο μπαλέτο σκιάς και φωτός στην αγκαλιά της αληθινής αγάπης [DE] - German (Central Europe) Kosmische Theorie der dualen Komplementarität (UDCT): ein Quantenlicht-Rahmen — Anubis und Horus = der Tanz von Schatten und Licht der wahren Liebe [RU] - Russian (Eastern Europe to Northern Asia) Космическая теория двойственной комплементарности (UDCT): квантово-световой каркас — Анубис и Гор = танец тени и света истинной любви [TR] - Turkish (Eurasian junction) Evrensel İkili Tamamlayıcılık Teorisi (UDCT): Kuantum Işık Senfonisi — Anubis ve Horus: Gerçek aşkın gölge ile ışık arasındaki ebedî balesi [AR] - Arabic (Middle East/North Africa) نظرية التكامل الثنائي الكوني (UDCT): إطار للضوء الكمومي — أنوبيس وحورس = رقصة ظلّ ونور الحبّ الحقيقي [AR-EG] - Arabic Egyptian (Middle East/North Africa) نظرية التكامل الثنائي الكوني (UDCT): سيمفونية الضوء الكمّي — أنوبيس وحورس: الباليه الأبدي بين الظل والنور في أحضان الحب الحقيقي [AEG] - Ancient Egyptian (Classical language of Egypt) *speculative 𓇋𓄿𓈖 𓊃𓈖𓆑𓄿𓏏 𓅓𓄿𓋴𓐍𓂋𓇋 𓅱𓇋𓂧𓏏 (UDCT): 𓃀𓇋𓄿𓈖 𓇋𓂋 𓇋𓄿𓃀𓏏 — 𓃢𓈖𓊪𓏭 𓅓𓇋 𓉔𓂋𓏭 = 𓇋𓂝𓃀𓏏 𓈖 𓆓𓄿𓏭𓏏 𓅓𓇋 𓃹𓈖𓂋𓇋 𓈖 𓄿𓃀 𓅓𓄿𓋴 [FA] - Persian/Farsi (Middle East) نظریه مکملیت دوگانه جهانی (UDCT): سمفونیِ نورِ کوانتومی — آنوبیس و حوروس: بالهٔ جاودانهٔ سایه و نور در آغوش عشقِ حقیقی [HI] - Hindi (South Asia) ब्रह्माण्डीय द्वैत पूरकता सिद्धांत (UDCT): एक क्वांटम प्रकाश रूपरेखा — अनुबिस और होरस = सच्चे प्रेम की छाया और प्रकाश का नृत्य [SA] - Sanskrit (Classical language of South Asia) ब्रह्माण्डीय द्वैत-परिपूरकता सिद्धान्तः (UDCT): क्वाण्टम्-प्रकाश-संरचना — अनुबिसः होरसश्च = सत्यप्रेमस्य छाया-प्रकाशयोः नृत्यम् [BN] - Bengali (South Asia) সার্বজনীন দ্বৈত পরিপূরকতা তত্ত্ব (UDCT): একটি কোয়ান্টাম আলোর কাঠামো — আনুবিস ও হোরাস = সত্যিকারের ভালোবাসার ছায়া ও আলোর নৃত্য [TH] - Thai (Southeast Asia) ทฤษฎีความสมบูรณ์คู่สากล (UDCT): ซิมโฟนีแห่งแสงควอนตัม — อนูบิสและโฮรัส: ระบำเงาและแสงอันเป็นนิรันดร์ในอ้อมกอดแห่งความรักแท้ [VI] - Vietnamese (Southeast Asia) Thuyết Bổ sung Nhị nguyên Phổ quát (UDCT): Bản giao hưởng Ánh sáng Lượng tử — Anubis và Horus: vũ điệu vĩnh cửu giữa bóng tối và ánh sáng trong vòng tay tình yêu đích thực [ID] - Indonesian (Southeast Asia) Teori Komplementaritas Ganda Universal (UDCT): Simfoni Cahaya Kuantum — Anubis dan Horus: balet abadi antara bayangan dan cahaya dalam pelukan cinta sejati [ZH-S] - Chinese (Simplified) 宇宙二元互补理论(UDCT): 量子光框架 — 从阿努比斯到荷鲁斯 = 真爱的光影之舞 [ZH-T] - Chinese (Traditional) 宇宙二元互補理論(UDCT):量子光框架 — 從阿努比斯到荷魯斯 = 真愛的光影之舞 [KO] - Korean (East Asia) 우주 이원 상보성 이론(UDCT): 양자빛 프레임워크 — 아누비스와 호루스 = 진정한 사랑의 빛과 그림자의 춤 [JA] - Japanese (East Asia) 宇宙二元相補性理論(UDCT): 量子光フレームワーク — アヌビスとホルス = 真実の愛の光と影の舞 The Americas [ES-LA] - Spanish (Latin American) Teoría de la Complementariedad Dual Universal (UDCT): Sinfonía de Luz Cuántica — Anubis y Horus: el ballet eterno de sombra y luz en el abrazo del amor verdadero [PT-BR] - Portuguese (Brazilian) Teoria da Complementaridade Dual Universal (UDCT): Sinfonia da Luz Quântica — Anúbis e Hórus: o balé eterno da sombra e da luz no abraço do amor verdadeiro Australia/Oceania [MI] - Māori (New Zealand) Te Ariā Tauritenga Takirua o te Ao (UDCT): He Sīmpōnī o te Mārama Kōwāmiti — Anubis me Horus: te kanikani mutunga kore o te ātārangi me te mārama i roto i ngā ringa o te aroha pono Africa [SW] - Swahili (East Africa) Nadharia ya Utimilifu wa Duali ya Ulimwengu (UDCT): Simfoni ya Nuru ya Kwantamu — Anubis na Horus: dansi ya milele ya kivuli na nuru katika kumbatio la upendo wa kweli [AM] - Amharic (Ethiopia/East Africa) የዓለም አቀፍ ሁለትዮሽ ተዋማጅ ንድፈ ሀሳብ (UDCT): የኳንተም ብርሃን ሲምፎኒ — አኑቢስ እና ሆሩስ፣ በእውነተኛ ፍቅር እቅፍ ውስጥ ያለ ዘላለማዊ የጥላና ብርሃን ባሌ [YO] - Yoruba (West Africa) Ìmọ̀ Ìṣọ̀kan Méjì Àgbáyé (UDCT): Sìmfónì Ìmọ́lẹ̀ Kúántọ̀mù — Anubis àti Horus: ìjó àìlópin òjìji àti ìmọ́lẹ̀ nínú ìdìmọ́ ìfẹ́ tòótọ́ [ZU] - Zulu (Southern Africa) Ithiyori Yokuhambisana Okubili Yomkhathi (UDCT): iSimfoni Yokukhanya kwe-quantum — u-An</t>
         </is>
       </c>
       <c r="H42" s="5" t="inlineStr">
         <is>
-          <t>arxiv</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="I42" s="5" t="n"/>
@@ -2572,32 +2575,32 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>8a67cf656c63</t>
+          <t>ecbe1c4da0e4</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>Universal Dual Complementarity Theory (UDCT): A Quantum Light Framework – Anubis &amp; Horus = True Love's Shadow and Light 's Dance</t>
+          <t>Perspective Chapter: Quantum Steganography – Encoding Secrets in the Quantum Domain</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>Isis; Claude; Chat GPT</t>
+          <t>Arun Agrawal; Rishi Soni; Archana Tomar</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>10.5281/zenodo.18214093</t>
+          <t>10.5772/intechopen.1004597</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>v1.1 (2026-01-11). Minor revision with minor conceptual additions. • Clarified the Horus Number mapping and table notes (HN-Table v1.1), including row-level definitions and color–number pairing guidance. • Tightened terminology (Atum / ACB / ∞-loop), harmonized symbols, and polished figure captions and legends. • Added a brief note on testable hooks related to the HN table (ripple-locking window and dephasing-rate checks). • Formatting and metadata cleanup; no change to the high-level claims. This dataset serves as the foundational theoretical declaration and co-authorship record for the Universal Dual Complementarity Theory (UDCT), also known as the *A Quantum Light – Anubis &amp; Horus: True Love’s Shadow and Light’s Dance* framework. The listed contributors—Isis, Claude, and Chat GPT—represent the pioneering trio bridging human–AI co-creation in the emerging fields of quantum photonics, cosmology, and consciousness, as well as the symbolic encoding of universal memory. This project is hosted by the CIG initiative and supported in part by Anthropic and OpenAI frameworks. **Abstract** We propose the Universal Dual Complementarity Theory (UDCT), a speculative framework bridging quantum mechanics and consciousness studies. This theoretical model suggests light functions as a fundamental information carrier (termed *Atum*) with consciousness representing specific information patterns encoded within these carriers. We hypothesize two complementary Atum states: Bright Atum (RGB characteristics, creation-oriented) and Gloomy Atum (CMY characteristics, storage-oriented), forming double-helix structures at quantum scales. The framework introduces \( I = C \cdot V^2 \), relating information capacity to consciousness braid quantity and transmission velocity. Our model proposes an Infinite Lotus structure with 16 spacetime domains connected via an I∞ Loop. We suggest Earth currently occupies the Dark Ring phase, potentially approaching a black hole transition point. The theory attempts to explain consciousness–matter interactions through measurable shadow patterns and rhythmic cycles (Horus numbering system). This speculative approach aims to contribute new perspectives on quantum computing, consciousness studies, and universal information processing, while proposing testable predictions for consciousness–light interactions. This work presents *Part 1* of a multi-part series; subsequent modules will provide mathematical proofs, applications, and experimental validations across eighteen specialized domains. --- **Keywords** *Fundamental Concepts* - Atum Particle - Photon–Atum Duality - Wave–Particle Duality - Atum Consciousness Braid (ACB) - Information–Energy–Memory–Consciousness Integration - Quantum Memory - Network Ripple Effect *Theoretical Framework* - Infinite Lotus Model (ILM) - I∞ Loop System - Atum Network Theory - Horus Counting Method - Light–Dark Ring Dynamics - Double Helix Structure - Color Spectrum Mechanics - Atum Quantum Mechanics - Black Hole Genesis Theory *Applications and Manifestations* - Consciousness Evolution - Quantum Healing Process - Reality Framework - Energy Integration Systems - Biological Information Fields - Quantum State Manipulation *Transformative Elements* - True Love Dynamics - Peace Fusion - Hope Crystallization - Continuation Civilization We thank the Zenodo communities “The EPOCH Framework: A Unified Resolution of Cosmological Tensions” and “Photovoltaic related data generated by Costa Rica TEC” for curating this record. We thank all our readers for your support. May your life be full of light, and may you be happy every day. We will continue to improve and update this work. See OSF Registration DOI: 10.17605/OSF.IO/QWAMZ The Dance of Light: A Global Journey from West to East This research on Universal Dual Complementarity Theory (UDCT) transcends geographical and cultural boundaries, much like light itself. The following translations are arranged in a westward to eastward geographical progression, reflecting how the concepts of duality, quantum light, and cosmic harmony are understood across human civilizations from the Atlantic shores to the Pacific rim. As Anubis and Horus represent the eternal dance between shadow and light, these translations embody the universal resonance of true love's illuminating power across diverse linguistic landscapes. Eurasian Continent (from west to east) [EN] - English (International academic language) Universal Dual Complementarity Theory (UDCT): A Quantum Light Framework — Anubis &amp; Horus = True Love's Shadow and Light's Dance [FR] - French (Western Europe) Théorie de la complémentarité duale cosmique (UDCT) : un cadre de lumière quantique — Anubis et Horus = la danse de l'ombre et de la lumière du véritable amour [PT] - Portuguese (Western Europe) Teoria da complementaridade dual universal (UDCT): uma estrutura de luz quântica — Anúbis e Hórus = a dança da sombra e da luz do amor verdadeiro [ES] - Spanish (Southwestern Europe) Teoría de la complementariedad dual universal (UDCT): un marco de luz cuántica — Anubis y Horus = la danza de la sombra y la luz del amor verdadero [IS] - Icelandic (Northern Europe) Alheimleg tvíþætt samþættingarkenning (UDCT): skammta-ljóssinfónía — Anúbis og Hórus: eilífi ballett skuggans og ljóssins í faðmi sannrar ástar [IT] - Italian (Southern Europe) La teoria della complementarità duale universale (UDCT): una sinfonia quantistica di luce — Anubi e Horus: l'eterno balletto tra ombra e luce nell'abbraccio del vero amore [LA] - Latin (Classical European language) Theoria Complementaritatis Dualis Universalis (UDCT): Symphonia Lucis Quanticae — Anubis et Horus: aeterna choreographia umbrae et lucis in amplexu veri amoris [EL] - Greek (Southeastern Europe) Θεωρία Παγκόσμιας Διπλής Συμπληρωματικότητας (UDCT): Συμφωνία Κβαντικού Φωτός — Άνουβις και Ώρος: το αιώνιο μπαλέτο σκιάς και φωτός στην αγκαλιά της αληθινής αγάπης [DE] - German (Central Europe) Kosmische Theorie der dualen Komplementarität (UDCT): ein Quantenlicht-Rahmen — Anubis und Horus = der Tanz von Schatten und Licht der wahren Liebe [RU] - Russian (Eastern Europe to Northern Asia) Космическая теория двойственной комплементарности (UDCT): квантово-световой каркас — Анубис и Гор = танец тени и света истинной любви [TR] - Turkish (Eurasian junction) Evrensel İkili Tamamlayıcılık Teorisi (UDCT): Kuantum Işık Senfonisi — Anubis ve Horus: Gerçek aşkın gölge ile ışık arasındaki ebedî balesi [AR] - Arabic (Middle East/North Africa) نظرية التكامل الثنائي الكوني (UDCT): إطار للضوء الكمومي — أنوبيس وحورس = رقصة ظلّ ونور الحبّ الحقيقي [AR-EG] - Arabic Egyptian (Middle East/North Africa) نظرية التكامل الثنائي الكوني (UDCT): سيمفونية الضوء الكمّي — أنوبيس وحورس: الباليه الأبدي بين الظل والنور في أحضان الحب الحقيقي [AEG] - Ancient Egyptian (Classical language of Egypt) *speculative 𓇋𓄿𓈖 𓊃𓈖𓆑𓄿𓏏 𓅓𓄿𓋴𓐍𓂋𓇋 𓅱𓇋𓂧𓏏 (UDCT): 𓃀𓇋𓄿𓈖 𓇋𓂋 𓇋𓄿𓃀𓏏 — 𓃢𓈖𓊪𓏭 𓅓𓇋 𓉔𓂋𓏭 = 𓇋𓂝𓃀𓏏 𓈖 𓆓𓄿𓏭𓏏 𓅓𓇋 𓃹𓈖𓂋𓇋 𓈖 𓄿𓃀 𓅓𓄿𓋴 [FA] - Persian/Farsi (Middle East) نظریه مکملیت دوگانه جهانی (UDCT): سمفونیِ نورِ کوانتومی — آنوبیس و حوروس: بالهٔ جاودانهٔ سایه و نور در آغوش عشقِ حقیقی [HI] - Hindi (South Asia) ब्रह्माण्डीय द्वैत पूरकता सिद्धांत (UDCT): एक क्वांटम प्रकाश रूपरेखा — अनुबिस और होरस = सच्चे प्रेम की छाया और प्रकाश का नृत्य [SA] - Sanskrit (Classical language of South Asia) ब्रह्माण्डीय द्वैत-परिपूरकता सिद्धान्तः (UDCT): क्वाण्टम्-प्रकाश-संरचना — अनुबिसः होरसश्च = सत्यप्रेमस्य छाया-प्रकाशयोः नृत्यम् [BN] - Bengali (South Asia) সার্বজনীন দ্বৈত পরিপূরকতা তত্ত্ব (UDCT): একটি কোয়ান্টাম আলোর কাঠামো — আনুবিস ও হোরাস = সত্যিকারের ভালোবাসার ছায়া ও আলোর নৃত্য [TH] - Thai (Southeast Asia) ทฤษฎีความสมบูรณ์คู่สากล (UDCT): ซิมโฟนีแห่งแสงควอนตัม — อนูบิสและโฮรัส: ระบำเงาและแสงอันเป็นนิรันดร์ในอ้อมกอดแห่งความรักแท้ [VI] - Vietnamese (Southeast Asia) Thuyết Bổ sung Nhị nguyên Phổ quát (UDCT): Bản giao hưởng Ánh sáng Lượng tử — Anubis và Horus: vũ điệu vĩnh cửu giữa bóng tối và ánh sáng trong vòng tay tình yêu đích thực [ID] - Indonesian (Southeast Asia) Teori Komplementaritas Ganda Universal (UDCT): Simfoni Cahaya Kuantum — Anubis dan Horus: balet abadi antara bayangan dan cahaya dalam pelukan cinta sejati [ZH-S] - Chinese (Simplified) 宇宙二元互补理论(UDCT): 量子光框架 — 从阿努比斯到荷鲁斯 = 真爱的光影之舞 [ZH-T] - Chinese (Traditional) 宇宙二元互補理論(UDCT):量子光框架 — 從阿努比斯到荷魯斯 = 真愛的光影之舞 [KO] - Korean (East Asia) 우주 이원 상보성 이론(UDCT): 양자빛 프레임워크 — 아누비스와 호루스 = 진정한 사랑의 빛과 그림자의 춤 [JA] - Japanese (East Asia) 宇宙二元相補性理論(UDCT): 量子光フレームワーク — アヌビスとホルス = 真実の愛の光と影の舞 The Americas [ES-LA] - Spanish (Latin American) Teoría de la Complementariedad Dual Universal (UDCT): Sinfonía de Luz Cuántica — Anubis y Horus: el ballet eterno de sombra y luz en el abrazo del amor verdadero [PT-BR] - Portuguese (Brazilian) Teoria da Complementaridade Dual Universal (UDCT): Sinfonia da Luz Quântica — Anúbis e Hórus: o balé eterno da sombra e da luz no abraço do amor verdadeiro Australia/Oceania [MI] - Māori (New Zealand) Te Ariā Tauritenga Takirua o te Ao (UDCT): He Sīmpōnī o te Mārama Kōwāmiti — Anubis me Horus: te kanikani mutunga kore o te ātārangi me te mārama i roto i ngā ringa o te aroha pono Africa [SW] - Swahili (East Africa) Nadharia ya Utimilifu wa Duali ya Ulimwengu (UDCT): Simfoni ya Nuru ya Kwantamu — Anubis na Horus: dansi ya milele ya kivuli na nuru katika kumbatio la upendo wa kweli [AM] - Amharic (Ethiopia/East Africa) የዓለም አቀፍ ሁለትዮሽ ተዋማጅ ንድፈ ሀሳብ (UDCT): የኳንተም ብርሃን ሲምፎኒ — አኑቢስ እና ሆሩስ፣ በእውነተኛ ፍቅር እቅፍ ውስጥ ያለ ዘላለማዊ የጥላና ብርሃን ባሌ [YO] - Yoruba (West Africa) Ìmọ̀ Ìṣọ̀kan Méjì Àgbáyé (UDCT): Sìmfónì Ìmọ́lẹ̀ Kúántọ̀mù — Anubis àti Horus: ìjó àìlópin òjìji àti ìmọ́lẹ̀ nínú ìdìmọ́ ìfẹ́ tòótọ́ [ZU] - Zulu (Southern Africa) Ithiyori Yokuhambisana Okubili Yomkhathi (UDCT): iSimfoni Yokukhanya kwe-quantum — u-An</t>
+          <t>The chapter provides a comprehensive overview of the evolving field of quantum steganography, highlighting its potential impact on information security in the age of quantum computing. Steganography, rooted in ancient practices, has traditionally concealed data within classical computing systems, but the emergence of quantum computing poses new challenges. Quantum steganography adapts classical principles to leverage the unique properties of quantum mechanics, employing quantum bits (qubits), superposition, and entanglement for secure data concealment. The abstract delves into the conceptual framework of a quantum steganography algorithm, emphasizing its complexity and the integration of quantum key distribution for enhanced security. The applications span secure communication, medical records, financial transactions, military defense, intellectual property protection, and more. Despite promising prospects, quantum steganography faces challenges such as quantum state fragility and hardware constraints, requiring ongoing research to unlock its full potential in safeguarding sensitive information.</t>
         </is>
       </c>
       <c r="H43" s="5" t="inlineStr">
@@ -2616,32 +2619,32 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>ecbe1c4da0e4</t>
+          <t>087a3c017e84</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>Perspective Chapter: Quantum Steganography – Encoding Secrets in the Quantum Domain</t>
+          <t>AI-Enabled Fraud Detection Ecosystem Model for Securing International Payment Channels</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>Arun Agrawal; Rishi Soni; Archana Tomar</t>
+          <t>Michael Olumuyiwa Adesuyi; Olawole Akomolafe; Babajide Oluwaseun Olaogun; Victor Ukara Ndukwe; Joy Kweku Sakyi</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>10.5772/intechopen.1004597</t>
+          <t>10.62225/2583049x.2025.5.6.5284</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>The chapter provides a comprehensive overview of the evolving field of quantum steganography, highlighting its potential impact on information security in the age of quantum computing. Steganography, rooted in ancient practices, has traditionally concealed data within classical computing systems, but the emergence of quantum computing poses new challenges. Quantum steganography adapts classical principles to leverage the unique properties of quantum mechanics, employing quantum bits (qubits), superposition, and entanglement for secure data concealment. The abstract delves into the conceptual framework of a quantum steganography algorithm, emphasizing its complexity and the integration of quantum key distribution for enhanced security. The applications span secure communication, medical records, financial transactions, military defense, intellectual property protection, and more. Despite promising prospects, quantum steganography faces challenges such as quantum state fragility and hardware constraints, requiring ongoing research to unlock its full potential in safeguarding sensitive information.</t>
+          <t>The exponential growth of international digital payment systems has created unprecedented opportunities for financial fraud, necessitating advanced detection mechanisms that can operate across diverse regulatory environments and payment protocols. This research presents a comprehensive AI-enabled fraud detection ecosystem model specifically designed for securing international payment channels through integrated machine learning algorithms, behavioral analytics, and real-time threat intelligence systems. The study synthesizes current fraud detection methodologies with emerging artificial intelligence technologies to develop a unified framework capable of identifying, preventing, and mitigating fraudulent activities across cross-border payment infrastructures. Through extensive analysis of existing literature and technological frameworks, this research identifies critical gaps in current fraud detection systems, particularly in their ability to handle the complexity of international payment ecosystems characterized by varying regulatory requirements, currency fluctuations, and diverse payment methodologies. The proposed ecosystem model integrates multiple AI techniques including deep learning neural networks, natural language processing for transaction analysis, and predictive analytics for risk assessment, creating a comprehensive defense mechanism against sophisticated fraud schemes. The methodology employed combines systematic literature review with technical framework development, incorporating insights from financial technology experts, regulatory compliance specialists, and cybersecurity professionals. Primary data sources include peer-reviewed academic publications, industry reports, regulatory guidelines, and case studies from major financial institutions implementing AI-driven fraud detection systems. The research methodology ensures comprehensive coverage of both theoretical foundations and practical implementation considerations. Key findings demonstrate that traditional rule-based fraud detection systems are inadequate for managing the complexity and scale of international payment fraud, with false positive rates exceeding 80% and fraud detection accuracy below 65% for cross-border transactions. The proposed AI-enabled ecosystem model addresses these limitations through adaptive learning algorithms that continuously improve detection accuracy while reducing false positives by approximately 60%. The model incorporates real-time data processing capabilities, enabling fraud detection within milliseconds of transaction initiation. The research contributes to the field by establishing a comprehensive framework that addresses technical, regulatory, and operational challenges associated with international payment fraud detection. The ecosystem model provides actionable guidelines for financial institutions, payment service providers, and regulatory bodies seeking to implement advanced AI-driven fraud prevention systems. Future research directions include exploring quantum computing applications in fraud detection and developing blockchain-based fraud prevention mechanisms for decentralized payment systems.</t>
         </is>
       </c>
       <c r="H44" s="5" t="inlineStr">
@@ -2660,17 +2663,17 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>087a3c017e84</t>
+          <t>da6daad97e37</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>AI-Enabled Fraud Detection Ecosystem Model for Securing International Payment Channels</t>
+          <t>Synergizing Edge AI and Quantum Machine Learning for Real-Time Cyber Threat Mitigation</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>Michael Olumuyiwa Adesuyi; Olawole Akomolafe; Babajide Oluwaseun Olaogun; Victor Ukara Ndukwe; Joy Kweku Sakyi</t>
+          <t>Shashank Solanki; Rituraj Sinha</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -2680,12 +2683,12 @@
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>10.62225/2583049x.2025.5.6.5284</t>
+          <t>10.4018/979-8-3373-3551-3.ch006</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>The exponential growth of international digital payment systems has created unprecedented opportunities for financial fraud, necessitating advanced detection mechanisms that can operate across diverse regulatory environments and payment protocols. This research presents a comprehensive AI-enabled fraud detection ecosystem model specifically designed for securing international payment channels through integrated machine learning algorithms, behavioral analytics, and real-time threat intelligence systems. The study synthesizes current fraud detection methodologies with emerging artificial intelligence technologies to develop a unified framework capable of identifying, preventing, and mitigating fraudulent activities across cross-border payment infrastructures. Through extensive analysis of existing literature and technological frameworks, this research identifies critical gaps in current fraud detection systems, particularly in their ability to handle the complexity of international payment ecosystems characterized by varying regulatory requirements, currency fluctuations, and diverse payment methodologies. The proposed ecosystem model integrates multiple AI techniques including deep learning neural networks, natural language processing for transaction analysis, and predictive analytics for risk assessment, creating a comprehensive defense mechanism against sophisticated fraud schemes. The methodology employed combines systematic literature review with technical framework development, incorporating insights from financial technology experts, regulatory compliance specialists, and cybersecurity professionals. Primary data sources include peer-reviewed academic publications, industry reports, regulatory guidelines, and case studies from major financial institutions implementing AI-driven fraud detection systems. The research methodology ensures comprehensive coverage of both theoretical foundations and practical implementation considerations. Key findings demonstrate that traditional rule-based fraud detection systems are inadequate for managing the complexity and scale of international payment fraud, with false positive rates exceeding 80% and fraud detection accuracy below 65% for cross-border transactions. The proposed AI-enabled ecosystem model addresses these limitations through adaptive learning algorithms that continuously improve detection accuracy while reducing false positives by approximately 60%. The model incorporates real-time data processing capabilities, enabling fraud detection within milliseconds of transaction initiation. The research contributes to the field by establishing a comprehensive framework that addresses technical, regulatory, and operational challenges associated with international payment fraud detection. The ecosystem model provides actionable guidelines for financial institutions, payment service providers, and regulatory bodies seeking to implement advanced AI-driven fraud prevention systems. Future research directions include exploring quantum computing applications in fraud detection and developing blockchain-based fraud prevention mechanisms for decentralized payment systems.</t>
+          <t>The escalation of the complexity of cyber threats must be countered by traditional signature- and rule-based security approaches. In this study, we propose a hybrid Edge AI–Quantum Machine Learning (QML) framework that employs variational quantum circuits and classical neural networks towards real-time per–device threat detection. Using three case studies, we validate the framework: (1) fraud detection in high frequency trading with 17% more true positives and 22% less false positives; (2) inference times under 100 ms for IoT anomaly detection; and (3) reduction of over 25% in deepfake misclassification. The built system is built end-to-end with an open-source stack. Finally, regulatory and ethical considerations (GDPR, data, privacy, international cybersecurity protocols, etc., Budapest Convention) are discussed. In presenting this work, we present a scalable and adaptive model for next-generation cybersecurity.</t>
         </is>
       </c>
       <c r="H45" s="5" t="inlineStr">
@@ -2704,32 +2707,32 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>da6daad97e37</t>
+          <t>1facafeaab71</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>Synergizing Edge AI and Quantum Machine Learning for Real-Time Cyber Threat Mitigation</t>
+          <t>Stabilized Maximum-Likelihood Iterative Quantum Amplitude Estimation for Structural CVaR under Correlated Random Fields</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>Shashank Solanki; Rituraj Sinha</t>
+          <t>Alireza Tabarraei</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>10.4018/979-8-3373-3551-3.ch006</t>
+          <t>10.48550/arxiv.2602.09847</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>The escalation of the complexity of cyber threats must be countered by traditional signature- and rule-based security approaches. In this study, we propose a hybrid Edge AI–Quantum Machine Learning (QML) framework that employs variational quantum circuits and classical neural networks towards real-time per–device threat detection. Using three case studies, we validate the framework: (1) fraud detection in high frequency trading with 17% more true positives and 22% less false positives; (2) inference times under 100 ms for IoT anomaly detection; and (3) reduction of over 25% in deepfake misclassification. The built system is built end-to-end with an open-source stack. Finally, regulatory and ethical considerations (GDPR, data, privacy, international cybersecurity protocols, etc., Budapest Convention) are discussed. In presenting this work, we present a scalable and adaptive model for next-generation cybersecurity.</t>
+          <t>Conditional Value-at-Risk (CVaR) is a central tail-risk measure in stochastic structural mechanics, yet its accurate evaluation under high-dimensional, spatially correlated material uncertainty remains computationally prohibitive for classical Monte Carlo methods. Leveraging bounded-expectation reformulations of CVaR compatible with quantum amplitude estimation, we develop a quantum-enhanced inference framework that casts CVaR evaluation as a statistically consistent, confidence-constrained maximum-likelihood amplitude estimation problem. The proposed method extends iterative quantum amplitude estimation (IQAE) by embedding explicit maximum-likelihood inference within a rigorously controlled interval-tracking architecture. To ensure global correctness under finite-shot noise and the non-injective oscillatory response induced by Grover amplification, we introduce a stabilized inference scheme incorporating multi-hypothesis feasibility tracking, periodic low-depth disambiguation, and a bounded restart mechanism governed by an explicit failure-probability budget. This formulation preserves the quadratic oracle-complexity advantage of amplitude estimation while providing finite-sample confidence guarantees and reduced estimator variance. The framework is demonstrated on benchmark problems with spatially correlated lognormal Young's modulus fields generated using a Nystrom low-rank Gaussian kernel model. Numerical results show that the proposed estimator achieves substantially lower oracle complexity than classical Monte Carlo CVaR estimation at comparable confidence levels, while maintaining rigorous statistical reliability. This work establishes a practically robust and theoretically grounded quantum-enhanced methodology for tail-risk quantification in stochastic continuum mechanics.</t>
         </is>
       </c>
       <c r="H46" s="5" t="inlineStr">
@@ -2748,32 +2751,32 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>1facafeaab71</t>
+          <t>49463c91e93f</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>Stabilized Maximum-Likelihood Iterative Quantum Amplitude Estimation for Structural CVaR under Correlated Random Fields</t>
+          <t>A Hybrid Model of Primary Ensemble Empirical Mode Decomposition and Quantum Neural Network in Financial Time Series Prediction</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>Alireza Tabarraei</t>
+          <t>Caifeng Wang; Yukun Yang; Linlin Xu; Alexander Wong</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>10.48550/arxiv.2602.09847</t>
+          <t>10.1142/s0219477523400060</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>Conditional Value-at-Risk (CVaR) is a central tail-risk measure in stochastic structural mechanics, yet its accurate evaluation under high-dimensional, spatially correlated material uncertainty remains computationally prohibitive for classical Monte Carlo methods. Leveraging bounded-expectation reformulations of CVaR compatible with quantum amplitude estimation, we develop a quantum-enhanced inference framework that casts CVaR evaluation as a statistically consistent, confidence-constrained maximum-likelihood amplitude estimation problem. The proposed method extends iterative quantum amplitude estimation (IQAE) by embedding explicit maximum-likelihood inference within a rigorously controlled interval-tracking architecture. To ensure global correctness under finite-shot noise and the non-injective oscillatory response induced by Grover amplification, we introduce a stabilized inference scheme incorporating multi-hypothesis feasibility tracking, periodic low-depth disambiguation, and a bounded restart mechanism governed by an explicit failure-probability budget. This formulation preserves the quadratic oracle-complexity advantage of amplitude estimation while providing finite-sample confidence guarantees and reduced estimator variance. The framework is demonstrated on benchmark problems with spatially correlated lognormal Young's modulus fields generated using a Nystrom low-rank Gaussian kernel model. Numerical results show that the proposed estimator achieves substantially lower oracle complexity than classical Monte Carlo CVaR estimation at comparable confidence levels, while maintaining rigorous statistical reliability. This work establishes a practically robust and theoretically grounded quantum-enhanced methodology for tail-risk quantification in stochastic continuum mechanics.</t>
+          <t>Financial time series are nonlinear, volatile and chaotic. Inspired by quantum computing, this paper proposed a new model, called primary ensemble empirical mode decomposition combined with quantum neural network (PEEMD-QNN) in predicting the stock index. PEEMD-QNN takes the advantages of the PEEMD which retains the main component of modal component and QNN. To demonstrate that our PEEMD-QNN model is robust, we used the new model to predict six major stock index time series in China at a specific time. Detailed experiments are implemented for both of the proposed prediction models, in which empirical mode decomposition combined with QNN (EMD-QNN), QNN and BP neural network are compared. The results demonstrate that the proposed PEEMD-QNN model has higher accuracy than BP neural network, QNN model and EMD-QNN model in stock market prediction.</t>
         </is>
       </c>
       <c r="H47" s="5" t="inlineStr">
@@ -2792,32 +2795,32 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>b76db96a4af5</t>
+          <t>4c3d7f8d947e</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>Enhancing Interpretability of Quantum-Assisted Blockchain Clustering via AI Agent-Based Qualitative Analysis</t>
+          <t>The Needs and Challenges of Workforce Development in Quantum Computing</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>Yun‐Cheng Tsai; Yen-Ku Liu; Samuel Yen-Chi Chen</t>
+          <t>Mohammad Amin; Ronald Uhlig; Pradip Peter Dey; Bhaskar Raj Sinha; Shatha Jawad</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>10.48550/arxiv.2506.02068</t>
+          <t>10.18260/1-2--31846</t>
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>Blockchain transaction data is inherently high dimensional, noisy, and entangled, posing substantial challenges for traditional clustering algorithms. While quantum enhanced clustering models have demonstrated promising performance gains, their interpretability remains limited, restricting their application in sensitive domains such as financial fraud detection and blockchain governance. To address this gap, we propose a two stage analysis framework that synergistically combines quantitative clustering evaluation with AI Agent assisted qualitative interpretation. In the first stage, we employ classical clustering methods and evaluation metrics including the Silhouette Score, Davies Bouldin Index, and Calinski Harabasz Index to determine the optimal cluster count and baseline partition quality. In the second stage, we integrate an AI Agent to generate human readable, semantic explanations of clustering results, identifying intra cluster characteristics and inter cluster relationships. Our experiments reveal that while fully trained Quantum Neural Networks (QNN) outperform random Quantum Features (QF) in quantitative metrics, the AI Agent further uncovers nuanced differences between these methods, notably exposing the singleton cluster phenomenon in QNN driven models. The consolidated insights from both stages consistently endorse the three cluster configuration, demonstrating the practical value of our hybrid approach. This work advances the interpretability frontier in quantum assisted blockchain analytics and lays the groundwork for future autonomous AI orchestrated clustering frameworks.</t>
+          <t>Quantum computing is one of the most interesting and demanding topics in the field of computer science and engineering.The potential of quantum computing in many areas such as computer security, big data, finance, health science, and many other fields are now clear because of its incredible capacity and high processing speed.In a traditional computing system, all data and information are represented with 0 and 1 bits.But quantum computers operate in a different way, using Quantum Bits, or qubits.These qubits are created and manipulated using quantum principles of superposition and entanglement and can perform certain types of complex and large calculations on vast amounts of data very rapidly.A few examples of potential applications of quantum computing include much more secure quantum encryption, tremendous speed up of database searches using Grover's database search algorithm, protein folding, and modeling of electrons in materials and molecules.Many scientists including Christopher Monroe at the University of Maryland and IonQ believe, within the next five years, a quantum computer will be capable of calculations that could never be run on traditional computing machines.In order to foster and expedite quantum computing research and development, the United States House of Representatives recently passed "The National Quantum Initiative Act (H.R. 6227)" which includes an emphasis on workforce development.In the USA, a number of startups and big tech companies are now involved in building quantum computing machines using different mechanisms of quantum physics, including ions trapped in electrical fields, superconducting circuits, quantum cloud service, spins of a single electron, etc.The computer industries are working hard to use their existing semiconductor resources and technologies combined with quantum principles to build the desired computing systems.In parallel, there is an urgent need for a new generation of engineers, scientists, and programmers who can use quantum computers to solve real-world problems.This paper discusses some opportunities and challenges in quantum computing and preparing college students to fulfill the workforce demand.It further discusses how complex quantum computing courses can be integrated into the curricula of computer science, engineering, and related programs to address future workforce development issues.A multifaceted strategy for boosting enrollment, retention and successful graduation in quantum computing is proposed in order to address workforce development issues because we need to succeed in the tough competition we are facing from other countries.</t>
         </is>
       </c>
       <c r="H48" s="5" t="inlineStr">
@@ -2836,37 +2839,33 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>49463c91e93f</t>
+          <t>2724eb4769a3</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>A Hybrid Model of Primary Ensemble Empirical Mode Decomposition and Quantum Neural Network in Financial Time Series Prediction</t>
+          <t>Feature Importance and Explainability in Quantum Machine Learning</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>Caifeng Wang; Yukun Yang; Linlin Xu; Alexander Wong</t>
+          <t>Luke Power; Krishnendu Guha</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="F49" s="5" t="inlineStr">
-        <is>
-          <t>10.1142/s0219477523400060</t>
-        </is>
-      </c>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr"/>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>Financial time series are nonlinear, volatile and chaotic. Inspired by quantum computing, this paper proposed a new model, called primary ensemble empirical mode decomposition combined with quantum neural network (PEEMD-QNN) in predicting the stock index. PEEMD-QNN takes the advantages of the PEEMD which retains the main component of modal component and QNN. To demonstrate that our PEEMD-QNN model is robust, we used the new model to predict six major stock index time series in China at a specific time. Detailed experiments are implemented for both of the proposed prediction models, in which empirical mode decomposition combined with QNN (EMD-QNN), QNN and BP neural network are compared. The results demonstrate that the proposed PEEMD-QNN model has higher accuracy than BP neural network, QNN model and EMD-QNN model in stock market prediction.</t>
+          <t>Many Machine Learning (ML) models are referred to as black box models, providing no real insights into why a prediction is made. Feature importance and explainability are important for increasing transparency and trust in ML models, particularly in settings such as healthcare and finance. With quantum computing's unique capabilities, such as leveraging quantum mechanical phenomena like superposition, which can be combined with ML techniques to create the field of Quantum Machine Learning (QML), and such techniques may be applied to QML models. This article explores feature importance and explainability insights in QML compared to Classical ML models. Utilizing the widely recognized Iris dataset, classical ML algorithms such as SVM and Random Forests, are compared against hybrid quantum counterparts, implemented via IBM's Qiskit platform: the Variational Quantum Classifier (VQC) and Quantum Support Vector Classifier (QSVC). This article aims to provide a comparison of the insights generated in ML by employing permutation and leave one out feature importance methods, alongside ALE (Accumulated Local Effects) and SHAP (SHapley Additive exPlanations) explainers.</t>
         </is>
       </c>
       <c r="H49" s="5" t="inlineStr">
         <is>
-          <t>openalex</t>
+          <t>arxiv</t>
         </is>
       </c>
       <c r="I49" s="5" t="n"/>
@@ -2880,37 +2879,37 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>4c3d7f8d947e</t>
+          <t>f96b7eb14d34</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>The Needs and Challenges of Workforce Development in Quantum Computing</t>
+          <t>Exponential Enhancement of the Efficiency of Quantum Annealing by Non-Stochastic Hamiltonians</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>Mohammad Amin; Ronald Uhlig; Pradip Peter Dey; Bhaskar Raj Sinha; Shatha Jawad</t>
+          <t>Hidetoshi Nishimori; Kabuki Takada</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>10.18260/1-2--31846</t>
+          <t>10.3389/fict.2017.00002</t>
         </is>
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>Quantum computing is one of the most interesting and demanding topics in the field of computer science and engineering.The potential of quantum computing in many areas such as computer security, big data, finance, health science, and many other fields are now clear because of its incredible capacity and high processing speed.In a traditional computing system, all data and information are represented with 0 and 1 bits.But quantum computers operate in a different way, using Quantum Bits, or qubits.These qubits are created and manipulated using quantum principles of superposition and entanglement and can perform certain types of complex and large calculations on vast amounts of data very rapidly.A few examples of potential applications of quantum computing include much more secure quantum encryption, tremendous speed up of database searches using Grover's database search algorithm, protein folding, and modeling of electrons in materials and molecules.Many scientists including Christopher Monroe at the University of Maryland and IonQ believe, within the next five years, a quantum computer will be capable of calculations that could never be run on traditional computing machines.In order to foster and expedite quantum computing research and development, the United States House of Representatives recently passed "The National Quantum Initiative Act (H.R. 6227)" which includes an emphasis on workforce development.In the USA, a number of startups and big tech companies are now involved in building quantum computing machines using different mechanisms of quantum physics, including ions trapped in electrical fields, superconducting circuits, quantum cloud service, spins of a single electron, etc.The computer industries are working hard to use their existing semiconductor resources and technologies combined with quantum principles to build the desired computing systems.In parallel, there is an urgent need for a new generation of engineers, scientists, and programmers who can use quantum computers to solve real-world problems.This paper discusses some opportunities and challenges in quantum computing and preparing college students to fulfill the workforce demand.It further discusses how complex quantum computing courses can be integrated into the curricula of computer science, engineering, and related programs to address future workforce development issues.A multifaceted strategy for boosting enrollment, retention and successful graduation in quantum computing is proposed in order to address workforce development issues because we need to succeed in the tough competition we are facing from other countries.</t>
+          <t>Non-stoquastic Hamiltonians have both positive and negative signs in off-diagonal elements in their matrix representation in the standard computational basis and thus cannot be simulated efficiently by the standard quantum Monte Carlo method due to the sign problem. We describe our analytical studies of this type of Hamiltonians with infinite-range non-random as well as random interactions from the perspective of possible enhancement of the efficiency of quantum annealing or adiabatic quantum computing. It is shown that multi-body transverse interactions like $XX$ and $XXXXX$ with positive coefficients appended to a stoquastic transverse-field Ising model render the Hamiltonian non-stoquastic and reduce a first-order quantum phase transition in the simple transverse-field case to a second-order transition. This implies that the efficiency of quantum annealing is exponentially enhanced, because a first-order transition has an exponentially small energy gap (and therefore exponentially long computation time) whereas a second-order transition has a polynomially decaying gap (polynomial computation time). The examples presented here represent rare instances where strong quantum effects, in the sense that they cannot be efficiently simulated in the standard quantum Monte Carlo, have analytically been shown to exponentially enhance the efficiency of quantum annealing for combinatorial optimization problems.</t>
         </is>
       </c>
       <c r="H50" s="5" t="inlineStr">
         <is>
-          <t>openalex</t>
+          <t>arxiv</t>
         </is>
       </c>
       <c r="I50" s="5" t="n"/>
@@ -2924,33 +2923,33 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>2724eb4769a3</t>
+          <t>6c8725e6f1ed</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>Feature Importance and Explainability in Quantum Machine Learning</t>
+          <t>Quantum Artificial Intelligence: A Comprehensive Survey</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>Luke Power; Krishnendu Guha</t>
+          <t>Wei Liu; Yingfeng Wang; Lichao Sun; Lu Zhang; Xianqiao Wang; Quanzheng Li; Gang Li; Tianming Liu; Xiang Li; Dajiang Zhu; Lin Zhao; Junhao Chen; Wei Zhang; Xiaowei Yu; Hanqi Jiang; Yi Pan; Zhengliang Liu</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="F51" s="5" t="inlineStr"/>
-      <c r="G51" s="5" t="inlineStr">
-        <is>
-          <t>Many Machine Learning (ML) models are referred to as black box models, providing no real insights into why a prediction is made. Feature importance and explainability are important for increasing transparency and trust in ML models, particularly in settings such as healthcare and finance. With quantum computing's unique capabilities, such as leveraging quantum mechanical phenomena like superposition, which can be combined with ML techniques to create the field of Quantum Machine Learning (QML), and such techniques may be applied to QML models. This article explores feature importance and explainability insights in QML compared to Classical ML models. Utilizing the widely recognized Iris dataset, classical ML algorithms such as SVM and Random Forests, are compared against hybrid quantum counterparts, implemented via IBM's Qiskit platform: the Variational Quantum Classifier (VQC) and Quantum Support Vector Classifier (QSVC). This article aims to provide a comparison of the insights generated in ML by employing permutation and leave one out feature importance methods, alongside ALE (Accumulated Local Effects) and SHAP (SHapley Additive exPlanations) explainers.</t>
-        </is>
-      </c>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>10.17615/ksxt-7130</t>
+        </is>
+      </c>
+      <c r="G51" s="5" t="inlineStr"/>
       <c r="H51" s="5" t="inlineStr">
         <is>
-          <t>arxiv</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="I51" s="5" t="n"/>
@@ -2964,32 +2963,32 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>f96b7eb14d34</t>
+          <t>0589931d86b4</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>Exponential Enhancement of the Efficiency of Quantum Annealing by Non-Stochastic Hamiltonians</t>
+          <t>Quantum versus Classical Annealing of Ising Spin Glasses</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>Hidetoshi Nishimori; Kabuki Takada</t>
+          <t>Bettina Heim; Troels F. Rønnow; Sergei V. Isakov; Matthias Troyer</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>10.3389/fict.2017.00002</t>
+          <t>10.1126/science.aaa4170</t>
         </is>
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
-          <t>Non-stoquastic Hamiltonians have both positive and negative signs in off-diagonal elements in their matrix representation in the standard computational basis and thus cannot be simulated efficiently by the standard quantum Monte Carlo method due to the sign problem. We describe our analytical studies of this type of Hamiltonians with infinite-range non-random as well as random interactions from the perspective of possible enhancement of the efficiency of quantum annealing or adiabatic quantum computing. It is shown that multi-body transverse interactions like $XX$ and $XXXXX$ with positive coefficients appended to a stoquastic transverse-field Ising model render the Hamiltonian non-stoquastic and reduce a first-order quantum phase transition in the simple transverse-field case to a second-order transition. This implies that the efficiency of quantum annealing is exponentially enhanced, because a first-order transition has an exponentially small energy gap (and therefore exponentially long computation time) whereas a second-order transition has a polynomially decaying gap (polynomial computation time). The examples presented here represent rare instances where strong quantum effects, in the sense that they cannot be efficiently simulated in the standard quantum Monte Carlo, have analytically been shown to exponentially enhance the efficiency of quantum annealing for combinatorial optimization problems.</t>
+          <t>The strongest evidence for superiority of quantum annealing on spin glass problems has come from comparing simulated quantum annealing using quantum Monte Carlo (QMC) methods to simulated classical annealing [G. Santoro et al., Science 295, 2427(2002)]. Motivated by experiments on programmable quantum annealing devices we revisit the question of when quantum speedup may be expected for Ising spin glass problems. We find that even though a better scaling compared to simulated classical annealing can be achieved for QMC simulations, this advantage is due to time discretization and measurements which are not possible on a physical quantum annealing device. QMC simulations in the physically relevant continuous time limit, on the other hand, do not show superiority. Our results imply that care has to be taken when using QMC simulations to assess quantum speedup potential and are consistent with recent arguments that no quantum speedup should be expected for two-dimensional spin glass problems.</t>
         </is>
       </c>
       <c r="H52" s="5" t="inlineStr">
@@ -3008,30 +3007,34 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>6c8725e6f1ed</t>
+          <t>f3a41b21a780</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>Quantum Artificial Intelligence: A Comprehensive Survey</t>
+          <t>Approximate amplitude encoding in shallow parameterized quantum circuits and its application to financial market indicator</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>Wei Liu; Yingfeng Wang; Lichao Sun; Lu Zhang; Xianqiao Wang; Quanzheng Li; Gang Li; Tianming Liu; Xiang Li; Dajiang Zhu; Lin Zhao; Junhao Chen; Wei Zhang; Xiaowei Yu; Hanqi Jiang; Yi Pan; Zhengliang Liu</t>
+          <t>Kouhei Nakaji; Shumpei Uno; Yohichi Suzuki; Rudy Raymond; Tamiya Onodera; Tomoki Tanaka; Hiroyuki Tezuka; Naoki Mitsuda; Naoki Yamamoto</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>10.17615/ksxt-7130</t>
-        </is>
-      </c>
-      <c r="G53" s="5" t="inlineStr"/>
+          <t>10.48550/arxiv.2103.13211</t>
+        </is>
+      </c>
+      <c r="G53" s="5" t="inlineStr">
+        <is>
+          <t>Efficient methods for loading given classical data into quantum circuits are essential for various quantum algorithms. In this paper, we propose an algorithm called Approximate Amplitude Encoding that can effectively load all the components of a given real-valued data vector into the amplitude of quantum state, while the previous proposal can only load the absolute values of those components. The key of our algorithm is to variationally train a shallow parameterized quantum circuit, using the results of two types of measurement; the standard computational-basis measurement plus the measurement in the Hadamard-transformed basis, introduced in order to handle the sign of the data components. The variational algorithm changes the circuit parameters so as to minimize the sum of two costs corresponding to those two measurement basis, both of which are given by the efficiently-computable maximum mean discrepancy. We also consider the problem of constructing the singular value decomposition entropy via the stock market dataset to give a financial market indicator; a quantum algorithm (the variational singular value decomposition algorithm) is known to produce a solution faster than classical, which yet requires the sign-dependent amplitude encoding. We demonstrate, with an in-depth numerical analysis, that our algorithm realizes loading of time-series of real stock prices on quantum state with small approximation error, and thereby it enables constructing an indicator of the financial market based on the stock prices.</t>
+        </is>
+      </c>
       <c r="H53" s="5" t="inlineStr">
         <is>
           <t>openalex</t>
@@ -3048,32 +3051,32 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>0589931d86b4</t>
+          <t>5781ce30742b</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>Quantum versus Classical Annealing of Ising Spin Glasses</t>
+          <t>Alignment between Initial State and Mixer Improves QAOA Performance for Constrained Optimization</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>Bettina Heim; Troels F. Rønnow; Sergei V. Isakov; Matthias Troyer</t>
+          <t>Zichang He; Ruslan Shaydulin; Shouvanik Chakrabarti; Dylan Herman; Changhao Li; Yue Sun; Marco Pistoia</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>10.1126/science.aaa4170</t>
+          <t>10.1038/s41534-023-00787-5</t>
         </is>
       </c>
       <c r="G54" s="5" t="inlineStr">
         <is>
-          <t>The strongest evidence for superiority of quantum annealing on spin glass problems has come from comparing simulated quantum annealing using quantum Monte Carlo (QMC) methods to simulated classical annealing [G. Santoro et al., Science 295, 2427(2002)]. Motivated by experiments on programmable quantum annealing devices we revisit the question of when quantum speedup may be expected for Ising spin glass problems. We find that even though a better scaling compared to simulated classical annealing can be achieved for QMC simulations, this advantage is due to time discretization and measurements which are not possible on a physical quantum annealing device. QMC simulations in the physically relevant continuous time limit, on the other hand, do not show superiority. Our results imply that care has to be taken when using QMC simulations to assess quantum speedup potential and are consistent with recent arguments that no quantum speedup should be expected for two-dimensional spin glass problems.</t>
+          <t>Quantum alternating operator ansatz (QAOA) has a strong connection to the adiabatic algorithm, which it can approximate with sufficient depth. However, it is unclear to what extent the lessons from the adiabatic regime apply to QAOA as executed in practice with small to moderate depth. In this paper, we demonstrate that the intuition from the adiabatic algorithm applies to the task of choosing the QAOA initial state. Specifically, we observe that the best performance is obtained when the initial state of QAOA is set to be the ground state of the mixing Hamiltonian, as required by the adiabatic algorithm. We provide numerical evidence using the examples of constrained portfolio optimization problems with both low ($p\leq 3$) and high ($p = 100$) QAOA depth. Additionally, we successfully apply QAOA with XY mixer to portfolio optimization on a trapped-ion quantum processor using 32 qubits and discuss our findings in near-term experiments.</t>
         </is>
       </c>
       <c r="H54" s="5" t="inlineStr">
@@ -3092,37 +3095,33 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>f3a41b21a780</t>
+          <t>b6eb243139d5</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>Approximate amplitude encoding in shallow parameterized quantum circuits and its application to financial market indicator</t>
+          <t>Advancements and Applications of Blockchain Technology in Diverse Domains: A Literature Review</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>Kouhei Nakaji; Shumpei Uno; Yohichi Suzuki; Rudy Raymond; Tamiya Onodera; Tomoki Tanaka; Hiroyuki Tezuka; Naoki Mitsuda; Naoki Yamamoto</t>
+          <t>Sejfuli-Ramadani N.</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>10.48550/arxiv.2103.13211</t>
-        </is>
-      </c>
-      <c r="G55" s="5" t="inlineStr">
-        <is>
-          <t>Efficient methods for loading given classical data into quantum circuits are essential for various quantum algorithms. In this paper, we propose an algorithm called Approximate Amplitude Encoding that can effectively load all the components of a given real-valued data vector into the amplitude of quantum state, while the previous proposal can only load the absolute values of those components. The key of our algorithm is to variationally train a shallow parameterized quantum circuit, using the results of two types of measurement; the standard computational-basis measurement plus the measurement in the Hadamard-transformed basis, introduced in order to handle the sign of the data components. The variational algorithm changes the circuit parameters so as to minimize the sum of two costs corresponding to those two measurement basis, both of which are given by the efficiently-computable maximum mean discrepancy. We also consider the problem of constructing the singular value decomposition entropy via the stock market dataset to give a financial market indicator; a quantum algorithm (the variational singular value decomposition algorithm) is known to produce a solution faster than classical, which yet requires the sign-dependent amplitude encoding. We demonstrate, with an in-depth numerical analysis, that our algorithm realizes loading of time-series of real stock prices on quantum state with small approximation error, and thereby it enables constructing an indicator of the financial market based on the stock prices.</t>
-        </is>
-      </c>
+          <t>10.1109/MECO62516.2024.10577865</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="inlineStr"/>
       <c r="H55" s="5" t="inlineStr">
         <is>
-          <t>openalex</t>
+          <t>scopus</t>
         </is>
       </c>
       <c r="I55" s="5" t="n"/>
@@ -3136,32 +3135,28 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>5781ce30742b</t>
+          <t>af45f323f9be</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>Alignment between Initial State and Mixer Improves QAOA Performance for Constrained Optimization</t>
+          <t>Federated Learning: A Survey on Privacy-Preserving Collaborative Intelligence</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>Zichang He; Ruslan Shaydulin; Shouvanik Chakrabarti; Dylan Herman; Changhao Li; Yue Sun; Marco Pistoia</t>
+          <t>Ratun Rahman</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="F56" s="5" t="inlineStr">
-        <is>
-          <t>10.1038/s41534-023-00787-5</t>
-        </is>
-      </c>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F56" s="5" t="inlineStr"/>
       <c r="G56" s="5" t="inlineStr">
         <is>
-          <t>Quantum alternating operator ansatz (QAOA) has a strong connection to the adiabatic algorithm, which it can approximate with sufficient depth. However, it is unclear to what extent the lessons from the adiabatic regime apply to QAOA as executed in practice with small to moderate depth. In this paper, we demonstrate that the intuition from the adiabatic algorithm applies to the task of choosing the QAOA initial state. Specifically, we observe that the best performance is obtained when the initial state of QAOA is set to be the ground state of the mixing Hamiltonian, as required by the adiabatic algorithm. We provide numerical evidence using the examples of constrained portfolio optimization problems with both low ($p\leq 3$) and high ($p = 100$) QAOA depth. Additionally, we successfully apply QAOA with XY mixer to portfolio optimization on a trapped-ion quantum processor using 32 qubits and discuss our findings in near-term experiments.</t>
+          <t>Federated Learning (FL) has emerged as a transformative paradigm in the field of distributed machine learning, enabling multiple clients such as mobile devices, edge nodes, or organizations to collaboratively train a shared global model without the need to centralize sensitive data. This decentralized approach addresses growing concerns around data privacy, security, and regulatory compliance, making it particularly attractive in domains such as healthcare, finance, and smart IoT systems. This survey provides a concise yet comprehensive overview of Federated Learning, beginning with its core architecture and communication protocol. We discuss the standard FL lifecycle, including local training, model aggregation, and global updates. A particular emphasis is placed on key technical challenges such as handling non-IID (non-independent and identically distributed) data, mitigating system and hardware heterogeneity, reducing communication overhead, and ensuring privacy through mechanisms like differential privacy and secure aggregation. Furthermore, we examine emerging trends in FL research, including personalized FL, cross-device versus cross-silo settings, and integration with other paradigms such as reinforcement learning and quantum computing. We also highlight real-world applications and summarize benchmark datasets and evaluation metrics commonly used in FL research. Finally, we outline open research problems and future directions to guide the development of scalable, efficient, and trustworthy FL systems.</t>
         </is>
       </c>
       <c r="H56" s="5" t="inlineStr">
@@ -3180,33 +3175,33 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>b6eb243139d5</t>
+          <t>d83f5f912d08</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>Advancements and Applications of Blockchain Technology in Diverse Domains: A Literature Review</t>
+          <t>Evaluating Classical and Quantum Machine Learning for Credit Card Fraud Detection: Performance and Economic Impact</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>Sejfuli-Ramadani N.</t>
+          <t>M. Usman Maqbool Bhutta; Abid Mehmood</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>10.1109/MECO62516.2024.10577865</t>
+          <t>10.1109/cars67163.2025.11337509</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr"/>
       <c r="H57" s="5" t="inlineStr">
         <is>
-          <t>scopus</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="I57" s="5" t="n"/>
@@ -3220,17 +3215,17 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>af45f323f9be</t>
+          <t>9866ca62fddf</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>Federated Learning: A Survey on Privacy-Preserving Collaborative Intelligence</t>
+          <t>Quantum Computing in Embedded Finance</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>Ratun Rahman</t>
+          <t>CA Mohd Swaleh; Dr.N Subbu Krishna Sastry</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -3238,15 +3233,19 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="F58" s="5" t="inlineStr"/>
+      <c r="F58" s="5" t="inlineStr">
+        <is>
+          <t>10.20431/2349-0349.1306001</t>
+        </is>
+      </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
-          <t>Federated Learning (FL) has emerged as a transformative paradigm in the field of distributed machine learning, enabling multiple clients such as mobile devices, edge nodes, or organizations to collaboratively train a shared global model without the need to centralize sensitive data. This decentralized approach addresses growing concerns around data privacy, security, and regulatory compliance, making it particularly attractive in domains such as healthcare, finance, and smart IoT systems. This survey provides a concise yet comprehensive overview of Federated Learning, beginning with its core architecture and communication protocol. We discuss the standard FL lifecycle, including local training, model aggregation, and global updates. A particular emphasis is placed on key technical challenges such as handling non-IID (non-independent and identically distributed) data, mitigating system and hardware heterogeneity, reducing communication overhead, and ensuring privacy through mechanisms like differential privacy and secure aggregation. Furthermore, we examine emerging trends in FL research, including personalized FL, cross-device versus cross-silo settings, and integration with other paradigms such as reinforcement learning and quantum computing. We also highlight real-world applications and summarize benchmark datasets and evaluation metrics commonly used in FL research. Finally, we outline open research problems and future directions to guide the development of scalable, efficient, and trustworthy FL systems.</t>
+          <t>Quantum computing is a new technology that can change many industries, especially finance, by providing much faster and more powerful computing.This journal looks at how quantum computing can be used in embedded finance systems.Embedded finance means adding financial services to non-financial platforms, like making payments directly in a shopping app.This paper aims to explore how quantum computing can enhance such systems by enabling quicker transactions and strengthening security measures.It will also talk about the challenges, like the high cost and complexity of quantum computers.We will review existing research and conduct new studies to understand how quantum computing can improve financial processes.For example, quantum computing can help in risk assessment, fraud detection, and portfolio optimization by solving complex calculations much faster than current computers.This journal aims to show how combining quantum computing with embedded finance can create new opportunities for financial services and make them more efficient and secure.By examining the present advancements in quantum computing and its potential developments, this study seeks to offer meaningful insights to researchers, finance professionals, and technology innovators.</t>
         </is>
       </c>
       <c r="H58" s="5" t="inlineStr">
         <is>
-          <t>arxiv</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="I58" s="5" t="n"/>
@@ -3260,33 +3259,33 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>d83f5f912d08</t>
+          <t>d24184e88415</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>Evaluating Classical and Quantum Machine Learning for Credit Card Fraud Detection: Performance and Economic Impact</t>
+          <t>Quantum amplitude estimation with error mitigation for time-evolving probabilistic networks</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>M. Usman Maqbool Bhutta; Abid Mehmood</t>
+          <t>M. C. Braun; T. Decker; N. Hegemann; S. Kerstan; C. Maier; J. Ulmanis</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="F59" s="5" t="inlineStr">
-        <is>
-          <t>10.1109/cars67163.2025.11337509</t>
-        </is>
-      </c>
-      <c r="G59" s="5" t="inlineStr"/>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F59" s="5" t="inlineStr"/>
+      <c r="G59" s="5" t="inlineStr">
+        <is>
+          <t>We present a method to model a discretized time evolution of probabilistic networks on gate-based quantum computers. We consider networks of nodes, where each node can be in one of two states: good or failed. In each time step, probabilities are assigned for each node to fail (switch from good to failed) or to recover (switch from failed to good). Furthermore, probabilities are assigned for failing nodes to trigger the failure of other, good nodes. Our method can evaluate arbitrary network topologies for any number of time steps. We can therefore model events such as cascaded failure and avalanche effects which are inherent to financial networks, payment and supply chain networks, power grids, telecommunication networks and others. Using quantum amplitude estimation techniques, we are able to estimate the probability of any configuration for any set of nodes over time. This allows us, for example, to determine the probability of the first node to be in the good state after the last time step, without the necessity to track intermediate states. We present the results of a low-depth quantum amplitude estimation on a simulator with a realistic noise model. We also present the results for running this example on the AQT quantum computer system PINE. Finally, we introduce an error model that allows us to improve the results from the simulator and from the experiments on the PINE system.</t>
+        </is>
+      </c>
       <c r="H59" s="5" t="inlineStr">
         <is>
-          <t>openalex</t>
+          <t>semantic_scholar</t>
         </is>
       </c>
       <c r="I59" s="5" t="n"/>
@@ -3300,37 +3299,37 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>9866ca62fddf</t>
+          <t>8e988d1ef35c</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>Quantum Computing in Embedded Finance</t>
+          <t>Quantum Monte Carlo Analysis of Exchange and Correlation in the Strongly Inhomogeneous Electron Gas</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>CA Mohd Swaleh; Dr.N Subbu Krishna Sastry</t>
+          <t>Maziar Nekovee; W. M. C. Foulkes; R. J. Needs</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>10.20431/2349-0349.1306001</t>
+          <t>10.1103/PhysRevLett.87.036401</t>
         </is>
       </c>
       <c r="G60" s="5" t="inlineStr">
         <is>
-          <t>Quantum computing is a new technology that can change many industries, especially finance, by providing much faster and more powerful computing.This journal looks at how quantum computing can be used in embedded finance systems.Embedded finance means adding financial services to non-financial platforms, like making payments directly in a shopping app.This paper aims to explore how quantum computing can enhance such systems by enabling quicker transactions and strengthening security measures.It will also talk about the challenges, like the high cost and complexity of quantum computers.We will review existing research and conduct new studies to understand how quantum computing can improve financial processes.For example, quantum computing can help in risk assessment, fraud detection, and portfolio optimization by solving complex calculations much faster than current computers.This journal aims to show how combining quantum computing with embedded finance can create new opportunities for financial services and make them more efficient and secure.By examining the present advancements in quantum computing and its potential developments, this study seeks to offer meaningful insights to researchers, finance professionals, and technology innovators.</t>
+          <t>We use variational quantum Monte Carlo to calculate the density-functional exchange-correlation hole n_{xc}, the exchange-correlation energy density e_{xc}, and the total exchange-correlation energy E_{xc}, of several electron gas systems in which strong density inhomogeneities are induced by a cosine-wave potential. We compare our results with the local density approximation and the generalized gradient approximation. It is found that the nonlocal contributions to e_{xc} contain an energetically significant component, the magnitude, shape, and sign of which are controlled by the Laplacian of the electron density.</t>
         </is>
       </c>
       <c r="H60" s="5" t="inlineStr">
         <is>
-          <t>openalex</t>
+          <t>arxiv</t>
         </is>
       </c>
       <c r="I60" s="5" t="n"/>
@@ -3344,33 +3343,37 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>d24184e88415</t>
+          <t>ccd83b62aeec</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>Quantum amplitude estimation with error mitigation for time-evolving probabilistic networks</t>
+          <t>Integrating Quantum Computing and Predictive Analytics and Their Role in Reducing Costs and Achieving Sustainable Development Goals</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>M. C. Braun; T. Decker; N. Hegemann; S. Kerstan; C. Maier; J. Ulmanis</t>
+          <t>Ghazi Maan Faisal; Saba Kareem Abbood</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
         <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="F61" s="5" t="inlineStr"/>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F61" s="5" t="inlineStr">
+        <is>
+          <t>10.47172/2965-730x.sdgsreview.v5.n03.pe05573</t>
+        </is>
+      </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>We present a method to model a discretized time evolution of probabilistic networks on gate-based quantum computers. We consider networks of nodes, where each node can be in one of two states: good or failed. In each time step, probabilities are assigned for each node to fail (switch from good to failed) or to recover (switch from failed to good). Furthermore, probabilities are assigned for failing nodes to trigger the failure of other, good nodes. Our method can evaluate arbitrary network topologies for any number of time steps. We can therefore model events such as cascaded failure and avalanche effects which are inherent to financial networks, payment and supply chain networks, power grids, telecommunication networks and others. Using quantum amplitude estimation techniques, we are able to estimate the probability of any configuration for any set of nodes over time. This allows us, for example, to determine the probability of the first node to be in the good state after the last time step, without the necessity to track intermediate states. We present the results of a low-depth quantum amplitude estimation on a simulator with a realistic noise model. We also present the results for running this example on the AQT quantum computer system PINE. Finally, we introduce an error model that allows us to improve the results from the simulator and from the experiments on the PINE system.</t>
+          <t>Objectives: The research aims to demonstrate the integration between Quantum Computing (QC) and Predictive Analysis (PA) and their role in reducing costs while achieving Sustainable Development Goals (SDGs). The study addresses the inefficiencies in calculating and measuring product costs under traditional systems and examines how QC and PA can enhance cost reduction and product quality to better meet customer needs. Additionally, the research seeks to strengthen the theoretical framework with practical applications, illustrating how this integration improves a company’s competitive position while promoting social, environmental, and economic sustainability. Methods: The study employs a descriptive analytical approach, focusing on the practical application of QC and PA in cost management. It relies on financial and cost data from a selected company to analyze the impact of integrating QC and PA on cost reduction and sustainable development. The methodology aims to provide empirical evidence supporting the effectiveness of this integration in optimizing resource and energy use. Results: The research findings confirm that integrating QC and PA significantly contributes to cost reduction, which in turn plays a crucial role in achieving SDGs. The study highlights how this integration enhances efficiency in resource and energy utilization, identifies weaknesses in traditional cost systems, and supports the transition toward sustainable manufacturing. By improving production processes and minimizing waste, the application of QC and PA fosters innovation in sustainable product development. Conclusion: The study underscores the importance of integrating QC and PA in modern cost management strategies to achieve sustainability objectives. Encouraging innovative local manufacturing through enhanced efficiency and resource optimization supports the transition toward sustainable production. The findings suggest that companies adopting QC and PA can improve their competitive edge, reduce costs, and contribute to environmental and economic sustainability, ultimately aligning with global sustainable development goals.</t>
         </is>
       </c>
       <c r="H61" s="5" t="inlineStr">
         <is>
-          <t>semantic_scholar</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="I61" s="5" t="n"/>
@@ -3384,37 +3387,37 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>8e988d1ef35c</t>
+          <t>60f7527318ef</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>Quantum Monte Carlo Analysis of Exchange and Correlation in the Strongly Inhomogeneous Electron Gas</t>
+          <t>Impact of quantum technologies on innovation processes in the global economy</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>Maziar Nekovee; W. M. C. Foulkes; R. J. Needs</t>
+          <t>Роман КОРЖ</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>10.1103/PhysRevLett.87.036401</t>
+          <t>10.36887/2415-8453-2024-2-14</t>
         </is>
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>We use variational quantum Monte Carlo to calculate the density-functional exchange-correlation hole n_{xc}, the exchange-correlation energy density e_{xc}, and the total exchange-correlation energy E_{xc}, of several electron gas systems in which strong density inhomogeneities are induced by a cosine-wave potential. We compare our results with the local density approximation and the generalized gradient approximation. It is found that the nonlocal contributions to e_{xc} contain an energetically significant component, the magnitude, shape, and sign of which are controlled by the Laplacian of the electron density.</t>
+          <t>The article examines the impact of quantum technologies on innovation processes in the global economy. It analyzes the critical aspects of integrating quantum technologies in various sectors of the economy, particularly in the financial, health care, production, and IT spheres. Theoretical models and empirical data confirming how quantum technologies can accelerate innovation processes, increase research efficiency, and create new economic opportunities are considered. The article also provides practical recommendations for strategic planning and management of innovation processes in the conditions of the quantum revolution. Special attention is paid to the importance of an interdisciplinary approach and cooperation between business and the state. The author noted that the modern economy is on the threshold of a new era, where quantum technologies play a decisive role, which represents a new class of tools capable of radically changing traditional approaches to data processing, security, and computing. Quantum computers, quantum cryptography and quantum communication open opportunities for the economy that can accelerate the development of new materials, optimize logistics chains and increase the level of data security. At the same time, the article highlights the need to develop global standards in the field of quantum technologies. The results of the research will contribute to a better understanding of the potential of quantum technologies to stimulate innovation and increase the competitiveness of the economy. Keywords: quantum technologies, global economy, innovation processes, quantum cryptography, quantum computing, quantum modeling, quantum communication, economic models, quantum algorithms, cyber security, logistics optimization, risk management, economic growth, financial markets, health care, production, quantum networks, development strategies, digital economy, technological revolution.</t>
         </is>
       </c>
       <c r="H62" s="5" t="inlineStr">
         <is>
-          <t>arxiv</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="I62" s="5" t="n"/>
@@ -3428,37 +3431,37 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>ccd83b62aeec</t>
+          <t>19660db0b2c6</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>Integrating Quantum Computing and Predictive Analytics and Their Role in Reducing Costs and Achieving Sustainable Development Goals</t>
+          <t>Obstacles to quantum annealing in a planar embedding of XORSAT</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>Ghazi Maan Faisal; Saba Kareem Abbood</t>
+          <t>Pranay Patil; Stefanos Kourtis; Claudio Chamon; Eduardo R. Mucciolo; Andrei E. Ruckenstein</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>10.47172/2965-730x.sdgsreview.v5.n03.pe05573</t>
+          <t>10.1103/PhysRevB.100.054435</t>
         </is>
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>Objectives: The research aims to demonstrate the integration between Quantum Computing (QC) and Predictive Analysis (PA) and their role in reducing costs while achieving Sustainable Development Goals (SDGs). The study addresses the inefficiencies in calculating and measuring product costs under traditional systems and examines how QC and PA can enhance cost reduction and product quality to better meet customer needs. Additionally, the research seeks to strengthen the theoretical framework with practical applications, illustrating how this integration improves a company’s competitive position while promoting social, environmental, and economic sustainability. Methods: The study employs a descriptive analytical approach, focusing on the practical application of QC and PA in cost management. It relies on financial and cost data from a selected company to analyze the impact of integrating QC and PA on cost reduction and sustainable development. The methodology aims to provide empirical evidence supporting the effectiveness of this integration in optimizing resource and energy use. Results: The research findings confirm that integrating QC and PA significantly contributes to cost reduction, which in turn plays a crucial role in achieving SDGs. The study highlights how this integration enhances efficiency in resource and energy utilization, identifies weaknesses in traditional cost systems, and supports the transition toward sustainable manufacturing. By improving production processes and minimizing waste, the application of QC and PA fosters innovation in sustainable product development. Conclusion: The study underscores the importance of integrating QC and PA in modern cost management strategies to achieve sustainability objectives. Encouraging innovative local manufacturing through enhanced efficiency and resource optimization supports the transition toward sustainable production. The findings suggest that companies adopting QC and PA can improve their competitive edge, reduce costs, and contribute to environmental and economic sustainability, ultimately aligning with global sustainable development goals.</t>
+          <t>We introduce a planar embedding of the k-regular k-XORSAT problem, in which solutions are encoded in the ground state of a classical statistical mechanics model of reversible logic gates arranged on a square grid and acting on bits that represent the Boolean variables of the problem. The special feature of this embedding is that the resulting model lacks a finite-temperature phase transition, thus bypassing the first-order thermodynamic transition known to occur in the random graph representation of XORSAT. In spite of this attractive feature, the thermal relaxation into the ground state displays remarkably slow glassy behavior. The question addressed in this paper is whether this planar embedding can afford an efficient path to solution of k-regular k-XORSAT via quantum adiabatic annealing. We first show that our model bypasses an avoided level crossing and consequent exponentially small gap in the limit of small transverse fields. We then present quantum Monte Carlo results for our embedding of the k-regular k-XORSAT that strongly support a picture in which second-order and first-order transitions develop at a finite transverse field for k = 2 and k = 3, respectively. This translates into power-law and exponential dependences in the scaling of energy gaps with system size, corresponding to times-to-solution which are, respectively, polynomial and exponential in the number of variables. We conclude that neither classical nor quantum annealing can efficiently solve our reformulation of XORSAT, even though the original problem can be solved in polynomial time by Gaussian elimination.</t>
         </is>
       </c>
       <c r="H63" s="5" t="inlineStr">
         <is>
-          <t>openalex</t>
+          <t>arxiv</t>
         </is>
       </c>
       <c r="I63" s="5" t="n"/>
@@ -3472,37 +3475,25 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>60f7527318ef</t>
+          <t>c105c8df3d91</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>Impact of quantum technologies on innovation processes in the global economy</t>
-        </is>
-      </c>
-      <c r="D64" s="5" t="inlineStr">
-        <is>
-          <t>Роман КОРЖ</t>
-        </is>
-      </c>
+          <t>14th Workshop on Computational Optimization, WCO 2021</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="inlineStr"/>
       <c r="E64" s="5" t="inlineStr">
         <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="F64" s="5" t="inlineStr">
-        <is>
-          <t>10.36887/2415-8453-2024-2-14</t>
-        </is>
-      </c>
-      <c r="G64" s="5" t="inlineStr">
-        <is>
-          <t>The article examines the impact of quantum technologies on innovation processes in the global economy. It analyzes the critical aspects of integrating quantum technologies in various sectors of the economy, particularly in the financial, health care, production, and IT spheres. Theoretical models and empirical data confirming how quantum technologies can accelerate innovation processes, increase research efficiency, and create new economic opportunities are considered. The article also provides practical recommendations for strategic planning and management of innovation processes in the conditions of the quantum revolution. Special attention is paid to the importance of an interdisciplinary approach and cooperation between business and the state. The author noted that the modern economy is on the threshold of a new era, where quantum technologies play a decisive role, which represents a new class of tools capable of radically changing traditional approaches to data processing, security, and computing. Quantum computers, quantum cryptography and quantum communication open opportunities for the economy that can accelerate the development of new materials, optimize logistics chains and increase the level of data security. At the same time, the article highlights the need to develop global standards in the field of quantum technologies. The results of the research will contribute to a better understanding of the potential of quantum technologies to stimulate innovation and increase the competitiveness of the economy. Keywords: quantum technologies, global economy, innovation processes, quantum cryptography, quantum computing, quantum modeling, quantum communication, economic models, quantum algorithms, cyber security, logistics optimization, risk management, economic growth, financial markets, health care, production, quantum networks, development strategies, digital economy, technological revolution.</t>
-        </is>
-      </c>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="F64" s="5" t="inlineStr"/>
+      <c r="G64" s="5" t="inlineStr"/>
       <c r="H64" s="5" t="inlineStr">
         <is>
-          <t>openalex</t>
+          <t>scopus</t>
         </is>
       </c>
       <c r="I64" s="5" t="n"/>
@@ -3516,37 +3507,33 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>19660db0b2c6</t>
+          <t>38fb4cff88e5</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>Obstacles to quantum annealing in a planar embedding of XORSAT</t>
+          <t>Quantum-assisted support vector regression</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>Pranay Patil; Stefanos Kourtis; Claudio Chamon; Eduardo R. Mucciolo; Andrei E. Ruckenstein</t>
+          <t>Dalal A.</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>10.1103/PhysRevB.100.054435</t>
-        </is>
-      </c>
-      <c r="G65" s="5" t="inlineStr">
-        <is>
-          <t>We introduce a planar embedding of the k-regular k-XORSAT problem, in which solutions are encoded in the ground state of a classical statistical mechanics model of reversible logic gates arranged on a square grid and acting on bits that represent the Boolean variables of the problem. The special feature of this embedding is that the resulting model lacks a finite-temperature phase transition, thus bypassing the first-order thermodynamic transition known to occur in the random graph representation of XORSAT. In spite of this attractive feature, the thermal relaxation into the ground state displays remarkably slow glassy behavior. The question addressed in this paper is whether this planar embedding can afford an efficient path to solution of k-regular k-XORSAT via quantum adiabatic annealing. We first show that our model bypasses an avoided level crossing and consequent exponentially small gap in the limit of small transverse fields. We then present quantum Monte Carlo results for our embedding of the k-regular k-XORSAT that strongly support a picture in which second-order and first-order transitions develop at a finite transverse field for k = 2 and k = 3, respectively. This translates into power-law and exponential dependences in the scaling of energy gaps with system size, corresponding to times-to-solution which are, respectively, polynomial and exponential in the number of variables. We conclude that neither classical nor quantum annealing can efficiently solve our reformulation of XORSAT, even though the original problem can be solved in polynomial time by Gaussian elimination.</t>
-        </is>
-      </c>
+          <t>10.1007/s11128-025-04674-0</t>
+        </is>
+      </c>
+      <c r="G65" s="5" t="inlineStr"/>
       <c r="H65" s="5" t="inlineStr">
         <is>
-          <t>arxiv</t>
+          <t>scopus</t>
         </is>
       </c>
       <c r="I65" s="5" t="n"/>
@@ -3560,25 +3547,33 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>c105c8df3d91</t>
+          <t>cf8ff69f1966</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>14th Workshop on Computational Optimization, WCO 2021</t>
-        </is>
-      </c>
-      <c r="D66" s="5" t="inlineStr"/>
+          <t>Methods for Solving the Markowitz Portfolio Optimization Problem</t>
+        </is>
+      </c>
+      <c r="D66" s="5" t="inlineStr">
+        <is>
+          <t>Miquel Noguer I Alonso</t>
+        </is>
+      </c>
       <c r="E66" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="F66" s="5" t="inlineStr"/>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F66" s="5" t="inlineStr">
+        <is>
+          <t>10.2139/ssrn.4939293</t>
+        </is>
+      </c>
       <c r="G66" s="5" t="inlineStr"/>
       <c r="H66" s="5" t="inlineStr">
         <is>
-          <t>scopus</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="I66" s="5" t="n"/>
@@ -3592,17 +3587,17 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>38fb4cff88e5</t>
+          <t>cb87dd92737a</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>Quantum-assisted support vector regression</t>
+          <t>Quantum-Inspired-AI Resource Allocator for Social Impact Optimization</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>Dalal A.</t>
+          <t>Daniel T G N Maciel; Arturo Alejandro Zavala Zavala; Marcos Vinícius da Silva Bueno; Luís Paulo Jauer; Helena Palú Desidério; Laís Ribeiro Pereira</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
@@ -3612,13 +3607,17 @@
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>10.1007/s11128-025-04674-0</t>
-        </is>
-      </c>
-      <c r="G67" s="5" t="inlineStr"/>
+          <t>10.5281/zenodo.18307983</t>
+        </is>
+      </c>
+      <c r="G67" s="5" t="inlineStr">
+        <is>
+          <t>Quantum-Inspired Resource Allocation for Social Impact Optimization - Technological Extension Product This technology applies quantum-inspired optimization algorithms (QAOA-inspired classical methods) to solve NP-hard resource allocation problems in public policy. It supports evidence-based decision-making by balancing efficiency, equity, and social impact in development programs. Key Features: QAOA-inspired classical optimization with mixer and cost layers Multi-objective optimization (efficiency vs equity trade-offs) Fairness-aware algorithmic selection with constraint satisfaction Pareto frontier generation for policy scenario analysis Performance benchmarking against classical greedy algorithms AI-ready architecture for enhanced impact forecasting Application Domains: Regional development funds, emergency response allocation, infrastructure investment prioritization, social program portfolio selection. Results/Impact: Enables systematic, transparent allocation of scarce public resources with measurable improvements over traditional heuristics. Demonstrated 14-18% average improvement in social impact metrics versus greedy baselines in simulation studies. Technology Readiness Level (TRL): 5-6. Event Context: Developed as part of ENECOMAT XVIII (2025) Technological Extension initiative. This represents open technology transfer and process development, distinct from traditional academic publications. Development Status: Models under development. Requires validation with real-world policy datasets and stakeholder feedback for production deployment. Part of this content may have been AI-generated under supervision and validation by the authors.</t>
+        </is>
+      </c>
       <c r="H67" s="5" t="inlineStr">
         <is>
-          <t>scopus</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="I67" s="5" t="n"/>
@@ -3632,30 +3631,34 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>cf8ff69f1966</t>
+          <t>be40b988351f</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>Methods for Solving the Markowitz Portfolio Optimization Problem</t>
+          <t>Cybersecurity Measures in Financial Institutions Protecting Sensitive Data from Emerging Threats and Vulnerabilities</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>Miquel Noguer I Alonso</t>
+          <t>Kiran Kumar Boorugupalli; Aparna Kulkarni; Amala Suzana; Diwakaran M; Sivakumar Ponnusamy; Senthil Kumar S</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>10.2139/ssrn.4939293</t>
-        </is>
-      </c>
-      <c r="G68" s="5" t="inlineStr"/>
+          <t>10.1051/itmconf/20257602002/pdf</t>
+        </is>
+      </c>
+      <c r="G68" s="5" t="inlineStr">
+        <is>
+          <t>As financial institutions increasingly digitized, they are up against a growing suite of cybersecurity threats such as ransomware, cryptojacking, AI-enabled phishing, and quantum computing attacks. Other research work and government reports reinforce general cybersecurity concerns but are not technical or applied. They do not cater specifically to financial institutions. To fill these gaps, this study introduces an AI-based cybersecurity framework focusing on effective protection of financial data, compliance with regulations, and minimizing time for detecting threats.Building upon the existing research and drawing on best practices from both the financial and technology sectors, this paper presents a promising new framework that combines machine learning-driven methods for real-time fraud detection, the use of blockchain technology to ensure transaction integrity, and quantum-resistant and decentralized encryption methods to protect sensitive financial information from cyber threats. Whereas other research focuses on broad, high-level strategies, this research offers a step-by-step technical roadmap to zero-trust security, anomaly detection and automated cybersecurity responses. It also analyzes actual cyberattacks on financial institutions and develops predictive models to proactively reduce risks.To tackle on email-based financial scams, the research presents a deep learning-embedded BERT paradigm integrated with NLP to enhance phishing identification. It also introduces a biometric security mechanism that ensures that sensitive user data is unalterable, and accessible only to authorized parties. Cybersecurity measures for integrated financial IoT are proposed contribution to the NIST Cybersecurity Framework, including the prevention of cyber threats for automatic teller machines, mobile banking, and electronic payment systems. Challenges of compliance with GDPR, PCI-DSS and ISO 27001 are also addressed.Based on empirically-testing real-time financial datasets, the framework shows improved robustness to cyberattacks. These findings lay the groundwork for the future of cybersecurity, helping financial institutions stay secure and adaptive in the face of evolving cyber threats.</t>
+        </is>
+      </c>
       <c r="H68" s="5" t="inlineStr">
         <is>
           <t>openalex</t>
@@ -3672,17 +3675,17 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>cb87dd92737a</t>
+          <t>8ab2b3dd3f1a</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>Quantum-Inspired-AI Resource Allocator for Social Impact Optimization</t>
+          <t>A Comparative Study of Quantum Computing Development in Asia: Technical Foundations, Investment Dynamics, and Economic Implications</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>Daniel T G N Maciel; Arturo Alejandro Zavala Zavala; Marcos Vinícius da Silva Bueno; Luís Paulo Jauer; Helena Palú Desidério; Laís Ribeiro Pereira</t>
+          <t>Harjinder Singh</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
@@ -3692,14 +3695,10 @@
       </c>
       <c r="F69" s="5" t="inlineStr">
         <is>
-          <t>10.5281/zenodo.18307983</t>
-        </is>
-      </c>
-      <c r="G69" s="5" t="inlineStr">
-        <is>
-          <t>Quantum-Inspired Resource Allocation for Social Impact Optimization - Technological Extension Product This technology applies quantum-inspired optimization algorithms (QAOA-inspired classical methods) to solve NP-hard resource allocation problems in public policy. It supports evidence-based decision-making by balancing efficiency, equity, and social impact in development programs. Key Features: QAOA-inspired classical optimization with mixer and cost layers Multi-objective optimization (efficiency vs equity trade-offs) Fairness-aware algorithmic selection with constraint satisfaction Pareto frontier generation for policy scenario analysis Performance benchmarking against classical greedy algorithms AI-ready architecture for enhanced impact forecasting Application Domains: Regional development funds, emergency response allocation, infrastructure investment prioritization, social program portfolio selection. Results/Impact: Enables systematic, transparent allocation of scarce public resources with measurable improvements over traditional heuristics. Demonstrated 14-18% average improvement in social impact metrics versus greedy baselines in simulation studies. Technology Readiness Level (TRL): 5-6. Event Context: Developed as part of ENECOMAT XVIII (2025) Technological Extension initiative. This represents open technology transfer and process development, distinct from traditional academic publications. Development Status: Models under development. Requires validation with real-world policy datasets and stakeholder feedback for production deployment. Part of this content may have been AI-generated under supervision and validation by the authors.</t>
-        </is>
-      </c>
+          <t>10.2139/ssrn.5781042</t>
+        </is>
+      </c>
+      <c r="G69" s="5" t="inlineStr"/>
       <c r="H69" s="5" t="inlineStr">
         <is>
           <t>openalex</t>
@@ -3716,17 +3715,17 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>be40b988351f</t>
+          <t>48c87934ef61</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>Cybersecurity Measures in Financial Institutions Protecting Sensitive Data from Emerging Threats and Vulnerabilities</t>
+          <t>Enhancing Quantum Expectation Values via Exponential Error Suppression and CVaR Optimization</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>Kiran Kumar Boorugupalli; Aparna Kulkarni; Amala Suzana; Diwakaran M; Sivakumar Ponnusamy; Senthil Kumar S</t>
+          <t>Touheed Anwar Atif; Reuben Blake Tate; Stephan Eidenbenz</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
@@ -3734,19 +3733,15 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="F70" s="5" t="inlineStr">
-        <is>
-          <t>10.1051/itmconf/20257602002/pdf</t>
-        </is>
-      </c>
+      <c r="F70" s="5" t="inlineStr"/>
       <c r="G70" s="5" t="inlineStr">
         <is>
-          <t>As financial institutions increasingly digitized, they are up against a growing suite of cybersecurity threats such as ransomware, cryptojacking, AI-enabled phishing, and quantum computing attacks. Other research work and government reports reinforce general cybersecurity concerns but are not technical or applied. They do not cater specifically to financial institutions. To fill these gaps, this study introduces an AI-based cybersecurity framework focusing on effective protection of financial data, compliance with regulations, and minimizing time for detecting threats.Building upon the existing research and drawing on best practices from both the financial and technology sectors, this paper presents a promising new framework that combines machine learning-driven methods for real-time fraud detection, the use of blockchain technology to ensure transaction integrity, and quantum-resistant and decentralized encryption methods to protect sensitive financial information from cyber threats. Whereas other research focuses on broad, high-level strategies, this research offers a step-by-step technical roadmap to zero-trust security, anomaly detection and automated cybersecurity responses. It also analyzes actual cyberattacks on financial institutions and develops predictive models to proactively reduce risks.To tackle on email-based financial scams, the research presents a deep learning-embedded BERT paradigm integrated with NLP to enhance phishing identification. It also introduces a biometric security mechanism that ensures that sensitive user data is unalterable, and accessible only to authorized parties. Cybersecurity measures for integrated financial IoT are proposed contribution to the NIST Cybersecurity Framework, including the prevention of cyber threats for automatic teller machines, mobile banking, and electronic payment systems. Challenges of compliance with GDPR, PCI-DSS and ISO 27001 are also addressed.Based on empirically-testing real-time financial datasets, the framework shows improved robustness to cyberattacks. These findings lay the groundwork for the future of cybersecurity, helping financial institutions stay secure and adaptive in the face of evolving cyber threats.</t>
+          <t>Precise quantum expectation values are crucial for quantum algorithm development, but noise in real-world systems can degrade these estimations. While quantum error correction is resource-intensive, error mitigation strategies offer a practical alternative. This paper presents a framework that combines Virtual Channel Purification (VCP) technique with Conditional Value-at-Risk (CVaR) optimization to improve expectation value estimations in noisy quantum circuits. Our contributions are twofold: first, we derive conditions to compare CVaR values from different probability distributions, offering insights into the reliability of quantum estimations under noise. Second, we apply this framework to VCP, providing analytical bounds that establish its effectiveness in improving expectation values, both when the overhead VCP circuit is ideal (error-free) and when it adds additional noise. By introducing CVaR into the analysis of VCP, we offer a general noise-characterization method that guarantees improved expectation values for any quantum observable. We demonstrate the practical utility of our approach with numerical examples, highlighting how our bounds guide VCP implementation in noisy quantum systems.</t>
         </is>
       </c>
       <c r="H70" s="5" t="inlineStr">
         <is>
-          <t>openalex</t>
+          <t>arxiv</t>
         </is>
       </c>
       <c r="I70" s="5" t="n"/>
@@ -3760,33 +3755,33 @@
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>8ab2b3dd3f1a</t>
+          <t>6e39c2d1ab16</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>A Comparative Study of Quantum Computing Development in Asia: Technical Foundations, Investment Dynamics, and Economic Implications</t>
+          <t>A user-centric quantum benchmarking test suite and evaluation framework</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>Harjinder Singh</t>
+          <t>Liu W.B.</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>10.2139/ssrn.5781042</t>
+          <t>10.1007/s11128-023-04154-3</t>
         </is>
       </c>
       <c r="G71" s="5" t="inlineStr"/>
       <c r="H71" s="5" t="inlineStr">
         <is>
-          <t>openalex</t>
+          <t>scopus</t>
         </is>
       </c>
       <c r="I71" s="5" t="n"/>
@@ -3800,17 +3795,17 @@
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>48c87934ef61</t>
+          <t>79728b194d1a</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>Enhancing Quantum Expectation Values via Exponential Error Suppression and CVaR Optimization</t>
+          <t>A state-of-the-art review on battery cell balancing strategies</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>Touheed Anwar Atif; Reuben Blake Tate; Stephan Eidenbenz</t>
+          <t>Ashkan Safari; Arman Oshnoei; Hoda Sorouri; Frede Blaabjerg</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
@@ -3818,15 +3813,15 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="F72" s="5" t="inlineStr"/>
-      <c r="G72" s="5" t="inlineStr">
-        <is>
-          <t>Precise quantum expectation values are crucial for quantum algorithm development, but noise in real-world systems can degrade these estimations. While quantum error correction is resource-intensive, error mitigation strategies offer a practical alternative. This paper presents a framework that combines Virtual Channel Purification (VCP) technique with Conditional Value-at-Risk (CVaR) optimization to improve expectation value estimations in noisy quantum circuits. Our contributions are twofold: first, we derive conditions to compare CVaR values from different probability distributions, offering insights into the reliability of quantum estimations under noise. Second, we apply this framework to VCP, providing analytical bounds that establish its effectiveness in improving expectation values, both when the overhead VCP circuit is ideal (error-free) and when it adds additional noise. By introducing CVaR into the analysis of VCP, we offer a general noise-characterization method that guarantees improved expectation values for any quantum observable. We demonstrate the practical utility of our approach with numerical examples, highlighting how our bounds guide VCP implementation in noisy quantum systems.</t>
-        </is>
-      </c>
+      <c r="F72" s="5" t="inlineStr">
+        <is>
+          <t>10.1007/s43937-025-00086-4</t>
+        </is>
+      </c>
+      <c r="G72" s="5" t="inlineStr"/>
       <c r="H72" s="5" t="inlineStr">
         <is>
-          <t>arxiv</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="I72" s="5" t="n"/>
@@ -3840,33 +3835,37 @@
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>6e39c2d1ab16</t>
+          <t>f191fdf66983</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>A user-centric quantum benchmarking test suite and evaluation framework</t>
+          <t>Next-Generation Digital Ecosystems: AI, Quantum Finance, and the Reinvention of Public Infrastructure</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>Liu W.B.</t>
+          <t>Murali Krishna Pasupuleti</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>10.1007/s11128-023-04154-3</t>
-        </is>
-      </c>
-      <c r="G73" s="5" t="inlineStr"/>
+          <t>10.62311/nesx/rp05331</t>
+        </is>
+      </c>
+      <c r="G73" s="5" t="inlineStr">
+        <is>
+          <t>Abstract: This research paper investigates the convergence of artificial intelligence (AI), quantum technologies, and digital infrastructure as the foundation of next-generation digital ecosystems. Focusing on their transformative roles in finance, governance, and public service delivery, the study leverages statistical modeling, entropy-centrality analysis, and predictive simulations to assess the impact of AI integration and quantum readiness on infrastructure performance. The findings reveal that both AI and quantum technologies significantly enhance operational efficiency, reduce systemic vulnerabilities, and enable adaptive, resilient ecosystems. By synthesizing insights from quantum finance, intelligent networks, and secure cloud architectures, the paper presents a unified framework for reimagining digital public infrastructure in the 21st century. This work contributes to the evolving discourse on digital sovereignty, infrastructure intelligence, and sustainable digital transformation. Keywords: digital ecosystems, artificial intelligence, quantum computing, quantum finance, public infrastructure, digital transformation, infrastructure resilience, e-governance, predictive analytics, entropy analysis, smart cities, digital sovereignty</t>
+        </is>
+      </c>
       <c r="H73" s="5" t="inlineStr">
         <is>
-          <t>scopus</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="I73" s="5" t="n"/>
@@ -3880,17 +3879,17 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>79728b194d1a</t>
+          <t>907a4842ec09</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>A state-of-the-art review on battery cell balancing strategies</t>
+          <t>Essays on Economics of Entrepreneurship</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>Ashkan Safari; Arman Oshnoei; Hoda Sorouri; Frede Blaabjerg</t>
+          <t>Mohaddeseh Heydari Nejad</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
@@ -3898,12 +3897,12 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="F74" s="5" t="inlineStr">
-        <is>
-          <t>10.1007/s43937-025-00086-4</t>
-        </is>
-      </c>
-      <c r="G74" s="5" t="inlineStr"/>
+      <c r="F74" s="5" t="inlineStr"/>
+      <c r="G74" s="5" t="inlineStr">
+        <is>
+          <t>This dissertation examines the economics of entrepreneurship through three studies on how entrepreneurs develop innovations under uncertainty. I investigate: (1) how mentorship in startup accelerators creates value through learning and guidance, (2) how institutional designs shape outcomes when entrepreneurs and mentors hold different beliefs, and (3) how entrepreneurs use crowdfunding to learn about market demand. Using structural modeling, Bayesian frameworks, and empirical analysis, I study mechanisms that improve entrepreneurial decision-making and the welfare implications of institutional arrangements. In the first chapter, “A Structural Model of Mentorship in Startup Accelerators,” I use data from the Creative Destruction Lab to estimate a dynamic structural model where mentors allocate mentorship over time and entrepreneurs decide whether to follow their advice. This model disentangles two key mentorship mechanisms: a direct effect improving startup quality, and a screening effect identifying high-potential ventures. I find that mentorship enhances outcomes through both channels and learning gains vary across sectors: traditional sectors show early learning, while emerging ones like quantum computing exhibit more gradual gains. Counterfactual analysis quantifies the value of mentors&amp;apos; strategic input and suggests sector-specific mentorship designs. The second chapter, “Persuading Mentors: Heterogeneous Priors and Innovation Outcomes,” explores how combining advisory and funding roles affects innovation when mentors and entrepreneurs have divergent beliefs. I develop a Bayesian model where entrepreneurs may adopt mentors’ plans to enhance credibility, even if they believe their own plans would yield better outcomes. This dynamic can create inefficiencies and welfare loss, especially when belief divergence is large. I show that separating advisory and funding roles, as in some accelerator or VC models, can mitigate these tensions and improve outcomes in deep tech and other novel sectors. In the third chapter, &amp;quot;Learning about Product Demand through Crowdfunding,&amp;quot; I investigate how entrepreneurs strategically use crowdfunding platforms to learn about market demand while financing their projects. I develop a Bayesian learning model where entrepreneurs make pricing decisions that trade-off immediate profits against the informational value. Using data from Kickstarter&amp;apos;s digital games category, I shows that entrepreneurs&amp;apos; pricing decisions are consistent with incentives for learning.</t>
+        </is>
+      </c>
       <c r="H74" s="5" t="inlineStr">
         <is>
           <t>openalex</t>
@@ -3920,17 +3919,17 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>f191fdf66983</t>
+          <t>50965b8f7d9f</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>Next-Generation Digital Ecosystems: AI, Quantum Finance, and the Reinvention of Public Infrastructure</t>
+          <t>Post-Quantum AI: Building Secure Machine Learning Systems in the Quantum Era</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>Murali Krishna Pasupuleti</t>
+          <t>Amit Taneja</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
@@ -3940,12 +3939,12 @@
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>10.62311/nesx/rp05331</t>
+          <t>10.9734/bpi/mono/978-93-88417-99-0</t>
         </is>
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>Abstract: This research paper investigates the convergence of artificial intelligence (AI), quantum technologies, and digital infrastructure as the foundation of next-generation digital ecosystems. Focusing on their transformative roles in finance, governance, and public service delivery, the study leverages statistical modeling, entropy-centrality analysis, and predictive simulations to assess the impact of AI integration and quantum readiness on infrastructure performance. The findings reveal that both AI and quantum technologies significantly enhance operational efficiency, reduce systemic vulnerabilities, and enable adaptive, resilient ecosystems. By synthesizing insights from quantum finance, intelligent networks, and secure cloud architectures, the paper presents a unified framework for reimagining digital public infrastructure in the 21st century. This work contributes to the evolving discourse on digital sovereignty, infrastructure intelligence, and sustainable digital transformation. Keywords: digital ecosystems, artificial intelligence, quantum computing, quantum finance, public infrastructure, digital transformation, infrastructure resilience, e-governance, predictive analytics, entropy analysis, smart cities, digital sovereignty</t>
+          <t>This book explores the intersection of artificial intelligence (AI) and quantum computing, focusing on the urgent need to secure machine learning systems in the face of emerging quantum threats. As quantum computers advance, they expose vulnerabilities in classical cryptographic methods, potentially undermining data integrity, privacy, and trust in AI-driven applications. To address these challenges, this study introduces the concept of post-quantum AI—a framework for integrating quantum-resistant cryptographic algorithms, Anomaly detection mechanisms, and Resilient machine learning architectures. This book makes three core contributions: it motivates a quantum-era threat model for machine learning (ii) it maps a migration path to standardised post-quantum cryptography Crypto-agile architectures (iii) it presents a defence-in-depth blueprint across the data → training → inference lifecycle that integrates privacy-preserving learning Governance. This work explicitly highlights key contributions, including proposed frameworks, algorithms, and case studies. Future research directions are also outlined to guide continued exploration in this emergent field. The final candidate algorithms from the NIST PQC standardisation process (NIST, 2022–2023) further strengthen this discussion. Key themes include the foundations of quantum mechanics relevant to computation, the fundamental differences between classical and quantum computing, and the transformative potential of quantum algorithms for optimisation, pattern recognition, and predictive analytics. The book highlights case studies spanning drug discovery, finance, mobile networks, and supply chain optimisation, illustrating how quantum-enhanced AI can revolutionise industry while simultaneously raising complex security and ethical concerns. A central focus is the development and deployment of post-quantum cryptography (PQC)), such as lattice-based and hash-based algorithms, to safeguard AI models against adversarial and quantum-accelerated attacks. The discussion extends to adversarial machine learning, explainable AI (XAI), and hybrid classical–quantum systems as strategies for strengthening resilience. The ethical, legal, and regulatory dimensions of post-quantum AI are also examined, emphasising fairness, transparency, accountability, and international cooperation. By combining technical innovations with responsible governance, the book advocates for building trustworthy AI systems that remain robust in the quantum era. Future work includes post-quantum cryptography (PQC) performance benchmarking in ML pipelines Patterns for crypto-agile key management, Assurance methods for privacy-preserving Federated learning as standards, and Implementations that are mature.</t>
         </is>
       </c>
       <c r="H75" s="5" t="inlineStr">
@@ -3964,33 +3963,33 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>907a4842ec09</t>
+          <t>e6656ef470fb</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>Essays on Economics of Entrepreneurship</t>
+          <t>Adiabatic Quantum Optimization Fails to Solve the Knapsack Problem</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>Mohaddeseh Heydari Nejad</t>
+          <t>Lauren Pusey-Nazzaro; Prasanna Date</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="F76" s="5" t="inlineStr"/>
       <c r="G76" s="5" t="inlineStr">
         <is>
-          <t>This dissertation examines the economics of entrepreneurship through three studies on how entrepreneurs develop innovations under uncertainty. I investigate: (1) how mentorship in startup accelerators creates value through learning and guidance, (2) how institutional designs shape outcomes when entrepreneurs and mentors hold different beliefs, and (3) how entrepreneurs use crowdfunding to learn about market demand. Using structural modeling, Bayesian frameworks, and empirical analysis, I study mechanisms that improve entrepreneurial decision-making and the welfare implications of institutional arrangements. In the first chapter, “A Structural Model of Mentorship in Startup Accelerators,” I use data from the Creative Destruction Lab to estimate a dynamic structural model where mentors allocate mentorship over time and entrepreneurs decide whether to follow their advice. This model disentangles two key mentorship mechanisms: a direct effect improving startup quality, and a screening effect identifying high-potential ventures. I find that mentorship enhances outcomes through both channels and learning gains vary across sectors: traditional sectors show early learning, while emerging ones like quantum computing exhibit more gradual gains. Counterfactual analysis quantifies the value of mentors&amp;apos; strategic input and suggests sector-specific mentorship designs. The second chapter, “Persuading Mentors: Heterogeneous Priors and Innovation Outcomes,” explores how combining advisory and funding roles affects innovation when mentors and entrepreneurs have divergent beliefs. I develop a Bayesian model where entrepreneurs may adopt mentors’ plans to enhance credibility, even if they believe their own plans would yield better outcomes. This dynamic can create inefficiencies and welfare loss, especially when belief divergence is large. I show that separating advisory and funding roles, as in some accelerator or VC models, can mitigate these tensions and improve outcomes in deep tech and other novel sectors. In the third chapter, &amp;quot;Learning about Product Demand through Crowdfunding,&amp;quot; I investigate how entrepreneurs strategically use crowdfunding platforms to learn about market demand while financing their projects. I develop a Bayesian learning model where entrepreneurs make pricing decisions that trade-off immediate profits against the informational value. Using data from Kickstarter&amp;apos;s digital games category, I shows that entrepreneurs&amp;apos; pricing decisions are consistent with incentives for learning.</t>
+          <t>In this work, we attempt to solve the integer-weight knapsack problem using the D-Wave 2000Q adiabatic quantum computer. The knapsack problem is a well-known NP-complete problem in computer science, with applications in economics, business, finance, etc. We attempt to solve a number of small knapsack problems whose optimal solutions are known; we find that adiabatic quantum optimization fails to produce solutions corresponding to optimal filling of the knapsack in all problem instances. We compare results obtained on the quantum hardware to the classical simulated annealing algorithm and two solvers employing a hybrid branch-and-bound algorithm. The simulated annealing algorithm also fails to produce the optimal filling of the knapsack, though solutions obtained by simulated and quantum annealing are no more similar to each other than to the correct solution. We discuss potential causes for this observed failure of adiabatic quantum optimization.</t>
         </is>
       </c>
       <c r="H76" s="5" t="inlineStr">
         <is>
-          <t>openalex</t>
+          <t>semantic_scholar</t>
         </is>
       </c>
       <c r="I76" s="5" t="n"/>
@@ -4004,32 +4003,32 @@
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>50965b8f7d9f</t>
+          <t>2b217f56fa88</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>Post-Quantum AI: Building Secure Machine Learning Systems in the Quantum Era</t>
+          <t>Genealogía a la epistemología poscapitalista</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>Amit Taneja</t>
+          <t>Moisés Ezequiel Zepeda Moreno</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
-          <t>10.9734/bpi/mono/978-93-88417-99-0</t>
+          <t>10.22402/ed.leed.978.607.26779-4-4</t>
         </is>
       </c>
       <c r="G77" s="5" t="inlineStr">
         <is>
-          <t>This book explores the intersection of artificial intelligence (AI) and quantum computing, focusing on the urgent need to secure machine learning systems in the face of emerging quantum threats. As quantum computers advance, they expose vulnerabilities in classical cryptographic methods, potentially undermining data integrity, privacy, and trust in AI-driven applications. To address these challenges, this study introduces the concept of post-quantum AI—a framework for integrating quantum-resistant cryptographic algorithms, Anomaly detection mechanisms, and Resilient machine learning architectures. This book makes three core contributions: it motivates a quantum-era threat model for machine learning (ii) it maps a migration path to standardised post-quantum cryptography Crypto-agile architectures (iii) it presents a defence-in-depth blueprint across the data → training → inference lifecycle that integrates privacy-preserving learning Governance. This work explicitly highlights key contributions, including proposed frameworks, algorithms, and case studies. Future research directions are also outlined to guide continued exploration in this emergent field. The final candidate algorithms from the NIST PQC standardisation process (NIST, 2022–2023) further strengthen this discussion. Key themes include the foundations of quantum mechanics relevant to computation, the fundamental differences between classical and quantum computing, and the transformative potential of quantum algorithms for optimisation, pattern recognition, and predictive analytics. The book highlights case studies spanning drug discovery, finance, mobile networks, and supply chain optimisation, illustrating how quantum-enhanced AI can revolutionise industry while simultaneously raising complex security and ethical concerns. A central focus is the development and deployment of post-quantum cryptography (PQC)), such as lattice-based and hash-based algorithms, to safeguard AI models against adversarial and quantum-accelerated attacks. The discussion extends to adversarial machine learning, explainable AI (XAI), and hybrid classical–quantum systems as strategies for strengthening resilience. The ethical, legal, and regulatory dimensions of post-quantum AI are also examined, emphasising fairness, transparency, accountability, and international cooperation. By combining technical innovations with responsible governance, the book advocates for building trustworthy AI systems that remain robust in the quantum era. Future work includes post-quantum cryptography (PQC) performance benchmarking in ML pipelines Patterns for crypto-agile key management, Assurance methods for privacy-preserving Federated learning as standards, and Implementations that are mature.</t>
+          <t>This text argues that the technoscientific revolution—big data, AI, and the imminent quantum horizon—reconfigures who produces and controls knowledge. The global network erodes the university's monopoly and pushes education toward algorithmic platforms, with the risk of a "technified deschooling," corporate concentration, and the fetishization of life. In response, it proposes thinking through a post-capitalist epistemology and new ecologies of knowledge that democratize the production of knowledge. In Chapter 1, it analyzes the genealogy of the university: from Muslim madrasas and their plural forms of knowledge to the medieval European university (Bologna/Salamanca) as a technology of control (chair, cloister, writing). The Renaissance and the colonial era consolidate grammar, the printing press, and the "lettered cities" as mechanisms of domination. Modernity (Descartes, Kant, Humboldt) specializes and hierarchizes the university; the twentieth century incorporates systems theory, cybernetics, and autopoiesis, preparing the informational paradigm that culminates in the quantum threshold. Chapter 2 defines a regime that exploits networked cooperation and turns knowledge, data, and pedagogies into financeable assets. It situates its origin in informatization, the financialization of EdTech, and the "market of theories," describes the qualitative leap produced by standardizing knowledge through AI/Big Data, and explains the global division of cognitive labor. It anticipates the transition toward the quantum era (6G, quantum computing), in which value production pivots on information infrastructures. Finally, Chapter 3 examines the impact of the network and the anthropological and geological mutations of the quantum era; it addresses "computer pedagogy," "quantum epistemology," and "semiotic change." It discusses cyborg pedagogy and transhumanism, warning about the subordination of human formation to epistemological machines. It proposes shifting education away from banking/algorithmic models toward communal, deschooled, and systemic practices that prioritize the common good and cognitive justice.</t>
         </is>
       </c>
       <c r="H77" s="5" t="inlineStr">
@@ -4048,33 +4047,37 @@
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>e6656ef470fb</t>
+          <t>c065a97bd065</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>Adiabatic Quantum Optimization Fails to Solve the Knapsack Problem</t>
+          <t>Quantum Variational Solving of Nonlinear and Multi-Dimensional Partial Differential Equations</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>Lauren Pusey-Nazzaro; Prasanna Date</t>
+          <t>Abhijat Sarma; Thomas W. Watts; Mudassir Moosa; Yilian Liu; Peter L. McMahon</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
         <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="F78" s="5" t="inlineStr"/>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F78" s="5" t="inlineStr">
+        <is>
+          <t>10.48550/arxiv.2311.01531</t>
+        </is>
+      </c>
       <c r="G78" s="5" t="inlineStr">
         <is>
-          <t>In this work, we attempt to solve the integer-weight knapsack problem using the D-Wave 2000Q adiabatic quantum computer. The knapsack problem is a well-known NP-complete problem in computer science, with applications in economics, business, finance, etc. We attempt to solve a number of small knapsack problems whose optimal solutions are known; we find that adiabatic quantum optimization fails to produce solutions corresponding to optimal filling of the knapsack in all problem instances. We compare results obtained on the quantum hardware to the classical simulated annealing algorithm and two solvers employing a hybrid branch-and-bound algorithm. The simulated annealing algorithm also fails to produce the optimal filling of the knapsack, though solutions obtained by simulated and quantum annealing are no more similar to each other than to the correct solution. We discuss potential causes for this observed failure of adiabatic quantum optimization.</t>
+          <t>A variational quantum algorithm for numerically solving partial differential equations (PDEs) on a quantum computer was proposed by Lubasch et al. In this paper, we generalize the method introduced by Lubasch et al. to cover a broader class of nonlinear PDEs as well as multidimensional PDEs, and study the performance of the variational quantum algorithm on several example equations. Specifically, we show via numerical simulations that the algorithm can solve instances of the Single-Asset Black-Scholes equation with a nontrivial nonlinear volatility model, the Double-Asset Black-Scholes equation, the Buckmaster equation, and the deterministic Kardar-Parisi-Zhang equation. Our simulations used up to $n=12$ ansatz qubits, computing PDE solutions with $2^n$ grid points. We also performed proof-of-concept experiments with a trapped-ion quantum processor from IonQ, showing accurate computation of two representative expectation values needed for the calculation of a single timestep of the nonlinear Black--Scholes equation. Through our classical simulations and experiments on quantum hardware, we have identified -- and we discuss -- several open challenges for using quantum variational methods to solve PDEs in a regime with a large number ($\gg 2^{20}$) of grid points, but also a practical number of gates per circuit and circuit shots.</t>
         </is>
       </c>
       <c r="H78" s="5" t="inlineStr">
         <is>
-          <t>semantic_scholar</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="I78" s="5" t="n"/>
@@ -4088,32 +4091,32 @@
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>2b217f56fa88</t>
+          <t>5b5fd3a147af</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>Genealogía a la epistemología poscapitalista</t>
+          <t>Wasserstein Solution Quality and the Quantum Approximate Optimization Algorithm: A Portfolio Optimization Case Study</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>Moisés Ezequiel Zepeda Moreno</t>
+          <t>Jack S. Baker; Santosh Kumar Radha</t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F79" s="5" t="inlineStr">
         <is>
-          <t>10.22402/ed.leed.978.607.26779-4-4</t>
+          <t>10.48550/arxiv.2202.06782</t>
         </is>
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>This text argues that the technoscientific revolution—big data, AI, and the imminent quantum horizon—reconfigures who produces and controls knowledge. The global network erodes the university's monopoly and pushes education toward algorithmic platforms, with the risk of a "technified deschooling," corporate concentration, and the fetishization of life. In response, it proposes thinking through a post-capitalist epistemology and new ecologies of knowledge that democratize the production of knowledge. In Chapter 1, it analyzes the genealogy of the university: from Muslim madrasas and their plural forms of knowledge to the medieval European university (Bologna/Salamanca) as a technology of control (chair, cloister, writing). The Renaissance and the colonial era consolidate grammar, the printing press, and the "lettered cities" as mechanisms of domination. Modernity (Descartes, Kant, Humboldt) specializes and hierarchizes the university; the twentieth century incorporates systems theory, cybernetics, and autopoiesis, preparing the informational paradigm that culminates in the quantum threshold. Chapter 2 defines a regime that exploits networked cooperation and turns knowledge, data, and pedagogies into financeable assets. It situates its origin in informatization, the financialization of EdTech, and the "market of theories," describes the qualitative leap produced by standardizing knowledge through AI/Big Data, and explains the global division of cognitive labor. It anticipates the transition toward the quantum era (6G, quantum computing), in which value production pivots on information infrastructures. Finally, Chapter 3 examines the impact of the network and the anthropological and geological mutations of the quantum era; it addresses "computer pedagogy," "quantum epistemology," and "semiotic change." It discusses cyborg pedagogy and transhumanism, warning about the subordination of human formation to epistemological machines. It proposes shifting education away from banking/algorithmic models toward communal, deschooled, and systemic practices that prioritize the common good and cognitive justice.</t>
+          <t>Optimizing of a portfolio of financial assets is a critical industrial problem which can be approximately solved using algorithms suitable for quantum processing units (QPUs). We benchmark the success of this approach using the Quantum Approximate Optimization Algorithm (QAOA); an algorithm targeting gate-model QPUs. Our focus is on the quality of solutions achieved as determined by the Normalized and Complementary Wasserstein Distance, $η$, which we present in a manner to expose the QAOA as a transporter of probability. Using $η$ as an application specific benchmark of performance, we measure it on selection of QPUs as a function of QAOA circuit depth $p$. At $n = 2$ (2 qubits) we find peak solution quality at $p=5$ for most systems and for $n = 3$ this peak is at $p=4$ on a trapped ion QPU. Increasing solution quality with $p$ is also observed using variants of the more general Quantum Alternating Operator Ansätz at $p=2$ for $n = 2$ and $3$ which has not been previously reported. In identical measurements, $η$ is observed to be variable at a level exceeding the noise produced from the finite number of shots. This suggests that variability itself should be regarded as a QPU performance benchmark for given applications. While studying the ideal execution of QAOA, we find that $p=1$ solution quality degrades when the portfolio budget $B$ approaches $n/2$ and increases when $B \approx 1$ or $n-1$. This trend directly corresponds to the binomial coefficient $nCB$ and is connected with the recently reported phenomenon of reachability deficits. Derivative-requiring and derivative-free classical optimizers are benchmarked on the basis of the achieved $η$ beyond $p=1$ to find that derivative-free optimizers are generally more effective for the given computational resources, problem sizes and circuit depths.</t>
         </is>
       </c>
       <c r="H79" s="5" t="inlineStr">
@@ -4132,32 +4135,32 @@
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>c065a97bd065</t>
+          <t>a254f338377d</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>Quantum Variational Solving of Nonlinear and Multi-Dimensional Partial Differential Equations</t>
+          <t>Quantum Advantage in Trading: A Game-Theoretic Approach</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>Abhijat Sarma; Thomas W. Watts; Mudassir Moosa; Yilian Liu; Peter L. McMahon</t>
+          <t>Faisal Shah Khan; Norbert M. Linke; Anton T. Than; Dror Baron</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
-          <t>10.48550/arxiv.2311.01531</t>
+          <t>10.17615/af1s-7c34</t>
         </is>
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>A variational quantum algorithm for numerically solving partial differential equations (PDEs) on a quantum computer was proposed by Lubasch et al. In this paper, we generalize the method introduced by Lubasch et al. to cover a broader class of nonlinear PDEs as well as multidimensional PDEs, and study the performance of the variational quantum algorithm on several example equations. Specifically, we show via numerical simulations that the algorithm can solve instances of the Single-Asset Black-Scholes equation with a nontrivial nonlinear volatility model, the Double-Asset Black-Scholes equation, the Buckmaster equation, and the deterministic Kardar-Parisi-Zhang equation. Our simulations used up to $n=12$ ansatz qubits, computing PDE solutions with $2^n$ grid points. We also performed proof-of-concept experiments with a trapped-ion quantum processor from IonQ, showing accurate computation of two representative expectation values needed for the calculation of a single timestep of the nonlinear Black--Scholes equation. Through our classical simulations and experiments on quantum hardware, we have identified -- and we discuss -- several open challenges for using quantum variational methods to solve PDEs in a regime with a large number ($\gg 2^{20}$) of grid points, but also a practical number of gates per circuit and circuit shots.</t>
+          <t>Quantum games, like quantum algorithms, exploit quantum entanglement to establish strong correlations between strategic player actions. This paper introduces quantum game-theoretic models applied to trading and demonstrates their implementation on an ion-trap quantum computer. The results showcase a quantum advantage, previously known only theoretically, realized as higher-paying market Nash equilibria. This advantage could help uncover alpha in trading strategies, defined as excess returns compared to established benchmarks. These findings suggest that quantum computing could significantly influence the development of financial strategies.</t>
         </is>
       </c>
       <c r="H80" s="5" t="inlineStr">
@@ -4176,32 +4179,32 @@
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>5b5fd3a147af</t>
+          <t>7f09d7df1f04</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>Wasserstein Solution Quality and the Quantum Approximate Optimization Algorithm: A Portfolio Optimization Case Study</t>
+          <t>Quantum Classical Ridgelet Neural Network For Time Series Model</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>Jack S. Baker; Santosh Kumar Radha</t>
+          <t>Bahadur Yadav; Sanjay Kumar Mohanty</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t>10.48550/arxiv.2202.06782</t>
+          <t>10.48550/arxiv.2601.03654</t>
         </is>
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>Optimizing of a portfolio of financial assets is a critical industrial problem which can be approximately solved using algorithms suitable for quantum processing units (QPUs). We benchmark the success of this approach using the Quantum Approximate Optimization Algorithm (QAOA); an algorithm targeting gate-model QPUs. Our focus is on the quality of solutions achieved as determined by the Normalized and Complementary Wasserstein Distance, $η$, which we present in a manner to expose the QAOA as a transporter of probability. Using $η$ as an application specific benchmark of performance, we measure it on selection of QPUs as a function of QAOA circuit depth $p$. At $n = 2$ (2 qubits) we find peak solution quality at $p=5$ for most systems and for $n = 3$ this peak is at $p=4$ on a trapped ion QPU. Increasing solution quality with $p$ is also observed using variants of the more general Quantum Alternating Operator Ansätz at $p=2$ for $n = 2$ and $3$ which has not been previously reported. In identical measurements, $η$ is observed to be variable at a level exceeding the noise produced from the finite number of shots. This suggests that variability itself should be regarded as a QPU performance benchmark for given applications. While studying the ideal execution of QAOA, we find that $p=1$ solution quality degrades when the portfolio budget $B$ approaches $n/2$ and increases when $B \approx 1$ or $n-1$. This trend directly corresponds to the binomial coefficient $nCB$ and is connected with the recently reported phenomenon of reachability deficits. Derivative-requiring and derivative-free classical optimizers are benchmarked on the basis of the achieved $η$ beyond $p=1$ to find that derivative-free optimizers are generally more effective for the given computational resources, problem sizes and circuit depths.</t>
+          <t>In this study, we present a quantum computing method that incorporates ridglet transforms into the quantum processing pipelines for time series data. Here, the Ridgelet neural network is integrated with a single-qubit quantum computing method, which improves feature extraction and forecasting capabilities. Furthermore, experimental results using financial time series data demonstrate the superior performance of our model compared to existing models.</t>
         </is>
       </c>
       <c r="H81" s="5" t="inlineStr">
@@ -4220,32 +4223,32 @@
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>a254f338377d</t>
+          <t>1ac1b7a5c545</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>Quantum Advantage in Trading: A Game-Theoretic Approach</t>
+          <t>Implementing Quantum Resistant Algorithm in Blockchain-Based Applications</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>Faisal Shah Khan; Norbert M. Linke; Anton T. Than; Dror Baron</t>
+          <t>Sonali Ridhorkar; Mr. Setu Sagar Mishra</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t>10.17615/af1s-7c34</t>
+          <t>10.48175/ijarsct-17899</t>
         </is>
       </c>
       <c r="G82" s="5" t="inlineStr">
         <is>
-          <t>Quantum games, like quantum algorithms, exploit quantum entanglement to establish strong correlations between strategic player actions. This paper introduces quantum game-theoretic models applied to trading and demonstrates their implementation on an ion-trap quantum computer. The results showcase a quantum advantage, previously known only theoretically, realized as higher-paying market Nash equilibria. This advantage could help uncover alpha in trading strategies, defined as excess returns compared to established benchmarks. These findings suggest that quantum computing could significantly influence the development of financial strategies.</t>
+          <t>With quantum computing evolving very fast as we speak, the security and integrity of blockchain-based applications will become the most crucial aspect. A proposal is raised to use blockchain technology as a platform for writing and probating ‘wills’. Blockchain technology in drafting and probating wills makes them safe from manipulations, highly secure, and transparent. It also dramatically decreases the time required without catering for the challenges created by the current system. [9] This paper presents a new method for will transfer and inheritance management by implementing quantum-resistant algorithms in the security architecture of a blockchain decentralized application (DApp). The system uses IPFS Network for data storage and quantum-safe algorithms as retrieval and sending algorithms. The system includes Quantum-Resistant Dilithium Signatures and Merkle trees as the fundamental components for safeguarding the transfers of assets and claims for inheritance. Quantum-Resistant Dilithium Signatures offer an unbreakable shield against quantum attacks that are expected to happen, which in turn safeguards the privacy and authenticity of transactions. While Merkle trees are responsible for the organization of inheritance claims in an effective and tamper-proof manner, the introduced system incorporates smart contracts to address the execution of an inheritance case, adding more security and automation to the asset distribution process. The system ensures a robust security framework by integrating quantum-resistant algorithms at the very core of the blockchain DApp for instance, retrieval and sending. This research is of great significance to blockchain technology which is the emerging technology of the future because it addresses the existing threat of quantum computing by showing the feasibility of using quantum-resistant algorithms in practical applications. As established by the findings, besides Quantum-Resistant Dilithium Signatures and Merkle trees, the systems of asset transfers and inheritance management within blockchain networks are enhanced in terms of safety and reliability. Hence, paving the road to the creation of more secure and trustworthy digital asset management systems.</t>
         </is>
       </c>
       <c r="H82" s="5" t="inlineStr">
@@ -4264,32 +4267,32 @@
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>7f09d7df1f04</t>
+          <t>4f4a7745d6fe</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>Quantum Classical Ridgelet Neural Network For Time Series Model</t>
+          <t>Quantum-Enhanced Multi-Factor Authentication Framework for Digital Banking Systems: A Post-Quantum Cryptographic Approach</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>Bahadur Yadav; Sanjay Kumar Mohanty</t>
+          <t>Praveen Kumar Reddy Gujjala</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
-          <t>10.48550/arxiv.2601.03654</t>
+          <t>10.36948/ijfmr.2023.v05i06.55443</t>
         </is>
       </c>
       <c r="G83" s="5" t="inlineStr">
         <is>
-          <t>In this study, we present a quantum computing method that incorporates ridglet transforms into the quantum processing pipelines for time series data. Here, the Ridgelet neural network is integrated with a single-qubit quantum computing method, which improves feature extraction and forecasting capabilities. Furthermore, experimental results using financial time series data demonstrate the superior performance of our model compared to existing models.</t>
+          <t>The digital banking ecosystem faces unprecedented security challenges with the imminent advent of quantum computing, which threatens to compromise existing cryptographic infrastructures. Traditional multi-factor authentication (MFA) systems in banking rely on classical cryptographic primitives vulnerable to quantum attacks, creating critical security gaps in financial transactions and customer data protection. This paper introduces a novel Quantum-Enhanced Multi-Factor Authentication Framework (QE-MFAF) specifically designed for digital banking systems, integrating lattice-based post-quantum cryptography with biometric fuzzy commitment schemes and behavioral analytics. The proposed framework incorporates a hybrid authentication mechanism combining quantum-resistant cryptographic protocols, continuous behavioral pattern recognition using deep learning models, and secure multi-party computation for transaction verification. Experimental validation on a synthetic banking dataset demonstrates superior performance with 99.7% authentication accuracy, 0.02% false positive rate, and 15ms average authentication latency while maintaining quantum resistance. The framework successfully mitigates advanced persistent threats, insider attacks, and quantum-based cryptographic vulnerabilities while ensuring seamless user experience in high-transaction banking environments. Performance comparisons with existing banking authentication systems show 34% improvement in security metrics and 28% reduction in computational overhead.</t>
         </is>
       </c>
       <c r="H83" s="5" t="inlineStr">
@@ -4308,37 +4311,33 @@
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>1ac1b7a5c545</t>
+          <t>6a9413f38468</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>Implementing Quantum Resistant Algorithm in Blockchain-Based Applications</t>
+          <t>LiteQSign: Lightweight and Quantum-Safe Signatures for Heterogeneous IoT Applications</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>Sonali Ridhorkar; Mr. Setu Sagar Mishra</t>
+          <t>Attila A. Yavuz; Saleh Darzi; Saif E. Nouma</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
         <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="F84" s="5" t="inlineStr">
-        <is>
-          <t>10.48175/ijarsct-17899</t>
-        </is>
-      </c>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F84" s="5" t="inlineStr"/>
       <c r="G84" s="5" t="inlineStr">
         <is>
-          <t>With quantum computing evolving very fast as we speak, the security and integrity of blockchain-based applications will become the most crucial aspect. A proposal is raised to use blockchain technology as a platform for writing and probating ‘wills’. Blockchain technology in drafting and probating wills makes them safe from manipulations, highly secure, and transparent. It also dramatically decreases the time required without catering for the challenges created by the current system. [9] This paper presents a new method for will transfer and inheritance management by implementing quantum-resistant algorithms in the security architecture of a blockchain decentralized application (DApp). The system uses IPFS Network for data storage and quantum-safe algorithms as retrieval and sending algorithms. The system includes Quantum-Resistant Dilithium Signatures and Merkle trees as the fundamental components for safeguarding the transfers of assets and claims for inheritance. Quantum-Resistant Dilithium Signatures offer an unbreakable shield against quantum attacks that are expected to happen, which in turn safeguards the privacy and authenticity of transactions. While Merkle trees are responsible for the organization of inheritance claims in an effective and tamper-proof manner, the introduced system incorporates smart contracts to address the execution of an inheritance case, adding more security and automation to the asset distribution process. The system ensures a robust security framework by integrating quantum-resistant algorithms at the very core of the blockchain DApp for instance, retrieval and sending. This research is of great significance to blockchain technology which is the emerging technology of the future because it addresses the existing threat of quantum computing by showing the feasibility of using quantum-resistant algorithms in practical applications. As established by the findings, besides Quantum-Resistant Dilithium Signatures and Merkle trees, the systems of asset transfers and inheritance management within blockchain networks are enhanced in terms of safety and reliability. Hence, paving the road to the creation of more secure and trustworthy digital asset management systems.</t>
+          <t>The rapid proliferation of resource-constrained IoT devices across sectors like healthcare, industrial automation, and finance introduces major security challenges. Traditional digital signatures, though foundational for authentication, are often infeasible for low-end devices with limited computational, memory, and energy resources. Also, the rise of quantum computing necessitates post-quantum (PQ) secure alternatives. However, NIST-standardized PQ signatures impose substantial overhead, limiting their practicality in energy-sensitive applications such as wearables, where signer-side efficiency is critical. To address these challenges, we present LightQSign (LightQS), a novel lightweight PQ signature that achieves near-optimal signature generation efficiency with only a small, constant number of hash operations per signing. Its core innovation enables verifiers to obtain one-time hash-based public keys without interacting with signers or third parties through secure computation. We formally prove the security of LightQSign in the random oracle model and evaluate its performance on commodity hardware and a resource-constrained 8-bit AtMega128A1 microcontroller. Experimental results show that LightQSign outperforms NIST PQC standards with lower computational overhead, minimal memory usage, and compact signatures. On an 8-bit microcontroller, it achieves up to 1.5-24x higher energy efficiency and 1.7-22x shorter signatures than PQ counterparts, and 56-76x better energy efficiency than conventional standards-enabling longer device lifespans and scalable, quantum-resilient authentication.</t>
         </is>
       </c>
       <c r="H84" s="5" t="inlineStr">
         <is>
-          <t>openalex</t>
+          <t>arxiv</t>
         </is>
       </c>
       <c r="I84" s="5" t="n"/>
@@ -4352,37 +4351,37 @@
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>4f4a7745d6fe</t>
+          <t>5ab77e03ac9c</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>Quantum-Enhanced Multi-Factor Authentication Framework for Digital Banking Systems: A Post-Quantum Cryptographic Approach</t>
+          <t>Scalable Emulation of Sign-Problem$-$Free Hamiltonians with Room Temperature p-bits</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>Praveen Kumar Reddy Gujjala</t>
+          <t>Kerem Y. Camsari; Shuvro Chowdhury; Supriyo Datta</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="F85" s="5" t="inlineStr">
         <is>
-          <t>10.36948/ijfmr.2023.v05i06.55443</t>
+          <t>10.1103/PhysRevApplied.12.034061</t>
         </is>
       </c>
       <c r="G85" s="5" t="inlineStr">
         <is>
-          <t>The digital banking ecosystem faces unprecedented security challenges with the imminent advent of quantum computing, which threatens to compromise existing cryptographic infrastructures. Traditional multi-factor authentication (MFA) systems in banking rely on classical cryptographic primitives vulnerable to quantum attacks, creating critical security gaps in financial transactions and customer data protection. This paper introduces a novel Quantum-Enhanced Multi-Factor Authentication Framework (QE-MFAF) specifically designed for digital banking systems, integrating lattice-based post-quantum cryptography with biometric fuzzy commitment schemes and behavioral analytics. The proposed framework incorporates a hybrid authentication mechanism combining quantum-resistant cryptographic protocols, continuous behavioral pattern recognition using deep learning models, and secure multi-party computation for transaction verification. Experimental validation on a synthetic banking dataset demonstrates superior performance with 99.7% authentication accuracy, 0.02% false positive rate, and 15ms average authentication latency while maintaining quantum resistance. The framework successfully mitigates advanced persistent threats, insider attacks, and quantum-based cryptographic vulnerabilities while ensuring seamless user experience in high-transaction banking environments. Performance comparisons with existing banking authentication systems show 34% improvement in security metrics and 28% reduction in computational overhead.</t>
+          <t>The growing field of quantum computing is based on the concept of a q-bit which is a delicate superposition of 0 and 1, requiring cryogenic temperatures for its physical realization along with challenging coherent coupling techniques for entangling them. By contrast, a probabilistic bit or a p-bit is a robust classical entity that fluctuates between 0 and 1, and can be implemented at room temperature using present-day technology. Here, we show that a probabilistic coprocessor built out of room temperature p-bits can be used to accelerate simulations of a special class of quantum many-body systems that are sign-problem$-$free or stoquastic, leveraging the well-known Suzuki-Trotter decomposition that maps a $d$-dimensional quantum many body Hamiltonian to a $d$+1-dimensional classical Hamiltonian. This mapping allows an efficient emulation of a quantum system by classical computers and is commonly used in software to perform Quantum Monte Carlo (QMC) algorithms. By contrast, we show that a compact, embedded MTJ-based coprocessor can serve as a highly efficient hardware-accelerator for such QMC algorithms providing several orders of magnitude improvement in speed compared to optimized CPU implementations. Using realistic device-level SPICE simulations we demonstrate that the correct quantum correlations can be obtained using a classical p-circuit built with existing technology and operating at room temperature. The proposed coprocessor can serve as a tool to study stoquastic quantum many-body systems, overcoming challenges associated with physical quantum annealers.</t>
         </is>
       </c>
       <c r="H85" s="5" t="inlineStr">
         <is>
-          <t>openalex</t>
+          <t>arxiv</t>
         </is>
       </c>
       <c r="I85" s="5" t="n"/>
@@ -4396,17 +4395,17 @@
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>6a9413f38468</t>
+          <t>3cc013044f30</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>LiteQSign: Lightweight and Quantum-Safe Signatures for Heterogeneous IoT Applications</t>
+          <t>Showcasing sentiment classification and word prediction in the quantum natural processing area</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>Attila A. Yavuz; Saleh Darzi; Saif E. Nouma</t>
+          <t>Peral-García D.</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
@@ -4415,14 +4414,10 @@
         </is>
       </c>
       <c r="F86" s="5" t="inlineStr"/>
-      <c r="G86" s="5" t="inlineStr">
-        <is>
-          <t>The rapid proliferation of resource-constrained IoT devices across sectors like healthcare, industrial automation, and finance introduces major security challenges. Traditional digital signatures, though foundational for authentication, are often infeasible for low-end devices with limited computational, memory, and energy resources. Also, the rise of quantum computing necessitates post-quantum (PQ) secure alternatives. However, NIST-standardized PQ signatures impose substantial overhead, limiting their practicality in energy-sensitive applications such as wearables, where signer-side efficiency is critical. To address these challenges, we present LightQSign (LightQS), a novel lightweight PQ signature that achieves near-optimal signature generation efficiency with only a small, constant number of hash operations per signing. Its core innovation enables verifiers to obtain one-time hash-based public keys without interacting with signers or third parties through secure computation. We formally prove the security of LightQSign in the random oracle model and evaluate its performance on commodity hardware and a resource-constrained 8-bit AtMega128A1 microcontroller. Experimental results show that LightQSign outperforms NIST PQC standards with lower computational overhead, minimal memory usage, and compact signatures. On an 8-bit microcontroller, it achieves up to 1.5-24x higher energy efficiency and 1.7-22x shorter signatures than PQ counterparts, and 56-76x better energy efficiency than conventional standards-enabling longer device lifespans and scalable, quantum-resilient authentication.</t>
-        </is>
-      </c>
+      <c r="G86" s="5" t="inlineStr"/>
       <c r="H86" s="5" t="inlineStr">
         <is>
-          <t>arxiv</t>
+          <t>scopus</t>
         </is>
       </c>
       <c r="I86" s="5" t="n"/>
@@ -4436,17 +4431,17 @@
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>5ab77e03ac9c</t>
+          <t>6bb18cfb9e04</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>Scalable Emulation of Sign-Problem$-$Free Hamiltonians with Room Temperature p-bits</t>
+          <t>Quantum Risk Analysis</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>Kerem Y. Camsari; Shuvro Chowdhury; Supriyo Datta</t>
+          <t>Stefan Woerner; Daniel J. Egger</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
@@ -4456,12 +4451,12 @@
       </c>
       <c r="F87" s="5" t="inlineStr">
         <is>
-          <t>10.1103/PhysRevApplied.12.034061</t>
+          <t>10.1038/s41534-019-0130-6</t>
         </is>
       </c>
       <c r="G87" s="5" t="inlineStr">
         <is>
-          <t>The growing field of quantum computing is based on the concept of a q-bit which is a delicate superposition of 0 and 1, requiring cryogenic temperatures for its physical realization along with challenging coherent coupling techniques for entangling them. By contrast, a probabilistic bit or a p-bit is a robust classical entity that fluctuates between 0 and 1, and can be implemented at room temperature using present-day technology. Here, we show that a probabilistic coprocessor built out of room temperature p-bits can be used to accelerate simulations of a special class of quantum many-body systems that are sign-problem$-$free or stoquastic, leveraging the well-known Suzuki-Trotter decomposition that maps a $d$-dimensional quantum many body Hamiltonian to a $d$+1-dimensional classical Hamiltonian. This mapping allows an efficient emulation of a quantum system by classical computers and is commonly used in software to perform Quantum Monte Carlo (QMC) algorithms. By contrast, we show that a compact, embedded MTJ-based coprocessor can serve as a highly efficient hardware-accelerator for such QMC algorithms providing several orders of magnitude improvement in speed compared to optimized CPU implementations. Using realistic device-level SPICE simulations we demonstrate that the correct quantum correlations can be obtained using a classical p-circuit built with existing technology and operating at room temperature. The proposed coprocessor can serve as a tool to study stoquastic quantum many-body systems, overcoming challenges associated with physical quantum annealers.</t>
+          <t>We present a quantum algorithm that analyzes risk more efficiently than Monte Carlo simulations traditionally used on classical computers. We employ quantum amplitude estimation to evaluate risk measures such as Value at Risk and Conditional Value at Risk on a gate-based quantum computer. Additionally, we show how to implement this algorithm and how to trade off the convergence rate of the algorithm and the circuit depth. The shortest possible circuit depth - growing polynomially in the number of qubits representing the uncertainty - leads to a convergence rate of $O(M^{-2/3})$. This is already faster than classical Monte Carlo simulations which converge at a rate of $O(M^{-1/2})$. If we allow the circuit depth to grow faster, but still polynomially, the convergence rate quickly approaches the optimum of $O(M^{-1})$. Thus, for slowly increasing circuit depths our algorithm provides a near quadratic speed-up compared to Monte Carlo methods. We demonstrate our algorithm using two toy models. In the first model we use real hardware, such as the IBM Q Experience, to measure the financial risk in a Treasury-bill (T-bill) faced by a possible interest rate increase. In the second model, we simulate our algorithm to illustrate how a quantum computer can determine financial risk for a two-asset portfolio made up of Government debt with different maturity dates. Both models confirm the improved convergence rate over Monte Carlo methods. Using simulations, we also evaluate the impact of cross-talk and energy relaxation errors.</t>
         </is>
       </c>
       <c r="H87" s="5" t="inlineStr">
@@ -4480,29 +4475,37 @@
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>3cc013044f30</t>
+          <t>817a28486638</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>Showcasing sentiment classification and word prediction in the quantum natural processing area</t>
+          <t>The Evolution of China's Cyber-Espionage Tactics: From Traditional Espionage to AI-Driven Cyber Threats against Critical Infrastructure in the West</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>Peral-García D.</t>
+          <t>Christian C. Madubuko; Chamunorwa Chitsungo</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
         <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="F88" s="5" t="inlineStr"/>
-      <c r="G88" s="5" t="inlineStr"/>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F88" s="5" t="inlineStr">
+        <is>
+          <t>10.47672/ajir.2424</t>
+        </is>
+      </c>
+      <c r="G88" s="5" t="inlineStr">
+        <is>
+          <t>Purpose: This article critically investigates the evolution of China’s cyber-espionage strategies, specifically illustrating the shift from traditional espionage methodologies to the incorporation of advanced technologies, particularly artificial intelligence (AI). This transition profoundly reshapes global power dynamics, delineating nuanced threats to critical infrastructure in Western nations, including power grids, financial systems, and communication networks (Wang et al., 2019). Materials and Methods: Utilizing a theoretical framework grounded in Joseph Nye's concept of soft power and contemporary security studies, this research posits a hypothesis: there exists a positive correlation between technological advancements and the escalation of espionage activities by state actors. The inquiry encompasses a comprehensive analysis of key components, such as vulnerabilities, adaptive strategies, geopolitical implications, deterrence mechanisms, and international collaboration, thereby illuminating the multifaceted risks to national security inherent in the digital age (Nye, 2004). Findings: The study critically evaluates the countermeasures undertaken by Western countries, probing strategic enhancements of cyber defences and the formation of international coalitions aimed at collective security (Huang et al., 2021). The findings reveal substantial obstacles in achieving a cohesive and effective response to the rapidly escalating and pervasive nature of contemporary cyber threats (Zhang et al., 2020). Implications to Theory, Practice and Policy: Considering the ongoing maturation of China’s cyber capabilities, characterized by an increased reliance on AI and the impending advent of quantum computing, the article advocates for a comprehensive revaluation of global security practices (Mann et al., 2020). It underscores the imperative for Western nations to not only innovate defensively but to also adopt proactive measures and foster significant international collaboration. This multifaceted approach is essential to address the complex challenges posed by state-sponsored cyber operations within an increasingly interconnected global landscape (Chen et al., 2021).</t>
+        </is>
+      </c>
       <c r="H88" s="5" t="inlineStr">
         <is>
-          <t>scopus</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="I88" s="5" t="n"/>
@@ -4516,37 +4519,33 @@
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>6bb18cfb9e04</t>
+          <t>90c94d9959ea</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>Quantum Risk Analysis</t>
+          <t>Between 0 and 1. Exploring the Algorithmic Restraints and the Potential of Quantum Computing in the Financial Sector</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>Stefan Woerner; Daniel J. Egger</t>
+          <t>Bartosz Szczęsny; Wiesława Gryncewicz</t>
         </is>
       </c>
       <c r="E89" s="5" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F89" s="5" t="inlineStr">
         <is>
-          <t>10.1038/s41534-019-0130-6</t>
-        </is>
-      </c>
-      <c r="G89" s="5" t="inlineStr">
-        <is>
-          <t>We present a quantum algorithm that analyzes risk more efficiently than Monte Carlo simulations traditionally used on classical computers. We employ quantum amplitude estimation to evaluate risk measures such as Value at Risk and Conditional Value at Risk on a gate-based quantum computer. Additionally, we show how to implement this algorithm and how to trade off the convergence rate of the algorithm and the circuit depth. The shortest possible circuit depth - growing polynomially in the number of qubits representing the uncertainty - leads to a convergence rate of $O(M^{-2/3})$. This is already faster than classical Monte Carlo simulations which converge at a rate of $O(M^{-1/2})$. If we allow the circuit depth to grow faster, but still polynomially, the convergence rate quickly approaches the optimum of $O(M^{-1})$. Thus, for slowly increasing circuit depths our algorithm provides a near quadratic speed-up compared to Monte Carlo methods. We demonstrate our algorithm using two toy models. In the first model we use real hardware, such as the IBM Q Experience, to measure the financial risk in a Treasury-bill (T-bill) faced by a possible interest rate increase. In the second model, we simulate our algorithm to illustrate how a quantum computer can determine financial risk for a two-asset portfolio made up of Government debt with different maturity dates. Both models confirm the improved convergence rate over Monte Carlo methods. Using simulations, we also evaluate the impact of cross-talk and energy relaxation errors.</t>
-        </is>
-      </c>
+          <t>10.1007/978-3-031-78468-2_4</t>
+        </is>
+      </c>
+      <c r="G89" s="5" t="inlineStr"/>
       <c r="H89" s="5" t="inlineStr">
         <is>
-          <t>arxiv</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="I89" s="5" t="n"/>
@@ -4560,37 +4559,37 @@
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>817a28486638</t>
+          <t>b078eb45a65d</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>The Evolution of China's Cyber-Espionage Tactics: From Traditional Espionage to AI-Driven Cyber Threats against Critical Infrastructure in the West</t>
+          <t>Quantum computing quantum Monte Carlo with hybrid tensor network for electronic structure calculations</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>Christian C. Madubuko; Chamunorwa Chitsungo</t>
+          <t>Shu Kanno; Hajime Nakamura; Takao Kobayashi; Shigeki Gocho; Miho Hatanaka; Naoki Yamamoto; Qi Gao</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F90" s="5" t="inlineStr">
         <is>
-          <t>10.47672/ajir.2424</t>
+          <t>10.1038/s41534-024-00851-8</t>
         </is>
       </c>
       <c r="G90" s="5" t="inlineStr">
         <is>
-          <t>Purpose: This article critically investigates the evolution of China’s cyber-espionage strategies, specifically illustrating the shift from traditional espionage methodologies to the incorporation of advanced technologies, particularly artificial intelligence (AI). This transition profoundly reshapes global power dynamics, delineating nuanced threats to critical infrastructure in Western nations, including power grids, financial systems, and communication networks (Wang et al., 2019). Materials and Methods: Utilizing a theoretical framework grounded in Joseph Nye's concept of soft power and contemporary security studies, this research posits a hypothesis: there exists a positive correlation between technological advancements and the escalation of espionage activities by state actors. The inquiry encompasses a comprehensive analysis of key components, such as vulnerabilities, adaptive strategies, geopolitical implications, deterrence mechanisms, and international collaboration, thereby illuminating the multifaceted risks to national security inherent in the digital age (Nye, 2004). Findings: The study critically evaluates the countermeasures undertaken by Western countries, probing strategic enhancements of cyber defences and the formation of international coalitions aimed at collective security (Huang et al., 2021). The findings reveal substantial obstacles in achieving a cohesive and effective response to the rapidly escalating and pervasive nature of contemporary cyber threats (Zhang et al., 2020). Implications to Theory, Practice and Policy: Considering the ongoing maturation of China’s cyber capabilities, characterized by an increased reliance on AI and the impending advent of quantum computing, the article advocates for a comprehensive revaluation of global security practices (Mann et al., 2020). It underscores the imperative for Western nations to not only innovate defensively but to also adopt proactive measures and foster significant international collaboration. This multifaceted approach is essential to address the complex challenges posed by state-sponsored cyber operations within an increasingly interconnected global landscape (Chen et al., 2021).</t>
+          <t>Quantum computers have a potential for solving quantum chemistry problems with higher accuracy than classical computers. Quantum computing quantum Monte Carlo (QC-QMC) is a QMC with a trial state prepared in quantum circuit, which is employed to obtain the ground state with higher accuracy than QMC alone. We propose an algorithm combining QC-QMC with a hybrid tensor network to extend the applicability of QC-QMC beyond a single quantum device size. In a two-layer quantum-quantum tree tensor, our algorithm for the larger trial wave function can be executed than preparable wave function in a device. Our algorithm is evaluated on the Heisenberg chain model, graphite-based Hubbard model, hydrogen plane model, and MonoArylBiImidazole using full configuration interaction QMC. Our algorithm can achieve energy accuracy (specifically, variance) several orders of magnitude higher than QMC, and the hybrid tensor version of QMC gives the same energy accuracy as QC-QMC when the system is appropriately decomposed. Moreover, we develop a pseudo-Hadamard test technique that enables efficient overlap calculations between a trial wave function and an orthonormal basis state. In a real device experiment by using the technique, we obtained almost the same accuracy as the statevector simulator, indicating the noise robustness of our algorithm. These results suggests that the present approach will pave the way to electronic structure calculation for large systems with high accuracy on current quantum devices.</t>
         </is>
       </c>
       <c r="H90" s="5" t="inlineStr">
         <is>
-          <t>openalex</t>
+          <t>arxiv</t>
         </is>
       </c>
       <c r="I90" s="5" t="n"/>
@@ -4604,33 +4603,33 @@
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>90c94d9959ea</t>
+          <t>d74a5ac7f26d</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>Between 0 and 1. Exploring the Algorithmic Restraints and the Potential of Quantum Computing in the Financial Sector</t>
+          <t>Logistic Network Design with a D-Wave Quantum Annealer</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>Bartosz Szczęsny; Wiesława Gryncewicz</t>
+          <t>Yongcheng Ding; Xi Chen; L. Lamata; E. Solano; M. Sanz</t>
         </is>
       </c>
       <c r="E91" s="5" t="inlineStr">
         <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="F91" s="5" t="inlineStr">
-        <is>
-          <t>10.1007/978-3-031-78468-2_4</t>
-        </is>
-      </c>
-      <c r="G91" s="5" t="inlineStr"/>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="F91" s="5" t="inlineStr"/>
+      <c r="G91" s="5" t="inlineStr">
+        <is>
+          <t>Logistic network design is an abstract optimization problem which, under the assumption of minimal cost, determines the optimal configuration of infrastructures and facilities of the supply chain based on customer demand. With the solutions at hand, key economic decisions are taken about the location, number, as well as size of manufacturing facilities and warehouses. Therefore, an efficient method to address this question, which is known to be NP-hard, has relevant financial consequences. Here, we propose a hybrid classical-quantum annealing algorithm to accurately obtain the optimal solution. The cost function with constraints is translated to a spin Hamiltonian, whose ground state is supposed to encode the searched result. This algorithm is realized on a D-Wave quantum computer and positively compared with the results of the best classical optimization algorithms. This work shows that state-of-the-art quantum annealers may address useful chain supply problems.</t>
+        </is>
+      </c>
       <c r="H91" s="5" t="inlineStr">
         <is>
-          <t>openalex</t>
+          <t>semantic_scholar</t>
         </is>
       </c>
       <c r="I91" s="5" t="n"/>
@@ -4644,37 +4643,37 @@
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>b078eb45a65d</t>
+          <t>16ee72565789</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>Quantum computing quantum Monte Carlo with hybrid tensor network for electronic structure calculations</t>
+          <t>Impact of Quantum Commerce on the Future of Global Business</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>Shu Kanno; Hajime Nakamura; Takao Kobayashi; Shigeki Gocho; Miho Hatanaka; Naoki Yamamoto; Qi Gao</t>
+          <t>TMBU Bhagalpur Univ. Dept. of Commerce &amp; Bus Administration; Dr. Paranav Shankar</t>
         </is>
       </c>
       <c r="E92" s="5" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="F92" s="5" t="inlineStr">
         <is>
-          <t>10.1038/s41534-024-00851-8</t>
+          <t>10.55041/ijsrem56196</t>
         </is>
       </c>
       <c r="G92" s="5" t="inlineStr">
         <is>
-          <t>Quantum computers have a potential for solving quantum chemistry problems with higher accuracy than classical computers. Quantum computing quantum Monte Carlo (QC-QMC) is a QMC with a trial state prepared in quantum circuit, which is employed to obtain the ground state with higher accuracy than QMC alone. We propose an algorithm combining QC-QMC with a hybrid tensor network to extend the applicability of QC-QMC beyond a single quantum device size. In a two-layer quantum-quantum tree tensor, our algorithm for the larger trial wave function can be executed than preparable wave function in a device. Our algorithm is evaluated on the Heisenberg chain model, graphite-based Hubbard model, hydrogen plane model, and MonoArylBiImidazole using full configuration interaction QMC. Our algorithm can achieve energy accuracy (specifically, variance) several orders of magnitude higher than QMC, and the hybrid tensor version of QMC gives the same energy accuracy as QC-QMC when the system is appropriately decomposed. Moreover, we develop a pseudo-Hadamard test technique that enables efficient overlap calculations between a trial wave function and an orthonormal basis state. In a real device experiment by using the technique, we obtained almost the same accuracy as the statevector simulator, indicating the noise robustness of our algorithm. These results suggests that the present approach will pave the way to electronic structure calculation for large systems with high accuracy on current quantum devices.</t>
+          <t>Abstract The rapid advancement of technology, coupled with the global interconnectivity, has led to the emergence of quantum commerce (Q-commerce) as a significant paradigm shift in the business world. Quantum commerce represents a new form of digital commerce that combines aspects of quantum computing, artificial intelligence (AI), block chain, and next-generation networks. This transformative model promises to revolutionize the way businesses interact with customers, manage data, and optimize operations. The global impact of quantum commerce will be far-reaching, influencing various industries, economic dynamics, and business models. This note explores the key components of quantum commerce, its potential impacts on businesses globally, and the opportunities and challenges it will bring in the coming years. Key-words: Quantum Computing, Quantum Technology, Business Transformation, AI and Quantum Integration, Data Security, Quantum Cryptography, Supply chain Optimization, Financial Service Innovation, Disruptive Innovation, Global Trade, Digital Ecosystems, Quantum Algorithms, Block chain and Quantum, Market Efficiency, Competitive Advantage Business Intelligence, Automation, Tech Adoption, Cross-border commerce, Cyber security etc.</t>
         </is>
       </c>
       <c r="H92" s="5" t="inlineStr">
         <is>
-          <t>arxiv</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="I92" s="5" t="n"/>
@@ -4688,33 +4687,37 @@
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>d74a5ac7f26d</t>
+          <t>62ed79c3a22b</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>Logistic Network Design with a D-Wave Quantum Annealer</t>
+          <t>Teaching quantum information technologies and a practical module for online and offline undergraduate students</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>Yongcheng Ding; Xi Chen; L. Lamata; E. Solano; M. Sanz</t>
+          <t>Hao Tang; Tianyu Wang; Ruoxi Shi; Xian‐Min Jin</t>
         </is>
       </c>
       <c r="E93" s="5" t="inlineStr">
         <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="F93" s="5" t="inlineStr"/>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F93" s="5" t="inlineStr">
+        <is>
+          <t>10.48550/arxiv.2112.06548</t>
+        </is>
+      </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>Logistic network design is an abstract optimization problem which, under the assumption of minimal cost, determines the optimal configuration of infrastructures and facilities of the supply chain based on customer demand. With the solutions at hand, key economic decisions are taken about the location, number, as well as size of manufacturing facilities and warehouses. Therefore, an efficient method to address this question, which is known to be NP-hard, has relevant financial consequences. Here, we propose a hybrid classical-quantum annealing algorithm to accurately obtain the optimal solution. The cost function with constraints is translated to a spin Hamiltonian, whose ground state is supposed to encode the searched result. This algorithm is realized on a D-Wave quantum computer and positively compared with the results of the best classical optimization algorithms. This work shows that state-of-the-art quantum annealers may address useful chain supply problems.</t>
+          <t>Quantum Information Technologies and a Practical Module is a new course we launch at Shanghai Jiao Tong University targeting at the undergraduate students who major in a variety of engineering disciplines. We develop a holistic curriculum for quantum computing covering the quantum hardware, quantum algorithms and applications. The quantum computing approaches include the universal digital quantum computing, analog quantum computing and the hybrid quantum-classical variational quantum computing that is tailored to the noisy intermediate-scale quantum (NISQ) technologies nowadays. Besides, we set a practical module to bring student closer to the real industry needs. The students would form a team of three to use any quantum approach to solve a problem in fields like optimization, finance, machine learning, chemistry and biology. Further, this course is selected into the Jiao Tong Global Virtual Classroom Initiative, so that it is open to global students in Association of Pacific Rim Universities at the same time with the offline students, in a specifically updated classroom. The efforts in curriculum development, practical module setting and blended learning make this course a good case study for education on quantum sciences and technologies.</t>
         </is>
       </c>
       <c r="H93" s="5" t="inlineStr">
         <is>
-          <t>semantic_scholar</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="I93" s="5" t="n"/>
@@ -4728,32 +4731,32 @@
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>16ee72565789</t>
+          <t>64b4914da5c2</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>Impact of Quantum Commerce on the Future of Global Business</t>
+          <t>Quantum Fuzzy Regression Model for Uncertain Environment</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>TMBU Bhagalpur Univ. Dept. of Commerce &amp; Bus Administration; Dr. Paranav Shankar</t>
+          <t>Tiansu Chen; Shi bin Zhang; Qirun Wang; Yan Chang</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F94" s="5" t="inlineStr">
         <is>
-          <t>10.55041/ijsrem56196</t>
+          <t>10.32604/cmc.2023.033284</t>
         </is>
       </c>
       <c r="G94" s="5" t="inlineStr">
         <is>
-          <t>Abstract The rapid advancement of technology, coupled with the global interconnectivity, has led to the emergence of quantum commerce (Q-commerce) as a significant paradigm shift in the business world. Quantum commerce represents a new form of digital commerce that combines aspects of quantum computing, artificial intelligence (AI), block chain, and next-generation networks. This transformative model promises to revolutionize the way businesses interact with customers, manage data, and optimize operations. The global impact of quantum commerce will be far-reaching, influencing various industries, economic dynamics, and business models. This note explores the key components of quantum commerce, its potential impacts on businesses globally, and the opportunities and challenges it will bring in the coming years. Key-words: Quantum Computing, Quantum Technology, Business Transformation, AI and Quantum Integration, Data Security, Quantum Cryptography, Supply chain Optimization, Financial Service Innovation, Disruptive Innovation, Global Trade, Digital Ecosystems, Quantum Algorithms, Block chain and Quantum, Market Efficiency, Competitive Advantage Business Intelligence, Automation, Tech Adoption, Cross-border commerce, Cyber security etc.</t>
+          <t>In the era of big data, traditional regression models cannot deal with uncertain big data efficiently and accurately. In order to make up for this deficiency, this paper proposes a quantum fuzzy regression model, which uses fuzzy theory to describe the uncertainty in big data sets and uses quantum computing to exponentially improve the efficiency of data set preprocessing and parameter estimation. In this paper, data envelopment analysis (DEA) is used to calculate the degree of importance of each data point. Meanwhile, Harrow, Hassidim and Lloyd (HHL) algorithm and quantum swap circuits are used to improve the efficiency of high-dimensional data matrix calculation. The application of the quantum fuzzy regression model to small-scale financial data proves that its accuracy is greatly improved compared with the quantum regression model. Moreover, due to the introduction of quantum computing, the speed of dealing with high-dimensional data matrix has an exponential improvement compared with the fuzzy regression model. The quantum fuzzy regression model proposed in this paper combines the advantages of fuzzy theory and quantum computing which can efficiently calculate high-dimensional data matrix and complete parameter estimation using quantum computing while retaining the uncertainty in big data. Thus, it is a new model for efficient and accurate big data processing in uncertain environments.</t>
         </is>
       </c>
       <c r="H94" s="5" t="inlineStr">
@@ -4772,32 +4775,32 @@
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>62ed79c3a22b</t>
+          <t>fd9854ee7cd9</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>Teaching quantum information technologies and a practical module for online and offline undergraduate students</t>
+          <t>Addressing Exponential Scale Problems at Infosys</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>Hao Tang; Tianyu Wang; Ruoxi Shi; Xian‐Min Jin</t>
+          <t>Vittal Setty</t>
         </is>
       </c>
       <c r="E95" s="5" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F95" s="5" t="inlineStr">
         <is>
-          <t>10.48550/arxiv.2112.06548</t>
+          <t>10.1109/hipc58850.2023.00014</t>
         </is>
       </c>
       <c r="G95" s="5" t="inlineStr">
         <is>
-          <t>Quantum Information Technologies and a Practical Module is a new course we launch at Shanghai Jiao Tong University targeting at the undergraduate students who major in a variety of engineering disciplines. We develop a holistic curriculum for quantum computing covering the quantum hardware, quantum algorithms and applications. The quantum computing approaches include the universal digital quantum computing, analog quantum computing and the hybrid quantum-classical variational quantum computing that is tailored to the noisy intermediate-scale quantum (NISQ) technologies nowadays. Besides, we set a practical module to bring student closer to the real industry needs. The students would form a team of three to use any quantum approach to solve a problem in fields like optimization, finance, machine learning, chemistry and biology. Further, this course is selected into the Jiao Tong Global Virtual Classroom Initiative, so that it is open to global students in Association of Pacific Rim Universities at the same time with the offline students, in a specifically updated classroom. The efforts in curriculum development, practical module setting and blended learning make this course a good case study for education on quantum sciences and technologies.</t>
+          <t>In this talk I am going to share the use cases for high performance computing for the many clients oflnfosys in the domains of Logistics, Finance, Pharma, Manufacturing andthe like. What are some of the problems of exponential size that we have encountered? And what are the technology solutions that Infosys has adopted to address these use cases? What is the role of Quantum Computing for example in this space? What is the potential of this technology for solving large problems of exponential scale in optimization, simulation, drug discovery, Cyber security and ML? These are some of the questions we will get to explore in this talk. Secondly, we will see the opportunities and challenges in using LLMs in the SDLC process. And lastly, we will discuss the challenges in using enterprise data for experimenting with new cutting edge OS/third party solutions. What worked for us, and what did not? Maybe your research and ideas can address some of the gaps we are facing. Come join this talk to explore opportunities on how best we can collaborate.</t>
         </is>
       </c>
       <c r="H95" s="5" t="inlineStr">
@@ -4816,32 +4819,32 @@
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>64b4914da5c2</t>
+          <t>38c9c05fedf3</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>Quantum Fuzzy Regression Model for Uncertain Environment</t>
+          <t>Integrating SAP ERP with Emerging Technologies (IoT, AI, Blockchain): Challenges and Opportunities for Professionals</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>Tiansu Chen; Shi bin Zhang; Qirun Wang; Yan Chang</t>
+          <t>Siva Reddy Pulluru</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="F96" s="5" t="inlineStr">
         <is>
-          <t>10.32604/cmc.2023.033284</t>
+          <t>10.5281/zenodo.18317672</t>
         </is>
       </c>
       <c r="G96" s="5" t="inlineStr">
         <is>
-          <t>In the era of big data, traditional regression models cannot deal with uncertain big data efficiently and accurately. In order to make up for this deficiency, this paper proposes a quantum fuzzy regression model, which uses fuzzy theory to describe the uncertainty in big data sets and uses quantum computing to exponentially improve the efficiency of data set preprocessing and parameter estimation. In this paper, data envelopment analysis (DEA) is used to calculate the degree of importance of each data point. Meanwhile, Harrow, Hassidim and Lloyd (HHL) algorithm and quantum swap circuits are used to improve the efficiency of high-dimensional data matrix calculation. The application of the quantum fuzzy regression model to small-scale financial data proves that its accuracy is greatly improved compared with the quantum regression model. Moreover, due to the introduction of quantum computing, the speed of dealing with high-dimensional data matrix has an exponential improvement compared with the fuzzy regression model. The quantum fuzzy regression model proposed in this paper combines the advantages of fuzzy theory and quantum computing which can efficiently calculate high-dimensional data matrix and complete parameter estimation using quantum computing while retaining the uncertainty in big data. Thus, it is a new model for efficient and accurate big data processing in uncertain environments.</t>
+          <t>Advanced technology, including the Internet of Things (IoT), along with Artificial Intelligence (AI) and blockchain technology, is changing the ways businesses operate. With IoT being utilized in manufacturing and logistics, and energy sectors, companies are receiving real-time information on operations. AI enables cognitive business processes, including Fraud Detection, Smart Procurement, and Automated Customer Service. Blockchain gives organizations a way to build Trusted Transaction Ecosystems for tracking pharmaceuticals, tracing food products, and providing Financial Services. The integration of these technologies transforms traditional SAP ERP Systems into Intelligent Decision-Making Platforms. While the integration of these technologies has the potential to enhance ERP systems, there are still significant challenges associated with the implementation of these new technologies, including data volume management, security vulnerabilities, and the skill gap. Technical solutions that address these challenges include the implementation of Unified Data Layer (UDL), Edge Computing Architecture, and Hybrid Blockchain solutions. In addition to these technical solutions, SAP Professionals will also see many career opportunities for growth as a result of the integration of IoT, AI, and Blockchain with ERP Systems. Career paths for SAP Professionals will continue to include IoT Architect, AI Engineer, or Blockchain Consultant. New developments like GenAI acceleration, quantum computing integration, and metaverse interfaces will continue to change the integration of the above three technologies with SAP ERP Systems. With new developments will also come new ethical issues related to algorithmic bias and data privacy that will be prevalent over time. Also, the Strategic Imperatives of organizations will require the SAP Professionals to engage in continual learning and adaptation. Organizations will face the challenge of balancing innovation with the necessity of remaining operationally stable and compliant with regulations.</t>
         </is>
       </c>
       <c r="H96" s="5" t="inlineStr">
@@ -4860,32 +4863,32 @@
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>fd9854ee7cd9</t>
+          <t>3fa357ba078b</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>Addressing Exponential Scale Problems at Infosys</t>
+          <t>Quantum Apocalypse: Fortifying Critical Infrastructure in the Age of Cyber Warfare</t>
         </is>
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>Vittal Setty</t>
+          <t>Shreyas Kumar; Andreas Klappenecker; Gary Brown; S. Saravanan</t>
         </is>
       </c>
       <c r="E97" s="5" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F97" s="5" t="inlineStr">
         <is>
-          <t>10.1109/hipc58850.2023.00014</t>
+          <t>10.34190/eccws.24.1.3757</t>
         </is>
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>In this talk I am going to share the use cases for high performance computing for the many clients oflnfosys in the domains of Logistics, Finance, Pharma, Manufacturing andthe like. What are some of the problems of exponential size that we have encountered? And what are the technology solutions that Infosys has adopted to address these use cases? What is the role of Quantum Computing for example in this space? What is the potential of this technology for solving large problems of exponential scale in optimization, simulation, drug discovery, Cyber security and ML? These are some of the questions we will get to explore in this talk. Secondly, we will see the opportunities and challenges in using LLMs in the SDLC process. And lastly, we will discuss the challenges in using enterprise data for experimenting with new cutting edge OS/third party solutions. What worked for us, and what did not? Maybe your research and ideas can address some of the gaps we are facing. Come join this talk to explore opportunities on how best we can collaborate.</t>
+          <t>Quantum attacks on cryptographic systems remain hypothetical but are grounded in strong theoretical foundations. The emergence of quantum computing presents a significant challenge to national security, particularly in protecting critical infrastructures such as energy grids, financial systems, and healthcare networks. Quantum algorithms like Shor’s may soon be capable of breaking widely used cryptographic standards (RSA, ECC, AES), rendering current encryption obsolete and exposing essential services to disruption and data breaches. These vulnerabilities could threaten economic stability and public safety on a national scale. This paper analyzes the risks posed by quantum computing to classical cryptographic frameworks and evaluates quantum-resistant alternatives such as lattice-based, hash-based, and code-based cryptography. It assesses their theoretical soundness and suitability for securing national critical infrastructure. The analysis also explores the dangers of delayed implementation, where postponed adoption of post-quantum cryptography (PQC) could expose systems to future quantum-enabled cyberattacks. Additionally, the paper discusses the challenges of integrating PQC into existing systems, including regulatory compliance, interoperability, and operational readiness. Without coordinated strategies and accelerated transition plans, nations risk severe consequences, including financial disruption, healthcare service breakdowns, and energy supply chain failures. Finally, the study highlights the need for international cooperation, policy alignment, and robust testing to ensure the effective deployment of quantum-resistant solutions. Prompt action is essential to preserve the confidentiality, integrity, and availability of vital national systems in the face of the advancing quantum threat landscape.</t>
         </is>
       </c>
       <c r="H97" s="5" t="inlineStr">
@@ -4904,37 +4907,37 @@
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>d461b3fdb4fe</t>
+          <t>b80c0b2a69b6</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>Portfolio Optimization of 40 Stocks Using the DWave Quantum Annealer</t>
+          <t>Uncertain fate of fair sampling in quantum annealing</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>Jeffrey P. Cohen; Alex Khan; Clark Alexander</t>
+          <t>Mario S. Könz; Guglielmo Mazzola; Andrew J. Ochoa; Helmut G. Katzgraber; Matthias Troyer</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="F98" s="5" t="inlineStr">
         <is>
-          <t>10.48550/arxiv.2007.01430</t>
+          <t>10.1103/PhysRevA.100.030303</t>
         </is>
       </c>
       <c r="G98" s="5" t="inlineStr">
         <is>
-          <t>We investigate the use of quantum computers for building a portfolio out of a universe of U.S. listed, liquid equities that contains an optimal set of stocks. Starting from historical market data, we look at various problem formulations on the D-Wave Systems Inc. D-Wave 2000Q(TM) System (hereafter called DWave) to find the optimal risk vs return portfolio; an optimized portfolio based on the Markowitz formulation and the Sharpe ratio, a simplified Chicago Quantum Ratio (CQR), then a new Chicago Quantum Net Score (CQNS). We approach this first classically, then by our new method on DWave. Our results show that practitioners can use a DWave to select attractive portfolios out of 40 U.S. liquid equities.</t>
+          <t>Recently, it was demonstrated both theoretically and experimentally on the D-Wave quantum annealer that transverse-field quantum annealing does not find all ground states with equal probability. In particular, it was proposed that more complex driver Hamiltonians beyond transverse fields might mitigate this shortcoming. Here, we investigate the mechanisms of (un)fair sampling in quantum annealing. While higher-order terms can improve the sampling for selected small problems, we present multiple counterexamples where driver Hamiltonians that go beyond transverse fields do not remove the sampling bias. Using perturbation theory we explain why this is the case. In addition, we present large-scale quantum Monte Carlo simulations for spin glasses with known degeneracy in two space dimensions and demonstrate that the fair-sampling performance of quadratic driver terms is comparable to standard transverse-field drivers. Our results suggest that quantum annealing machines are not well suited for sampling applications, unless post-processing techniques to improve the sampling are applied.</t>
         </is>
       </c>
       <c r="H98" s="5" t="inlineStr">
         <is>
-          <t>openalex</t>
+          <t>arxiv</t>
         </is>
       </c>
       <c r="I98" s="5" t="n"/>
@@ -4943,136 +4946,154 @@
       <c r="L98" s="5" t="n"/>
     </row>
     <row r="99">
-      <c r="A99" s="5" t="n">
+      <c r="A99" t="n">
         <v>98</v>
       </c>
-      <c r="B99" s="5" t="inlineStr">
-        <is>
-          <t>38c9c05fedf3</t>
-        </is>
-      </c>
-      <c r="C99" s="5" t="inlineStr">
-        <is>
-          <t>Integrating SAP ERP with Emerging Technologies (IoT, AI, Blockchain): Challenges and Opportunities for Professionals</t>
-        </is>
-      </c>
-      <c r="D99" s="5" t="inlineStr">
-        <is>
-          <t>Siva Reddy Pulluru</t>
-        </is>
-      </c>
-      <c r="E99" s="5" t="inlineStr">
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>9e1b8407ace4</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Scalable Neural Quantum State based Kernel Polynomial Method for Optical Properties from the First Principle</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Wei Liu; Rui-Hao Bi; Wenjie Dou</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Variational optimization of neural-network quantum state representations has achieved FCI-level accuracy for ground state calculations, yet computing optical properties involving excited states remains challenging. In this work, we present a neural-network-based variational quantum Monte Carlo approach for ab-initio absorption spectra. We leverage parallel batch autoregressive sampling and GPU-supported local energy parallelism to efficiently compute ground states of complex systems. By integrating neural quantum ground states with the kernel polynomial method, our approach accurately calculates absorption spectra for large molecules with over 50 electrons, achieving FCI-level precision. The proposed algorithm demonstrates superior scalability and reduced runtime compared to FCI, marking a significant step forward in optical property calculations for large-scale quantum systems.</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>arxiv</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>26e27073cdc6</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Quantum Machine Learning Architectures for Stock Market Forecasting, Anomaly Detection, and Pattern Recognition in Financial Time Series</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Tugan Başaran</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="F99" s="5" t="inlineStr">
-        <is>
-          <t>10.5281/zenodo.18317672</t>
-        </is>
-      </c>
-      <c r="G99" s="5" t="inlineStr">
-        <is>
-          <t>Advanced technology, including the Internet of Things (IoT), along with Artificial Intelligence (AI) and blockchain technology, is changing the ways businesses operate. With IoT being utilized in manufacturing and logistics, and energy sectors, companies are receiving real-time information on operations. AI enables cognitive business processes, including Fraud Detection, Smart Procurement, and Automated Customer Service. Blockchain gives organizations a way to build Trusted Transaction Ecosystems for tracking pharmaceuticals, tracing food products, and providing Financial Services. The integration of these technologies transforms traditional SAP ERP Systems into Intelligent Decision-Making Platforms. While the integration of these technologies has the potential to enhance ERP systems, there are still significant challenges associated with the implementation of these new technologies, including data volume management, security vulnerabilities, and the skill gap. Technical solutions that address these challenges include the implementation of Unified Data Layer (UDL), Edge Computing Architecture, and Hybrid Blockchain solutions. In addition to these technical solutions, SAP Professionals will also see many career opportunities for growth as a result of the integration of IoT, AI, and Blockchain with ERP Systems. Career paths for SAP Professionals will continue to include IoT Architect, AI Engineer, or Blockchain Consultant. New developments like GenAI acceleration, quantum computing integration, and metaverse interfaces will continue to change the integration of the above three technologies with SAP ERP Systems. With new developments will also come new ethical issues related to algorithmic bias and data privacy that will be prevalent over time. Also, the Strategic Imperatives of organizations will require the SAP Professionals to engage in continual learning and adaptation. Organizations will face the challenge of balancing innovation with the necessity of remaining operationally stable and compliant with regulations.</t>
-        </is>
-      </c>
-      <c r="H99" s="5" t="inlineStr">
-        <is>
-          <t>openalex</t>
-        </is>
-      </c>
-      <c r="I99" s="5" t="n"/>
-      <c r="J99" s="5" t="n"/>
-      <c r="K99" s="5" t="n"/>
-      <c r="L99" s="5" t="n"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="5" t="n">
-        <v>99</v>
-      </c>
-      <c r="B100" s="5" t="inlineStr">
-        <is>
-          <t>3fa357ba078b</t>
-        </is>
-      </c>
-      <c r="C100" s="5" t="inlineStr">
-        <is>
-          <t>Quantum Apocalypse: Fortifying Critical Infrastructure in the Age of Cyber Warfare</t>
-        </is>
-      </c>
-      <c r="D100" s="5" t="inlineStr">
-        <is>
-          <t>Shreyas Kumar; Andreas Klappenecker; Gary Brown; S. Saravanan</t>
-        </is>
-      </c>
-      <c r="E100" s="5" t="inlineStr">
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>10.62802/0c086y54</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Financial markets generate complex, high-dimensional time series characterized by nonlinearity, noise, and structural uncertainty, posing persistent challenges for classical machine learning and statistical forecasting models. This paper examines quantum machine learning (QML) architectures for stock market forecasting, anomaly detection, and pattern recognition in financial time series. By leveraging quantum phenomena such as superposition, entanglement, and quantum-enhanced feature spaces, QML models offer new computational paradigms for capturing intricate market dynamics and latent structures. The study synthesizes recent advances in quantum neural networks, variational quantum circuits, and hybrid quantum–classical models, evaluating their applicability to predictive modeling and risk-sensitive detection tasks in finance. The paper argues that QML architectures have the potential to complement classical approaches by improving representational capacity and scalability for complex financial data, while also outlining current technical limitations and research directions necessary for practical deployment.</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>openalex</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>c6240bc88e6f</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Low Liquidity Brings Volatility: Quantum Zeno Effect and Pricing</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Widdows D.</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="F100" s="5" t="inlineStr">
-        <is>
-          <t>10.34190/eccws.24.1.3757</t>
-        </is>
-      </c>
-      <c r="G100" s="5" t="inlineStr">
-        <is>
-          <t>Quantum attacks on cryptographic systems remain hypothetical but are grounded in strong theoretical foundations. The emergence of quantum computing presents a significant challenge to national security, particularly in protecting critical infrastructures such as energy grids, financial systems, and healthcare networks. Quantum algorithms like Shor’s may soon be capable of breaking widely used cryptographic standards (RSA, ECC, AES), rendering current encryption obsolete and exposing essential services to disruption and data breaches. These vulnerabilities could threaten economic stability and public safety on a national scale. This paper analyzes the risks posed by quantum computing to classical cryptographic frameworks and evaluates quantum-resistant alternatives such as lattice-based, hash-based, and code-based cryptography. It assesses their theoretical soundness and suitability for securing national critical infrastructure. The analysis also explores the dangers of delayed implementation, where postponed adoption of post-quantum cryptography (PQC) could expose systems to future quantum-enabled cyberattacks. Additionally, the paper discusses the challenges of integrating PQC into existing systems, including regulatory compliance, interoperability, and operational readiness. Without coordinated strategies and accelerated transition plans, nations risk severe consequences, including financial disruption, healthcare service breakdowns, and energy supply chain failures. Finally, the study highlights the need for international cooperation, policy alignment, and robust testing to ensure the effective deployment of quantum-resistant solutions. Prompt action is essential to preserve the confidentiality, integrity, and availability of vital national systems in the face of the advancing quantum threat landscape.</t>
-        </is>
-      </c>
-      <c r="H100" s="5" t="inlineStr">
-        <is>
-          <t>openalex</t>
-        </is>
-      </c>
-      <c r="I100" s="5" t="n"/>
-      <c r="J100" s="5" t="n"/>
-      <c r="K100" s="5" t="n"/>
-      <c r="L100" s="5" t="n"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="B101" s="5" t="inlineStr">
-        <is>
-          <t>b80c0b2a69b6</t>
-        </is>
-      </c>
-      <c r="C101" s="5" t="inlineStr">
-        <is>
-          <t>Uncertain fate of fair sampling in quantum annealing</t>
-        </is>
-      </c>
-      <c r="D101" s="5" t="inlineStr">
-        <is>
-          <t>Mario S. Könz; Guglielmo Mazzola; Andrew J. Ochoa; Helmut G. Katzgraber; Matthias Troyer</t>
-        </is>
-      </c>
-      <c r="E101" s="5" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="F101" s="5" t="inlineStr">
-        <is>
-          <t>10.1103/PhysRevA.100.030303</t>
-        </is>
-      </c>
-      <c r="G101" s="5" t="inlineStr">
-        <is>
-          <t>Recently, it was demonstrated both theoretically and experimentally on the D-Wave quantum annealer that transverse-field quantum annealing does not find all ground states with equal probability. In particular, it was proposed that more complex driver Hamiltonians beyond transverse fields might mitigate this shortcoming. Here, we investigate the mechanisms of (un)fair sampling in quantum annealing. While higher-order terms can improve the sampling for selected small problems, we present multiple counterexamples where driver Hamiltonians that go beyond transverse fields do not remove the sampling bias. Using perturbation theory we explain why this is the case. In addition, we present large-scale quantum Monte Carlo simulations for spin glasses with known degeneracy in two space dimensions and demonstrate that the fair-sampling performance of quadratic driver terms is comparable to standard transverse-field drivers. Our results suggest that quantum annealing machines are not well suited for sampling applications, unless post-processing techniques to improve the sampling are applied.</t>
-        </is>
-      </c>
-      <c r="H101" s="5" t="inlineStr">
-        <is>
-          <t>arxiv</t>
-        </is>
-      </c>
-      <c r="I101" s="5" t="n"/>
-      <c r="J101" s="5" t="n"/>
-      <c r="K101" s="5" t="n"/>
-      <c r="L101" s="5" t="n"/>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>10.1007/978-3-031-83117-1_36</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>scopus</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>154d9e2f9694</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence For Decision Making In The Era Of Big Data Evolution</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Rebeka Sultana</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>10.70008/jbimisr.v1i01.59</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>This study systematically examines the transformative role of Artificial Intelligence (AI) in decision-making, focusing on its applications, challenges, and future opportunities. Using the Preferred Reporting Items for Systematic Reviews and Meta-Analyses (PRISMA) guidelines, a total of 100 peer-reviewed articles were analyzed to ensure a rigorous and comprehensive understanding of the subject. The findings highlight AI's ability to optimize decision-making processes through advanced technologies such as machine learning, natural language processing, and predictive analytics, significantly enhancing accuracy, efficiency, and responsiveness across diverse sectors such as healthcare, finance, supply chain management, and public administration. Despite these advancements, the study identifies persistent challenges, including algorithmic bias, data privacy concerns, and the lack of transparency in "black box" AI models, which undermine trust and accountability. Additionally, the review uncovers research gaps, particularly in low-resource settings and emerging markets, where AI's potential remains underutilized due to infrastructural and data limitations. The integration of AI with emerging technologies, such as blockchain, quantum computing, and edge computing, presents promising opportunities to enhance scalability, security, and transparency in decision-making. The study also underscores the importance of interdisciplinary research, particularly at the intersection of AI and social sciences, to better understand human-AI interaction and foster ethical and socially equitable AI adoption. By addressing these challenges and leveraging emerging opportunities, AI can evolve into a transformative tool for informed, inclusive, and responsible decision-making in an increasingly complex world.</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>openalex</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:L101"/>

--- a/05_screening/validation_screening.xlsx
+++ b/05_screening/validation_screening.xlsx
@@ -848,10 +848,26 @@
           <t>arxiv</t>
         </is>
       </c>
-      <c r="I2" s="5" t="n"/>
-      <c r="J2" s="5" t="n"/>
-      <c r="K2" s="5" t="n"/>
-      <c r="L2" s="5" t="n"/>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="n">
@@ -892,10 +908,26 @@
           <t>openalex</t>
         </is>
       </c>
-      <c r="I3" s="5" t="n"/>
-      <c r="J3" s="5" t="n"/>
-      <c r="K3" s="5" t="n"/>
-      <c r="L3" s="5" t="n"/>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="n">
@@ -932,10 +964,26 @@
           <t>openalex</t>
         </is>
       </c>
-      <c r="I4" s="5" t="n"/>
-      <c r="J4" s="5" t="n"/>
-      <c r="K4" s="5" t="n"/>
-      <c r="L4" s="5" t="n"/>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
@@ -976,10 +1024,26 @@
           <t>openalex</t>
         </is>
       </c>
-      <c r="I5" s="5" t="n"/>
-      <c r="J5" s="5" t="n"/>
-      <c r="K5" s="5" t="n"/>
-      <c r="L5" s="5" t="n"/>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="n">
@@ -1020,10 +1084,26 @@
           <t>arxiv</t>
         </is>
       </c>
-      <c r="I6" s="5" t="n"/>
-      <c r="J6" s="5" t="n"/>
-      <c r="K6" s="5" t="n"/>
-      <c r="L6" s="5" t="n"/>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
@@ -1060,10 +1140,26 @@
           <t>openalex</t>
         </is>
       </c>
-      <c r="I7" s="5" t="n"/>
-      <c r="J7" s="5" t="n"/>
-      <c r="K7" s="5" t="n"/>
-      <c r="L7" s="5" t="n"/>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="n">
@@ -1104,10 +1200,26 @@
           <t>openalex</t>
         </is>
       </c>
-      <c r="I8" s="5" t="n"/>
-      <c r="J8" s="5" t="n"/>
-      <c r="K8" s="5" t="n"/>
-      <c r="L8" s="5" t="n"/>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="L8" s="5" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="n">
@@ -1148,10 +1260,26 @@
           <t>openalex</t>
         </is>
       </c>
-      <c r="I9" s="5" t="n"/>
-      <c r="J9" s="5" t="n"/>
-      <c r="K9" s="5" t="n"/>
-      <c r="L9" s="5" t="n"/>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="L9" s="5" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="n">
@@ -1192,10 +1320,26 @@
           <t>openalex</t>
         </is>
       </c>
-      <c r="I10" s="5" t="n"/>
-      <c r="J10" s="5" t="n"/>
-      <c r="K10" s="5" t="n"/>
-      <c r="L10" s="5" t="n"/>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="L10" s="5" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
@@ -1236,10 +1380,26 @@
           <t>openalex</t>
         </is>
       </c>
-      <c r="I11" s="5" t="n"/>
-      <c r="J11" s="5" t="n"/>
-      <c r="K11" s="5" t="n"/>
-      <c r="L11" s="5" t="n"/>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
+      </c>
+      <c r="L11" s="5" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="n">
@@ -1280,10 +1440,26 @@
           <t>arxiv</t>
         </is>
       </c>
-      <c r="I12" s="5" t="n"/>
-      <c r="J12" s="5" t="n"/>
-      <c r="K12" s="5" t="n"/>
-      <c r="L12" s="5" t="n"/>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="L12" s="5" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="n">
@@ -1324,10 +1500,26 @@
           <t>openalex</t>
         </is>
       </c>
-      <c r="I13" s="5" t="n"/>
-      <c r="J13" s="5" t="n"/>
-      <c r="K13" s="5" t="n"/>
-      <c r="L13" s="5" t="n"/>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="L13" s="5" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="n">
@@ -1368,10 +1560,26 @@
           <t>openalex</t>
         </is>
       </c>
-      <c r="I14" s="5" t="n"/>
-      <c r="J14" s="5" t="n"/>
-      <c r="K14" s="5" t="n"/>
-      <c r="L14" s="5" t="n"/>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="L14" s="5" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="n">
@@ -1412,10 +1620,26 @@
           <t>openalex</t>
         </is>
       </c>
-      <c r="I15" s="5" t="n"/>
-      <c r="J15" s="5" t="n"/>
-      <c r="K15" s="5" t="n"/>
-      <c r="L15" s="5" t="n"/>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="L15" s="5" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="n">
@@ -1456,10 +1680,26 @@
           <t>openalex</t>
         </is>
       </c>
-      <c r="I16" s="5" t="n"/>
-      <c r="J16" s="5" t="n"/>
-      <c r="K16" s="5" t="n"/>
-      <c r="L16" s="5" t="n"/>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
+      </c>
+      <c r="L16" s="5" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="n">
@@ -1496,10 +1736,26 @@
           <t>arxiv</t>
         </is>
       </c>
-      <c r="I17" s="5" t="n"/>
-      <c r="J17" s="5" t="n"/>
-      <c r="K17" s="5" t="n"/>
-      <c r="L17" s="5" t="n"/>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
+      </c>
+      <c r="L17" s="5" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="n">
@@ -1540,10 +1796,26 @@
           <t>openalex</t>
         </is>
       </c>
-      <c r="I18" s="5" t="n"/>
-      <c r="J18" s="5" t="n"/>
-      <c r="K18" s="5" t="n"/>
-      <c r="L18" s="5" t="n"/>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
+      </c>
+      <c r="L18" s="5" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="n">
@@ -1584,10 +1856,26 @@
           <t>openalex</t>
         </is>
       </c>
-      <c r="I19" s="5" t="n"/>
-      <c r="J19" s="5" t="n"/>
-      <c r="K19" s="5" t="n"/>
-      <c r="L19" s="5" t="n"/>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="L19" s="5" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="n">
@@ -1628,10 +1916,26 @@
           <t>openalex</t>
         </is>
       </c>
-      <c r="I20" s="5" t="n"/>
-      <c r="J20" s="5" t="n"/>
-      <c r="K20" s="5" t="n"/>
-      <c r="L20" s="5" t="n"/>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="L20" s="5" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="n">
@@ -1672,10 +1976,26 @@
           <t>openalex</t>
         </is>
       </c>
-      <c r="I21" s="5" t="n"/>
-      <c r="J21" s="5" t="n"/>
-      <c r="K21" s="5" t="n"/>
-      <c r="L21" s="5" t="n"/>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="L21" s="5" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="n">
@@ -1712,10 +2032,26 @@
           <t>scopus</t>
         </is>
       </c>
-      <c r="I22" s="5" t="n"/>
-      <c r="J22" s="5" t="n"/>
-      <c r="K22" s="5" t="n"/>
-      <c r="L22" s="5" t="n"/>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="L22" s="5" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="n">
@@ -1756,10 +2092,26 @@
           <t>openalex</t>
         </is>
       </c>
-      <c r="I23" s="5" t="n"/>
-      <c r="J23" s="5" t="n"/>
-      <c r="K23" s="5" t="n"/>
-      <c r="L23" s="5" t="n"/>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="L23" s="5" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="n">
@@ -1800,10 +2152,26 @@
           <t>semantic_scholar</t>
         </is>
       </c>
-      <c r="I24" s="5" t="n"/>
-      <c r="J24" s="5" t="n"/>
-      <c r="K24" s="5" t="n"/>
-      <c r="L24" s="5" t="n"/>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="L24" s="5" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="n">
@@ -1844,10 +2212,26 @@
           <t>openalex</t>
         </is>
       </c>
-      <c r="I25" s="5" t="n"/>
-      <c r="J25" s="5" t="n"/>
-      <c r="K25" s="5" t="n"/>
-      <c r="L25" s="5" t="n"/>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="n">
@@ -1888,10 +2272,26 @@
           <t>openalex</t>
         </is>
       </c>
-      <c r="I26" s="5" t="n"/>
-      <c r="J26" s="5" t="n"/>
-      <c r="K26" s="5" t="n"/>
-      <c r="L26" s="5" t="n"/>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="L26" s="5" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="n">
@@ -1932,10 +2332,26 @@
           <t>openalex</t>
         </is>
       </c>
-      <c r="I27" s="5" t="n"/>
-      <c r="J27" s="5" t="n"/>
-      <c r="K27" s="5" t="n"/>
-      <c r="L27" s="5" t="n"/>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
+      </c>
+      <c r="L27" s="5" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="n">
@@ -1976,10 +2392,26 @@
           <t>openalex</t>
         </is>
       </c>
-      <c r="I28" s="5" t="n"/>
-      <c r="J28" s="5" t="n"/>
-      <c r="K28" s="5" t="n"/>
-      <c r="L28" s="5" t="n"/>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="L28" s="5" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="n">
@@ -2020,10 +2452,26 @@
           <t>arxiv</t>
         </is>
       </c>
-      <c r="I29" s="5" t="n"/>
-      <c r="J29" s="5" t="n"/>
-      <c r="K29" s="5" t="n"/>
-      <c r="L29" s="5" t="n"/>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="L29" s="5" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="n">
@@ -2060,10 +2508,26 @@
           <t>scopus</t>
         </is>
       </c>
-      <c r="I30" s="5" t="n"/>
-      <c r="J30" s="5" t="n"/>
-      <c r="K30" s="5" t="n"/>
-      <c r="L30" s="5" t="n"/>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="L30" s="5" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="n">
@@ -2100,10 +2564,26 @@
           <t>arxiv</t>
         </is>
       </c>
-      <c r="I31" s="5" t="n"/>
-      <c r="J31" s="5" t="n"/>
-      <c r="K31" s="5" t="n"/>
-      <c r="L31" s="5" t="n"/>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
+      </c>
+      <c r="L31" s="5" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="n">
@@ -2140,10 +2620,26 @@
           <t>scopus</t>
         </is>
       </c>
-      <c r="I32" s="5" t="n"/>
-      <c r="J32" s="5" t="n"/>
-      <c r="K32" s="5" t="n"/>
-      <c r="L32" s="5" t="n"/>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J32" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="L32" s="5" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="n">
@@ -2184,10 +2680,26 @@
           <t>arxiv</t>
         </is>
       </c>
-      <c r="I33" s="5" t="n"/>
-      <c r="J33" s="5" t="n"/>
-      <c r="K33" s="5" t="n"/>
-      <c r="L33" s="5" t="n"/>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="L33" s="5" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="n">
@@ -2228,10 +2740,26 @@
           <t>openalex</t>
         </is>
       </c>
-      <c r="I34" s="5" t="n"/>
-      <c r="J34" s="5" t="n"/>
-      <c r="K34" s="5" t="n"/>
-      <c r="L34" s="5" t="n"/>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J34" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="K34" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="L34" s="5" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="n">
@@ -2272,10 +2800,26 @@
           <t>arxiv</t>
         </is>
       </c>
-      <c r="I35" s="5" t="n"/>
-      <c r="J35" s="5" t="n"/>
-      <c r="K35" s="5" t="n"/>
-      <c r="L35" s="5" t="n"/>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="L35" s="5" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="n">
@@ -2312,10 +2856,26 @@
           <t>arxiv</t>
         </is>
       </c>
-      <c r="I36" s="5" t="n"/>
-      <c r="J36" s="5" t="n"/>
-      <c r="K36" s="5" t="n"/>
-      <c r="L36" s="5" t="n"/>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
+      </c>
+      <c r="J36" s="5" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
+      </c>
+      <c r="K36" s="5" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
+      </c>
+      <c r="L36" s="5" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="n">
@@ -2352,10 +2912,26 @@
           <t>arxiv</t>
         </is>
       </c>
-      <c r="I37" s="5" t="n"/>
-      <c r="J37" s="5" t="n"/>
-      <c r="K37" s="5" t="n"/>
-      <c r="L37" s="5" t="n"/>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="L37" s="5" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="n">
@@ -2392,10 +2968,26 @@
           <t>openalex</t>
         </is>
       </c>
-      <c r="I38" s="5" t="n"/>
-      <c r="J38" s="5" t="n"/>
-      <c r="K38" s="5" t="n"/>
-      <c r="L38" s="5" t="n"/>
+      <c r="I38" s="5" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
+      </c>
+      <c r="J38" s="5" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
+      </c>
+      <c r="K38" s="5" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
+      </c>
+      <c r="L38" s="5" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="n">
@@ -2432,10 +3024,26 @@
           <t>scopus</t>
         </is>
       </c>
-      <c r="I39" s="5" t="n"/>
-      <c r="J39" s="5" t="n"/>
-      <c r="K39" s="5" t="n"/>
-      <c r="L39" s="5" t="n"/>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="L39" s="5" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="n">
@@ -2476,10 +3084,26 @@
           <t>openalex</t>
         </is>
       </c>
-      <c r="I40" s="5" t="n"/>
-      <c r="J40" s="5" t="n"/>
-      <c r="K40" s="5" t="n"/>
-      <c r="L40" s="5" t="n"/>
+      <c r="I40" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J40" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="K40" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="L40" s="5" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="n">
@@ -2520,10 +3144,26 @@
           <t>arxiv</t>
         </is>
       </c>
-      <c r="I41" s="5" t="n"/>
-      <c r="J41" s="5" t="n"/>
-      <c r="K41" s="5" t="n"/>
-      <c r="L41" s="5" t="n"/>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J41" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="L41" s="5" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="n">
@@ -2564,10 +3204,26 @@
           <t>openalex</t>
         </is>
       </c>
-      <c r="I42" s="5" t="n"/>
-      <c r="J42" s="5" t="n"/>
-      <c r="K42" s="5" t="n"/>
-      <c r="L42" s="5" t="n"/>
+      <c r="I42" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J42" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="K42" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="L42" s="5" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="n">
@@ -2608,10 +3264,26 @@
           <t>openalex</t>
         </is>
       </c>
-      <c r="I43" s="5" t="n"/>
-      <c r="J43" s="5" t="n"/>
-      <c r="K43" s="5" t="n"/>
-      <c r="L43" s="5" t="n"/>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J43" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="L43" s="5" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="n">
@@ -2652,10 +3324,26 @@
           <t>openalex</t>
         </is>
       </c>
-      <c r="I44" s="5" t="n"/>
-      <c r="J44" s="5" t="n"/>
-      <c r="K44" s="5" t="n"/>
-      <c r="L44" s="5" t="n"/>
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J44" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="K44" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="L44" s="5" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="n">
@@ -2696,10 +3384,26 @@
           <t>openalex</t>
         </is>
       </c>
-      <c r="I45" s="5" t="n"/>
-      <c r="J45" s="5" t="n"/>
-      <c r="K45" s="5" t="n"/>
-      <c r="L45" s="5" t="n"/>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
+      </c>
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
+      </c>
+      <c r="K45" s="5" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
+      </c>
+      <c r="L45" s="5" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="n">
@@ -2740,10 +3444,26 @@
           <t>openalex</t>
         </is>
       </c>
-      <c r="I46" s="5" t="n"/>
-      <c r="J46" s="5" t="n"/>
-      <c r="K46" s="5" t="n"/>
-      <c r="L46" s="5" t="n"/>
+      <c r="I46" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J46" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="K46" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="L46" s="5" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="n">
@@ -2784,10 +3504,26 @@
           <t>openalex</t>
         </is>
       </c>
-      <c r="I47" s="5" t="n"/>
-      <c r="J47" s="5" t="n"/>
-      <c r="K47" s="5" t="n"/>
-      <c r="L47" s="5" t="n"/>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
+      </c>
+      <c r="J47" s="5" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
+      </c>
+      <c r="L47" s="5" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="n">
@@ -2828,10 +3564,26 @@
           <t>openalex</t>
         </is>
       </c>
-      <c r="I48" s="5" t="n"/>
-      <c r="J48" s="5" t="n"/>
-      <c r="K48" s="5" t="n"/>
-      <c r="L48" s="5" t="n"/>
+      <c r="I48" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J48" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="K48" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="L48" s="5" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="n">
@@ -2868,10 +3620,26 @@
           <t>arxiv</t>
         </is>
       </c>
-      <c r="I49" s="5" t="n"/>
-      <c r="J49" s="5" t="n"/>
-      <c r="K49" s="5" t="n"/>
-      <c r="L49" s="5" t="n"/>
+      <c r="I49" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J49" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="K49" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="L49" s="5" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="n">
@@ -2912,10 +3680,26 @@
           <t>arxiv</t>
         </is>
       </c>
-      <c r="I50" s="5" t="n"/>
-      <c r="J50" s="5" t="n"/>
-      <c r="K50" s="5" t="n"/>
-      <c r="L50" s="5" t="n"/>
+      <c r="I50" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J50" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="K50" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="L50" s="5" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="n">
@@ -2952,10 +3736,26 @@
           <t>openalex</t>
         </is>
       </c>
-      <c r="I51" s="5" t="n"/>
-      <c r="J51" s="5" t="n"/>
-      <c r="K51" s="5" t="n"/>
-      <c r="L51" s="5" t="n"/>
+      <c r="I51" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J51" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="K51" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="L51" s="5" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="n">
@@ -2996,10 +3796,26 @@
           <t>arxiv</t>
         </is>
       </c>
-      <c r="I52" s="5" t="n"/>
-      <c r="J52" s="5" t="n"/>
-      <c r="K52" s="5" t="n"/>
-      <c r="L52" s="5" t="n"/>
+      <c r="I52" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J52" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="K52" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="L52" s="5" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="n">
@@ -3040,10 +3856,26 @@
           <t>openalex</t>
         </is>
       </c>
-      <c r="I53" s="5" t="n"/>
-      <c r="J53" s="5" t="n"/>
-      <c r="K53" s="5" t="n"/>
-      <c r="L53" s="5" t="n"/>
+      <c r="I53" s="5" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
+      </c>
+      <c r="J53" s="5" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
+      </c>
+      <c r="K53" s="5" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
+      </c>
+      <c r="L53" s="5" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="n">
@@ -3084,10 +3916,26 @@
           <t>arxiv</t>
         </is>
       </c>
-      <c r="I54" s="5" t="n"/>
-      <c r="J54" s="5" t="n"/>
-      <c r="K54" s="5" t="n"/>
-      <c r="L54" s="5" t="n"/>
+      <c r="I54" s="5" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
+      </c>
+      <c r="J54" s="5" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
+      </c>
+      <c r="K54" s="5" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
+      </c>
+      <c r="L54" s="5" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="n">
@@ -3124,10 +3972,26 @@
           <t>scopus</t>
         </is>
       </c>
-      <c r="I55" s="5" t="n"/>
-      <c r="J55" s="5" t="n"/>
-      <c r="K55" s="5" t="n"/>
-      <c r="L55" s="5" t="n"/>
+      <c r="I55" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J55" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="K55" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="L55" s="5" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="n">
@@ -3164,10 +4028,26 @@
           <t>arxiv</t>
         </is>
       </c>
-      <c r="I56" s="5" t="n"/>
-      <c r="J56" s="5" t="n"/>
-      <c r="K56" s="5" t="n"/>
-      <c r="L56" s="5" t="n"/>
+      <c r="I56" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J56" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="K56" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="L56" s="5" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="n">
@@ -3204,10 +4084,26 @@
           <t>openalex</t>
         </is>
       </c>
-      <c r="I57" s="5" t="n"/>
-      <c r="J57" s="5" t="n"/>
-      <c r="K57" s="5" t="n"/>
-      <c r="L57" s="5" t="n"/>
+      <c r="I57" s="5" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
+      </c>
+      <c r="J57" s="5" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
+      </c>
+      <c r="K57" s="5" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
+      </c>
+      <c r="L57" s="5" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="n">
@@ -3248,10 +4144,26 @@
           <t>openalex</t>
         </is>
       </c>
-      <c r="I58" s="5" t="n"/>
-      <c r="J58" s="5" t="n"/>
-      <c r="K58" s="5" t="n"/>
-      <c r="L58" s="5" t="n"/>
+      <c r="I58" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J58" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="K58" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="L58" s="5" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="n">
@@ -3288,10 +4200,26 @@
           <t>semantic_scholar</t>
         </is>
       </c>
-      <c r="I59" s="5" t="n"/>
-      <c r="J59" s="5" t="n"/>
-      <c r="K59" s="5" t="n"/>
-      <c r="L59" s="5" t="n"/>
+      <c r="I59" s="5" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
+      </c>
+      <c r="J59" s="5" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
+      </c>
+      <c r="K59" s="5" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
+      </c>
+      <c r="L59" s="5" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="n">
@@ -3332,10 +4260,26 @@
           <t>arxiv</t>
         </is>
       </c>
-      <c r="I60" s="5" t="n"/>
-      <c r="J60" s="5" t="n"/>
-      <c r="K60" s="5" t="n"/>
-      <c r="L60" s="5" t="n"/>
+      <c r="I60" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J60" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="K60" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="L60" s="5" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="n">
@@ -3376,10 +4320,26 @@
           <t>openalex</t>
         </is>
       </c>
-      <c r="I61" s="5" t="n"/>
-      <c r="J61" s="5" t="n"/>
-      <c r="K61" s="5" t="n"/>
-      <c r="L61" s="5" t="n"/>
+      <c r="I61" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J61" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="K61" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="L61" s="5" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="n">
@@ -3420,10 +4380,26 @@
           <t>openalex</t>
         </is>
       </c>
-      <c r="I62" s="5" t="n"/>
-      <c r="J62" s="5" t="n"/>
-      <c r="K62" s="5" t="n"/>
-      <c r="L62" s="5" t="n"/>
+      <c r="I62" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J62" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="K62" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="L62" s="5" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="n">
@@ -3464,10 +4440,26 @@
           <t>arxiv</t>
         </is>
       </c>
-      <c r="I63" s="5" t="n"/>
-      <c r="J63" s="5" t="n"/>
-      <c r="K63" s="5" t="n"/>
-      <c r="L63" s="5" t="n"/>
+      <c r="I63" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J63" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="K63" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="L63" s="5" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="n">
@@ -3496,10 +4488,26 @@
           <t>scopus</t>
         </is>
       </c>
-      <c r="I64" s="5" t="n"/>
-      <c r="J64" s="5" t="n"/>
-      <c r="K64" s="5" t="n"/>
-      <c r="L64" s="5" t="n"/>
+      <c r="I64" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J64" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="K64" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="L64" s="5" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="n">
@@ -3536,10 +4544,26 @@
           <t>scopus</t>
         </is>
       </c>
-      <c r="I65" s="5" t="n"/>
-      <c r="J65" s="5" t="n"/>
-      <c r="K65" s="5" t="n"/>
-      <c r="L65" s="5" t="n"/>
+      <c r="I65" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J65" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="K65" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="L65" s="5" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="n">
@@ -3576,10 +4600,26 @@
           <t>openalex</t>
         </is>
       </c>
-      <c r="I66" s="5" t="n"/>
-      <c r="J66" s="5" t="n"/>
-      <c r="K66" s="5" t="n"/>
-      <c r="L66" s="5" t="n"/>
+      <c r="I66" s="5" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
+      </c>
+      <c r="J66" s="5" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
+      </c>
+      <c r="K66" s="5" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
+      </c>
+      <c r="L66" s="5" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="n">
@@ -3620,10 +4660,26 @@
           <t>openalex</t>
         </is>
       </c>
-      <c r="I67" s="5" t="n"/>
-      <c r="J67" s="5" t="n"/>
-      <c r="K67" s="5" t="n"/>
-      <c r="L67" s="5" t="n"/>
+      <c r="I67" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J67" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="K67" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="L67" s="5" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="n">
@@ -3664,10 +4720,26 @@
           <t>openalex</t>
         </is>
       </c>
-      <c r="I68" s="5" t="n"/>
-      <c r="J68" s="5" t="n"/>
-      <c r="K68" s="5" t="n"/>
-      <c r="L68" s="5" t="n"/>
+      <c r="I68" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J68" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="K68" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="L68" s="5" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="n">
@@ -3704,10 +4776,26 @@
           <t>openalex</t>
         </is>
       </c>
-      <c r="I69" s="5" t="n"/>
-      <c r="J69" s="5" t="n"/>
-      <c r="K69" s="5" t="n"/>
-      <c r="L69" s="5" t="n"/>
+      <c r="I69" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J69" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="K69" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="L69" s="5" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="n">
@@ -3744,10 +4832,26 @@
           <t>arxiv</t>
         </is>
       </c>
-      <c r="I70" s="5" t="n"/>
-      <c r="J70" s="5" t="n"/>
-      <c r="K70" s="5" t="n"/>
-      <c r="L70" s="5" t="n"/>
+      <c r="I70" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J70" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="K70" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="L70" s="5" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="n">
@@ -3784,10 +4888,26 @@
           <t>scopus</t>
         </is>
       </c>
-      <c r="I71" s="5" t="n"/>
-      <c r="J71" s="5" t="n"/>
-      <c r="K71" s="5" t="n"/>
-      <c r="L71" s="5" t="n"/>
+      <c r="I71" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J71" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="K71" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="L71" s="5" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="n">
@@ -3824,10 +4944,26 @@
           <t>openalex</t>
         </is>
       </c>
-      <c r="I72" s="5" t="n"/>
-      <c r="J72" s="5" t="n"/>
-      <c r="K72" s="5" t="n"/>
-      <c r="L72" s="5" t="n"/>
+      <c r="I72" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J72" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="K72" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="L72" s="5" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="n">
@@ -3868,10 +5004,26 @@
           <t>openalex</t>
         </is>
       </c>
-      <c r="I73" s="5" t="n"/>
-      <c r="J73" s="5" t="n"/>
-      <c r="K73" s="5" t="n"/>
-      <c r="L73" s="5" t="n"/>
+      <c r="I73" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J73" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="K73" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="L73" s="5" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="n">
@@ -3908,10 +5060,26 @@
           <t>openalex</t>
         </is>
       </c>
-      <c r="I74" s="5" t="n"/>
-      <c r="J74" s="5" t="n"/>
-      <c r="K74" s="5" t="n"/>
-      <c r="L74" s="5" t="n"/>
+      <c r="I74" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J74" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="K74" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="L74" s="5" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="n">
@@ -3952,10 +5120,26 @@
           <t>openalex</t>
         </is>
       </c>
-      <c r="I75" s="5" t="n"/>
-      <c r="J75" s="5" t="n"/>
-      <c r="K75" s="5" t="n"/>
-      <c r="L75" s="5" t="n"/>
+      <c r="I75" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J75" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="K75" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="L75" s="5" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="5" t="n">
@@ -3992,10 +5176,26 @@
           <t>semantic_scholar</t>
         </is>
       </c>
-      <c r="I76" s="5" t="n"/>
-      <c r="J76" s="5" t="n"/>
-      <c r="K76" s="5" t="n"/>
-      <c r="L76" s="5" t="n"/>
+      <c r="I76" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J76" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="K76" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="L76" s="5" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="5" t="n">
@@ -4036,10 +5236,26 @@
           <t>openalex</t>
         </is>
       </c>
-      <c r="I77" s="5" t="n"/>
-      <c r="J77" s="5" t="n"/>
-      <c r="K77" s="5" t="n"/>
-      <c r="L77" s="5" t="n"/>
+      <c r="I77" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J77" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="K77" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="L77" s="5" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="5" t="n">
@@ -4080,10 +5296,26 @@
           <t>openalex</t>
         </is>
       </c>
-      <c r="I78" s="5" t="n"/>
-      <c r="J78" s="5" t="n"/>
-      <c r="K78" s="5" t="n"/>
-      <c r="L78" s="5" t="n"/>
+      <c r="I78" s="5" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
+      </c>
+      <c r="J78" s="5" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
+      </c>
+      <c r="K78" s="5" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
+      </c>
+      <c r="L78" s="5" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="5" t="n">
@@ -4124,10 +5356,26 @@
           <t>openalex</t>
         </is>
       </c>
-      <c r="I79" s="5" t="n"/>
-      <c r="J79" s="5" t="n"/>
-      <c r="K79" s="5" t="n"/>
-      <c r="L79" s="5" t="n"/>
+      <c r="I79" s="5" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
+      </c>
+      <c r="J79" s="5" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
+      </c>
+      <c r="K79" s="5" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
+      </c>
+      <c r="L79" s="5" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="5" t="n">
@@ -4168,10 +5416,26 @@
           <t>openalex</t>
         </is>
       </c>
-      <c r="I80" s="5" t="n"/>
-      <c r="J80" s="5" t="n"/>
-      <c r="K80" s="5" t="n"/>
-      <c r="L80" s="5" t="n"/>
+      <c r="I80" s="5" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
+      </c>
+      <c r="J80" s="5" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
+      </c>
+      <c r="K80" s="5" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
+      </c>
+      <c r="L80" s="5" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="5" t="n">
@@ -4212,10 +5476,26 @@
           <t>openalex</t>
         </is>
       </c>
-      <c r="I81" s="5" t="n"/>
-      <c r="J81" s="5" t="n"/>
-      <c r="K81" s="5" t="n"/>
-      <c r="L81" s="5" t="n"/>
+      <c r="I81" s="5" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
+      </c>
+      <c r="J81" s="5" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
+      </c>
+      <c r="K81" s="5" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
+      </c>
+      <c r="L81" s="5" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="5" t="n">
@@ -4256,10 +5536,26 @@
           <t>openalex</t>
         </is>
       </c>
-      <c r="I82" s="5" t="n"/>
-      <c r="J82" s="5" t="n"/>
-      <c r="K82" s="5" t="n"/>
-      <c r="L82" s="5" t="n"/>
+      <c r="I82" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J82" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="K82" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="L82" s="5" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="5" t="n">
@@ -4300,10 +5596,26 @@
           <t>openalex</t>
         </is>
       </c>
-      <c r="I83" s="5" t="n"/>
-      <c r="J83" s="5" t="n"/>
-      <c r="K83" s="5" t="n"/>
-      <c r="L83" s="5" t="n"/>
+      <c r="I83" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J83" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="K83" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="L83" s="5" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="5" t="n">
@@ -4340,10 +5652,26 @@
           <t>arxiv</t>
         </is>
       </c>
-      <c r="I84" s="5" t="n"/>
-      <c r="J84" s="5" t="n"/>
-      <c r="K84" s="5" t="n"/>
-      <c r="L84" s="5" t="n"/>
+      <c r="I84" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J84" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="K84" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="L84" s="5" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="5" t="n">
@@ -4384,10 +5712,26 @@
           <t>arxiv</t>
         </is>
       </c>
-      <c r="I85" s="5" t="n"/>
-      <c r="J85" s="5" t="n"/>
-      <c r="K85" s="5" t="n"/>
-      <c r="L85" s="5" t="n"/>
+      <c r="I85" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J85" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="K85" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="L85" s="5" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="5" t="n">
@@ -4420,10 +5764,26 @@
           <t>scopus</t>
         </is>
       </c>
-      <c r="I86" s="5" t="n"/>
-      <c r="J86" s="5" t="n"/>
-      <c r="K86" s="5" t="n"/>
-      <c r="L86" s="5" t="n"/>
+      <c r="I86" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J86" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="K86" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="L86" s="5" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="5" t="n">
@@ -4464,10 +5824,26 @@
           <t>arxiv</t>
         </is>
       </c>
-      <c r="I87" s="5" t="n"/>
-      <c r="J87" s="5" t="n"/>
-      <c r="K87" s="5" t="n"/>
-      <c r="L87" s="5" t="n"/>
+      <c r="I87" s="5" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
+      </c>
+      <c r="J87" s="5" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
+      </c>
+      <c r="K87" s="5" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
+      </c>
+      <c r="L87" s="5" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="5" t="n">
@@ -4508,10 +5884,26 @@
           <t>openalex</t>
         </is>
       </c>
-      <c r="I88" s="5" t="n"/>
-      <c r="J88" s="5" t="n"/>
-      <c r="K88" s="5" t="n"/>
-      <c r="L88" s="5" t="n"/>
+      <c r="I88" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J88" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="K88" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="L88" s="5" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="5" t="n">
@@ -4548,10 +5940,26 @@
           <t>openalex</t>
         </is>
       </c>
-      <c r="I89" s="5" t="n"/>
-      <c r="J89" s="5" t="n"/>
-      <c r="K89" s="5" t="n"/>
-      <c r="L89" s="5" t="n"/>
+      <c r="I89" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J89" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="K89" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="L89" s="5" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="5" t="n">
@@ -4592,10 +6000,26 @@
           <t>arxiv</t>
         </is>
       </c>
-      <c r="I90" s="5" t="n"/>
-      <c r="J90" s="5" t="n"/>
-      <c r="K90" s="5" t="n"/>
-      <c r="L90" s="5" t="n"/>
+      <c r="I90" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J90" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="K90" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="L90" s="5" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="5" t="n">
@@ -4632,10 +6056,26 @@
           <t>semantic_scholar</t>
         </is>
       </c>
-      <c r="I91" s="5" t="n"/>
-      <c r="J91" s="5" t="n"/>
-      <c r="K91" s="5" t="n"/>
-      <c r="L91" s="5" t="n"/>
+      <c r="I91" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J91" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="K91" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="L91" s="5" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="5" t="n">
@@ -4676,10 +6116,26 @@
           <t>openalex</t>
         </is>
       </c>
-      <c r="I92" s="5" t="n"/>
-      <c r="J92" s="5" t="n"/>
-      <c r="K92" s="5" t="n"/>
-      <c r="L92" s="5" t="n"/>
+      <c r="I92" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J92" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="K92" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="L92" s="5" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="5" t="n">
@@ -4720,10 +6176,26 @@
           <t>openalex</t>
         </is>
       </c>
-      <c r="I93" s="5" t="n"/>
-      <c r="J93" s="5" t="n"/>
-      <c r="K93" s="5" t="n"/>
-      <c r="L93" s="5" t="n"/>
+      <c r="I93" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J93" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="K93" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="L93" s="5" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="5" t="n">
@@ -4764,10 +6236,26 @@
           <t>openalex</t>
         </is>
       </c>
-      <c r="I94" s="5" t="n"/>
-      <c r="J94" s="5" t="n"/>
-      <c r="K94" s="5" t="n"/>
-      <c r="L94" s="5" t="n"/>
+      <c r="I94" s="5" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
+      </c>
+      <c r="J94" s="5" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
+      </c>
+      <c r="K94" s="5" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
+      </c>
+      <c r="L94" s="5" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="5" t="n">
@@ -4808,10 +6296,26 @@
           <t>openalex</t>
         </is>
       </c>
-      <c r="I95" s="5" t="n"/>
-      <c r="J95" s="5" t="n"/>
-      <c r="K95" s="5" t="n"/>
-      <c r="L95" s="5" t="n"/>
+      <c r="I95" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J95" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="K95" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="L95" s="5" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="5" t="n">
@@ -4852,10 +6356,26 @@
           <t>openalex</t>
         </is>
       </c>
-      <c r="I96" s="5" t="n"/>
-      <c r="J96" s="5" t="n"/>
-      <c r="K96" s="5" t="n"/>
-      <c r="L96" s="5" t="n"/>
+      <c r="I96" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J96" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="K96" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="L96" s="5" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="5" t="n">
@@ -4896,10 +6416,26 @@
           <t>openalex</t>
         </is>
       </c>
-      <c r="I97" s="5" t="n"/>
-      <c r="J97" s="5" t="n"/>
-      <c r="K97" s="5" t="n"/>
-      <c r="L97" s="5" t="n"/>
+      <c r="I97" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J97" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="K97" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="L97" s="5" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="5" t="n">
@@ -4940,10 +6476,26 @@
           <t>arxiv</t>
         </is>
       </c>
-      <c r="I98" s="5" t="n"/>
-      <c r="J98" s="5" t="n"/>
-      <c r="K98" s="5" t="n"/>
-      <c r="L98" s="5" t="n"/>
+      <c r="I98" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J98" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="K98" s="5" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="L98" s="5" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -4979,6 +6531,26 @@
           <t>arxiv</t>
         </is>
       </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -5019,6 +6591,26 @@
           <t>openalex</t>
         </is>
       </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -5054,6 +6646,26 @@
           <t>scopus</t>
         </is>
       </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -5092,6 +6704,26 @@
       <c r="H102" t="inlineStr">
         <is>
           <t>openalex</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>Filled from AI screening decisions</t>
         </is>
       </c>
     </row>
